--- a/output/V3_SIM_Results_Summary.xlsx
+++ b/output/V3_SIM_Results_Summary.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://adminliveunc-my.sharepoint.com/personal/beibo_ad_unc_edu/Documents/CSCC/HCHS/V3_SIM/suddan/HCHS_simulation/output/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1377" documentId="11_F25DC773A252ABDACC10487F29D85E365BDE58E9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{228ED95D-C9BF-42B1-AF4D-EC3D4F20D593}"/>
+  <xr:revisionPtr revIDLastSave="1414" documentId="11_F25DC773A252ABDACC10487F29D85E365BDE58E9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{19CE2448-857B-470F-B4B4-6B854B00F7AB}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="761" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="761" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary  (coverage)" sheetId="16" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="76">
   <si>
     <t>Continous Outcome, PROC GENMOD</t>
   </si>
@@ -247,20 +247,32 @@
     <t>Good coverage range: [0.925, 0.975]</t>
   </si>
   <si>
-    <t>Good relative eff threshold: &lt;= 10%</t>
-  </si>
-  <si>
     <t>RR_glm (ref)</t>
   </si>
   <si>
     <t>RR_glm_strat (ref)</t>
+  </si>
+  <si>
+    <t># of samples: 1000</t>
+  </si>
+  <si>
+    <t># of imputations: 5</t>
+  </si>
+  <si>
+    <t>Continuous Outcome, SUDAAN</t>
+  </si>
+  <si>
+    <t>Good relative eff threshold: &lt;= 1%</t>
+  </si>
+  <si>
+    <t>Based on n = 1000, the approximate 95% CI is (0.9365, 0.9635)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -354,6 +366,18 @@
     <font>
       <sz val="16"/>
       <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="15"/>
+      <color theme="9"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color rgb="FF7030A0"/>
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
@@ -458,7 +482,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -480,18 +504,9 @@
     <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -501,43 +516,16 @@
     <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -548,22 +536,69 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -876,16 +911,25 @@
       <c r="A2" t="s">
         <v>63</v>
       </c>
+      <c r="J2" s="1" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>64</v>
       </c>
+      <c r="J3" s="1" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>18</v>
       </c>
+      <c r="J4" s="1" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
@@ -903,112 +947,112 @@
       </c>
     </row>
     <row r="10" spans="1:17" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="22" t="s">
+      <c r="A10" s="42" t="s">
         <v>1</v>
       </c>
-      <c r="B10" s="22"/>
-      <c r="C10" s="22"/>
-      <c r="D10" s="22"/>
-      <c r="E10" s="22"/>
-      <c r="F10" s="22"/>
-      <c r="G10" s="13"/>
-      <c r="H10" s="13"/>
-      <c r="I10" s="22" t="s">
+      <c r="B10" s="42"/>
+      <c r="C10" s="42"/>
+      <c r="D10" s="42"/>
+      <c r="E10" s="42"/>
+      <c r="F10" s="42"/>
+      <c r="G10" s="12"/>
+      <c r="H10" s="12"/>
+      <c r="I10" s="42" t="s">
         <v>2</v>
       </c>
-      <c r="J10" s="22"/>
-      <c r="K10" s="22"/>
-      <c r="L10" s="22"/>
-      <c r="M10" s="22"/>
-      <c r="N10" s="22"/>
-      <c r="O10" s="22"/>
-      <c r="P10" s="22"/>
+      <c r="J10" s="42"/>
+      <c r="K10" s="42"/>
+      <c r="L10" s="42"/>
+      <c r="M10" s="42"/>
+      <c r="N10" s="42"/>
+      <c r="O10" s="42"/>
+      <c r="P10" s="42"/>
     </row>
     <row r="11" spans="1:17" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="A11" s="25" t="s">
-        <v>0</v>
-      </c>
-      <c r="B11" s="25"/>
-      <c r="C11" s="25"/>
-      <c r="D11" s="25"/>
-      <c r="E11" s="25"/>
-      <c r="F11" s="25"/>
-      <c r="H11" s="25" t="s">
-        <v>0</v>
-      </c>
-      <c r="I11" s="25"/>
-      <c r="J11" s="25"/>
-      <c r="K11" s="25"/>
-      <c r="L11" s="25"/>
-      <c r="M11" s="25"/>
-      <c r="N11" s="25"/>
-      <c r="O11" s="25"/>
+      <c r="A11" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="B11" s="29"/>
+      <c r="C11" s="29"/>
+      <c r="D11" s="29"/>
+      <c r="E11" s="29"/>
+      <c r="F11" s="29"/>
+      <c r="H11" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="I11" s="29"/>
+      <c r="J11" s="29"/>
+      <c r="K11" s="29"/>
+      <c r="L11" s="29"/>
+      <c r="M11" s="29"/>
+      <c r="N11" s="29"/>
+      <c r="O11" s="29"/>
     </row>
     <row r="12" spans="1:17" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A12" s="16" t="s">
+      <c r="A12" s="30" t="s">
         <v>61</v>
       </c>
-      <c r="B12" s="16"/>
-      <c r="C12" s="23" t="s">
+      <c r="B12" s="30"/>
+      <c r="C12" s="32" t="s">
         <v>3</v>
       </c>
-      <c r="D12" s="23"/>
-      <c r="E12" s="38" t="s">
+      <c r="D12" s="32"/>
+      <c r="E12" s="39" t="s">
         <v>4</v>
       </c>
-      <c r="F12" s="23"/>
+      <c r="F12" s="32"/>
       <c r="G12" s="4"/>
-      <c r="H12" s="16" t="s">
+      <c r="H12" s="30" t="s">
         <v>61</v>
       </c>
-      <c r="I12" s="16"/>
-      <c r="J12" s="20" t="s">
+      <c r="I12" s="30"/>
+      <c r="J12" s="35" t="s">
         <v>3</v>
       </c>
-      <c r="K12" s="20"/>
-      <c r="L12" s="20"/>
-      <c r="M12" s="34" t="s">
+      <c r="K12" s="35"/>
+      <c r="L12" s="35"/>
+      <c r="M12" s="40" t="s">
         <v>4</v>
       </c>
-      <c r="N12" s="20"/>
-      <c r="O12" s="20"/>
+      <c r="N12" s="35"/>
+      <c r="O12" s="35"/>
       <c r="P12" s="4"/>
       <c r="Q12" s="4"/>
     </row>
     <row r="13" spans="1:17" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A13" s="14"/>
-      <c r="B13" s="14"/>
-      <c r="C13" s="15" t="s">
+      <c r="A13" s="31"/>
+      <c r="B13" s="31"/>
+      <c r="C13" s="46" t="s">
         <v>5</v>
       </c>
-      <c r="D13" s="15" t="s">
+      <c r="D13" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="E13" s="39" t="s">
+      <c r="E13" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="F13" s="15" t="s">
+      <c r="F13" s="13" t="s">
         <v>6</v>
       </c>
       <c r="G13" s="5"/>
-      <c r="H13" s="14"/>
-      <c r="I13" s="14"/>
-      <c r="J13" s="21" t="s">
+      <c r="H13" s="31"/>
+      <c r="I13" s="31"/>
+      <c r="J13" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="K13" s="21" t="s">
+      <c r="K13" s="48" t="s">
         <v>8</v>
       </c>
-      <c r="L13" s="21" t="s">
+      <c r="L13" s="48" t="s">
         <v>9</v>
       </c>
-      <c r="M13" s="35" t="s">
+      <c r="M13" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="N13" s="21" t="s">
+      <c r="N13" s="48" t="s">
         <v>8</v>
       </c>
-      <c r="O13" s="21" t="s">
+      <c r="O13" s="48" t="s">
         <v>9</v>
       </c>
       <c r="P13" s="5"/>
@@ -1021,16 +1065,16 @@
       <c r="B14" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C14" s="28">
-        <v>0</v>
-      </c>
-      <c r="D14" s="28">
-        <v>0</v>
-      </c>
-      <c r="E14" s="28">
-        <v>0</v>
-      </c>
-      <c r="F14" s="28">
+      <c r="C14" s="20">
+        <v>0</v>
+      </c>
+      <c r="D14" s="49">
+        <v>0</v>
+      </c>
+      <c r="E14" s="20">
+        <v>0</v>
+      </c>
+      <c r="F14" s="20">
         <v>1</v>
       </c>
       <c r="G14" s="8"/>
@@ -1040,22 +1084,22 @@
       <c r="I14" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="J14" s="28">
-        <v>0</v>
-      </c>
-      <c r="K14" s="28">
-        <v>0</v>
-      </c>
-      <c r="L14" s="28">
-        <v>0</v>
-      </c>
-      <c r="M14" s="28">
-        <v>0</v>
-      </c>
-      <c r="N14" s="28">
+      <c r="J14" s="20">
+        <v>0</v>
+      </c>
+      <c r="K14" s="20">
+        <v>0</v>
+      </c>
+      <c r="L14" s="20">
+        <v>0</v>
+      </c>
+      <c r="M14" s="20">
+        <v>0</v>
+      </c>
+      <c r="N14" s="20">
         <v>1</v>
       </c>
-      <c r="O14" s="28">
+      <c r="O14" s="20">
         <v>0</v>
       </c>
       <c r="P14" s="8"/>
@@ -1068,16 +1112,16 @@
       <c r="B15" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C15" s="28">
+      <c r="C15" s="20">
         <v>5</v>
       </c>
-      <c r="D15" s="28">
+      <c r="D15" s="20">
         <v>5</v>
       </c>
-      <c r="E15" s="28">
+      <c r="E15" s="20">
         <v>6</v>
       </c>
-      <c r="F15" s="28">
+      <c r="F15" s="20">
         <v>6</v>
       </c>
       <c r="G15" s="8"/>
@@ -1087,22 +1131,22 @@
       <c r="I15" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="J15" s="28">
+      <c r="J15" s="20">
         <v>5</v>
       </c>
-      <c r="K15" s="28">
+      <c r="K15" s="20">
         <v>5</v>
       </c>
-      <c r="L15" s="28">
+      <c r="L15" s="20">
         <v>5</v>
       </c>
-      <c r="M15" s="28">
+      <c r="M15" s="20">
         <v>6</v>
       </c>
-      <c r="N15" s="28">
+      <c r="N15" s="20">
         <v>6</v>
       </c>
-      <c r="O15" s="28">
+      <c r="O15" s="20">
         <v>6</v>
       </c>
       <c r="P15" s="8"/>
@@ -1115,16 +1159,16 @@
       <c r="B16" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C16" s="28">
-        <v>0</v>
-      </c>
-      <c r="D16" s="28">
+      <c r="C16" s="20">
+        <v>0</v>
+      </c>
+      <c r="D16" s="20">
         <v>1</v>
       </c>
-      <c r="E16" s="28">
-        <v>0</v>
-      </c>
-      <c r="F16" s="28">
+      <c r="E16" s="20">
+        <v>0</v>
+      </c>
+      <c r="F16" s="20">
         <v>2</v>
       </c>
       <c r="G16" s="8"/>
@@ -1134,22 +1178,22 @@
       <c r="I16" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="J16" s="28">
-        <v>0</v>
-      </c>
-      <c r="K16" s="28">
-        <v>0</v>
-      </c>
-      <c r="L16" s="28">
-        <v>0</v>
-      </c>
-      <c r="M16" s="28">
-        <v>0</v>
-      </c>
-      <c r="N16" s="28">
-        <v>0</v>
-      </c>
-      <c r="O16" s="28">
+      <c r="J16" s="20">
+        <v>0</v>
+      </c>
+      <c r="K16" s="20">
+        <v>0</v>
+      </c>
+      <c r="L16" s="20">
+        <v>0</v>
+      </c>
+      <c r="M16" s="20">
+        <v>0</v>
+      </c>
+      <c r="N16" s="20">
+        <v>0</v>
+      </c>
+      <c r="O16" s="20">
         <v>0</v>
       </c>
       <c r="P16" s="8"/>
@@ -1162,16 +1206,16 @@
       <c r="B17" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="C17" s="28">
-        <v>0</v>
-      </c>
-      <c r="D17" s="28">
+      <c r="C17" s="20">
+        <v>0</v>
+      </c>
+      <c r="D17" s="20">
         <v>2</v>
       </c>
-      <c r="E17" s="28">
+      <c r="E17" s="20">
         <v>1</v>
       </c>
-      <c r="F17" s="28">
+      <c r="F17" s="20">
         <v>2</v>
       </c>
       <c r="G17" s="8"/>
@@ -1181,22 +1225,22 @@
       <c r="I17" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="J17" s="28">
-        <v>0</v>
-      </c>
-      <c r="K17" s="28">
-        <v>0</v>
-      </c>
-      <c r="L17" s="28">
-        <v>0</v>
-      </c>
-      <c r="M17" s="28">
+      <c r="J17" s="20">
+        <v>0</v>
+      </c>
+      <c r="K17" s="20">
+        <v>0</v>
+      </c>
+      <c r="L17" s="20">
+        <v>0</v>
+      </c>
+      <c r="M17" s="20">
         <v>1</v>
       </c>
-      <c r="N17" s="28">
+      <c r="N17" s="20">
         <v>2</v>
       </c>
-      <c r="O17" s="28">
+      <c r="O17" s="20">
         <v>1</v>
       </c>
       <c r="P17" s="8"/>
@@ -1209,16 +1253,16 @@
       <c r="B18" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C18" s="28">
+      <c r="C18" s="20">
         <v>4</v>
       </c>
-      <c r="D18" s="28">
+      <c r="D18" s="20">
         <v>5</v>
       </c>
-      <c r="E18" s="28">
+      <c r="E18" s="20">
         <v>3</v>
       </c>
-      <c r="F18" s="28">
+      <c r="F18" s="20">
         <v>6</v>
       </c>
       <c r="G18" s="8"/>
@@ -1228,44 +1272,44 @@
       <c r="I18" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="J18" s="28">
+      <c r="J18" s="20">
         <v>5</v>
       </c>
-      <c r="K18" s="28">
+      <c r="K18" s="20">
         <v>5</v>
       </c>
-      <c r="L18" s="28">
+      <c r="L18" s="20">
         <v>5</v>
       </c>
-      <c r="M18" s="28">
+      <c r="M18" s="20">
         <v>5</v>
       </c>
-      <c r="N18" s="28">
+      <c r="N18" s="20">
         <v>6</v>
       </c>
-      <c r="O18" s="28">
+      <c r="O18" s="20">
         <v>6</v>
       </c>
       <c r="P18" s="8"/>
       <c r="Q18" s="4"/>
     </row>
     <row r="19" spans="1:17" ht="21" x14ac:dyDescent="0.35">
-      <c r="A19" s="17">
+      <c r="A19" s="14">
         <v>6</v>
       </c>
-      <c r="B19" s="17" t="s">
+      <c r="B19" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C19" s="29">
-        <v>0</v>
-      </c>
-      <c r="D19" s="29">
+      <c r="C19" s="21">
+        <v>0</v>
+      </c>
+      <c r="D19" s="21">
         <v>2</v>
       </c>
-      <c r="E19" s="29">
+      <c r="E19" s="21">
         <v>3</v>
       </c>
-      <c r="F19" s="29">
+      <c r="F19" s="21">
         <v>5</v>
       </c>
       <c r="G19" s="8"/>
@@ -1275,22 +1319,22 @@
       <c r="I19" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="J19" s="29">
-        <v>0</v>
-      </c>
-      <c r="K19" s="29">
-        <v>0</v>
-      </c>
-      <c r="L19" s="29">
-        <v>0</v>
-      </c>
-      <c r="M19" s="29">
+      <c r="J19" s="21">
+        <v>0</v>
+      </c>
+      <c r="K19" s="21">
+        <v>0</v>
+      </c>
+      <c r="L19" s="21">
+        <v>0</v>
+      </c>
+      <c r="M19" s="21">
         <v>3</v>
       </c>
-      <c r="N19" s="29">
+      <c r="N19" s="21">
         <v>3</v>
       </c>
-      <c r="O19" s="29">
+      <c r="O19" s="21">
         <v>3</v>
       </c>
       <c r="P19" s="8"/>
@@ -1315,94 +1359,94 @@
       <c r="P20" s="8"/>
       <c r="Q20" s="4"/>
     </row>
-    <row r="21" spans="1:17" ht="21" x14ac:dyDescent="0.35">
-      <c r="A21" s="26" t="s">
+    <row r="21" spans="1:17" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="41" t="s">
         <v>16</v>
       </c>
-      <c r="B21" s="26"/>
-      <c r="C21" s="26"/>
-      <c r="D21" s="26"/>
-      <c r="E21" s="26"/>
-      <c r="F21" s="26"/>
-      <c r="G21" s="24"/>
-      <c r="H21" s="8"/>
-      <c r="I21" s="27" t="s">
+      <c r="B21" s="41"/>
+      <c r="C21" s="41"/>
+      <c r="D21" s="41"/>
+      <c r="E21" s="41"/>
+      <c r="F21" s="41"/>
+      <c r="G21" s="19"/>
+      <c r="H21" s="44" t="s">
         <v>16</v>
       </c>
-      <c r="J21" s="27"/>
-      <c r="K21" s="27"/>
-      <c r="L21" s="27"/>
-      <c r="M21" s="27"/>
-      <c r="N21" s="27"/>
-      <c r="O21" s="27"/>
-      <c r="P21" s="27"/>
+      <c r="I21" s="44"/>
+      <c r="J21" s="44"/>
+      <c r="K21" s="44"/>
+      <c r="L21" s="44"/>
+      <c r="M21" s="44"/>
+      <c r="N21" s="44"/>
+      <c r="O21" s="44"/>
+      <c r="P21" s="45"/>
       <c r="Q21" s="4"/>
     </row>
     <row r="22" spans="1:17" ht="21" x14ac:dyDescent="0.35">
-      <c r="A22" s="16" t="s">
+      <c r="A22" s="30" t="s">
         <v>61</v>
       </c>
-      <c r="B22" s="16"/>
-      <c r="C22" s="23" t="s">
+      <c r="B22" s="30"/>
+      <c r="C22" s="32" t="s">
         <v>3</v>
       </c>
-      <c r="D22" s="23"/>
-      <c r="E22" s="40" t="s">
+      <c r="D22" s="32"/>
+      <c r="E22" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="F22" s="30"/>
+      <c r="F22" s="34"/>
       <c r="G22" s="8"/>
-      <c r="H22" s="16" t="s">
+      <c r="H22" s="30" t="s">
         <v>61</v>
       </c>
-      <c r="I22" s="16"/>
-      <c r="J22" s="20" t="s">
+      <c r="I22" s="30"/>
+      <c r="J22" s="35" t="s">
         <v>3</v>
       </c>
-      <c r="K22" s="20"/>
-      <c r="L22" s="20"/>
-      <c r="M22" s="42" t="s">
+      <c r="K22" s="35"/>
+      <c r="L22" s="35"/>
+      <c r="M22" s="36" t="s">
         <v>4</v>
       </c>
-      <c r="N22" s="32"/>
-      <c r="O22" s="32"/>
+      <c r="N22" s="37"/>
+      <c r="O22" s="37"/>
       <c r="P22" s="8"/>
       <c r="Q22" s="4"/>
     </row>
     <row r="23" spans="1:17" ht="21" x14ac:dyDescent="0.35">
-      <c r="A23" s="14"/>
-      <c r="B23" s="14"/>
-      <c r="C23" s="15" t="s">
+      <c r="A23" s="31"/>
+      <c r="B23" s="31"/>
+      <c r="C23" s="46" t="s">
         <v>5</v>
       </c>
-      <c r="D23" s="15" t="s">
+      <c r="D23" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="E23" s="41" t="s">
+      <c r="E23" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="F23" s="31" t="s">
+      <c r="F23" s="22" t="s">
         <v>6</v>
       </c>
       <c r="G23" s="8"/>
-      <c r="H23" s="14"/>
-      <c r="I23" s="14"/>
-      <c r="J23" s="21" t="s">
+      <c r="H23" s="31"/>
+      <c r="I23" s="31"/>
+      <c r="J23" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="K23" s="21" t="s">
+      <c r="K23" s="48" t="s">
         <v>8</v>
       </c>
-      <c r="L23" s="21" t="s">
+      <c r="L23" s="48" t="s">
         <v>9</v>
       </c>
-      <c r="M23" s="43" t="s">
+      <c r="M23" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="N23" s="33" t="s">
+      <c r="N23" s="48" t="s">
         <v>8</v>
       </c>
-      <c r="O23" s="33" t="s">
+      <c r="O23" s="48" t="s">
         <v>9</v>
       </c>
       <c r="P23" s="8"/>
@@ -1415,16 +1459,16 @@
       <c r="B24" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="C24" s="28">
+      <c r="C24" s="20">
         <v>4</v>
       </c>
-      <c r="D24" s="28">
+      <c r="D24" s="20">
         <v>4</v>
       </c>
-      <c r="E24" s="28">
+      <c r="E24" s="20">
         <v>4</v>
       </c>
-      <c r="F24" s="28">
+      <c r="F24" s="20">
         <v>3</v>
       </c>
       <c r="G24" s="10"/>
@@ -1434,22 +1478,22 @@
       <c r="I24" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="J24" s="28">
-        <v>0</v>
-      </c>
-      <c r="K24" s="28">
-        <v>0</v>
-      </c>
-      <c r="L24" s="28">
-        <v>0</v>
-      </c>
-      <c r="M24" s="28">
-        <v>0</v>
-      </c>
-      <c r="N24" s="28">
-        <v>0</v>
-      </c>
-      <c r="O24" s="28">
+      <c r="J24" s="20">
+        <v>0</v>
+      </c>
+      <c r="K24" s="20">
+        <v>0</v>
+      </c>
+      <c r="L24" s="20">
+        <v>0</v>
+      </c>
+      <c r="M24" s="20">
+        <v>0</v>
+      </c>
+      <c r="N24" s="20">
+        <v>0</v>
+      </c>
+      <c r="O24" s="20">
         <v>0</v>
       </c>
       <c r="P24" s="10"/>
@@ -1462,16 +1506,16 @@
       <c r="B25" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="C25" s="28">
+      <c r="C25" s="20">
         <v>4</v>
       </c>
-      <c r="D25" s="28">
+      <c r="D25" s="20">
         <v>4</v>
       </c>
-      <c r="E25" s="28">
+      <c r="E25" s="20">
         <v>4</v>
       </c>
-      <c r="F25" s="28">
+      <c r="F25" s="20">
         <v>4</v>
       </c>
       <c r="G25" s="10"/>
@@ -1481,22 +1525,22 @@
       <c r="I25" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="J25" s="28">
+      <c r="J25" s="20">
         <v>4</v>
       </c>
-      <c r="K25" s="28">
+      <c r="K25" s="20">
         <v>4</v>
       </c>
-      <c r="L25" s="28">
+      <c r="L25" s="20">
         <v>4</v>
       </c>
-      <c r="M25" s="28">
+      <c r="M25" s="20">
         <v>4</v>
       </c>
-      <c r="N25" s="28">
+      <c r="N25" s="20">
         <v>4</v>
       </c>
-      <c r="O25" s="28">
+      <c r="O25" s="20">
         <v>4</v>
       </c>
       <c r="P25" s="10"/>
@@ -1509,16 +1553,16 @@
       <c r="B26" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="C26" s="28">
+      <c r="C26" s="20">
         <v>5</v>
       </c>
-      <c r="D26" s="28">
+      <c r="D26" s="20">
         <v>6</v>
       </c>
-      <c r="E26" s="28">
+      <c r="E26" s="20">
         <v>5</v>
       </c>
-      <c r="F26" s="28">
+      <c r="F26" s="20">
         <v>6</v>
       </c>
       <c r="G26" s="10"/>
@@ -1528,22 +1572,22 @@
       <c r="I26" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="J26" s="28">
+      <c r="J26" s="20">
         <v>3</v>
       </c>
-      <c r="K26" s="28">
+      <c r="K26" s="20">
         <v>3</v>
       </c>
-      <c r="L26" s="28">
+      <c r="L26" s="20">
         <v>2</v>
       </c>
-      <c r="M26" s="28">
+      <c r="M26" s="20">
         <v>3</v>
       </c>
-      <c r="N26" s="28">
+      <c r="N26" s="20">
         <v>3</v>
       </c>
-      <c r="O26" s="28">
+      <c r="O26" s="20">
         <v>3</v>
       </c>
       <c r="P26" s="10"/>
@@ -1556,16 +1600,16 @@
       <c r="B27" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="C27" s="28">
+      <c r="C27" s="20">
         <v>1</v>
       </c>
-      <c r="D27" s="28">
+      <c r="D27" s="20">
         <v>2</v>
       </c>
-      <c r="E27" s="28">
-        <v>0</v>
-      </c>
-      <c r="F27" s="28">
+      <c r="E27" s="20">
+        <v>0</v>
+      </c>
+      <c r="F27" s="20">
         <v>2</v>
       </c>
       <c r="G27" s="10"/>
@@ -1575,22 +1619,22 @@
       <c r="I27" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="J27" s="28">
-        <v>0</v>
-      </c>
-      <c r="K27" s="28">
-        <v>0</v>
-      </c>
-      <c r="L27" s="28">
-        <v>0</v>
-      </c>
-      <c r="M27" s="28">
-        <v>0</v>
-      </c>
-      <c r="N27" s="28">
-        <v>0</v>
-      </c>
-      <c r="O27" s="28">
+      <c r="J27" s="20">
+        <v>0</v>
+      </c>
+      <c r="K27" s="20">
+        <v>0</v>
+      </c>
+      <c r="L27" s="20">
+        <v>0</v>
+      </c>
+      <c r="M27" s="20">
+        <v>0</v>
+      </c>
+      <c r="N27" s="20">
+        <v>0</v>
+      </c>
+      <c r="O27" s="20">
         <v>0</v>
       </c>
       <c r="P27" s="10"/>
@@ -1603,16 +1647,16 @@
       <c r="B28" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="C28" s="28">
+      <c r="C28" s="20">
         <v>7</v>
       </c>
-      <c r="D28" s="28">
+      <c r="D28" s="20">
         <v>2</v>
       </c>
-      <c r="E28" s="28">
+      <c r="E28" s="20">
         <v>7</v>
       </c>
-      <c r="F28" s="28">
+      <c r="F28" s="20">
         <v>3</v>
       </c>
       <c r="G28" s="10"/>
@@ -1622,69 +1666,69 @@
       <c r="I28" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="J28" s="28">
+      <c r="J28" s="20">
         <v>1</v>
       </c>
-      <c r="K28" s="28">
+      <c r="K28" s="20">
         <v>1</v>
       </c>
-      <c r="L28" s="28">
+      <c r="L28" s="20">
         <v>1</v>
       </c>
-      <c r="M28" s="28">
+      <c r="M28" s="20">
         <v>2</v>
       </c>
-      <c r="N28" s="28">
+      <c r="N28" s="20">
         <v>2</v>
       </c>
-      <c r="O28" s="28">
+      <c r="O28" s="20">
         <v>2</v>
       </c>
       <c r="P28" s="10"/>
       <c r="Q28" s="4"/>
     </row>
     <row r="29" spans="1:17" ht="21" x14ac:dyDescent="0.35">
-      <c r="A29" s="19">
+      <c r="A29" s="16">
         <v>6</v>
       </c>
-      <c r="B29" s="19" t="s">
+      <c r="B29" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C29" s="29">
-        <v>0</v>
-      </c>
-      <c r="D29" s="29">
+      <c r="C29" s="21">
+        <v>0</v>
+      </c>
+      <c r="D29" s="21">
         <v>2</v>
       </c>
-      <c r="E29" s="29">
+      <c r="E29" s="21">
         <v>1</v>
       </c>
-      <c r="F29" s="29">
+      <c r="F29" s="21">
         <v>2</v>
       </c>
       <c r="G29" s="10"/>
-      <c r="H29" s="19">
+      <c r="H29" s="16">
         <v>6</v>
       </c>
-      <c r="I29" s="19" t="s">
+      <c r="I29" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="J29" s="29">
-        <v>0</v>
-      </c>
-      <c r="K29" s="29">
-        <v>0</v>
-      </c>
-      <c r="L29" s="29">
+      <c r="J29" s="21">
+        <v>0</v>
+      </c>
+      <c r="K29" s="21">
+        <v>0</v>
+      </c>
+      <c r="L29" s="21">
         <v>1</v>
       </c>
-      <c r="M29" s="29">
+      <c r="M29" s="21">
         <v>1</v>
       </c>
-      <c r="N29" s="29">
+      <c r="N29" s="21">
         <v>1</v>
       </c>
-      <c r="O29" s="29">
+      <c r="O29" s="21">
         <v>2</v>
       </c>
       <c r="P29" s="10"/>
@@ -1728,58 +1772,94 @@
       <c r="P31" s="4"/>
       <c r="Q31" s="4"/>
     </row>
-    <row r="32" spans="1:17" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="A32" s="25" t="s">
+    <row r="32" spans="1:17" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="A32" s="29" t="s">
         <v>62</v>
       </c>
-      <c r="B32" s="25"/>
-      <c r="C32" s="25"/>
-      <c r="D32" s="25"/>
-      <c r="E32" s="25"/>
-      <c r="F32" s="25"/>
+      <c r="B32" s="29"/>
+      <c r="C32" s="29"/>
+      <c r="D32" s="29"/>
+      <c r="E32" s="29"/>
+      <c r="F32" s="29"/>
       <c r="G32" s="4"/>
-      <c r="H32" s="4"/>
-      <c r="I32" s="4"/>
-      <c r="J32" s="4"/>
-      <c r="K32" s="4"/>
-      <c r="L32" s="4"/>
-      <c r="M32" s="4"/>
-      <c r="N32" s="4"/>
-      <c r="O32" s="4"/>
+      <c r="H32" s="44" t="s">
+        <v>73</v>
+      </c>
+      <c r="I32" s="44"/>
+      <c r="J32" s="44"/>
+      <c r="K32" s="44"/>
+      <c r="L32" s="44"/>
+      <c r="M32" s="44"/>
+      <c r="N32" s="44"/>
+      <c r="O32" s="44"/>
       <c r="P32" s="4"/>
       <c r="Q32" s="4"/>
     </row>
-    <row r="33" spans="1:6" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A33" s="16" t="s">
+    <row r="33" spans="1:15" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="A33" s="30" t="s">
         <v>61</v>
       </c>
-      <c r="B33" s="16"/>
-      <c r="C33" s="23" t="s">
+      <c r="B33" s="30"/>
+      <c r="C33" s="32" t="s">
         <v>3</v>
       </c>
-      <c r="D33" s="23"/>
-      <c r="E33" s="23" t="s">
+      <c r="D33" s="32"/>
+      <c r="E33" s="32" t="s">
         <v>4</v>
       </c>
-      <c r="F33" s="23"/>
-    </row>
-    <row r="34" spans="1:6" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A34" s="14"/>
-      <c r="B34" s="14"/>
-      <c r="C34" s="15" t="s">
+      <c r="F33" s="32"/>
+      <c r="H33" s="30" t="s">
+        <v>61</v>
+      </c>
+      <c r="I33" s="30"/>
+      <c r="J33" s="35" t="s">
+        <v>3</v>
+      </c>
+      <c r="K33" s="35"/>
+      <c r="L33" s="35"/>
+      <c r="M33" s="40" t="s">
+        <v>4</v>
+      </c>
+      <c r="N33" s="35"/>
+      <c r="O33" s="35"/>
+    </row>
+    <row r="34" spans="1:15" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="A34" s="31"/>
+      <c r="B34" s="31"/>
+      <c r="C34" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="D34" s="15" t="s">
+      <c r="D34" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="E34" s="15" t="s">
+      <c r="E34" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="F34" s="15" t="s">
+      <c r="F34" s="13" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="35" spans="1:6" ht="21" x14ac:dyDescent="0.35">
+      <c r="H34" s="31"/>
+      <c r="I34" s="31"/>
+      <c r="J34" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="K34" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="L34" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="M34" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="N34" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="O34" s="18" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15" ht="21" x14ac:dyDescent="0.35">
       <c r="A35" s="6">
         <v>1</v>
       </c>
@@ -1790,8 +1870,20 @@
       <c r="D35" s="11"/>
       <c r="E35" s="11"/>
       <c r="F35" s="7"/>
-    </row>
-    <row r="36" spans="1:6" ht="21" x14ac:dyDescent="0.35">
+      <c r="H35" s="9">
+        <v>1</v>
+      </c>
+      <c r="I35" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="J35" s="20"/>
+      <c r="K35" s="20"/>
+      <c r="L35" s="20"/>
+      <c r="M35" s="20"/>
+      <c r="N35" s="20"/>
+      <c r="O35" s="20"/>
+    </row>
+    <row r="36" spans="1:15" ht="21" x14ac:dyDescent="0.35">
       <c r="A36" s="6">
         <v>2</v>
       </c>
@@ -1802,8 +1894,20 @@
       <c r="D36" s="7"/>
       <c r="E36" s="7"/>
       <c r="F36" s="7"/>
-    </row>
-    <row r="37" spans="1:6" ht="21" x14ac:dyDescent="0.35">
+      <c r="H36" s="9">
+        <v>2</v>
+      </c>
+      <c r="I36" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="J36" s="20"/>
+      <c r="K36" s="20"/>
+      <c r="L36" s="20"/>
+      <c r="M36" s="20"/>
+      <c r="N36" s="20"/>
+      <c r="O36" s="20"/>
+    </row>
+    <row r="37" spans="1:15" ht="21" x14ac:dyDescent="0.35">
       <c r="A37" s="6">
         <v>3</v>
       </c>
@@ -1814,8 +1918,20 @@
       <c r="D37" s="7"/>
       <c r="E37" s="7"/>
       <c r="F37" s="7"/>
-    </row>
-    <row r="38" spans="1:6" ht="21" x14ac:dyDescent="0.35">
+      <c r="H37" s="9">
+        <v>3</v>
+      </c>
+      <c r="I37" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="J37" s="20"/>
+      <c r="K37" s="20"/>
+      <c r="L37" s="20"/>
+      <c r="M37" s="20"/>
+      <c r="N37" s="20"/>
+      <c r="O37" s="20"/>
+    </row>
+    <row r="38" spans="1:15" ht="21" x14ac:dyDescent="0.35">
       <c r="A38" s="6">
         <v>4</v>
       </c>
@@ -1826,8 +1942,20 @@
       <c r="D38" s="7"/>
       <c r="E38" s="7"/>
       <c r="F38" s="7"/>
-    </row>
-    <row r="39" spans="1:6" ht="21" x14ac:dyDescent="0.35">
+      <c r="H38" s="9">
+        <v>4</v>
+      </c>
+      <c r="I38" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J38" s="20"/>
+      <c r="K38" s="20"/>
+      <c r="L38" s="20"/>
+      <c r="M38" s="20"/>
+      <c r="N38" s="20"/>
+      <c r="O38" s="20"/>
+    </row>
+    <row r="39" spans="1:15" ht="21" x14ac:dyDescent="0.35">
       <c r="A39" s="6">
         <v>5</v>
       </c>
@@ -1838,21 +1966,63 @@
       <c r="D39" s="7"/>
       <c r="E39" s="7"/>
       <c r="F39" s="7"/>
-    </row>
-    <row r="40" spans="1:6" ht="21" x14ac:dyDescent="0.35">
-      <c r="A40" s="17">
+      <c r="H39" s="9">
+        <v>5</v>
+      </c>
+      <c r="I39" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="J39" s="20"/>
+      <c r="K39" s="20"/>
+      <c r="L39" s="20"/>
+      <c r="M39" s="20"/>
+      <c r="N39" s="20"/>
+      <c r="O39" s="20"/>
+    </row>
+    <row r="40" spans="1:15" ht="21" x14ac:dyDescent="0.35">
+      <c r="A40" s="14">
         <v>6</v>
       </c>
-      <c r="B40" s="17" t="s">
+      <c r="B40" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C40" s="18"/>
-      <c r="D40" s="18"/>
-      <c r="E40" s="18"/>
-      <c r="F40" s="18"/>
+      <c r="C40" s="15"/>
+      <c r="D40" s="15"/>
+      <c r="E40" s="15"/>
+      <c r="F40" s="15"/>
+      <c r="H40" s="16">
+        <v>6</v>
+      </c>
+      <c r="I40" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="J40" s="21"/>
+      <c r="K40" s="21"/>
+      <c r="L40" s="21"/>
+      <c r="M40" s="21"/>
+      <c r="N40" s="21"/>
+      <c r="O40" s="21"/>
     </row>
   </sheetData>
-  <mergeCells count="22">
+  <mergeCells count="26">
+    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="I10:P10"/>
+    <mergeCell ref="H21:O21"/>
+    <mergeCell ref="H32:O32"/>
+    <mergeCell ref="H33:I34"/>
+    <mergeCell ref="J33:L33"/>
+    <mergeCell ref="M33:O33"/>
+    <mergeCell ref="A12:B13"/>
+    <mergeCell ref="H12:I13"/>
+    <mergeCell ref="A21:F21"/>
+    <mergeCell ref="A11:F11"/>
+    <mergeCell ref="H11:O11"/>
+    <mergeCell ref="J22:L22"/>
+    <mergeCell ref="M22:O22"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="J12:L12"/>
+    <mergeCell ref="M12:O12"/>
     <mergeCell ref="A32:F32"/>
     <mergeCell ref="A22:B23"/>
     <mergeCell ref="H22:I23"/>
@@ -1861,22 +2031,28 @@
     <mergeCell ref="E33:F33"/>
     <mergeCell ref="C22:D22"/>
     <mergeCell ref="E22:F22"/>
-    <mergeCell ref="J22:L22"/>
-    <mergeCell ref="M22:O22"/>
-    <mergeCell ref="I21:P21"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="E12:F12"/>
-    <mergeCell ref="J12:L12"/>
-    <mergeCell ref="M12:O12"/>
-    <mergeCell ref="A12:B13"/>
-    <mergeCell ref="H12:I13"/>
-    <mergeCell ref="A21:F21"/>
-    <mergeCell ref="A11:F11"/>
-    <mergeCell ref="H11:O11"/>
-    <mergeCell ref="A10:F10"/>
-    <mergeCell ref="I10:P10"/>
   </mergeCells>
   <conditionalFormatting sqref="C14:D19">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="7"/>
+        <color theme="9"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C24:D29">
+    <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="7"/>
+        <color theme="9"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E14:F19">
     <cfRule type="colorScale" priority="7">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -1886,17 +2062,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E14:F19">
-    <cfRule type="colorScale" priority="6">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="7"/>
-        <color theme="9"/>
-        <color rgb="FFFF0000"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C24:D29">
+  <conditionalFormatting sqref="E24:F29">
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -1906,7 +2072,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E24:F29">
+  <conditionalFormatting sqref="J14:L19">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -1916,7 +2082,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J14:L19">
+  <conditionalFormatting sqref="J24:O29">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -1926,7 +2092,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J24:O29">
+  <conditionalFormatting sqref="M14:O19">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -1936,7 +2102,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M14:O19">
+  <conditionalFormatting sqref="J35:O40">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -1977,7 +2143,7 @@
         <v>17</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
@@ -1989,11 +2155,17 @@
       <c r="A3" t="s">
         <v>64</v>
       </c>
+      <c r="J3" s="1" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>18</v>
       </c>
+      <c r="J4" s="1" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
@@ -2011,112 +2183,112 @@
       </c>
     </row>
     <row r="10" spans="1:17" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="22" t="s">
+      <c r="A10" s="42" t="s">
         <v>1</v>
       </c>
-      <c r="B10" s="22"/>
-      <c r="C10" s="22"/>
-      <c r="D10" s="22"/>
-      <c r="E10" s="22"/>
-      <c r="F10" s="22"/>
-      <c r="G10" s="13"/>
-      <c r="H10" s="13"/>
-      <c r="I10" s="22" t="s">
+      <c r="B10" s="42"/>
+      <c r="C10" s="42"/>
+      <c r="D10" s="42"/>
+      <c r="E10" s="42"/>
+      <c r="F10" s="42"/>
+      <c r="G10" s="12"/>
+      <c r="H10" s="12"/>
+      <c r="I10" s="42" t="s">
         <v>2</v>
       </c>
-      <c r="J10" s="22"/>
-      <c r="K10" s="22"/>
-      <c r="L10" s="22"/>
-      <c r="M10" s="22"/>
-      <c r="N10" s="22"/>
-      <c r="O10" s="22"/>
-      <c r="P10" s="22"/>
+      <c r="J10" s="42"/>
+      <c r="K10" s="42"/>
+      <c r="L10" s="42"/>
+      <c r="M10" s="42"/>
+      <c r="N10" s="42"/>
+      <c r="O10" s="42"/>
+      <c r="P10" s="42"/>
     </row>
     <row r="11" spans="1:17" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="A11" s="25" t="s">
-        <v>0</v>
-      </c>
-      <c r="B11" s="25"/>
-      <c r="C11" s="25"/>
-      <c r="D11" s="25"/>
-      <c r="E11" s="25"/>
-      <c r="F11" s="25"/>
-      <c r="H11" s="25" t="s">
-        <v>0</v>
-      </c>
-      <c r="I11" s="25"/>
-      <c r="J11" s="25"/>
-      <c r="K11" s="25"/>
-      <c r="L11" s="25"/>
-      <c r="M11" s="25"/>
-      <c r="N11" s="25"/>
-      <c r="O11" s="25"/>
+      <c r="A11" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="B11" s="29"/>
+      <c r="C11" s="29"/>
+      <c r="D11" s="29"/>
+      <c r="E11" s="29"/>
+      <c r="F11" s="29"/>
+      <c r="H11" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="I11" s="29"/>
+      <c r="J11" s="29"/>
+      <c r="K11" s="29"/>
+      <c r="L11" s="29"/>
+      <c r="M11" s="29"/>
+      <c r="N11" s="29"/>
+      <c r="O11" s="29"/>
     </row>
     <row r="12" spans="1:17" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A12" s="16" t="s">
+      <c r="A12" s="30" t="s">
         <v>61</v>
       </c>
-      <c r="B12" s="16"/>
-      <c r="C12" s="23" t="s">
+      <c r="B12" s="30"/>
+      <c r="C12" s="32" t="s">
         <v>3</v>
       </c>
-      <c r="D12" s="23"/>
-      <c r="E12" s="38" t="s">
+      <c r="D12" s="32"/>
+      <c r="E12" s="39" t="s">
         <v>4</v>
       </c>
-      <c r="F12" s="23"/>
+      <c r="F12" s="32"/>
       <c r="G12" s="4"/>
-      <c r="H12" s="16" t="s">
+      <c r="H12" s="30" t="s">
         <v>61</v>
       </c>
-      <c r="I12" s="16"/>
-      <c r="J12" s="20" t="s">
+      <c r="I12" s="30"/>
+      <c r="J12" s="35" t="s">
         <v>3</v>
       </c>
-      <c r="K12" s="20"/>
-      <c r="L12" s="20"/>
-      <c r="M12" s="34" t="s">
+      <c r="K12" s="35"/>
+      <c r="L12" s="35"/>
+      <c r="M12" s="40" t="s">
         <v>4</v>
       </c>
-      <c r="N12" s="20"/>
-      <c r="O12" s="20"/>
+      <c r="N12" s="35"/>
+      <c r="O12" s="35"/>
       <c r="P12" s="4"/>
       <c r="Q12" s="4"/>
     </row>
     <row r="13" spans="1:17" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="A13" s="14"/>
-      <c r="B13" s="14"/>
-      <c r="C13" s="15" t="s">
+      <c r="A13" s="31"/>
+      <c r="B13" s="31"/>
+      <c r="C13" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="D13" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="E13" s="23" t="s">
+        <v>69</v>
+      </c>
+      <c r="F13" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="G13" s="5"/>
+      <c r="H13" s="31"/>
+      <c r="I13" s="31"/>
+      <c r="J13" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="D13" s="44" t="s">
-        <v>6</v>
-      </c>
-      <c r="E13" s="35" t="s">
+      <c r="K13" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="L13" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="M13" s="23" t="s">
         <v>70</v>
       </c>
-      <c r="F13" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="G13" s="5"/>
-      <c r="H13" s="14"/>
-      <c r="I13" s="14"/>
-      <c r="J13" s="21" t="s">
-        <v>71</v>
-      </c>
-      <c r="K13" s="21" t="s">
+      <c r="N13" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="L13" s="21" t="s">
-        <v>9</v>
-      </c>
-      <c r="M13" s="35" t="s">
-        <v>71</v>
-      </c>
-      <c r="N13" s="21" t="s">
-        <v>8</v>
-      </c>
-      <c r="O13" s="21" t="s">
+      <c r="O13" s="17" t="s">
         <v>9</v>
       </c>
       <c r="P13" s="5"/>
@@ -2129,11 +2301,11 @@
       <c r="B14" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="28">
-        <v>0</v>
-      </c>
-      <c r="E14" s="36"/>
-      <c r="F14" s="28">
+      <c r="D14" s="20">
+        <v>0</v>
+      </c>
+      <c r="E14" s="24"/>
+      <c r="F14" s="20">
         <v>0</v>
       </c>
       <c r="G14" s="8"/>
@@ -2143,18 +2315,18 @@
       <c r="I14" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="J14" s="28"/>
-      <c r="K14" s="28">
-        <v>0</v>
-      </c>
-      <c r="L14" s="28">
-        <v>0</v>
-      </c>
-      <c r="M14" s="36"/>
-      <c r="N14" s="28">
-        <v>0</v>
-      </c>
-      <c r="O14" s="28">
+      <c r="J14" s="20"/>
+      <c r="K14" s="20">
+        <v>0</v>
+      </c>
+      <c r="L14" s="20">
+        <v>0</v>
+      </c>
+      <c r="M14" s="24"/>
+      <c r="N14" s="20">
+        <v>0</v>
+      </c>
+      <c r="O14" s="20">
         <v>0</v>
       </c>
       <c r="P14" s="8"/>
@@ -2167,12 +2339,12 @@
       <c r="B15" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C15" s="28"/>
-      <c r="D15" s="28">
-        <v>0</v>
-      </c>
-      <c r="E15" s="36"/>
-      <c r="F15" s="28">
+      <c r="C15" s="20"/>
+      <c r="D15" s="20">
+        <v>0</v>
+      </c>
+      <c r="E15" s="24"/>
+      <c r="F15" s="20">
         <v>0</v>
       </c>
       <c r="G15" s="8"/>
@@ -2182,18 +2354,18 @@
       <c r="I15" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="J15" s="28"/>
-      <c r="K15" s="28">
-        <v>0</v>
-      </c>
-      <c r="L15" s="28">
-        <v>0</v>
-      </c>
-      <c r="M15" s="36"/>
-      <c r="N15" s="28">
-        <v>0</v>
-      </c>
-      <c r="O15" s="28">
+      <c r="J15" s="20"/>
+      <c r="K15" s="20">
+        <v>0</v>
+      </c>
+      <c r="L15" s="20">
+        <v>0</v>
+      </c>
+      <c r="M15" s="24"/>
+      <c r="N15" s="20">
+        <v>0</v>
+      </c>
+      <c r="O15" s="20">
         <v>0</v>
       </c>
       <c r="P15" s="8"/>
@@ -2206,12 +2378,12 @@
       <c r="B16" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C16" s="28"/>
-      <c r="D16" s="28">
-        <v>0</v>
-      </c>
-      <c r="E16" s="36"/>
-      <c r="F16" s="28">
+      <c r="C16" s="20"/>
+      <c r="D16" s="20">
+        <v>0</v>
+      </c>
+      <c r="E16" s="24"/>
+      <c r="F16" s="20">
         <v>0</v>
       </c>
       <c r="G16" s="8"/>
@@ -2221,18 +2393,18 @@
       <c r="I16" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="J16" s="28"/>
-      <c r="K16" s="28">
-        <v>0</v>
-      </c>
-      <c r="L16" s="28">
-        <v>0</v>
-      </c>
-      <c r="M16" s="36"/>
-      <c r="N16" s="28">
-        <v>0</v>
-      </c>
-      <c r="O16" s="28">
+      <c r="J16" s="20"/>
+      <c r="K16" s="20">
+        <v>0</v>
+      </c>
+      <c r="L16" s="20">
+        <v>0</v>
+      </c>
+      <c r="M16" s="24"/>
+      <c r="N16" s="20">
+        <v>0</v>
+      </c>
+      <c r="O16" s="20">
         <v>0</v>
       </c>
       <c r="P16" s="8"/>
@@ -2245,12 +2417,12 @@
       <c r="B17" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="C17" s="28"/>
-      <c r="D17" s="28">
-        <v>0</v>
-      </c>
-      <c r="E17" s="36"/>
-      <c r="F17" s="28">
+      <c r="C17" s="20"/>
+      <c r="D17" s="20">
+        <v>0</v>
+      </c>
+      <c r="E17" s="24"/>
+      <c r="F17" s="20">
         <v>0</v>
       </c>
       <c r="G17" s="8"/>
@@ -2260,18 +2432,18 @@
       <c r="I17" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="J17" s="28"/>
-      <c r="K17" s="28">
-        <v>0</v>
-      </c>
-      <c r="L17" s="28">
-        <v>0</v>
-      </c>
-      <c r="M17" s="36"/>
-      <c r="N17" s="28">
-        <v>0</v>
-      </c>
-      <c r="O17" s="28">
+      <c r="J17" s="20"/>
+      <c r="K17" s="20">
+        <v>0</v>
+      </c>
+      <c r="L17" s="20">
+        <v>0</v>
+      </c>
+      <c r="M17" s="24"/>
+      <c r="N17" s="20">
+        <v>0</v>
+      </c>
+      <c r="O17" s="20">
         <v>0</v>
       </c>
       <c r="P17" s="8"/>
@@ -2284,12 +2456,12 @@
       <c r="B18" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C18" s="28"/>
-      <c r="D18" s="28">
+      <c r="C18" s="20"/>
+      <c r="D18" s="20">
         <v>7</v>
       </c>
-      <c r="E18" s="36"/>
-      <c r="F18" s="28">
+      <c r="E18" s="24"/>
+      <c r="F18" s="20">
         <v>7</v>
       </c>
       <c r="G18" s="8"/>
@@ -2299,36 +2471,36 @@
       <c r="I18" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="J18" s="28"/>
-      <c r="K18" s="28">
-        <v>0</v>
-      </c>
-      <c r="L18" s="28">
-        <v>0</v>
-      </c>
-      <c r="M18" s="36"/>
-      <c r="N18" s="28">
-        <v>0</v>
-      </c>
-      <c r="O18" s="28">
+      <c r="J18" s="20"/>
+      <c r="K18" s="20">
+        <v>0</v>
+      </c>
+      <c r="L18" s="20">
+        <v>0</v>
+      </c>
+      <c r="M18" s="24"/>
+      <c r="N18" s="20">
+        <v>0</v>
+      </c>
+      <c r="O18" s="20">
         <v>0</v>
       </c>
       <c r="P18" s="8"/>
       <c r="Q18" s="4"/>
     </row>
     <row r="19" spans="1:17" ht="21" x14ac:dyDescent="0.35">
-      <c r="A19" s="17">
+      <c r="A19" s="14">
         <v>6</v>
       </c>
-      <c r="B19" s="17" t="s">
+      <c r="B19" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C19" s="29"/>
-      <c r="D19" s="29">
-        <v>0</v>
-      </c>
-      <c r="E19" s="37"/>
-      <c r="F19" s="29">
+      <c r="C19" s="21"/>
+      <c r="D19" s="21">
+        <v>0</v>
+      </c>
+      <c r="E19" s="25"/>
+      <c r="F19" s="21">
         <v>0</v>
       </c>
       <c r="G19" s="8"/>
@@ -2338,18 +2510,18 @@
       <c r="I19" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="J19" s="29"/>
-      <c r="K19" s="29">
-        <v>0</v>
-      </c>
-      <c r="L19" s="29">
-        <v>0</v>
-      </c>
-      <c r="M19" s="37"/>
-      <c r="N19" s="29">
-        <v>0</v>
-      </c>
-      <c r="O19" s="29">
+      <c r="J19" s="21"/>
+      <c r="K19" s="21">
+        <v>0</v>
+      </c>
+      <c r="L19" s="21">
+        <v>0</v>
+      </c>
+      <c r="M19" s="25"/>
+      <c r="N19" s="21">
+        <v>0</v>
+      </c>
+      <c r="O19" s="21">
         <v>0</v>
       </c>
       <c r="P19" s="8"/>
@@ -2375,93 +2547,93 @@
       <c r="Q20" s="4"/>
     </row>
     <row r="21" spans="1:17" ht="21" x14ac:dyDescent="0.35">
-      <c r="A21" s="26" t="s">
+      <c r="A21" s="41" t="s">
         <v>16</v>
       </c>
-      <c r="B21" s="26"/>
-      <c r="C21" s="26"/>
-      <c r="D21" s="26"/>
-      <c r="E21" s="26"/>
-      <c r="F21" s="26"/>
-      <c r="G21" s="24"/>
+      <c r="B21" s="41"/>
+      <c r="C21" s="41"/>
+      <c r="D21" s="41"/>
+      <c r="E21" s="41"/>
+      <c r="F21" s="41"/>
+      <c r="G21" s="19"/>
       <c r="H21" s="8"/>
-      <c r="I21" s="27" t="s">
+      <c r="I21" s="38" t="s">
         <v>16</v>
       </c>
-      <c r="J21" s="27"/>
-      <c r="K21" s="27"/>
-      <c r="L21" s="27"/>
-      <c r="M21" s="27"/>
-      <c r="N21" s="27"/>
-      <c r="O21" s="27"/>
-      <c r="P21" s="27"/>
+      <c r="J21" s="38"/>
+      <c r="K21" s="38"/>
+      <c r="L21" s="38"/>
+      <c r="M21" s="38"/>
+      <c r="N21" s="38"/>
+      <c r="O21" s="38"/>
+      <c r="P21" s="38"/>
       <c r="Q21" s="4"/>
     </row>
     <row r="22" spans="1:17" ht="21" x14ac:dyDescent="0.35">
-      <c r="A22" s="16" t="s">
+      <c r="A22" s="30" t="s">
         <v>61</v>
       </c>
-      <c r="B22" s="16"/>
-      <c r="C22" s="23" t="s">
+      <c r="B22" s="30"/>
+      <c r="C22" s="32" t="s">
         <v>3</v>
       </c>
-      <c r="D22" s="23"/>
-      <c r="E22" s="38" t="s">
+      <c r="D22" s="32"/>
+      <c r="E22" s="39" t="s">
         <v>4</v>
       </c>
-      <c r="F22" s="23"/>
+      <c r="F22" s="32"/>
       <c r="G22" s="8"/>
-      <c r="H22" s="16" t="s">
+      <c r="H22" s="30" t="s">
         <v>61</v>
       </c>
-      <c r="I22" s="16"/>
-      <c r="J22" s="20" t="s">
+      <c r="I22" s="30"/>
+      <c r="J22" s="35" t="s">
         <v>3</v>
       </c>
-      <c r="K22" s="20"/>
-      <c r="L22" s="20"/>
-      <c r="M22" s="34" t="s">
+      <c r="K22" s="35"/>
+      <c r="L22" s="35"/>
+      <c r="M22" s="40" t="s">
         <v>4</v>
       </c>
-      <c r="N22" s="20"/>
-      <c r="O22" s="20"/>
+      <c r="N22" s="35"/>
+      <c r="O22" s="35"/>
       <c r="P22" s="8"/>
       <c r="Q22" s="4"/>
     </row>
     <row r="23" spans="1:17" ht="21" x14ac:dyDescent="0.35">
-      <c r="A23" s="14"/>
-      <c r="B23" s="14"/>
-      <c r="C23" s="15" t="s">
+      <c r="A23" s="31"/>
+      <c r="B23" s="31"/>
+      <c r="C23" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="D23" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="E23" s="23" t="s">
+        <v>69</v>
+      </c>
+      <c r="F23" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="G23" s="8"/>
+      <c r="H23" s="31"/>
+      <c r="I23" s="31"/>
+      <c r="J23" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="D23" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="E23" s="35" t="s">
+      <c r="K23" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="L23" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="M23" s="23" t="s">
         <v>70</v>
       </c>
-      <c r="F23" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="G23" s="8"/>
-      <c r="H23" s="14"/>
-      <c r="I23" s="14"/>
-      <c r="J23" s="21" t="s">
-        <v>71</v>
-      </c>
-      <c r="K23" s="21" t="s">
+      <c r="N23" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="L23" s="21" t="s">
-        <v>9</v>
-      </c>
-      <c r="M23" s="35" t="s">
-        <v>71</v>
-      </c>
-      <c r="N23" s="21" t="s">
-        <v>8</v>
-      </c>
-      <c r="O23" s="21" t="s">
+      <c r="O23" s="17" t="s">
         <v>9</v>
       </c>
       <c r="P23" s="8"/>
@@ -2474,12 +2646,12 @@
       <c r="B24" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="C24" s="28"/>
-      <c r="D24" s="28">
-        <v>0</v>
-      </c>
-      <c r="E24" s="36"/>
-      <c r="F24" s="28">
+      <c r="C24" s="20"/>
+      <c r="D24" s="20">
+        <v>0</v>
+      </c>
+      <c r="E24" s="24"/>
+      <c r="F24" s="20">
         <v>0</v>
       </c>
       <c r="G24" s="10"/>
@@ -2489,18 +2661,18 @@
       <c r="I24" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="J24" s="28"/>
-      <c r="K24" s="28">
-        <v>0</v>
-      </c>
-      <c r="L24" s="28">
-        <v>0</v>
-      </c>
-      <c r="M24" s="36"/>
-      <c r="N24" s="28">
-        <v>0</v>
-      </c>
-      <c r="O24" s="28">
+      <c r="J24" s="20"/>
+      <c r="K24" s="20">
+        <v>0</v>
+      </c>
+      <c r="L24" s="20">
+        <v>0</v>
+      </c>
+      <c r="M24" s="24"/>
+      <c r="N24" s="20">
+        <v>0</v>
+      </c>
+      <c r="O24" s="20">
         <v>0</v>
       </c>
       <c r="P24" s="10"/>
@@ -2513,12 +2685,12 @@
       <c r="B25" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="C25" s="28"/>
-      <c r="D25" s="28">
-        <v>0</v>
-      </c>
-      <c r="E25" s="36"/>
-      <c r="F25" s="28">
+      <c r="C25" s="20"/>
+      <c r="D25" s="20">
+        <v>0</v>
+      </c>
+      <c r="E25" s="24"/>
+      <c r="F25" s="20">
         <v>0</v>
       </c>
       <c r="G25" s="10"/>
@@ -2528,18 +2700,18 @@
       <c r="I25" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="J25" s="28"/>
-      <c r="K25" s="28">
-        <v>0</v>
-      </c>
-      <c r="L25" s="28">
-        <v>0</v>
-      </c>
-      <c r="M25" s="36"/>
-      <c r="N25" s="28">
-        <v>0</v>
-      </c>
-      <c r="O25" s="28">
+      <c r="J25" s="20"/>
+      <c r="K25" s="20">
+        <v>0</v>
+      </c>
+      <c r="L25" s="20">
+        <v>0</v>
+      </c>
+      <c r="M25" s="24"/>
+      <c r="N25" s="20">
+        <v>0</v>
+      </c>
+      <c r="O25" s="20">
         <v>0</v>
       </c>
       <c r="P25" s="10"/>
@@ -2552,12 +2724,12 @@
       <c r="B26" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="C26" s="28"/>
-      <c r="D26" s="28">
+      <c r="C26" s="20"/>
+      <c r="D26" s="20">
         <v>3</v>
       </c>
-      <c r="E26" s="36"/>
-      <c r="F26" s="28">
+      <c r="E26" s="24"/>
+      <c r="F26" s="20">
         <v>5</v>
       </c>
       <c r="G26" s="10"/>
@@ -2567,18 +2739,18 @@
       <c r="I26" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="J26" s="28"/>
-      <c r="K26" s="28">
-        <v>0</v>
-      </c>
-      <c r="L26" s="28">
-        <v>0</v>
-      </c>
-      <c r="M26" s="36"/>
-      <c r="N26" s="28">
-        <v>0</v>
-      </c>
-      <c r="O26" s="28">
+      <c r="J26" s="20"/>
+      <c r="K26" s="20">
+        <v>0</v>
+      </c>
+      <c r="L26" s="20">
+        <v>0</v>
+      </c>
+      <c r="M26" s="24"/>
+      <c r="N26" s="20">
+        <v>0</v>
+      </c>
+      <c r="O26" s="20">
         <v>0</v>
       </c>
       <c r="P26" s="10"/>
@@ -2591,12 +2763,12 @@
       <c r="B27" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="C27" s="28"/>
-      <c r="D27" s="28">
-        <v>0</v>
-      </c>
-      <c r="E27" s="36"/>
-      <c r="F27" s="28">
+      <c r="C27" s="20"/>
+      <c r="D27" s="20">
+        <v>0</v>
+      </c>
+      <c r="E27" s="24"/>
+      <c r="F27" s="20">
         <v>0</v>
       </c>
       <c r="G27" s="10"/>
@@ -2606,18 +2778,18 @@
       <c r="I27" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="J27" s="28"/>
-      <c r="K27" s="28">
-        <v>0</v>
-      </c>
-      <c r="L27" s="28">
-        <v>0</v>
-      </c>
-      <c r="M27" s="36"/>
-      <c r="N27" s="28">
-        <v>0</v>
-      </c>
-      <c r="O27" s="28">
+      <c r="J27" s="20"/>
+      <c r="K27" s="20">
+        <v>0</v>
+      </c>
+      <c r="L27" s="20">
+        <v>0</v>
+      </c>
+      <c r="M27" s="24"/>
+      <c r="N27" s="20">
+        <v>0</v>
+      </c>
+      <c r="O27" s="20">
         <v>0</v>
       </c>
       <c r="P27" s="10"/>
@@ -2630,12 +2802,12 @@
       <c r="B28" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="C28" s="28"/>
-      <c r="D28" s="28">
+      <c r="C28" s="20"/>
+      <c r="D28" s="20">
         <v>3</v>
       </c>
-      <c r="E28" s="36"/>
-      <c r="F28" s="28">
+      <c r="E28" s="24"/>
+      <c r="F28" s="20">
         <v>3</v>
       </c>
       <c r="G28" s="10"/>
@@ -2645,57 +2817,57 @@
       <c r="I28" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="J28" s="28"/>
-      <c r="K28" s="28">
-        <v>0</v>
-      </c>
-      <c r="L28" s="28">
-        <v>0</v>
-      </c>
-      <c r="M28" s="36"/>
-      <c r="N28" s="28">
-        <v>0</v>
-      </c>
-      <c r="O28" s="28">
+      <c r="J28" s="20"/>
+      <c r="K28" s="20">
+        <v>0</v>
+      </c>
+      <c r="L28" s="20">
+        <v>0</v>
+      </c>
+      <c r="M28" s="24"/>
+      <c r="N28" s="20">
+        <v>0</v>
+      </c>
+      <c r="O28" s="20">
         <v>0</v>
       </c>
       <c r="P28" s="10"/>
       <c r="Q28" s="4"/>
     </row>
     <row r="29" spans="1:17" ht="21" x14ac:dyDescent="0.35">
-      <c r="A29" s="19">
+      <c r="A29" s="16">
         <v>6</v>
       </c>
-      <c r="B29" s="19" t="s">
+      <c r="B29" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C29" s="29"/>
-      <c r="D29" s="29">
-        <v>0</v>
-      </c>
-      <c r="E29" s="37"/>
-      <c r="F29" s="29">
+      <c r="C29" s="21"/>
+      <c r="D29" s="21">
+        <v>0</v>
+      </c>
+      <c r="E29" s="25"/>
+      <c r="F29" s="21">
         <v>0</v>
       </c>
       <c r="G29" s="10"/>
-      <c r="H29" s="19">
+      <c r="H29" s="16">
         <v>6</v>
       </c>
-      <c r="I29" s="19" t="s">
+      <c r="I29" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="J29" s="29"/>
-      <c r="K29" s="29">
-        <v>0</v>
-      </c>
-      <c r="L29" s="29">
-        <v>0</v>
-      </c>
-      <c r="M29" s="37"/>
-      <c r="N29" s="29">
-        <v>0</v>
-      </c>
-      <c r="O29" s="29">
+      <c r="J29" s="21"/>
+      <c r="K29" s="21">
+        <v>0</v>
+      </c>
+      <c r="L29" s="21">
+        <v>0</v>
+      </c>
+      <c r="M29" s="25"/>
+      <c r="N29" s="21">
+        <v>0</v>
+      </c>
+      <c r="O29" s="21">
         <v>0</v>
       </c>
       <c r="P29" s="10"/>
@@ -2740,14 +2912,14 @@
       <c r="Q31" s="4"/>
     </row>
     <row r="32" spans="1:17" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="A32" s="25" t="s">
+      <c r="A32" s="29" t="s">
         <v>62</v>
       </c>
-      <c r="B32" s="25"/>
-      <c r="C32" s="25"/>
-      <c r="D32" s="25"/>
-      <c r="E32" s="25"/>
-      <c r="F32" s="25"/>
+      <c r="B32" s="29"/>
+      <c r="C32" s="29"/>
+      <c r="D32" s="29"/>
+      <c r="E32" s="29"/>
+      <c r="F32" s="29"/>
       <c r="G32" s="4"/>
       <c r="H32" s="4"/>
       <c r="I32" s="4"/>
@@ -2761,32 +2933,32 @@
       <c r="Q32" s="4"/>
     </row>
     <row r="33" spans="1:6" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A33" s="16" t="s">
+      <c r="A33" s="30" t="s">
         <v>61</v>
       </c>
-      <c r="B33" s="16"/>
-      <c r="C33" s="23" t="s">
+      <c r="B33" s="30"/>
+      <c r="C33" s="32" t="s">
         <v>3</v>
       </c>
-      <c r="D33" s="23"/>
-      <c r="E33" s="23" t="s">
+      <c r="D33" s="32"/>
+      <c r="E33" s="32" t="s">
         <v>4</v>
       </c>
-      <c r="F33" s="23"/>
+      <c r="F33" s="32"/>
     </row>
     <row r="34" spans="1:6" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A34" s="14"/>
-      <c r="B34" s="14"/>
-      <c r="C34" s="15" t="s">
+      <c r="A34" s="31"/>
+      <c r="B34" s="31"/>
+      <c r="C34" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="D34" s="15" t="s">
+      <c r="D34" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="E34" s="15" t="s">
+      <c r="E34" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="F34" s="15" t="s">
+      <c r="F34" s="13" t="s">
         <v>6</v>
       </c>
     </row>
@@ -2851,31 +3023,19 @@
       <c r="F39" s="7"/>
     </row>
     <row r="40" spans="1:6" ht="21" x14ac:dyDescent="0.35">
-      <c r="A40" s="17">
+      <c r="A40" s="14">
         <v>6</v>
       </c>
-      <c r="B40" s="17" t="s">
+      <c r="B40" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C40" s="18"/>
-      <c r="D40" s="18"/>
-      <c r="E40" s="18"/>
-      <c r="F40" s="18"/>
+      <c r="C40" s="15"/>
+      <c r="D40" s="15"/>
+      <c r="E40" s="15"/>
+      <c r="F40" s="15"/>
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="A32:F32"/>
-    <mergeCell ref="A33:B34"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="E33:F33"/>
-    <mergeCell ref="A21:F21"/>
-    <mergeCell ref="I21:P21"/>
-    <mergeCell ref="A22:B23"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="H22:I23"/>
-    <mergeCell ref="J22:L22"/>
-    <mergeCell ref="M22:O22"/>
     <mergeCell ref="A10:F10"/>
     <mergeCell ref="I10:P10"/>
     <mergeCell ref="A11:F11"/>
@@ -2886,19 +3046,21 @@
     <mergeCell ref="H12:I13"/>
     <mergeCell ref="J12:L12"/>
     <mergeCell ref="M12:O12"/>
+    <mergeCell ref="I21:P21"/>
+    <mergeCell ref="A22:B23"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="H22:I23"/>
+    <mergeCell ref="J22:L22"/>
+    <mergeCell ref="M22:O22"/>
+    <mergeCell ref="A32:F32"/>
+    <mergeCell ref="A33:B34"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="E33:F33"/>
+    <mergeCell ref="A21:F21"/>
   </mergeCells>
   <conditionalFormatting sqref="C15:C19 E14:E19">
     <cfRule type="colorScale" priority="19">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color theme="9"/>
-        <color rgb="FFFF0000"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J14:J19 M14:M19">
-    <cfRule type="colorScale" priority="18">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -2917,16 +3079,6 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J24:J29 M24:M29">
-    <cfRule type="colorScale" priority="16">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color theme="9"/>
-        <color rgb="FFFF0000"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="D13">
     <cfRule type="colorScale" priority="15">
       <colorScale>
@@ -2937,8 +3089,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D24:D29">
-    <cfRule type="colorScale" priority="9">
+  <conditionalFormatting sqref="D14:D19">
+    <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="7"/>
@@ -2947,8 +3099,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D14:D19">
-    <cfRule type="colorScale" priority="8">
+  <conditionalFormatting sqref="D24:D29">
+    <cfRule type="colorScale" priority="9">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="7"/>
@@ -2972,6 +3124,26 @@
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="7"/>
+        <color theme="9"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J14:J19 M14:M19">
+    <cfRule type="colorScale" priority="18">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color theme="9"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J24:J29 M24:M29">
+    <cfRule type="colorScale" priority="16">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
         <color theme="9"/>
         <color rgb="FFFF0000"/>
       </colorScale>
@@ -3039,10 +3211,10 @@
   </cols>
   <sheetData>
     <row r="3" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="L3" s="12" t="s">
+      <c r="L3" s="43" t="s">
         <v>60</v>
       </c>
-      <c r="M3" s="12"/>
+      <c r="M3" s="43"/>
       <c r="N3" t="s">
         <v>59</v>
       </c>
@@ -3238,7 +3410,7 @@
       <c r="L17" t="s">
         <v>48</v>
       </c>
-      <c r="M17" s="12" t="s">
+      <c r="M17" s="43" t="s">
         <v>49</v>
       </c>
     </row>
@@ -3258,7 +3430,7 @@
       <c r="L18" t="s">
         <v>50</v>
       </c>
-      <c r="M18" s="12"/>
+      <c r="M18" s="43"/>
     </row>
     <row r="19" spans="6:13" x14ac:dyDescent="0.25">
       <c r="G19" t="s">
@@ -3348,12 +3520,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="e8c8a8d2-cf65-4fdf-b6bc-794ebda6188e" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f72adabb-0ee4-4963-acd9-9efc158f92a6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3605,20 +3779,28 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="e8c8a8d2-cf65-4fdf-b6bc-794ebda6188e" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f72adabb-0ee4-4963-acd9-9efc158f92a6">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{29C58647-0154-48BC-9EDF-8ABD72381C6C}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{78150E95-1CCA-47FB-B6E6-99D8675B2929}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="f72adabb-0ee4-4963-acd9-9efc158f92a6"/>
+    <ds:schemaRef ds:uri="cc5908d1-2a89-4186-9c08-2c76e53ac163"/>
+    <ds:schemaRef ds:uri="e8c8a8d2-cf65-4fdf-b6bc-794ebda6188e"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -3644,19 +3826,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{78150E95-1CCA-47FB-B6E6-99D8675B2929}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{29C58647-0154-48BC-9EDF-8ABD72381C6C}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="f72adabb-0ee4-4963-acd9-9efc158f92a6"/>
-    <ds:schemaRef ds:uri="cc5908d1-2a89-4186-9c08-2c76e53ac163"/>
-    <ds:schemaRef ds:uri="e8c8a8d2-cf65-4fdf-b6bc-794ebda6188e"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/output/V3_SIM_Results_Summary.xlsx
+++ b/output/V3_SIM_Results_Summary.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://adminliveunc-my.sharepoint.com/personal/beibo_ad_unc_edu/Documents/CSCC/HCHS/V3_SIM/suddan/HCHS_simulation/output/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1414" documentId="11_F25DC773A252ABDACC10487F29D85E365BDE58E9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{19CE2448-857B-470F-B4B4-6B854B00F7AB}"/>
+  <xr:revisionPtr revIDLastSave="1417" documentId="11_F25DC773A252ABDACC10487F29D85E365BDE58E9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F35004BD-FF4F-4B20-B355-787D1FF51F84}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="761" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="77">
   <si>
     <t>Continous Outcome, PROC GENMOD</t>
   </si>
@@ -266,6 +266,9 @@
   </si>
   <si>
     <t>Based on n = 1000, the approximate 95% CI is (0.9365, 0.9635)</t>
+  </si>
+  <si>
+    <t># of samples: 1000 (unless specified otherwise)</t>
   </si>
 </sst>
 </file>
@@ -482,7 +485,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -540,9 +543,16 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -561,44 +571,36 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -920,7 +922,7 @@
         <v>64</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
@@ -947,112 +949,112 @@
       </c>
     </row>
     <row r="10" spans="1:17" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="42" t="s">
+      <c r="A10" s="41" t="s">
         <v>1</v>
       </c>
-      <c r="B10" s="42"/>
-      <c r="C10" s="42"/>
-      <c r="D10" s="42"/>
-      <c r="E10" s="42"/>
-      <c r="F10" s="42"/>
+      <c r="B10" s="41"/>
+      <c r="C10" s="41"/>
+      <c r="D10" s="41"/>
+      <c r="E10" s="41"/>
+      <c r="F10" s="41"/>
       <c r="G10" s="12"/>
       <c r="H10" s="12"/>
-      <c r="I10" s="42" t="s">
+      <c r="I10" s="41" t="s">
         <v>2</v>
       </c>
-      <c r="J10" s="42"/>
-      <c r="K10" s="42"/>
-      <c r="L10" s="42"/>
-      <c r="M10" s="42"/>
-      <c r="N10" s="42"/>
-      <c r="O10" s="42"/>
-      <c r="P10" s="42"/>
+      <c r="J10" s="41"/>
+      <c r="K10" s="41"/>
+      <c r="L10" s="41"/>
+      <c r="M10" s="41"/>
+      <c r="N10" s="41"/>
+      <c r="O10" s="41"/>
+      <c r="P10" s="41"/>
     </row>
     <row r="11" spans="1:17" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="A11" s="29" t="s">
-        <v>0</v>
-      </c>
-      <c r="B11" s="29"/>
-      <c r="C11" s="29"/>
-      <c r="D11" s="29"/>
-      <c r="E11" s="29"/>
-      <c r="F11" s="29"/>
-      <c r="H11" s="29" t="s">
-        <v>0</v>
-      </c>
-      <c r="I11" s="29"/>
-      <c r="J11" s="29"/>
-      <c r="K11" s="29"/>
-      <c r="L11" s="29"/>
-      <c r="M11" s="29"/>
-      <c r="N11" s="29"/>
-      <c r="O11" s="29"/>
+      <c r="A11" s="40" t="s">
+        <v>0</v>
+      </c>
+      <c r="B11" s="40"/>
+      <c r="C11" s="40"/>
+      <c r="D11" s="40"/>
+      <c r="E11" s="40"/>
+      <c r="F11" s="40"/>
+      <c r="H11" s="40" t="s">
+        <v>0</v>
+      </c>
+      <c r="I11" s="40"/>
+      <c r="J11" s="40"/>
+      <c r="K11" s="40"/>
+      <c r="L11" s="40"/>
+      <c r="M11" s="40"/>
+      <c r="N11" s="40"/>
+      <c r="O11" s="40"/>
     </row>
     <row r="12" spans="1:17" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A12" s="30" t="s">
+      <c r="A12" s="33" t="s">
         <v>61</v>
       </c>
-      <c r="B12" s="30"/>
-      <c r="C12" s="32" t="s">
+      <c r="B12" s="33"/>
+      <c r="C12" s="35" t="s">
         <v>3</v>
       </c>
-      <c r="D12" s="32"/>
-      <c r="E12" s="39" t="s">
+      <c r="D12" s="35"/>
+      <c r="E12" s="46" t="s">
         <v>4</v>
       </c>
-      <c r="F12" s="32"/>
+      <c r="F12" s="35"/>
       <c r="G12" s="4"/>
-      <c r="H12" s="30" t="s">
+      <c r="H12" s="33" t="s">
         <v>61</v>
       </c>
-      <c r="I12" s="30"/>
-      <c r="J12" s="35" t="s">
+      <c r="I12" s="33"/>
+      <c r="J12" s="38" t="s">
         <v>3</v>
       </c>
-      <c r="K12" s="35"/>
-      <c r="L12" s="35"/>
-      <c r="M12" s="40" t="s">
+      <c r="K12" s="38"/>
+      <c r="L12" s="38"/>
+      <c r="M12" s="39" t="s">
         <v>4</v>
       </c>
-      <c r="N12" s="35"/>
-      <c r="O12" s="35"/>
+      <c r="N12" s="38"/>
+      <c r="O12" s="38"/>
       <c r="P12" s="4"/>
       <c r="Q12" s="4"/>
     </row>
     <row r="13" spans="1:17" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A13" s="31"/>
-      <c r="B13" s="31"/>
-      <c r="C13" s="46" t="s">
+      <c r="A13" s="34"/>
+      <c r="B13" s="34"/>
+      <c r="C13" s="29" t="s">
         <v>5</v>
       </c>
       <c r="D13" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="E13" s="47" t="s">
+      <c r="E13" s="30" t="s">
         <v>5</v>
       </c>
       <c r="F13" s="13" t="s">
         <v>6</v>
       </c>
       <c r="G13" s="5"/>
-      <c r="H13" s="31"/>
-      <c r="I13" s="31"/>
+      <c r="H13" s="34"/>
+      <c r="I13" s="34"/>
       <c r="J13" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="K13" s="48" t="s">
+      <c r="K13" s="31" t="s">
         <v>8</v>
       </c>
-      <c r="L13" s="48" t="s">
+      <c r="L13" s="31" t="s">
         <v>9</v>
       </c>
       <c r="M13" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="N13" s="48" t="s">
+      <c r="N13" s="31" t="s">
         <v>8</v>
       </c>
-      <c r="O13" s="48" t="s">
+      <c r="O13" s="31" t="s">
         <v>9</v>
       </c>
       <c r="P13" s="5"/>
@@ -1068,7 +1070,7 @@
       <c r="C14" s="20">
         <v>0</v>
       </c>
-      <c r="D14" s="49">
+      <c r="D14" s="32">
         <v>0</v>
       </c>
       <c r="E14" s="20">
@@ -1360,93 +1362,93 @@
       <c r="Q20" s="4"/>
     </row>
     <row r="21" spans="1:17" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="41" t="s">
+      <c r="A21" s="43" t="s">
         <v>16</v>
       </c>
-      <c r="B21" s="41"/>
-      <c r="C21" s="41"/>
-      <c r="D21" s="41"/>
-      <c r="E21" s="41"/>
-      <c r="F21" s="41"/>
+      <c r="B21" s="43"/>
+      <c r="C21" s="43"/>
+      <c r="D21" s="43"/>
+      <c r="E21" s="43"/>
+      <c r="F21" s="43"/>
       <c r="G21" s="19"/>
-      <c r="H21" s="44" t="s">
+      <c r="H21" s="42" t="s">
         <v>16</v>
       </c>
-      <c r="I21" s="44"/>
-      <c r="J21" s="44"/>
-      <c r="K21" s="44"/>
-      <c r="L21" s="44"/>
-      <c r="M21" s="44"/>
-      <c r="N21" s="44"/>
-      <c r="O21" s="44"/>
-      <c r="P21" s="45"/>
+      <c r="I21" s="42"/>
+      <c r="J21" s="42"/>
+      <c r="K21" s="42"/>
+      <c r="L21" s="42"/>
+      <c r="M21" s="42"/>
+      <c r="N21" s="42"/>
+      <c r="O21" s="42"/>
+      <c r="P21" s="19"/>
       <c r="Q21" s="4"/>
     </row>
     <row r="22" spans="1:17" ht="21" x14ac:dyDescent="0.35">
-      <c r="A22" s="30" t="s">
+      <c r="A22" s="33" t="s">
         <v>61</v>
       </c>
-      <c r="B22" s="30"/>
-      <c r="C22" s="32" t="s">
+      <c r="B22" s="33"/>
+      <c r="C22" s="35" t="s">
         <v>3</v>
       </c>
-      <c r="D22" s="32"/>
-      <c r="E22" s="33" t="s">
+      <c r="D22" s="35"/>
+      <c r="E22" s="36" t="s">
         <v>4</v>
       </c>
-      <c r="F22" s="34"/>
+      <c r="F22" s="37"/>
       <c r="G22" s="8"/>
-      <c r="H22" s="30" t="s">
+      <c r="H22" s="33" t="s">
         <v>61</v>
       </c>
-      <c r="I22" s="30"/>
-      <c r="J22" s="35" t="s">
+      <c r="I22" s="33"/>
+      <c r="J22" s="38" t="s">
         <v>3</v>
       </c>
-      <c r="K22" s="35"/>
-      <c r="L22" s="35"/>
-      <c r="M22" s="36" t="s">
+      <c r="K22" s="38"/>
+      <c r="L22" s="38"/>
+      <c r="M22" s="44" t="s">
         <v>4</v>
       </c>
-      <c r="N22" s="37"/>
-      <c r="O22" s="37"/>
+      <c r="N22" s="45"/>
+      <c r="O22" s="45"/>
       <c r="P22" s="8"/>
       <c r="Q22" s="4"/>
     </row>
     <row r="23" spans="1:17" ht="21" x14ac:dyDescent="0.35">
-      <c r="A23" s="31"/>
-      <c r="B23" s="31"/>
-      <c r="C23" s="46" t="s">
+      <c r="A23" s="34"/>
+      <c r="B23" s="34"/>
+      <c r="C23" s="29" t="s">
         <v>5</v>
       </c>
       <c r="D23" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="E23" s="47" t="s">
+      <c r="E23" s="30" t="s">
         <v>5</v>
       </c>
       <c r="F23" s="22" t="s">
         <v>6</v>
       </c>
       <c r="G23" s="8"/>
-      <c r="H23" s="31"/>
-      <c r="I23" s="31"/>
+      <c r="H23" s="34"/>
+      <c r="I23" s="34"/>
       <c r="J23" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="K23" s="48" t="s">
+      <c r="K23" s="31" t="s">
         <v>8</v>
       </c>
-      <c r="L23" s="48" t="s">
+      <c r="L23" s="31" t="s">
         <v>9</v>
       </c>
       <c r="M23" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="N23" s="48" t="s">
+      <c r="N23" s="31" t="s">
         <v>8</v>
       </c>
-      <c r="O23" s="48" t="s">
+      <c r="O23" s="31" t="s">
         <v>9</v>
       </c>
       <c r="P23" s="8"/>
@@ -1773,59 +1775,59 @@
       <c r="Q31" s="4"/>
     </row>
     <row r="32" spans="1:17" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="A32" s="29" t="s">
+      <c r="A32" s="40" t="s">
         <v>62</v>
       </c>
-      <c r="B32" s="29"/>
-      <c r="C32" s="29"/>
-      <c r="D32" s="29"/>
-      <c r="E32" s="29"/>
-      <c r="F32" s="29"/>
+      <c r="B32" s="40"/>
+      <c r="C32" s="40"/>
+      <c r="D32" s="40"/>
+      <c r="E32" s="40"/>
+      <c r="F32" s="40"/>
       <c r="G32" s="4"/>
-      <c r="H32" s="44" t="s">
+      <c r="H32" s="42" t="s">
         <v>73</v>
       </c>
-      <c r="I32" s="44"/>
-      <c r="J32" s="44"/>
-      <c r="K32" s="44"/>
-      <c r="L32" s="44"/>
-      <c r="M32" s="44"/>
-      <c r="N32" s="44"/>
-      <c r="O32" s="44"/>
+      <c r="I32" s="42"/>
+      <c r="J32" s="42"/>
+      <c r="K32" s="42"/>
+      <c r="L32" s="42"/>
+      <c r="M32" s="42"/>
+      <c r="N32" s="42"/>
+      <c r="O32" s="42"/>
       <c r="P32" s="4"/>
       <c r="Q32" s="4"/>
     </row>
     <row r="33" spans="1:15" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A33" s="30" t="s">
+      <c r="A33" s="33" t="s">
         <v>61</v>
       </c>
-      <c r="B33" s="30"/>
-      <c r="C33" s="32" t="s">
+      <c r="B33" s="33"/>
+      <c r="C33" s="35" t="s">
         <v>3</v>
       </c>
-      <c r="D33" s="32"/>
-      <c r="E33" s="32" t="s">
+      <c r="D33" s="35"/>
+      <c r="E33" s="35" t="s">
         <v>4</v>
       </c>
-      <c r="F33" s="32"/>
-      <c r="H33" s="30" t="s">
+      <c r="F33" s="35"/>
+      <c r="H33" s="33" t="s">
         <v>61</v>
       </c>
-      <c r="I33" s="30"/>
-      <c r="J33" s="35" t="s">
+      <c r="I33" s="33"/>
+      <c r="J33" s="38" t="s">
         <v>3</v>
       </c>
-      <c r="K33" s="35"/>
-      <c r="L33" s="35"/>
-      <c r="M33" s="40" t="s">
+      <c r="K33" s="38"/>
+      <c r="L33" s="38"/>
+      <c r="M33" s="39" t="s">
         <v>4</v>
       </c>
-      <c r="N33" s="35"/>
-      <c r="O33" s="35"/>
+      <c r="N33" s="38"/>
+      <c r="O33" s="38"/>
     </row>
     <row r="34" spans="1:15" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A34" s="31"/>
-      <c r="B34" s="31"/>
+      <c r="A34" s="34"/>
+      <c r="B34" s="34"/>
       <c r="C34" s="13" t="s">
         <v>5</v>
       </c>
@@ -1838,8 +1840,8 @@
       <c r="F34" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="H34" s="31"/>
-      <c r="I34" s="31"/>
+      <c r="H34" s="34"/>
+      <c r="I34" s="34"/>
       <c r="J34" s="17" t="s">
         <v>7</v>
       </c>
@@ -2092,8 +2094,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M14:O19">
-    <cfRule type="colorScale" priority="2">
+  <conditionalFormatting sqref="J35:O40">
+    <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="7"/>
@@ -2102,8 +2104,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J35:O40">
-    <cfRule type="colorScale" priority="1">
+  <conditionalFormatting sqref="M14:O19">
+    <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="7"/>
@@ -2183,81 +2185,81 @@
       </c>
     </row>
     <row r="10" spans="1:17" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="42" t="s">
+      <c r="A10" s="41" t="s">
         <v>1</v>
       </c>
-      <c r="B10" s="42"/>
-      <c r="C10" s="42"/>
-      <c r="D10" s="42"/>
-      <c r="E10" s="42"/>
-      <c r="F10" s="42"/>
+      <c r="B10" s="41"/>
+      <c r="C10" s="41"/>
+      <c r="D10" s="41"/>
+      <c r="E10" s="41"/>
+      <c r="F10" s="41"/>
       <c r="G10" s="12"/>
       <c r="H10" s="12"/>
-      <c r="I10" s="42" t="s">
+      <c r="I10" s="41" t="s">
         <v>2</v>
       </c>
-      <c r="J10" s="42"/>
-      <c r="K10" s="42"/>
-      <c r="L10" s="42"/>
-      <c r="M10" s="42"/>
-      <c r="N10" s="42"/>
-      <c r="O10" s="42"/>
-      <c r="P10" s="42"/>
+      <c r="J10" s="41"/>
+      <c r="K10" s="41"/>
+      <c r="L10" s="41"/>
+      <c r="M10" s="41"/>
+      <c r="N10" s="41"/>
+      <c r="O10" s="41"/>
+      <c r="P10" s="41"/>
     </row>
     <row r="11" spans="1:17" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="A11" s="29" t="s">
-        <v>0</v>
-      </c>
-      <c r="B11" s="29"/>
-      <c r="C11" s="29"/>
-      <c r="D11" s="29"/>
-      <c r="E11" s="29"/>
-      <c r="F11" s="29"/>
-      <c r="H11" s="29" t="s">
-        <v>0</v>
-      </c>
-      <c r="I11" s="29"/>
-      <c r="J11" s="29"/>
-      <c r="K11" s="29"/>
-      <c r="L11" s="29"/>
-      <c r="M11" s="29"/>
-      <c r="N11" s="29"/>
-      <c r="O11" s="29"/>
+      <c r="A11" s="40" t="s">
+        <v>0</v>
+      </c>
+      <c r="B11" s="40"/>
+      <c r="C11" s="40"/>
+      <c r="D11" s="40"/>
+      <c r="E11" s="40"/>
+      <c r="F11" s="40"/>
+      <c r="H11" s="40" t="s">
+        <v>0</v>
+      </c>
+      <c r="I11" s="40"/>
+      <c r="J11" s="40"/>
+      <c r="K11" s="40"/>
+      <c r="L11" s="40"/>
+      <c r="M11" s="40"/>
+      <c r="N11" s="40"/>
+      <c r="O11" s="40"/>
     </row>
     <row r="12" spans="1:17" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A12" s="30" t="s">
+      <c r="A12" s="33" t="s">
         <v>61</v>
       </c>
-      <c r="B12" s="30"/>
-      <c r="C12" s="32" t="s">
+      <c r="B12" s="33"/>
+      <c r="C12" s="35" t="s">
         <v>3</v>
       </c>
-      <c r="D12" s="32"/>
-      <c r="E12" s="39" t="s">
+      <c r="D12" s="35"/>
+      <c r="E12" s="46" t="s">
         <v>4</v>
       </c>
-      <c r="F12" s="32"/>
+      <c r="F12" s="35"/>
       <c r="G12" s="4"/>
-      <c r="H12" s="30" t="s">
+      <c r="H12" s="33" t="s">
         <v>61</v>
       </c>
-      <c r="I12" s="30"/>
-      <c r="J12" s="35" t="s">
+      <c r="I12" s="33"/>
+      <c r="J12" s="38" t="s">
         <v>3</v>
       </c>
-      <c r="K12" s="35"/>
-      <c r="L12" s="35"/>
-      <c r="M12" s="40" t="s">
+      <c r="K12" s="38"/>
+      <c r="L12" s="38"/>
+      <c r="M12" s="39" t="s">
         <v>4</v>
       </c>
-      <c r="N12" s="35"/>
-      <c r="O12" s="35"/>
+      <c r="N12" s="38"/>
+      <c r="O12" s="38"/>
       <c r="P12" s="4"/>
       <c r="Q12" s="4"/>
     </row>
     <row r="13" spans="1:17" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="A13" s="31"/>
-      <c r="B13" s="31"/>
+      <c r="A13" s="34"/>
+      <c r="B13" s="34"/>
       <c r="C13" s="13" t="s">
         <v>69</v>
       </c>
@@ -2271,8 +2273,8 @@
         <v>6</v>
       </c>
       <c r="G13" s="5"/>
-      <c r="H13" s="31"/>
-      <c r="I13" s="31"/>
+      <c r="H13" s="34"/>
+      <c r="I13" s="34"/>
       <c r="J13" s="17" t="s">
         <v>70</v>
       </c>
@@ -2547,62 +2549,62 @@
       <c r="Q20" s="4"/>
     </row>
     <row r="21" spans="1:17" ht="21" x14ac:dyDescent="0.35">
-      <c r="A21" s="41" t="s">
+      <c r="A21" s="43" t="s">
         <v>16</v>
       </c>
-      <c r="B21" s="41"/>
-      <c r="C21" s="41"/>
-      <c r="D21" s="41"/>
-      <c r="E21" s="41"/>
-      <c r="F21" s="41"/>
+      <c r="B21" s="43"/>
+      <c r="C21" s="43"/>
+      <c r="D21" s="43"/>
+      <c r="E21" s="43"/>
+      <c r="F21" s="43"/>
       <c r="G21" s="19"/>
       <c r="H21" s="8"/>
-      <c r="I21" s="38" t="s">
+      <c r="I21" s="47" t="s">
         <v>16</v>
       </c>
-      <c r="J21" s="38"/>
-      <c r="K21" s="38"/>
-      <c r="L21" s="38"/>
-      <c r="M21" s="38"/>
-      <c r="N21" s="38"/>
-      <c r="O21" s="38"/>
-      <c r="P21" s="38"/>
+      <c r="J21" s="47"/>
+      <c r="K21" s="47"/>
+      <c r="L21" s="47"/>
+      <c r="M21" s="47"/>
+      <c r="N21" s="47"/>
+      <c r="O21" s="47"/>
+      <c r="P21" s="47"/>
       <c r="Q21" s="4"/>
     </row>
     <row r="22" spans="1:17" ht="21" x14ac:dyDescent="0.35">
-      <c r="A22" s="30" t="s">
+      <c r="A22" s="33" t="s">
         <v>61</v>
       </c>
-      <c r="B22" s="30"/>
-      <c r="C22" s="32" t="s">
+      <c r="B22" s="33"/>
+      <c r="C22" s="35" t="s">
         <v>3</v>
       </c>
-      <c r="D22" s="32"/>
-      <c r="E22" s="39" t="s">
+      <c r="D22" s="35"/>
+      <c r="E22" s="46" t="s">
         <v>4</v>
       </c>
-      <c r="F22" s="32"/>
+      <c r="F22" s="35"/>
       <c r="G22" s="8"/>
-      <c r="H22" s="30" t="s">
+      <c r="H22" s="33" t="s">
         <v>61</v>
       </c>
-      <c r="I22" s="30"/>
-      <c r="J22" s="35" t="s">
+      <c r="I22" s="33"/>
+      <c r="J22" s="38" t="s">
         <v>3</v>
       </c>
-      <c r="K22" s="35"/>
-      <c r="L22" s="35"/>
-      <c r="M22" s="40" t="s">
+      <c r="K22" s="38"/>
+      <c r="L22" s="38"/>
+      <c r="M22" s="39" t="s">
         <v>4</v>
       </c>
-      <c r="N22" s="35"/>
-      <c r="O22" s="35"/>
+      <c r="N22" s="38"/>
+      <c r="O22" s="38"/>
       <c r="P22" s="8"/>
       <c r="Q22" s="4"/>
     </row>
     <row r="23" spans="1:17" ht="21" x14ac:dyDescent="0.35">
-      <c r="A23" s="31"/>
-      <c r="B23" s="31"/>
+      <c r="A23" s="34"/>
+      <c r="B23" s="34"/>
       <c r="C23" s="13" t="s">
         <v>69</v>
       </c>
@@ -2616,8 +2618,8 @@
         <v>6</v>
       </c>
       <c r="G23" s="8"/>
-      <c r="H23" s="31"/>
-      <c r="I23" s="31"/>
+      <c r="H23" s="34"/>
+      <c r="I23" s="34"/>
       <c r="J23" s="17" t="s">
         <v>70</v>
       </c>
@@ -2912,14 +2914,14 @@
       <c r="Q31" s="4"/>
     </row>
     <row r="32" spans="1:17" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="A32" s="29" t="s">
+      <c r="A32" s="40" t="s">
         <v>62</v>
       </c>
-      <c r="B32" s="29"/>
-      <c r="C32" s="29"/>
-      <c r="D32" s="29"/>
-      <c r="E32" s="29"/>
-      <c r="F32" s="29"/>
+      <c r="B32" s="40"/>
+      <c r="C32" s="40"/>
+      <c r="D32" s="40"/>
+      <c r="E32" s="40"/>
+      <c r="F32" s="40"/>
       <c r="G32" s="4"/>
       <c r="H32" s="4"/>
       <c r="I32" s="4"/>
@@ -2933,22 +2935,22 @@
       <c r="Q32" s="4"/>
     </row>
     <row r="33" spans="1:6" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A33" s="30" t="s">
+      <c r="A33" s="33" t="s">
         <v>61</v>
       </c>
-      <c r="B33" s="30"/>
-      <c r="C33" s="32" t="s">
+      <c r="B33" s="33"/>
+      <c r="C33" s="35" t="s">
         <v>3</v>
       </c>
-      <c r="D33" s="32"/>
-      <c r="E33" s="32" t="s">
+      <c r="D33" s="35"/>
+      <c r="E33" s="35" t="s">
         <v>4</v>
       </c>
-      <c r="F33" s="32"/>
+      <c r="F33" s="35"/>
     </row>
     <row r="34" spans="1:6" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A34" s="31"/>
-      <c r="B34" s="31"/>
+      <c r="A34" s="34"/>
+      <c r="B34" s="34"/>
       <c r="C34" s="13" t="s">
         <v>5</v>
       </c>
@@ -3211,10 +3213,10 @@
   </cols>
   <sheetData>
     <row r="3" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="L3" s="43" t="s">
+      <c r="L3" s="48" t="s">
         <v>60</v>
       </c>
-      <c r="M3" s="43"/>
+      <c r="M3" s="48"/>
       <c r="N3" t="s">
         <v>59</v>
       </c>
@@ -3410,7 +3412,7 @@
       <c r="L17" t="s">
         <v>48</v>
       </c>
-      <c r="M17" s="43" t="s">
+      <c r="M17" s="48" t="s">
         <v>49</v>
       </c>
     </row>
@@ -3430,7 +3432,7 @@
       <c r="L18" t="s">
         <v>50</v>
       </c>
-      <c r="M18" s="43"/>
+      <c r="M18" s="48"/>
     </row>
     <row r="19" spans="6:13" x14ac:dyDescent="0.25">
       <c r="G19" t="s">

--- a/output/V3_SIM_Results_Summary.xlsx
+++ b/output/V3_SIM_Results_Summary.xlsx
@@ -8,14 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://adminliveunc-my.sharepoint.com/personal/beibo_ad_unc_edu/Documents/CSCC/HCHS/V3_SIM/suddan/HCHS_simulation/output/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1417" documentId="11_F25DC773A252ABDACC10487F29D85E365BDE58E9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F35004BD-FF4F-4B20-B355-787D1FF51F84}"/>
+  <xr:revisionPtr revIDLastSave="1694" documentId="11_F25DC773A252ABDACC10487F29D85E365BDE58E9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B8EB9779-EEAE-4283-8753-38B943B85BF0}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="761" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary  (coverage)" sheetId="16" r:id="rId1"/>
-    <sheet name="Summary (eff comp)" sheetId="17" r:id="rId2"/>
-    <sheet name="note" sheetId="3" r:id="rId3"/>
+    <sheet name="Summary  (coverage) (2)" sheetId="18" r:id="rId2"/>
+    <sheet name="Summary (eff comp)" sheetId="17" r:id="rId3"/>
+    <sheet name="Summary (eff comp) (2)" sheetId="19" r:id="rId4"/>
+    <sheet name="note" sheetId="3" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -38,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="533" uniqueCount="84">
   <si>
     <t>Continous Outcome, PROC GENMOD</t>
   </si>
@@ -269,13 +271,34 @@
   </si>
   <si>
     <t># of samples: 1000 (unless specified otherwise)</t>
+  </si>
+  <si>
+    <t>Binary Outcome, SUDAAN</t>
+  </si>
+  <si>
+    <t>SUDAAN Sample Size</t>
+  </si>
+  <si>
+    <t>Good coverage range: [0.9365, 0.9635]</t>
+  </si>
+  <si>
+    <t>Good relative eff threshold: &lt;= 5%</t>
+  </si>
+  <si>
+    <t xml:space="preserve"># in the cell: # of parameters with coverages not in the good coverage range </t>
+  </si>
+  <si>
+    <t>Scenario 4, Independent, RR_glm, "1" out-of-range coverage is 0.923</t>
+  </si>
+  <si>
+    <t>Scenario 6, Exchangeable, RR_glm, "1" out-of-range coverage is 0.920</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -384,6 +407,21 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -485,7 +523,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -543,23 +581,47 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -568,37 +630,69 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -882,7 +976,1888 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAB8470B-C760-491C-B73B-F574B62DA7BA}">
-  <dimension ref="A1:Q40"/>
+  <dimension ref="A1:Y55"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="3.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="64.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="4.140625" customWidth="1"/>
+    <col min="8" max="8" width="2.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="65.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14" customWidth="1"/>
+    <col min="15" max="15" width="9.5703125" customWidth="1"/>
+    <col min="16" max="16" width="2.85546875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="65.28515625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="17" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="27.7109375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="17" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="27.7109375" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="19.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="K1" s="1"/>
+    </row>
+    <row r="2" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>63</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="K2" s="1"/>
+    </row>
+    <row r="3" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>64</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="K3" s="1"/>
+    </row>
+    <row r="4" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="K4" s="1"/>
+    </row>
+    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="6" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="32" t="s">
+        <v>1</v>
+      </c>
+      <c r="B10" s="32"/>
+      <c r="C10" s="32"/>
+      <c r="D10" s="32"/>
+      <c r="E10" s="32"/>
+      <c r="F10" s="32"/>
+      <c r="G10" s="31"/>
+      <c r="H10" s="32" t="s">
+        <v>1</v>
+      </c>
+      <c r="I10" s="32"/>
+      <c r="J10" s="32"/>
+      <c r="K10" s="32"/>
+      <c r="L10" s="32"/>
+      <c r="M10" s="32"/>
+      <c r="N10" s="31"/>
+      <c r="O10" s="12"/>
+      <c r="P10" s="62" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q10" s="62"/>
+      <c r="R10" s="62"/>
+      <c r="S10" s="62"/>
+      <c r="T10" s="62"/>
+      <c r="U10" s="62"/>
+      <c r="V10" s="62"/>
+      <c r="W10" s="62"/>
+      <c r="X10" s="61"/>
+    </row>
+    <row r="11" spans="1:25" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="A11" s="39" t="s">
+        <v>0</v>
+      </c>
+      <c r="B11" s="39"/>
+      <c r="C11" s="39"/>
+      <c r="D11" s="39"/>
+      <c r="E11" s="39"/>
+      <c r="F11" s="39"/>
+      <c r="G11" s="53"/>
+      <c r="H11" s="39" t="s">
+        <v>62</v>
+      </c>
+      <c r="I11" s="39"/>
+      <c r="J11" s="39"/>
+      <c r="K11" s="39"/>
+      <c r="L11" s="39"/>
+      <c r="M11" s="39"/>
+      <c r="N11" s="53"/>
+      <c r="P11" s="39" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="39"/>
+      <c r="R11" s="39"/>
+      <c r="S11" s="39"/>
+      <c r="T11" s="39"/>
+      <c r="U11" s="39"/>
+      <c r="V11" s="39"/>
+      <c r="W11" s="39"/>
+    </row>
+    <row r="12" spans="1:25" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="A12" s="34" t="s">
+        <v>61</v>
+      </c>
+      <c r="B12" s="34"/>
+      <c r="C12" s="42" t="s">
+        <v>3</v>
+      </c>
+      <c r="D12" s="42"/>
+      <c r="E12" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="F12" s="42"/>
+      <c r="G12" s="54"/>
+      <c r="H12" s="34" t="s">
+        <v>61</v>
+      </c>
+      <c r="I12" s="34"/>
+      <c r="J12" s="42" t="s">
+        <v>3</v>
+      </c>
+      <c r="K12" s="42"/>
+      <c r="L12" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="M12" s="42"/>
+      <c r="N12" s="54"/>
+      <c r="O12" s="4"/>
+      <c r="P12" s="34" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q12" s="34"/>
+      <c r="R12" s="36" t="s">
+        <v>3</v>
+      </c>
+      <c r="S12" s="36"/>
+      <c r="T12" s="36"/>
+      <c r="U12" s="37" t="s">
+        <v>4</v>
+      </c>
+      <c r="V12" s="36"/>
+      <c r="W12" s="36"/>
+      <c r="X12" s="4"/>
+      <c r="Y12" s="4"/>
+    </row>
+    <row r="13" spans="1:25" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="A13" s="35"/>
+      <c r="B13" s="35"/>
+      <c r="C13" s="48" t="s">
+        <v>5</v>
+      </c>
+      <c r="D13" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="E13" s="49" t="s">
+        <v>5</v>
+      </c>
+      <c r="F13" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="G13" s="55"/>
+      <c r="H13" s="35"/>
+      <c r="I13" s="35"/>
+      <c r="J13" s="48" t="s">
+        <v>5</v>
+      </c>
+      <c r="K13" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="L13" s="49" t="s">
+        <v>5</v>
+      </c>
+      <c r="M13" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="N13" s="55"/>
+      <c r="O13" s="5"/>
+      <c r="P13" s="35"/>
+      <c r="Q13" s="35"/>
+      <c r="R13" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="S13" s="29" t="s">
+        <v>8</v>
+      </c>
+      <c r="T13" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="U13" s="23" t="s">
+        <v>7</v>
+      </c>
+      <c r="V13" s="29" t="s">
+        <v>8</v>
+      </c>
+      <c r="W13" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="X13" s="5"/>
+      <c r="Y13" s="4"/>
+    </row>
+    <row r="14" spans="1:25" ht="21" x14ac:dyDescent="0.35">
+      <c r="A14" s="6">
+        <v>1</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C14" s="20">
+        <v>0</v>
+      </c>
+      <c r="D14" s="30">
+        <v>0</v>
+      </c>
+      <c r="E14" s="20">
+        <v>0</v>
+      </c>
+      <c r="F14" s="20">
+        <v>1</v>
+      </c>
+      <c r="G14" s="56"/>
+      <c r="H14" s="6">
+        <v>1</v>
+      </c>
+      <c r="I14" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="J14" s="20">
+        <v>0</v>
+      </c>
+      <c r="K14" s="20">
+        <v>0</v>
+      </c>
+      <c r="L14" s="20">
+        <v>2</v>
+      </c>
+      <c r="M14" s="20">
+        <v>3</v>
+      </c>
+      <c r="N14" s="20"/>
+      <c r="O14" s="8"/>
+      <c r="P14" s="6">
+        <v>1</v>
+      </c>
+      <c r="Q14" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="R14" s="20">
+        <v>0</v>
+      </c>
+      <c r="S14" s="20">
+        <v>0</v>
+      </c>
+      <c r="T14" s="20">
+        <v>0</v>
+      </c>
+      <c r="U14" s="20">
+        <v>0</v>
+      </c>
+      <c r="V14" s="20">
+        <v>1</v>
+      </c>
+      <c r="W14" s="20">
+        <v>0</v>
+      </c>
+      <c r="X14" s="8"/>
+      <c r="Y14" s="4"/>
+    </row>
+    <row r="15" spans="1:25" ht="21" x14ac:dyDescent="0.35">
+      <c r="A15" s="6">
+        <v>2</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C15" s="20">
+        <v>5</v>
+      </c>
+      <c r="D15" s="20">
+        <v>5</v>
+      </c>
+      <c r="E15" s="20">
+        <v>6</v>
+      </c>
+      <c r="F15" s="20">
+        <v>6</v>
+      </c>
+      <c r="G15" s="56"/>
+      <c r="H15" s="6">
+        <v>2</v>
+      </c>
+      <c r="I15" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="J15" s="20">
+        <v>5</v>
+      </c>
+      <c r="K15" s="20">
+        <v>0</v>
+      </c>
+      <c r="L15" s="20">
+        <v>6</v>
+      </c>
+      <c r="M15" s="20">
+        <v>0</v>
+      </c>
+      <c r="N15" s="20"/>
+      <c r="O15" s="8"/>
+      <c r="P15" s="6">
+        <v>2</v>
+      </c>
+      <c r="Q15" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="R15" s="20">
+        <v>5</v>
+      </c>
+      <c r="S15" s="20">
+        <v>5</v>
+      </c>
+      <c r="T15" s="20">
+        <v>5</v>
+      </c>
+      <c r="U15" s="20">
+        <v>6</v>
+      </c>
+      <c r="V15" s="20">
+        <v>6</v>
+      </c>
+      <c r="W15" s="20">
+        <v>6</v>
+      </c>
+      <c r="X15" s="8"/>
+      <c r="Y15" s="4"/>
+    </row>
+    <row r="16" spans="1:25" ht="21" x14ac:dyDescent="0.35">
+      <c r="A16" s="6">
+        <v>3</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C16" s="20">
+        <v>0</v>
+      </c>
+      <c r="D16" s="20">
+        <v>1</v>
+      </c>
+      <c r="E16" s="20">
+        <v>0</v>
+      </c>
+      <c r="F16" s="20">
+        <v>2</v>
+      </c>
+      <c r="G16" s="56"/>
+      <c r="H16" s="6">
+        <v>3</v>
+      </c>
+      <c r="I16" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="J16" s="20">
+        <v>2</v>
+      </c>
+      <c r="K16" s="20">
+        <v>3</v>
+      </c>
+      <c r="L16" s="20">
+        <v>5</v>
+      </c>
+      <c r="M16" s="20">
+        <v>2</v>
+      </c>
+      <c r="N16" s="20"/>
+      <c r="O16" s="8"/>
+      <c r="P16" s="6">
+        <v>3</v>
+      </c>
+      <c r="Q16" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="R16" s="20">
+        <v>0</v>
+      </c>
+      <c r="S16" s="20">
+        <v>0</v>
+      </c>
+      <c r="T16" s="20">
+        <v>0</v>
+      </c>
+      <c r="U16" s="20">
+        <v>0</v>
+      </c>
+      <c r="V16" s="20">
+        <v>0</v>
+      </c>
+      <c r="W16" s="20">
+        <v>0</v>
+      </c>
+      <c r="X16" s="8"/>
+      <c r="Y16" s="4"/>
+    </row>
+    <row r="17" spans="1:25" ht="21" x14ac:dyDescent="0.35">
+      <c r="A17" s="6">
+        <v>4</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C17" s="20">
+        <v>0</v>
+      </c>
+      <c r="D17" s="20">
+        <v>2</v>
+      </c>
+      <c r="E17" s="20">
+        <v>1</v>
+      </c>
+      <c r="F17" s="20">
+        <v>2</v>
+      </c>
+      <c r="G17" s="56"/>
+      <c r="H17" s="6">
+        <v>4</v>
+      </c>
+      <c r="I17" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="J17" s="20">
+        <v>0</v>
+      </c>
+      <c r="K17" s="20">
+        <v>2</v>
+      </c>
+      <c r="L17" s="20">
+        <v>2</v>
+      </c>
+      <c r="M17" s="20">
+        <v>2</v>
+      </c>
+      <c r="N17" s="20"/>
+      <c r="O17" s="8"/>
+      <c r="P17" s="6">
+        <v>4</v>
+      </c>
+      <c r="Q17" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="R17" s="20">
+        <v>0</v>
+      </c>
+      <c r="S17" s="20">
+        <v>0</v>
+      </c>
+      <c r="T17" s="20">
+        <v>0</v>
+      </c>
+      <c r="U17" s="20">
+        <v>1</v>
+      </c>
+      <c r="V17" s="20">
+        <v>2</v>
+      </c>
+      <c r="W17" s="20">
+        <v>1</v>
+      </c>
+      <c r="X17" s="8"/>
+      <c r="Y17" s="4"/>
+    </row>
+    <row r="18" spans="1:25" ht="21" x14ac:dyDescent="0.35">
+      <c r="A18" s="6">
+        <v>5</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C18" s="20">
+        <v>4</v>
+      </c>
+      <c r="D18" s="20">
+        <v>5</v>
+      </c>
+      <c r="E18" s="20">
+        <v>3</v>
+      </c>
+      <c r="F18" s="20">
+        <v>6</v>
+      </c>
+      <c r="G18" s="56"/>
+      <c r="H18" s="6">
+        <v>5</v>
+      </c>
+      <c r="I18" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J18" s="20"/>
+      <c r="K18" s="20"/>
+      <c r="L18" s="20"/>
+      <c r="M18" s="20"/>
+      <c r="N18" s="20"/>
+      <c r="O18" s="8"/>
+      <c r="P18" s="6">
+        <v>5</v>
+      </c>
+      <c r="Q18" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="R18" s="20">
+        <v>5</v>
+      </c>
+      <c r="S18" s="20">
+        <v>5</v>
+      </c>
+      <c r="T18" s="20">
+        <v>5</v>
+      </c>
+      <c r="U18" s="20">
+        <v>5</v>
+      </c>
+      <c r="V18" s="20">
+        <v>6</v>
+      </c>
+      <c r="W18" s="20">
+        <v>6</v>
+      </c>
+      <c r="X18" s="8"/>
+      <c r="Y18" s="4"/>
+    </row>
+    <row r="19" spans="1:25" ht="21" x14ac:dyDescent="0.35">
+      <c r="A19" s="14">
+        <v>6</v>
+      </c>
+      <c r="B19" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="C19" s="21">
+        <v>0</v>
+      </c>
+      <c r="D19" s="21">
+        <v>2</v>
+      </c>
+      <c r="E19" s="21">
+        <v>3</v>
+      </c>
+      <c r="F19" s="21">
+        <v>5</v>
+      </c>
+      <c r="G19" s="56"/>
+      <c r="H19" s="14">
+        <v>6</v>
+      </c>
+      <c r="I19" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="J19" s="21">
+        <v>0</v>
+      </c>
+      <c r="K19" s="21">
+        <v>2</v>
+      </c>
+      <c r="L19" s="21">
+        <v>4</v>
+      </c>
+      <c r="M19" s="21">
+        <v>6</v>
+      </c>
+      <c r="N19" s="56"/>
+      <c r="O19" s="8"/>
+      <c r="P19" s="6">
+        <v>6</v>
+      </c>
+      <c r="Q19" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="R19" s="21">
+        <v>0</v>
+      </c>
+      <c r="S19" s="21">
+        <v>0</v>
+      </c>
+      <c r="T19" s="21">
+        <v>0</v>
+      </c>
+      <c r="U19" s="21">
+        <v>3</v>
+      </c>
+      <c r="V19" s="21">
+        <v>3</v>
+      </c>
+      <c r="W19" s="21">
+        <v>3</v>
+      </c>
+      <c r="X19" s="8"/>
+      <c r="Y19" s="4"/>
+    </row>
+    <row r="20" spans="1:25" ht="21" x14ac:dyDescent="0.35">
+      <c r="A20" s="8"/>
+      <c r="B20" s="8"/>
+      <c r="C20" s="8"/>
+      <c r="D20" s="8"/>
+      <c r="E20" s="8"/>
+      <c r="F20" s="8"/>
+      <c r="G20" s="60"/>
+      <c r="H20" s="8"/>
+      <c r="I20" s="8"/>
+      <c r="J20" s="8"/>
+      <c r="K20" s="8"/>
+      <c r="L20" s="8"/>
+      <c r="M20" s="8"/>
+      <c r="N20" s="8"/>
+      <c r="O20" s="8"/>
+      <c r="P20" s="8"/>
+      <c r="Q20" s="8"/>
+      <c r="R20" s="8"/>
+      <c r="S20" s="4"/>
+    </row>
+    <row r="21" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="38" t="s">
+        <v>16</v>
+      </c>
+      <c r="B21" s="38"/>
+      <c r="C21" s="38"/>
+      <c r="D21" s="38"/>
+      <c r="E21" s="38"/>
+      <c r="F21" s="38"/>
+      <c r="G21" s="57"/>
+      <c r="H21" s="38" t="s">
+        <v>77</v>
+      </c>
+      <c r="I21" s="38"/>
+      <c r="J21" s="38"/>
+      <c r="K21" s="38"/>
+      <c r="L21" s="38"/>
+      <c r="M21" s="38"/>
+      <c r="N21" s="57"/>
+      <c r="O21" s="19"/>
+      <c r="P21" s="33" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q21" s="33"/>
+      <c r="R21" s="33"/>
+      <c r="S21" s="33"/>
+      <c r="T21" s="33"/>
+      <c r="U21" s="33"/>
+      <c r="V21" s="33"/>
+      <c r="W21" s="33"/>
+      <c r="X21" s="19"/>
+      <c r="Y21" s="4"/>
+    </row>
+    <row r="22" spans="1:25" ht="21" x14ac:dyDescent="0.35">
+      <c r="A22" s="34" t="s">
+        <v>61</v>
+      </c>
+      <c r="B22" s="34"/>
+      <c r="C22" s="42" t="s">
+        <v>3</v>
+      </c>
+      <c r="D22" s="42"/>
+      <c r="E22" s="44" t="s">
+        <v>4</v>
+      </c>
+      <c r="F22" s="45"/>
+      <c r="G22" s="58"/>
+      <c r="H22" s="34" t="s">
+        <v>61</v>
+      </c>
+      <c r="I22" s="34"/>
+      <c r="J22" s="42" t="s">
+        <v>3</v>
+      </c>
+      <c r="K22" s="42"/>
+      <c r="L22" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="M22" s="42"/>
+      <c r="N22" s="54"/>
+      <c r="O22" s="8"/>
+      <c r="P22" s="34" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q22" s="34"/>
+      <c r="R22" s="36" t="s">
+        <v>3</v>
+      </c>
+      <c r="S22" s="36"/>
+      <c r="T22" s="36"/>
+      <c r="U22" s="40" t="s">
+        <v>4</v>
+      </c>
+      <c r="V22" s="41"/>
+      <c r="W22" s="41"/>
+      <c r="X22" s="8"/>
+      <c r="Y22" s="4"/>
+    </row>
+    <row r="23" spans="1:25" ht="21" x14ac:dyDescent="0.35">
+      <c r="A23" s="35"/>
+      <c r="B23" s="35"/>
+      <c r="C23" s="48" t="s">
+        <v>5</v>
+      </c>
+      <c r="D23" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="E23" s="50" t="s">
+        <v>5</v>
+      </c>
+      <c r="F23" s="22" t="s">
+        <v>6</v>
+      </c>
+      <c r="G23" s="58"/>
+      <c r="H23" s="35"/>
+      <c r="I23" s="35"/>
+      <c r="J23" s="48" t="s">
+        <v>5</v>
+      </c>
+      <c r="K23" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="L23" s="49" t="s">
+        <v>5</v>
+      </c>
+      <c r="M23" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="N23" s="55"/>
+      <c r="O23" s="8"/>
+      <c r="P23" s="35"/>
+      <c r="Q23" s="35"/>
+      <c r="R23" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="S23" s="29" t="s">
+        <v>8</v>
+      </c>
+      <c r="T23" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="U23" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="V23" s="29" t="s">
+        <v>8</v>
+      </c>
+      <c r="W23" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="X23" s="8"/>
+      <c r="Y23" s="4"/>
+    </row>
+    <row r="24" spans="1:25" ht="21" x14ac:dyDescent="0.35">
+      <c r="A24" s="9">
+        <v>1</v>
+      </c>
+      <c r="B24" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C24" s="20">
+        <v>4</v>
+      </c>
+      <c r="D24" s="20">
+        <v>4</v>
+      </c>
+      <c r="E24" s="20">
+        <v>4</v>
+      </c>
+      <c r="F24" s="20">
+        <v>3</v>
+      </c>
+      <c r="G24" s="20"/>
+      <c r="H24" s="9">
+        <v>1</v>
+      </c>
+      <c r="I24" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="J24" s="20">
+        <v>5</v>
+      </c>
+      <c r="K24" s="20">
+        <v>4</v>
+      </c>
+      <c r="L24" s="20">
+        <v>5</v>
+      </c>
+      <c r="M24" s="20">
+        <v>4</v>
+      </c>
+      <c r="N24" s="20"/>
+      <c r="O24" s="10"/>
+      <c r="P24" s="9">
+        <v>1</v>
+      </c>
+      <c r="Q24" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="R24" s="20">
+        <v>0</v>
+      </c>
+      <c r="S24" s="20">
+        <v>0</v>
+      </c>
+      <c r="T24" s="20">
+        <v>0</v>
+      </c>
+      <c r="U24" s="20">
+        <v>0</v>
+      </c>
+      <c r="V24" s="20">
+        <v>0</v>
+      </c>
+      <c r="W24" s="20">
+        <v>0</v>
+      </c>
+      <c r="X24" s="10"/>
+      <c r="Y24" s="4"/>
+    </row>
+    <row r="25" spans="1:25" ht="21" x14ac:dyDescent="0.35">
+      <c r="A25" s="9">
+        <v>2</v>
+      </c>
+      <c r="B25" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="20">
+        <v>4</v>
+      </c>
+      <c r="D25" s="20">
+        <v>4</v>
+      </c>
+      <c r="E25" s="20">
+        <v>4</v>
+      </c>
+      <c r="F25" s="20">
+        <v>4</v>
+      </c>
+      <c r="G25" s="20"/>
+      <c r="H25" s="9">
+        <v>2</v>
+      </c>
+      <c r="I25" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="J25" s="20">
+        <v>4</v>
+      </c>
+      <c r="K25" s="20">
+        <v>0</v>
+      </c>
+      <c r="L25" s="20">
+        <v>4</v>
+      </c>
+      <c r="M25" s="20">
+        <v>0</v>
+      </c>
+      <c r="N25" s="20"/>
+      <c r="O25" s="10"/>
+      <c r="P25" s="9">
+        <v>2</v>
+      </c>
+      <c r="Q25" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="R25" s="20">
+        <v>4</v>
+      </c>
+      <c r="S25" s="20">
+        <v>4</v>
+      </c>
+      <c r="T25" s="20">
+        <v>4</v>
+      </c>
+      <c r="U25" s="20">
+        <v>4</v>
+      </c>
+      <c r="V25" s="20">
+        <v>4</v>
+      </c>
+      <c r="W25" s="20">
+        <v>4</v>
+      </c>
+      <c r="X25" s="10"/>
+      <c r="Y25" s="4"/>
+    </row>
+    <row r="26" spans="1:25" ht="21" x14ac:dyDescent="0.35">
+      <c r="A26" s="9">
+        <v>3</v>
+      </c>
+      <c r="B26" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C26" s="20">
+        <v>5</v>
+      </c>
+      <c r="D26" s="20">
+        <v>6</v>
+      </c>
+      <c r="E26" s="20">
+        <v>5</v>
+      </c>
+      <c r="F26" s="20">
+        <v>6</v>
+      </c>
+      <c r="G26" s="20"/>
+      <c r="H26" s="9">
+        <v>3</v>
+      </c>
+      <c r="I26" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="J26" s="20">
+        <v>4</v>
+      </c>
+      <c r="K26" s="20">
+        <v>6</v>
+      </c>
+      <c r="L26" s="20">
+        <v>3</v>
+      </c>
+      <c r="M26" s="20">
+        <v>3</v>
+      </c>
+      <c r="N26" s="20"/>
+      <c r="O26" s="10"/>
+      <c r="P26" s="9">
+        <v>3</v>
+      </c>
+      <c r="Q26" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="R26" s="20">
+        <v>3</v>
+      </c>
+      <c r="S26" s="20">
+        <v>3</v>
+      </c>
+      <c r="T26" s="20">
+        <v>2</v>
+      </c>
+      <c r="U26" s="20">
+        <v>3</v>
+      </c>
+      <c r="V26" s="20">
+        <v>3</v>
+      </c>
+      <c r="W26" s="20">
+        <v>3</v>
+      </c>
+      <c r="X26" s="10"/>
+      <c r="Y26" s="4"/>
+    </row>
+    <row r="27" spans="1:25" ht="21" x14ac:dyDescent="0.35">
+      <c r="A27" s="9">
+        <v>4</v>
+      </c>
+      <c r="B27" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="C27" s="20">
+        <v>1</v>
+      </c>
+      <c r="D27" s="20">
+        <v>2</v>
+      </c>
+      <c r="E27" s="20">
+        <v>0</v>
+      </c>
+      <c r="F27" s="20">
+        <v>2</v>
+      </c>
+      <c r="G27" s="20"/>
+      <c r="H27" s="9">
+        <v>4</v>
+      </c>
+      <c r="I27" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J27" s="20">
+        <v>0</v>
+      </c>
+      <c r="K27" s="20">
+        <v>2</v>
+      </c>
+      <c r="L27" s="20">
+        <v>0</v>
+      </c>
+      <c r="M27" s="20">
+        <v>2</v>
+      </c>
+      <c r="N27" s="20"/>
+      <c r="O27" s="10"/>
+      <c r="P27" s="9">
+        <v>4</v>
+      </c>
+      <c r="Q27" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="R27" s="20">
+        <v>0</v>
+      </c>
+      <c r="S27" s="20">
+        <v>0</v>
+      </c>
+      <c r="T27" s="20">
+        <v>0</v>
+      </c>
+      <c r="U27" s="20">
+        <v>0</v>
+      </c>
+      <c r="V27" s="20">
+        <v>0</v>
+      </c>
+      <c r="W27" s="20">
+        <v>0</v>
+      </c>
+      <c r="X27" s="10"/>
+      <c r="Y27" s="4"/>
+    </row>
+    <row r="28" spans="1:25" ht="21" x14ac:dyDescent="0.35">
+      <c r="A28" s="9">
+        <v>5</v>
+      </c>
+      <c r="B28" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C28" s="20">
+        <v>7</v>
+      </c>
+      <c r="D28" s="20">
+        <v>2</v>
+      </c>
+      <c r="E28" s="20">
+        <v>7</v>
+      </c>
+      <c r="F28" s="20">
+        <v>3</v>
+      </c>
+      <c r="G28" s="20"/>
+      <c r="H28" s="9">
+        <v>5</v>
+      </c>
+      <c r="I28" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="J28" s="20"/>
+      <c r="K28" s="20"/>
+      <c r="L28" s="20"/>
+      <c r="M28" s="20"/>
+      <c r="N28" s="20"/>
+      <c r="O28" s="10"/>
+      <c r="P28" s="9">
+        <v>5</v>
+      </c>
+      <c r="Q28" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="R28" s="20">
+        <v>1</v>
+      </c>
+      <c r="S28" s="20">
+        <v>1</v>
+      </c>
+      <c r="T28" s="20">
+        <v>1</v>
+      </c>
+      <c r="U28" s="20">
+        <v>2</v>
+      </c>
+      <c r="V28" s="20">
+        <v>2</v>
+      </c>
+      <c r="W28" s="20">
+        <v>2</v>
+      </c>
+      <c r="X28" s="10"/>
+      <c r="Y28" s="4"/>
+    </row>
+    <row r="29" spans="1:25" ht="21" x14ac:dyDescent="0.35">
+      <c r="A29" s="16">
+        <v>6</v>
+      </c>
+      <c r="B29" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="C29" s="21">
+        <v>0</v>
+      </c>
+      <c r="D29" s="21">
+        <v>2</v>
+      </c>
+      <c r="E29" s="21">
+        <v>1</v>
+      </c>
+      <c r="F29" s="21">
+        <v>2</v>
+      </c>
+      <c r="G29" s="56"/>
+      <c r="H29" s="16">
+        <v>6</v>
+      </c>
+      <c r="I29" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="J29" s="21">
+        <v>0</v>
+      </c>
+      <c r="K29" s="21">
+        <v>3</v>
+      </c>
+      <c r="L29" s="21">
+        <v>2</v>
+      </c>
+      <c r="M29" s="21">
+        <v>4</v>
+      </c>
+      <c r="N29" s="56"/>
+      <c r="O29" s="10"/>
+      <c r="P29" s="16">
+        <v>6</v>
+      </c>
+      <c r="Q29" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="R29" s="21">
+        <v>0</v>
+      </c>
+      <c r="S29" s="21">
+        <v>0</v>
+      </c>
+      <c r="T29" s="21">
+        <v>1</v>
+      </c>
+      <c r="U29" s="21">
+        <v>1</v>
+      </c>
+      <c r="V29" s="21">
+        <v>1</v>
+      </c>
+      <c r="W29" s="21">
+        <v>2</v>
+      </c>
+      <c r="X29" s="10"/>
+      <c r="Y29" s="4"/>
+    </row>
+    <row r="30" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A30" s="4"/>
+      <c r="B30" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="C30" s="4"/>
+      <c r="D30" s="4"/>
+      <c r="E30" s="4"/>
+      <c r="F30" s="4"/>
+      <c r="G30" s="4"/>
+      <c r="H30" s="4"/>
+      <c r="I30" s="4"/>
+      <c r="J30" s="4"/>
+      <c r="K30" s="4"/>
+      <c r="L30" s="4"/>
+      <c r="M30" s="4"/>
+      <c r="N30" s="4"/>
+      <c r="O30" s="4"/>
+      <c r="P30" s="4"/>
+      <c r="Q30" s="4"/>
+      <c r="R30" s="4"/>
+      <c r="S30" s="4"/>
+    </row>
+    <row r="31" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A31" s="4"/>
+      <c r="B31" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C31" s="4"/>
+      <c r="D31" s="4"/>
+      <c r="E31" s="4"/>
+      <c r="F31" s="4"/>
+      <c r="G31" s="4"/>
+      <c r="H31" s="4"/>
+      <c r="I31" s="4"/>
+      <c r="J31" s="4"/>
+      <c r="K31" s="4"/>
+      <c r="L31" s="4"/>
+      <c r="M31" s="4"/>
+      <c r="N31" s="4"/>
+      <c r="O31" s="4"/>
+      <c r="P31" s="4"/>
+      <c r="Q31" s="4"/>
+      <c r="R31" s="4"/>
+      <c r="S31" s="4"/>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A33" s="63"/>
+      <c r="B33" s="63"/>
+      <c r="C33" s="63"/>
+      <c r="D33" s="63"/>
+      <c r="E33" s="63"/>
+      <c r="F33" s="63"/>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A34" s="64"/>
+      <c r="B34" s="63"/>
+      <c r="C34" s="63"/>
+      <c r="D34" s="63"/>
+      <c r="E34" s="63"/>
+      <c r="F34" s="63"/>
+      <c r="H34" s="1"/>
+      <c r="I34" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="A35" s="65"/>
+      <c r="B35" s="65"/>
+      <c r="C35" s="65"/>
+      <c r="D35" s="65"/>
+      <c r="E35" s="65"/>
+      <c r="F35" s="65"/>
+      <c r="G35" s="59"/>
+      <c r="H35" s="51" t="s">
+        <v>62</v>
+      </c>
+      <c r="I35" s="51"/>
+      <c r="J35" s="51"/>
+      <c r="K35" s="51"/>
+      <c r="L35" s="51"/>
+      <c r="M35" s="51"/>
+      <c r="N35" s="59"/>
+    </row>
+    <row r="36" spans="1:14" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="A36" s="66"/>
+      <c r="B36" s="66"/>
+      <c r="C36" s="67"/>
+      <c r="D36" s="67"/>
+      <c r="E36" s="67"/>
+      <c r="F36" s="67"/>
+      <c r="G36" s="54"/>
+      <c r="H36" s="34" t="s">
+        <v>61</v>
+      </c>
+      <c r="I36" s="34"/>
+      <c r="J36" s="42" t="s">
+        <v>3</v>
+      </c>
+      <c r="K36" s="42"/>
+      <c r="L36" s="42" t="s">
+        <v>4</v>
+      </c>
+      <c r="M36" s="42"/>
+      <c r="N36" s="54"/>
+    </row>
+    <row r="37" spans="1:14" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="A37" s="66"/>
+      <c r="B37" s="66"/>
+      <c r="C37" s="55"/>
+      <c r="D37" s="55"/>
+      <c r="E37" s="55"/>
+      <c r="F37" s="55"/>
+      <c r="G37" s="55"/>
+      <c r="H37" s="35"/>
+      <c r="I37" s="35"/>
+      <c r="J37" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="K37" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="L37" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="M37" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="N37" s="55"/>
+    </row>
+    <row r="38" spans="1:14" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="A38" s="68"/>
+      <c r="B38" s="68"/>
+      <c r="C38" s="56"/>
+      <c r="D38" s="56"/>
+      <c r="E38" s="56"/>
+      <c r="F38" s="56"/>
+      <c r="G38" s="20"/>
+      <c r="H38" s="6">
+        <v>1</v>
+      </c>
+      <c r="I38" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="J38" s="20">
+        <v>500</v>
+      </c>
+      <c r="K38" s="20">
+        <v>500</v>
+      </c>
+      <c r="L38" s="20">
+        <v>500</v>
+      </c>
+      <c r="M38" s="20">
+        <v>500</v>
+      </c>
+      <c r="N38" s="20"/>
+    </row>
+    <row r="39" spans="1:14" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="A39" s="68"/>
+      <c r="B39" s="68"/>
+      <c r="C39" s="56"/>
+      <c r="D39" s="56"/>
+      <c r="E39" s="56"/>
+      <c r="F39" s="56"/>
+      <c r="G39" s="20"/>
+      <c r="H39" s="6">
+        <v>2</v>
+      </c>
+      <c r="I39" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="J39" s="20">
+        <v>500</v>
+      </c>
+      <c r="K39" s="20"/>
+      <c r="L39" s="20">
+        <v>500</v>
+      </c>
+      <c r="M39" s="20"/>
+      <c r="N39" s="20"/>
+    </row>
+    <row r="40" spans="1:14" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="A40" s="68"/>
+      <c r="B40" s="68"/>
+      <c r="C40" s="56"/>
+      <c r="D40" s="56"/>
+      <c r="E40" s="56"/>
+      <c r="F40" s="56"/>
+      <c r="G40" s="20"/>
+      <c r="H40" s="6">
+        <v>3</v>
+      </c>
+      <c r="I40" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="J40" s="20">
+        <v>100</v>
+      </c>
+      <c r="K40" s="20">
+        <v>100</v>
+      </c>
+      <c r="L40" s="20">
+        <v>100</v>
+      </c>
+      <c r="M40" s="20">
+        <v>100</v>
+      </c>
+      <c r="N40" s="20"/>
+    </row>
+    <row r="41" spans="1:14" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="A41" s="68"/>
+      <c r="B41" s="68"/>
+      <c r="C41" s="56"/>
+      <c r="D41" s="56"/>
+      <c r="E41" s="56"/>
+      <c r="F41" s="56"/>
+      <c r="G41" s="20"/>
+      <c r="H41" s="6">
+        <v>4</v>
+      </c>
+      <c r="I41" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="J41" s="20">
+        <v>500</v>
+      </c>
+      <c r="K41" s="20">
+        <v>500</v>
+      </c>
+      <c r="L41" s="20">
+        <v>500</v>
+      </c>
+      <c r="M41" s="20">
+        <v>500</v>
+      </c>
+      <c r="N41" s="20"/>
+    </row>
+    <row r="42" spans="1:14" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="A42" s="69"/>
+      <c r="B42" s="69"/>
+      <c r="C42" s="56"/>
+      <c r="D42" s="56"/>
+      <c r="E42" s="56"/>
+      <c r="F42" s="56"/>
+      <c r="G42" s="20"/>
+      <c r="H42" s="9">
+        <v>5</v>
+      </c>
+      <c r="I42" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="J42" s="20"/>
+      <c r="K42" s="20"/>
+      <c r="L42" s="20"/>
+      <c r="M42" s="20"/>
+      <c r="N42" s="20"/>
+    </row>
+    <row r="43" spans="1:14" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="A43" s="68"/>
+      <c r="B43" s="68"/>
+      <c r="C43" s="56"/>
+      <c r="D43" s="56"/>
+      <c r="E43" s="56"/>
+      <c r="F43" s="56"/>
+      <c r="G43" s="56"/>
+      <c r="H43" s="14">
+        <v>6</v>
+      </c>
+      <c r="I43" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="J43" s="21">
+        <v>500</v>
+      </c>
+      <c r="K43" s="21">
+        <v>500</v>
+      </c>
+      <c r="L43" s="21">
+        <v>500</v>
+      </c>
+      <c r="M43" s="21">
+        <v>500</v>
+      </c>
+      <c r="N43" s="56"/>
+    </row>
+    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A44" s="63"/>
+      <c r="B44" s="63"/>
+      <c r="C44" s="63"/>
+      <c r="D44" s="63"/>
+      <c r="E44" s="63"/>
+      <c r="F44" s="63"/>
+    </row>
+    <row r="45" spans="1:14" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="A45" s="70"/>
+      <c r="B45" s="70"/>
+      <c r="C45" s="70"/>
+      <c r="D45" s="70"/>
+      <c r="E45" s="70"/>
+      <c r="F45" s="70"/>
+      <c r="G45" s="57"/>
+      <c r="H45" s="38" t="s">
+        <v>77</v>
+      </c>
+      <c r="I45" s="38"/>
+      <c r="J45" s="38"/>
+      <c r="K45" s="38"/>
+      <c r="L45" s="38"/>
+      <c r="M45" s="38"/>
+      <c r="N45" s="57"/>
+    </row>
+    <row r="46" spans="1:14" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="A46" s="66"/>
+      <c r="B46" s="66"/>
+      <c r="C46" s="67"/>
+      <c r="D46" s="67"/>
+      <c r="E46" s="67"/>
+      <c r="F46" s="67"/>
+      <c r="G46" s="54"/>
+      <c r="H46" s="34" t="s">
+        <v>61</v>
+      </c>
+      <c r="I46" s="34"/>
+      <c r="J46" s="42" t="s">
+        <v>3</v>
+      </c>
+      <c r="K46" s="42"/>
+      <c r="L46" s="42" t="s">
+        <v>4</v>
+      </c>
+      <c r="M46" s="42"/>
+      <c r="N46" s="54"/>
+    </row>
+    <row r="47" spans="1:14" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="A47" s="66"/>
+      <c r="B47" s="66"/>
+      <c r="C47" s="55"/>
+      <c r="D47" s="55"/>
+      <c r="E47" s="55"/>
+      <c r="F47" s="55"/>
+      <c r="G47" s="55"/>
+      <c r="H47" s="35"/>
+      <c r="I47" s="35"/>
+      <c r="J47" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="K47" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="L47" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="M47" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="N47" s="55"/>
+    </row>
+    <row r="48" spans="1:14" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="A48" s="68"/>
+      <c r="B48" s="68"/>
+      <c r="C48" s="56"/>
+      <c r="D48" s="56"/>
+      <c r="E48" s="56"/>
+      <c r="F48" s="56"/>
+      <c r="G48" s="20"/>
+      <c r="H48" s="6">
+        <v>1</v>
+      </c>
+      <c r="I48" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="J48" s="20">
+        <v>100</v>
+      </c>
+      <c r="K48" s="20">
+        <v>100</v>
+      </c>
+      <c r="L48" s="20">
+        <v>100</v>
+      </c>
+      <c r="M48" s="20">
+        <v>100</v>
+      </c>
+      <c r="N48" s="20"/>
+    </row>
+    <row r="49" spans="1:14" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="A49" s="68"/>
+      <c r="B49" s="68"/>
+      <c r="C49" s="56"/>
+      <c r="D49" s="56"/>
+      <c r="E49" s="56"/>
+      <c r="F49" s="56"/>
+      <c r="G49" s="20"/>
+      <c r="H49" s="6">
+        <v>2</v>
+      </c>
+      <c r="I49" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="J49" s="20">
+        <v>500</v>
+      </c>
+      <c r="K49" s="20"/>
+      <c r="L49" s="20">
+        <v>500</v>
+      </c>
+      <c r="M49" s="20"/>
+      <c r="N49" s="20"/>
+    </row>
+    <row r="50" spans="1:14" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="A50" s="68"/>
+      <c r="B50" s="68"/>
+      <c r="C50" s="56"/>
+      <c r="D50" s="56"/>
+      <c r="E50" s="56"/>
+      <c r="F50" s="56"/>
+      <c r="G50" s="20"/>
+      <c r="H50" s="6">
+        <v>3</v>
+      </c>
+      <c r="I50" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="J50" s="20">
+        <v>100</v>
+      </c>
+      <c r="K50" s="20">
+        <v>100</v>
+      </c>
+      <c r="L50" s="20">
+        <v>100</v>
+      </c>
+      <c r="M50" s="20">
+        <v>100</v>
+      </c>
+      <c r="N50" s="20"/>
+    </row>
+    <row r="51" spans="1:14" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="A51" s="68"/>
+      <c r="B51" s="68"/>
+      <c r="C51" s="56"/>
+      <c r="D51" s="56"/>
+      <c r="E51" s="56"/>
+      <c r="F51" s="56"/>
+      <c r="G51" s="20"/>
+      <c r="H51" s="6">
+        <v>4</v>
+      </c>
+      <c r="I51" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="J51" s="20">
+        <v>500</v>
+      </c>
+      <c r="K51" s="20">
+        <v>500</v>
+      </c>
+      <c r="L51" s="20">
+        <v>500</v>
+      </c>
+      <c r="M51" s="20">
+        <v>500</v>
+      </c>
+      <c r="N51" s="20"/>
+    </row>
+    <row r="52" spans="1:14" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="A52" s="69"/>
+      <c r="B52" s="69"/>
+      <c r="C52" s="56"/>
+      <c r="D52" s="56"/>
+      <c r="E52" s="56"/>
+      <c r="F52" s="56"/>
+      <c r="G52" s="20"/>
+      <c r="H52" s="9">
+        <v>5</v>
+      </c>
+      <c r="I52" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="J52" s="20"/>
+      <c r="K52" s="20"/>
+      <c r="L52" s="20"/>
+      <c r="M52" s="20"/>
+      <c r="N52" s="20"/>
+    </row>
+    <row r="53" spans="1:14" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="A53" s="68"/>
+      <c r="B53" s="68"/>
+      <c r="C53" s="56"/>
+      <c r="D53" s="56"/>
+      <c r="E53" s="56"/>
+      <c r="F53" s="56"/>
+      <c r="G53" s="56"/>
+      <c r="H53" s="14">
+        <v>6</v>
+      </c>
+      <c r="I53" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="J53" s="21">
+        <v>500</v>
+      </c>
+      <c r="K53" s="21">
+        <v>500</v>
+      </c>
+      <c r="L53" s="21">
+        <v>500</v>
+      </c>
+      <c r="M53" s="21">
+        <v>500</v>
+      </c>
+      <c r="N53" s="56"/>
+    </row>
+    <row r="54" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A54" s="63"/>
+      <c r="B54" s="63"/>
+      <c r="C54" s="63"/>
+      <c r="D54" s="63"/>
+      <c r="E54" s="63"/>
+      <c r="F54" s="63"/>
+    </row>
+    <row r="55" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A55" s="63"/>
+      <c r="B55" s="63"/>
+      <c r="C55" s="63"/>
+      <c r="D55" s="63"/>
+      <c r="E55" s="63"/>
+      <c r="F55" s="63"/>
+    </row>
+  </sheetData>
+  <mergeCells count="43">
+    <mergeCell ref="H46:I47"/>
+    <mergeCell ref="J46:K46"/>
+    <mergeCell ref="L46:M46"/>
+    <mergeCell ref="H35:M35"/>
+    <mergeCell ref="H36:I37"/>
+    <mergeCell ref="J36:K36"/>
+    <mergeCell ref="L36:M36"/>
+    <mergeCell ref="H45:M45"/>
+    <mergeCell ref="H10:M10"/>
+    <mergeCell ref="P10:W10"/>
+    <mergeCell ref="H21:M21"/>
+    <mergeCell ref="H22:I23"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="L22:M22"/>
+    <mergeCell ref="H11:M11"/>
+    <mergeCell ref="H12:I13"/>
+    <mergeCell ref="J12:K12"/>
+    <mergeCell ref="L12:M12"/>
+    <mergeCell ref="A36:B37"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="E36:F36"/>
+    <mergeCell ref="A45:F45"/>
+    <mergeCell ref="A46:B47"/>
+    <mergeCell ref="C46:D46"/>
+    <mergeCell ref="E46:F46"/>
+    <mergeCell ref="A35:F35"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="R12:T12"/>
+    <mergeCell ref="U12:W12"/>
+    <mergeCell ref="A22:B23"/>
+    <mergeCell ref="P22:Q23"/>
+    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="P21:W21"/>
+    <mergeCell ref="A12:B13"/>
+    <mergeCell ref="P12:Q13"/>
+    <mergeCell ref="A21:F21"/>
+    <mergeCell ref="A11:F11"/>
+    <mergeCell ref="P11:W11"/>
+    <mergeCell ref="R22:T22"/>
+    <mergeCell ref="U22:W22"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="E12:F12"/>
+  </mergeCells>
+  <conditionalFormatting sqref="C14:D19">
+    <cfRule type="colorScale" priority="27">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="7"/>
+        <color theme="9"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C24:D29">
+    <cfRule type="colorScale" priority="25">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="7"/>
+        <color theme="9"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E14:G19">
+    <cfRule type="colorScale" priority="26">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="7"/>
+        <color theme="9"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E24:G29">
+    <cfRule type="colorScale" priority="24">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="7"/>
+        <color theme="9"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R14:T19">
+    <cfRule type="colorScale" priority="23">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="7"/>
+        <color theme="9"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R24:W29">
+    <cfRule type="colorScale" priority="22">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="7"/>
+        <color theme="9"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="U14:W19">
+    <cfRule type="colorScale" priority="21">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="7"/>
+        <color theme="9"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J14:K19">
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="7"/>
+        <color theme="9"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L14:N19">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="7"/>
+        <color theme="9"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J24:K29">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="7"/>
+        <color theme="9"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L24:N29">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="7"/>
+        <color theme="9"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F085D31-3344-4382-97B3-94AD3FAC1A70}">
+  <dimension ref="A1:Q72"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3.140625" bestFit="1" customWidth="1"/>
@@ -906,7 +2881,7 @@
         <v>17</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
@@ -948,113 +2923,118 @@
         <v>67</v>
       </c>
     </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
     <row r="10" spans="1:17" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="41" t="s">
+      <c r="A10" s="32" t="s">
         <v>1</v>
       </c>
-      <c r="B10" s="41"/>
-      <c r="C10" s="41"/>
-      <c r="D10" s="41"/>
-      <c r="E10" s="41"/>
-      <c r="F10" s="41"/>
+      <c r="B10" s="32"/>
+      <c r="C10" s="32"/>
+      <c r="D10" s="32"/>
+      <c r="E10" s="32"/>
+      <c r="F10" s="32"/>
       <c r="G10" s="12"/>
       <c r="H10" s="12"/>
-      <c r="I10" s="41" t="s">
-        <v>2</v>
-      </c>
-      <c r="J10" s="41"/>
-      <c r="K10" s="41"/>
-      <c r="L10" s="41"/>
-      <c r="M10" s="41"/>
-      <c r="N10" s="41"/>
-      <c r="O10" s="41"/>
-      <c r="P10" s="41"/>
+      <c r="I10" s="32" t="s">
+        <v>2</v>
+      </c>
+      <c r="J10" s="32"/>
+      <c r="K10" s="32"/>
+      <c r="L10" s="32"/>
+      <c r="M10" s="32"/>
+      <c r="N10" s="32"/>
+      <c r="O10" s="32"/>
+      <c r="P10" s="32"/>
     </row>
     <row r="11" spans="1:17" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="A11" s="40" t="s">
-        <v>0</v>
-      </c>
-      <c r="B11" s="40"/>
-      <c r="C11" s="40"/>
-      <c r="D11" s="40"/>
-      <c r="E11" s="40"/>
-      <c r="F11" s="40"/>
-      <c r="H11" s="40" t="s">
-        <v>0</v>
-      </c>
-      <c r="I11" s="40"/>
-      <c r="J11" s="40"/>
-      <c r="K11" s="40"/>
-      <c r="L11" s="40"/>
-      <c r="M11" s="40"/>
-      <c r="N11" s="40"/>
-      <c r="O11" s="40"/>
+      <c r="A11" s="39" t="s">
+        <v>0</v>
+      </c>
+      <c r="B11" s="39"/>
+      <c r="C11" s="39"/>
+      <c r="D11" s="39"/>
+      <c r="E11" s="39"/>
+      <c r="F11" s="39"/>
+      <c r="H11" s="39" t="s">
+        <v>0</v>
+      </c>
+      <c r="I11" s="39"/>
+      <c r="J11" s="39"/>
+      <c r="K11" s="39"/>
+      <c r="L11" s="39"/>
+      <c r="M11" s="39"/>
+      <c r="N11" s="39"/>
+      <c r="O11" s="39"/>
     </row>
     <row r="12" spans="1:17" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A12" s="33" t="s">
+      <c r="A12" s="34" t="s">
         <v>61</v>
       </c>
-      <c r="B12" s="33"/>
-      <c r="C12" s="35" t="s">
-        <v>3</v>
-      </c>
-      <c r="D12" s="35"/>
-      <c r="E12" s="46" t="s">
-        <v>4</v>
-      </c>
-      <c r="F12" s="35"/>
+      <c r="B12" s="34"/>
+      <c r="C12" s="42" t="s">
+        <v>3</v>
+      </c>
+      <c r="D12" s="42"/>
+      <c r="E12" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="F12" s="42"/>
       <c r="G12" s="4"/>
-      <c r="H12" s="33" t="s">
+      <c r="H12" s="34" t="s">
         <v>61</v>
       </c>
-      <c r="I12" s="33"/>
-      <c r="J12" s="38" t="s">
-        <v>3</v>
-      </c>
-      <c r="K12" s="38"/>
-      <c r="L12" s="38"/>
-      <c r="M12" s="39" t="s">
-        <v>4</v>
-      </c>
-      <c r="N12" s="38"/>
-      <c r="O12" s="38"/>
+      <c r="I12" s="34"/>
+      <c r="J12" s="36" t="s">
+        <v>3</v>
+      </c>
+      <c r="K12" s="36"/>
+      <c r="L12" s="36"/>
+      <c r="M12" s="37" t="s">
+        <v>4</v>
+      </c>
+      <c r="N12" s="36"/>
+      <c r="O12" s="36"/>
       <c r="P12" s="4"/>
       <c r="Q12" s="4"/>
     </row>
     <row r="13" spans="1:17" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A13" s="34"/>
-      <c r="B13" s="34"/>
-      <c r="C13" s="29" t="s">
+      <c r="A13" s="35"/>
+      <c r="B13" s="35"/>
+      <c r="C13" s="48" t="s">
         <v>5</v>
       </c>
       <c r="D13" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="E13" s="30" t="s">
+      <c r="E13" s="49" t="s">
         <v>5</v>
       </c>
       <c r="F13" s="13" t="s">
         <v>6</v>
       </c>
       <c r="G13" s="5"/>
-      <c r="H13" s="34"/>
-      <c r="I13" s="34"/>
+      <c r="H13" s="35"/>
+      <c r="I13" s="35"/>
       <c r="J13" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="K13" s="31" t="s">
+      <c r="K13" s="29" t="s">
         <v>8</v>
       </c>
-      <c r="L13" s="31" t="s">
+      <c r="L13" s="29" t="s">
         <v>9</v>
       </c>
       <c r="M13" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="N13" s="31" t="s">
+      <c r="N13" s="29" t="s">
         <v>8</v>
       </c>
-      <c r="O13" s="31" t="s">
+      <c r="O13" s="29" t="s">
         <v>9</v>
       </c>
       <c r="P13" s="5"/>
@@ -1070,14 +3050,14 @@
       <c r="C14" s="20">
         <v>0</v>
       </c>
-      <c r="D14" s="32">
-        <v>0</v>
+      <c r="D14" s="20">
+        <v>1</v>
       </c>
       <c r="E14" s="20">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F14" s="20">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G14" s="8"/>
       <c r="H14" s="6">
@@ -1096,13 +3076,13 @@
         <v>0</v>
       </c>
       <c r="M14" s="20">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N14" s="20">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O14" s="20">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P14" s="8"/>
       <c r="Q14" s="4"/>
@@ -1162,16 +3142,16 @@
         <v>12</v>
       </c>
       <c r="C16" s="20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D16" s="20">
+        <v>4</v>
+      </c>
+      <c r="E16" s="20">
         <v>1</v>
       </c>
-      <c r="E16" s="20">
-        <v>0</v>
-      </c>
       <c r="F16" s="20">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G16" s="8"/>
       <c r="H16" s="6">
@@ -1181,22 +3161,22 @@
         <v>12</v>
       </c>
       <c r="J16" s="20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" s="20">
         <v>0</v>
       </c>
       <c r="L16" s="20">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M16" s="20">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N16" s="20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O16" s="20">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P16" s="8"/>
       <c r="Q16" s="4"/>
@@ -1209,16 +3189,16 @@
         <v>13</v>
       </c>
       <c r="C17" s="20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D17" s="20">
         <v>2</v>
       </c>
       <c r="E17" s="20">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F17" s="20">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G17" s="8"/>
       <c r="H17" s="6">
@@ -1234,16 +3214,16 @@
         <v>0</v>
       </c>
       <c r="L17" s="20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M17" s="20">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N17" s="20">
         <v>2</v>
       </c>
       <c r="O17" s="20">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P17" s="8"/>
       <c r="Q17" s="4"/>
@@ -1256,13 +3236,13 @@
         <v>14</v>
       </c>
       <c r="C18" s="20">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D18" s="20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E18" s="20">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F18" s="20">
         <v>6</v>
@@ -1275,16 +3255,16 @@
         <v>14</v>
       </c>
       <c r="J18" s="20">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K18" s="20">
         <v>5</v>
       </c>
       <c r="L18" s="20">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M18" s="20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N18" s="20">
         <v>6</v>
@@ -1309,10 +3289,10 @@
         <v>2</v>
       </c>
       <c r="E19" s="21">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F19" s="21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G19" s="8"/>
       <c r="H19" s="6">
@@ -1322,22 +3302,22 @@
         <v>15</v>
       </c>
       <c r="J19" s="21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" s="21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L19" s="21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M19" s="21">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N19" s="21">
         <v>3</v>
       </c>
       <c r="O19" s="21">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P19" s="8"/>
       <c r="Q19" s="4"/>
@@ -1362,93 +3342,93 @@
       <c r="Q20" s="4"/>
     </row>
     <row r="21" spans="1:17" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="43" t="s">
+      <c r="A21" s="38" t="s">
         <v>16</v>
       </c>
-      <c r="B21" s="43"/>
-      <c r="C21" s="43"/>
-      <c r="D21" s="43"/>
-      <c r="E21" s="43"/>
-      <c r="F21" s="43"/>
+      <c r="B21" s="38"/>
+      <c r="C21" s="38"/>
+      <c r="D21" s="38"/>
+      <c r="E21" s="38"/>
+      <c r="F21" s="38"/>
       <c r="G21" s="19"/>
-      <c r="H21" s="42" t="s">
+      <c r="H21" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="I21" s="42"/>
-      <c r="J21" s="42"/>
-      <c r="K21" s="42"/>
-      <c r="L21" s="42"/>
-      <c r="M21" s="42"/>
-      <c r="N21" s="42"/>
-      <c r="O21" s="42"/>
+      <c r="I21" s="33"/>
+      <c r="J21" s="33"/>
+      <c r="K21" s="33"/>
+      <c r="L21" s="33"/>
+      <c r="M21" s="33"/>
+      <c r="N21" s="33"/>
+      <c r="O21" s="33"/>
       <c r="P21" s="19"/>
       <c r="Q21" s="4"/>
     </row>
     <row r="22" spans="1:17" ht="21" x14ac:dyDescent="0.35">
-      <c r="A22" s="33" t="s">
+      <c r="A22" s="34" t="s">
         <v>61</v>
       </c>
-      <c r="B22" s="33"/>
-      <c r="C22" s="35" t="s">
-        <v>3</v>
-      </c>
-      <c r="D22" s="35"/>
-      <c r="E22" s="36" t="s">
-        <v>4</v>
-      </c>
-      <c r="F22" s="37"/>
+      <c r="B22" s="34"/>
+      <c r="C22" s="42" t="s">
+        <v>3</v>
+      </c>
+      <c r="D22" s="42"/>
+      <c r="E22" s="44" t="s">
+        <v>4</v>
+      </c>
+      <c r="F22" s="45"/>
       <c r="G22" s="8"/>
-      <c r="H22" s="33" t="s">
+      <c r="H22" s="34" t="s">
         <v>61</v>
       </c>
-      <c r="I22" s="33"/>
-      <c r="J22" s="38" t="s">
-        <v>3</v>
-      </c>
-      <c r="K22" s="38"/>
-      <c r="L22" s="38"/>
-      <c r="M22" s="44" t="s">
-        <v>4</v>
-      </c>
-      <c r="N22" s="45"/>
-      <c r="O22" s="45"/>
+      <c r="I22" s="34"/>
+      <c r="J22" s="36" t="s">
+        <v>3</v>
+      </c>
+      <c r="K22" s="36"/>
+      <c r="L22" s="36"/>
+      <c r="M22" s="40" t="s">
+        <v>4</v>
+      </c>
+      <c r="N22" s="41"/>
+      <c r="O22" s="41"/>
       <c r="P22" s="8"/>
       <c r="Q22" s="4"/>
     </row>
     <row r="23" spans="1:17" ht="21" x14ac:dyDescent="0.35">
-      <c r="A23" s="34"/>
-      <c r="B23" s="34"/>
-      <c r="C23" s="29" t="s">
+      <c r="A23" s="35"/>
+      <c r="B23" s="35"/>
+      <c r="C23" s="48" t="s">
         <v>5</v>
       </c>
       <c r="D23" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="E23" s="30" t="s">
+      <c r="E23" s="50" t="s">
         <v>5</v>
       </c>
       <c r="F23" s="22" t="s">
         <v>6</v>
       </c>
       <c r="G23" s="8"/>
-      <c r="H23" s="34"/>
-      <c r="I23" s="34"/>
+      <c r="H23" s="35"/>
+      <c r="I23" s="35"/>
       <c r="J23" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="K23" s="31" t="s">
+      <c r="K23" s="29" t="s">
         <v>8</v>
       </c>
-      <c r="L23" s="31" t="s">
+      <c r="L23" s="29" t="s">
         <v>9</v>
       </c>
       <c r="M23" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="N23" s="31" t="s">
+      <c r="N23" s="29" t="s">
         <v>8</v>
       </c>
-      <c r="O23" s="31" t="s">
+      <c r="O23" s="29" t="s">
         <v>9</v>
       </c>
       <c r="P23" s="8"/>
@@ -1462,16 +3442,16 @@
         <v>10</v>
       </c>
       <c r="C24" s="20">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D24" s="20">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E24" s="20">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F24" s="20">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G24" s="10"/>
       <c r="H24" s="9">
@@ -1481,22 +3461,22 @@
         <v>10</v>
       </c>
       <c r="J24" s="20">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K24" s="20">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L24" s="20">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M24" s="20">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N24" s="20">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O24" s="20">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P24" s="10"/>
       <c r="Q24" s="4"/>
@@ -1509,16 +3489,16 @@
         <v>11</v>
       </c>
       <c r="C25" s="20">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D25" s="20">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E25" s="20">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F25" s="20">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G25" s="10"/>
       <c r="H25" s="9">
@@ -1528,22 +3508,22 @@
         <v>11</v>
       </c>
       <c r="J25" s="20">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K25" s="20">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L25" s="20">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M25" s="20">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N25" s="20">
         <v>4</v>
       </c>
       <c r="O25" s="20">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P25" s="10"/>
       <c r="Q25" s="4"/>
@@ -1575,22 +3555,22 @@
         <v>12</v>
       </c>
       <c r="J26" s="20">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K26" s="20">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L26" s="20">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M26" s="20">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N26" s="20">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O26" s="20">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P26" s="10"/>
       <c r="Q26" s="4"/>
@@ -1603,16 +3583,16 @@
         <v>13</v>
       </c>
       <c r="C27" s="20">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D27" s="20">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E27" s="20">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F27" s="20">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G27" s="10"/>
       <c r="H27" s="9">
@@ -1625,7 +3605,7 @@
         <v>0</v>
       </c>
       <c r="K27" s="20">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L27" s="20">
         <v>0</v>
@@ -1634,7 +3614,7 @@
         <v>0</v>
       </c>
       <c r="N27" s="20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O27" s="20">
         <v>0</v>
@@ -1653,13 +3633,13 @@
         <v>7</v>
       </c>
       <c r="D28" s="20">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E28" s="20">
         <v>7</v>
       </c>
       <c r="F28" s="20">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G28" s="10"/>
       <c r="H28" s="9">
@@ -1669,22 +3649,22 @@
         <v>14</v>
       </c>
       <c r="J28" s="20">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K28" s="20">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L28" s="20">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M28" s="20">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N28" s="20">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O28" s="20">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P28" s="10"/>
       <c r="Q28" s="4"/>
@@ -1697,16 +3677,16 @@
         <v>15</v>
       </c>
       <c r="C29" s="21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D29" s="21">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E29" s="21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F29" s="21">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G29" s="10"/>
       <c r="H29" s="16">
@@ -1716,22 +3696,22 @@
         <v>15</v>
       </c>
       <c r="J29" s="21">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K29" s="21">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L29" s="21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M29" s="21">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N29" s="21">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O29" s="21">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P29" s="10"/>
       <c r="Q29" s="4"/>
@@ -1775,59 +3755,59 @@
       <c r="Q31" s="4"/>
     </row>
     <row r="32" spans="1:17" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="A32" s="40" t="s">
+      <c r="A32" s="51" t="s">
         <v>62</v>
       </c>
-      <c r="B32" s="40"/>
-      <c r="C32" s="40"/>
-      <c r="D32" s="40"/>
-      <c r="E32" s="40"/>
-      <c r="F32" s="40"/>
+      <c r="B32" s="51"/>
+      <c r="C32" s="51"/>
+      <c r="D32" s="51"/>
+      <c r="E32" s="51"/>
+      <c r="F32" s="51"/>
       <c r="G32" s="4"/>
-      <c r="H32" s="42" t="s">
+      <c r="H32" s="33" t="s">
         <v>73</v>
       </c>
-      <c r="I32" s="42"/>
-      <c r="J32" s="42"/>
-      <c r="K32" s="42"/>
-      <c r="L32" s="42"/>
-      <c r="M32" s="42"/>
-      <c r="N32" s="42"/>
-      <c r="O32" s="42"/>
+      <c r="I32" s="33"/>
+      <c r="J32" s="33"/>
+      <c r="K32" s="33"/>
+      <c r="L32" s="33"/>
+      <c r="M32" s="33"/>
+      <c r="N32" s="33"/>
+      <c r="O32" s="33"/>
       <c r="P32" s="4"/>
       <c r="Q32" s="4"/>
     </row>
     <row r="33" spans="1:15" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A33" s="33" t="s">
+      <c r="A33" s="34" t="s">
         <v>61</v>
       </c>
-      <c r="B33" s="33"/>
-      <c r="C33" s="35" t="s">
-        <v>3</v>
-      </c>
-      <c r="D33" s="35"/>
-      <c r="E33" s="35" t="s">
-        <v>4</v>
-      </c>
-      <c r="F33" s="35"/>
-      <c r="H33" s="33" t="s">
+      <c r="B33" s="34"/>
+      <c r="C33" s="42" t="s">
+        <v>3</v>
+      </c>
+      <c r="D33" s="42"/>
+      <c r="E33" s="42" t="s">
+        <v>4</v>
+      </c>
+      <c r="F33" s="42"/>
+      <c r="H33" s="34" t="s">
         <v>61</v>
       </c>
-      <c r="I33" s="33"/>
-      <c r="J33" s="38" t="s">
-        <v>3</v>
-      </c>
-      <c r="K33" s="38"/>
-      <c r="L33" s="38"/>
-      <c r="M33" s="39" t="s">
-        <v>4</v>
-      </c>
-      <c r="N33" s="38"/>
-      <c r="O33" s="38"/>
+      <c r="I33" s="34"/>
+      <c r="J33" s="36" t="s">
+        <v>3</v>
+      </c>
+      <c r="K33" s="36"/>
+      <c r="L33" s="36"/>
+      <c r="M33" s="37" t="s">
+        <v>4</v>
+      </c>
+      <c r="N33" s="36"/>
+      <c r="O33" s="36"/>
     </row>
     <row r="34" spans="1:15" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A34" s="34"/>
-      <c r="B34" s="34"/>
+      <c r="A34" s="35"/>
+      <c r="B34" s="35"/>
       <c r="C34" s="13" t="s">
         <v>5</v>
       </c>
@@ -1840,8 +3820,8 @@
       <c r="F34" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="H34" s="34"/>
-      <c r="I34" s="34"/>
+      <c r="H34" s="35"/>
+      <c r="I34" s="35"/>
       <c r="J34" s="17" t="s">
         <v>7</v>
       </c>
@@ -1861,17 +3841,17 @@
         <v>9</v>
       </c>
     </row>
-    <row r="35" spans="1:15" ht="21" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:15" ht="20.25" x14ac:dyDescent="0.3">
       <c r="A35" s="6">
         <v>1</v>
       </c>
       <c r="B35" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C35" s="11"/>
-      <c r="D35" s="11"/>
-      <c r="E35" s="11"/>
-      <c r="F35" s="7"/>
+      <c r="C35" s="20"/>
+      <c r="D35" s="20"/>
+      <c r="E35" s="20"/>
+      <c r="F35" s="20"/>
       <c r="H35" s="9">
         <v>1</v>
       </c>
@@ -1885,17 +3865,17 @@
       <c r="N35" s="20"/>
       <c r="O35" s="20"/>
     </row>
-    <row r="36" spans="1:15" ht="21" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:15" ht="20.25" x14ac:dyDescent="0.3">
       <c r="A36" s="6">
         <v>2</v>
       </c>
       <c r="B36" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C36" s="7"/>
-      <c r="D36" s="7"/>
-      <c r="E36" s="7"/>
-      <c r="F36" s="7"/>
+      <c r="C36" s="20"/>
+      <c r="D36" s="20"/>
+      <c r="E36" s="20"/>
+      <c r="F36" s="20"/>
       <c r="H36" s="9">
         <v>2</v>
       </c>
@@ -1909,17 +3889,17 @@
       <c r="N36" s="20"/>
       <c r="O36" s="20"/>
     </row>
-    <row r="37" spans="1:15" ht="21" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:15" ht="20.25" x14ac:dyDescent="0.3">
       <c r="A37" s="6">
         <v>3</v>
       </c>
       <c r="B37" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C37" s="7"/>
-      <c r="D37" s="7"/>
-      <c r="E37" s="7"/>
-      <c r="F37" s="7"/>
+      <c r="C37" s="20"/>
+      <c r="D37" s="20"/>
+      <c r="E37" s="20"/>
+      <c r="F37" s="20"/>
       <c r="H37" s="9">
         <v>3</v>
       </c>
@@ -1933,17 +3913,17 @@
       <c r="N37" s="20"/>
       <c r="O37" s="20"/>
     </row>
-    <row r="38" spans="1:15" ht="21" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:15" ht="20.25" x14ac:dyDescent="0.3">
       <c r="A38" s="6">
         <v>4</v>
       </c>
       <c r="B38" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="C38" s="7"/>
-      <c r="D38" s="7"/>
-      <c r="E38" s="7"/>
-      <c r="F38" s="7"/>
+      <c r="C38" s="20"/>
+      <c r="D38" s="20"/>
+      <c r="E38" s="20"/>
+      <c r="F38" s="20"/>
       <c r="H38" s="9">
         <v>4</v>
       </c>
@@ -1957,17 +3937,17 @@
       <c r="N38" s="20"/>
       <c r="O38" s="20"/>
     </row>
-    <row r="39" spans="1:15" ht="21" x14ac:dyDescent="0.35">
-      <c r="A39" s="6">
-        <v>5</v>
-      </c>
-      <c r="B39" s="6" t="s">
+    <row r="39" spans="1:15" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="A39" s="9">
+        <v>5</v>
+      </c>
+      <c r="B39" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="C39" s="7"/>
-      <c r="D39" s="7"/>
-      <c r="E39" s="7"/>
-      <c r="F39" s="7"/>
+      <c r="C39" s="20"/>
+      <c r="D39" s="20"/>
+      <c r="E39" s="20"/>
+      <c r="F39" s="20"/>
       <c r="H39" s="9">
         <v>5</v>
       </c>
@@ -1981,17 +3961,17 @@
       <c r="N39" s="20"/>
       <c r="O39" s="20"/>
     </row>
-    <row r="40" spans="1:15" ht="21" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:15" ht="20.25" x14ac:dyDescent="0.3">
       <c r="A40" s="14">
         <v>6</v>
       </c>
       <c r="B40" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C40" s="15"/>
-      <c r="D40" s="15"/>
-      <c r="E40" s="15"/>
-      <c r="F40" s="15"/>
+      <c r="C40" s="21"/>
+      <c r="D40" s="21"/>
+      <c r="E40" s="21"/>
+      <c r="F40" s="21"/>
       <c r="H40" s="16">
         <v>6</v>
       </c>
@@ -2005,36 +3985,521 @@
       <c r="N40" s="21"/>
       <c r="O40" s="21"/>
     </row>
+    <row r="42" spans="1:15" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="A42" s="38" t="s">
+        <v>77</v>
+      </c>
+      <c r="B42" s="38"/>
+      <c r="C42" s="38"/>
+      <c r="D42" s="38"/>
+      <c r="E42" s="38"/>
+      <c r="F42" s="38"/>
+    </row>
+    <row r="43" spans="1:15" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="A43" s="34" t="s">
+        <v>61</v>
+      </c>
+      <c r="B43" s="34"/>
+      <c r="C43" s="42" t="s">
+        <v>3</v>
+      </c>
+      <c r="D43" s="42"/>
+      <c r="E43" s="42" t="s">
+        <v>4</v>
+      </c>
+      <c r="F43" s="42"/>
+    </row>
+    <row r="44" spans="1:15" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="A44" s="35"/>
+      <c r="B44" s="35"/>
+      <c r="C44" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="D44" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="E44" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="F44" s="13" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="A45" s="6">
+        <v>1</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C45" s="20"/>
+      <c r="D45" s="20"/>
+      <c r="E45" s="20"/>
+      <c r="F45" s="20"/>
+    </row>
+    <row r="46" spans="1:15" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="A46" s="6">
+        <v>2</v>
+      </c>
+      <c r="B46" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C46" s="20"/>
+      <c r="D46" s="20"/>
+      <c r="E46" s="20"/>
+      <c r="F46" s="20"/>
+    </row>
+    <row r="47" spans="1:15" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="A47" s="6">
+        <v>3</v>
+      </c>
+      <c r="B47" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C47" s="20"/>
+      <c r="D47" s="20"/>
+      <c r="E47" s="20"/>
+      <c r="F47" s="20"/>
+    </row>
+    <row r="48" spans="1:15" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="A48" s="6">
+        <v>4</v>
+      </c>
+      <c r="B48" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C48" s="20"/>
+      <c r="D48" s="20"/>
+      <c r="E48" s="20"/>
+      <c r="F48" s="20"/>
+    </row>
+    <row r="49" spans="1:6" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="A49" s="9">
+        <v>5</v>
+      </c>
+      <c r="B49" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C49" s="20"/>
+      <c r="D49" s="20"/>
+      <c r="E49" s="20"/>
+      <c r="F49" s="20"/>
+    </row>
+    <row r="50" spans="1:6" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="A50" s="14">
+        <v>6</v>
+      </c>
+      <c r="B50" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="C50" s="21"/>
+      <c r="D50" s="21"/>
+      <c r="E50" s="21"/>
+      <c r="F50" s="21"/>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A53" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="A54" s="51" t="s">
+        <v>62</v>
+      </c>
+      <c r="B54" s="51"/>
+      <c r="C54" s="51"/>
+      <c r="D54" s="51"/>
+      <c r="E54" s="51"/>
+      <c r="F54" s="51"/>
+    </row>
+    <row r="55" spans="1:6" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="A55" s="34" t="s">
+        <v>61</v>
+      </c>
+      <c r="B55" s="34"/>
+      <c r="C55" s="42" t="s">
+        <v>3</v>
+      </c>
+      <c r="D55" s="42"/>
+      <c r="E55" s="42" t="s">
+        <v>4</v>
+      </c>
+      <c r="F55" s="42"/>
+    </row>
+    <row r="56" spans="1:6" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="A56" s="35"/>
+      <c r="B56" s="35"/>
+      <c r="C56" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="D56" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="E56" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="F56" s="13" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="A57" s="6">
+        <v>1</v>
+      </c>
+      <c r="B57" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C57" s="20">
+        <v>500</v>
+      </c>
+      <c r="D57" s="20">
+        <v>500</v>
+      </c>
+      <c r="E57" s="20">
+        <v>500</v>
+      </c>
+      <c r="F57" s="20">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="A58" s="6">
+        <v>2</v>
+      </c>
+      <c r="B58" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C58" s="20">
+        <v>500</v>
+      </c>
+      <c r="D58" s="20"/>
+      <c r="E58" s="20">
+        <v>500</v>
+      </c>
+      <c r="F58" s="20"/>
+    </row>
+    <row r="59" spans="1:6" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="A59" s="6">
+        <v>3</v>
+      </c>
+      <c r="B59" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C59" s="20">
+        <v>100</v>
+      </c>
+      <c r="D59" s="20">
+        <v>100</v>
+      </c>
+      <c r="E59" s="20">
+        <v>100</v>
+      </c>
+      <c r="F59" s="20">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="A60" s="6">
+        <v>4</v>
+      </c>
+      <c r="B60" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C60" s="20">
+        <v>500</v>
+      </c>
+      <c r="D60" s="20">
+        <v>500</v>
+      </c>
+      <c r="E60" s="20">
+        <v>500</v>
+      </c>
+      <c r="F60" s="20">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="A61" s="9">
+        <v>5</v>
+      </c>
+      <c r="B61" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C61" s="20"/>
+      <c r="D61" s="20"/>
+      <c r="E61" s="20"/>
+      <c r="F61" s="20"/>
+    </row>
+    <row r="62" spans="1:6" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="A62" s="14">
+        <v>6</v>
+      </c>
+      <c r="B62" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="C62" s="21">
+        <v>500</v>
+      </c>
+      <c r="D62" s="21">
+        <v>500</v>
+      </c>
+      <c r="E62" s="21">
+        <v>500</v>
+      </c>
+      <c r="F62" s="21">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="A64" s="38" t="s">
+        <v>77</v>
+      </c>
+      <c r="B64" s="38"/>
+      <c r="C64" s="38"/>
+      <c r="D64" s="38"/>
+      <c r="E64" s="38"/>
+      <c r="F64" s="38"/>
+    </row>
+    <row r="65" spans="1:6" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="A65" s="34" t="s">
+        <v>61</v>
+      </c>
+      <c r="B65" s="34"/>
+      <c r="C65" s="42" t="s">
+        <v>3</v>
+      </c>
+      <c r="D65" s="42"/>
+      <c r="E65" s="42" t="s">
+        <v>4</v>
+      </c>
+      <c r="F65" s="42"/>
+    </row>
+    <row r="66" spans="1:6" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="A66" s="35"/>
+      <c r="B66" s="35"/>
+      <c r="C66" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="D66" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="E66" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="F66" s="13" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="A67" s="6">
+        <v>1</v>
+      </c>
+      <c r="B67" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C67" s="20">
+        <v>100</v>
+      </c>
+      <c r="D67" s="20">
+        <v>100</v>
+      </c>
+      <c r="E67" s="20">
+        <v>100</v>
+      </c>
+      <c r="F67" s="20">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="A68" s="6">
+        <v>2</v>
+      </c>
+      <c r="B68" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C68" s="20">
+        <v>500</v>
+      </c>
+      <c r="D68" s="20"/>
+      <c r="E68" s="20">
+        <v>500</v>
+      </c>
+      <c r="F68" s="20"/>
+    </row>
+    <row r="69" spans="1:6" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="A69" s="6">
+        <v>3</v>
+      </c>
+      <c r="B69" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C69" s="20">
+        <v>100</v>
+      </c>
+      <c r="D69" s="20">
+        <v>100</v>
+      </c>
+      <c r="E69" s="20">
+        <v>100</v>
+      </c>
+      <c r="F69" s="20">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="A70" s="6">
+        <v>4</v>
+      </c>
+      <c r="B70" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C70" s="20">
+        <v>500</v>
+      </c>
+      <c r="D70" s="20">
+        <v>500</v>
+      </c>
+      <c r="E70" s="20">
+        <v>500</v>
+      </c>
+      <c r="F70" s="20">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="A71" s="9">
+        <v>5</v>
+      </c>
+      <c r="B71" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C71" s="20"/>
+      <c r="D71" s="20"/>
+      <c r="E71" s="20"/>
+      <c r="F71" s="20"/>
+    </row>
+    <row r="72" spans="1:6" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="A72" s="14">
+        <v>6</v>
+      </c>
+      <c r="B72" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="C72" s="21">
+        <v>500</v>
+      </c>
+      <c r="D72" s="21">
+        <v>500</v>
+      </c>
+      <c r="E72" s="21">
+        <v>500</v>
+      </c>
+      <c r="F72" s="21">
+        <v>500</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="26">
-    <mergeCell ref="A10:F10"/>
-    <mergeCell ref="I10:P10"/>
-    <mergeCell ref="H21:O21"/>
+  <mergeCells count="38">
+    <mergeCell ref="A64:F64"/>
+    <mergeCell ref="A65:B66"/>
+    <mergeCell ref="C65:D65"/>
+    <mergeCell ref="E65:F65"/>
+    <mergeCell ref="A42:F42"/>
+    <mergeCell ref="A43:B44"/>
+    <mergeCell ref="C43:D43"/>
+    <mergeCell ref="E43:F43"/>
+    <mergeCell ref="A54:F54"/>
+    <mergeCell ref="A55:B56"/>
+    <mergeCell ref="C55:D55"/>
+    <mergeCell ref="E55:F55"/>
+    <mergeCell ref="A32:F32"/>
     <mergeCell ref="H32:O32"/>
+    <mergeCell ref="A33:B34"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="E33:F33"/>
     <mergeCell ref="H33:I34"/>
     <mergeCell ref="J33:L33"/>
     <mergeCell ref="M33:O33"/>
-    <mergeCell ref="A12:B13"/>
-    <mergeCell ref="H12:I13"/>
     <mergeCell ref="A21:F21"/>
+    <mergeCell ref="H21:O21"/>
+    <mergeCell ref="A22:B23"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="H22:I23"/>
+    <mergeCell ref="J22:L22"/>
+    <mergeCell ref="M22:O22"/>
+    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="I10:P10"/>
     <mergeCell ref="A11:F11"/>
     <mergeCell ref="H11:O11"/>
-    <mergeCell ref="J22:L22"/>
-    <mergeCell ref="M22:O22"/>
+    <mergeCell ref="A12:B13"/>
     <mergeCell ref="C12:D12"/>
     <mergeCell ref="E12:F12"/>
+    <mergeCell ref="H12:I13"/>
     <mergeCell ref="J12:L12"/>
     <mergeCell ref="M12:O12"/>
-    <mergeCell ref="A32:F32"/>
-    <mergeCell ref="A22:B23"/>
-    <mergeCell ref="H22:I23"/>
-    <mergeCell ref="A33:B34"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="E33:F33"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
   </mergeCells>
+  <conditionalFormatting sqref="J35:O40">
+    <cfRule type="colorScale" priority="20">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="7"/>
+        <color theme="9"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C35:D40">
+    <cfRule type="colorScale" priority="13">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="7"/>
+        <color theme="9"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E35:F40">
+    <cfRule type="colorScale" priority="12">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="7"/>
+        <color theme="9"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C45:D50">
+    <cfRule type="colorScale" priority="11">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="7"/>
+        <color theme="9"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E45:F50">
+    <cfRule type="colorScale" priority="10">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="7"/>
+        <color theme="9"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="C14:D19">
+    <cfRule type="colorScale" priority="9">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="7"/>
+        <color theme="9"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E14:F19">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -2044,17 +4509,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C24:D29">
-    <cfRule type="colorScale" priority="6">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="7"/>
-        <color theme="9"/>
-        <color rgb="FFFF0000"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E14:F19">
+  <conditionalFormatting sqref="J14:O19">
     <cfRule type="colorScale" priority="7">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -2064,8 +4519,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E24:F29">
-    <cfRule type="colorScale" priority="5">
+  <conditionalFormatting sqref="C24:D29">
+    <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="7"/>
@@ -2074,8 +4529,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J14:L19">
-    <cfRule type="colorScale" priority="4">
+  <conditionalFormatting sqref="E24:F29">
+    <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="7"/>
@@ -2085,27 +4540,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J24:O29">
-    <cfRule type="colorScale" priority="3">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="7"/>
-        <color theme="9"/>
-        <color rgb="FFFF0000"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J35:O40">
     <cfRule type="colorScale" priority="1">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="7"/>
-        <color theme="9"/>
-        <color rgb="FFFF0000"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M14:O19">
-    <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="7"/>
@@ -2119,7 +4554,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53FEF222-F6C6-4B1A-A480-25EE149DFD4F}">
   <dimension ref="A1:Q40"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2144,8 +4579,8 @@
       <c r="A1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="J1" s="1" t="s">
-        <v>74</v>
+      <c r="J1" s="52" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
@@ -2185,81 +4620,81 @@
       </c>
     </row>
     <row r="10" spans="1:17" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="41" t="s">
+      <c r="A10" s="32" t="s">
         <v>1</v>
       </c>
-      <c r="B10" s="41"/>
-      <c r="C10" s="41"/>
-      <c r="D10" s="41"/>
-      <c r="E10" s="41"/>
-      <c r="F10" s="41"/>
+      <c r="B10" s="32"/>
+      <c r="C10" s="32"/>
+      <c r="D10" s="32"/>
+      <c r="E10" s="32"/>
+      <c r="F10" s="32"/>
       <c r="G10" s="12"/>
       <c r="H10" s="12"/>
-      <c r="I10" s="41" t="s">
-        <v>2</v>
-      </c>
-      <c r="J10" s="41"/>
-      <c r="K10" s="41"/>
-      <c r="L10" s="41"/>
-      <c r="M10" s="41"/>
-      <c r="N10" s="41"/>
-      <c r="O10" s="41"/>
-      <c r="P10" s="41"/>
+      <c r="I10" s="32" t="s">
+        <v>2</v>
+      </c>
+      <c r="J10" s="32"/>
+      <c r="K10" s="32"/>
+      <c r="L10" s="32"/>
+      <c r="M10" s="32"/>
+      <c r="N10" s="32"/>
+      <c r="O10" s="32"/>
+      <c r="P10" s="32"/>
     </row>
     <row r="11" spans="1:17" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="A11" s="40" t="s">
-        <v>0</v>
-      </c>
-      <c r="B11" s="40"/>
-      <c r="C11" s="40"/>
-      <c r="D11" s="40"/>
-      <c r="E11" s="40"/>
-      <c r="F11" s="40"/>
-      <c r="H11" s="40" t="s">
-        <v>0</v>
-      </c>
-      <c r="I11" s="40"/>
-      <c r="J11" s="40"/>
-      <c r="K11" s="40"/>
-      <c r="L11" s="40"/>
-      <c r="M11" s="40"/>
-      <c r="N11" s="40"/>
-      <c r="O11" s="40"/>
+      <c r="A11" s="39" t="s">
+        <v>0</v>
+      </c>
+      <c r="B11" s="39"/>
+      <c r="C11" s="39"/>
+      <c r="D11" s="39"/>
+      <c r="E11" s="39"/>
+      <c r="F11" s="39"/>
+      <c r="H11" s="39" t="s">
+        <v>0</v>
+      </c>
+      <c r="I11" s="39"/>
+      <c r="J11" s="39"/>
+      <c r="K11" s="39"/>
+      <c r="L11" s="39"/>
+      <c r="M11" s="39"/>
+      <c r="N11" s="39"/>
+      <c r="O11" s="39"/>
     </row>
     <row r="12" spans="1:17" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A12" s="33" t="s">
+      <c r="A12" s="34" t="s">
         <v>61</v>
       </c>
-      <c r="B12" s="33"/>
-      <c r="C12" s="35" t="s">
-        <v>3</v>
-      </c>
-      <c r="D12" s="35"/>
-      <c r="E12" s="46" t="s">
-        <v>4</v>
-      </c>
-      <c r="F12" s="35"/>
+      <c r="B12" s="34"/>
+      <c r="C12" s="42" t="s">
+        <v>3</v>
+      </c>
+      <c r="D12" s="42"/>
+      <c r="E12" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="F12" s="42"/>
       <c r="G12" s="4"/>
-      <c r="H12" s="33" t="s">
+      <c r="H12" s="34" t="s">
         <v>61</v>
       </c>
-      <c r="I12" s="33"/>
-      <c r="J12" s="38" t="s">
-        <v>3</v>
-      </c>
-      <c r="K12" s="38"/>
-      <c r="L12" s="38"/>
-      <c r="M12" s="39" t="s">
-        <v>4</v>
-      </c>
-      <c r="N12" s="38"/>
-      <c r="O12" s="38"/>
+      <c r="I12" s="34"/>
+      <c r="J12" s="36" t="s">
+        <v>3</v>
+      </c>
+      <c r="K12" s="36"/>
+      <c r="L12" s="36"/>
+      <c r="M12" s="37" t="s">
+        <v>4</v>
+      </c>
+      <c r="N12" s="36"/>
+      <c r="O12" s="36"/>
       <c r="P12" s="4"/>
       <c r="Q12" s="4"/>
     </row>
     <row r="13" spans="1:17" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="A13" s="34"/>
-      <c r="B13" s="34"/>
+      <c r="A13" s="35"/>
+      <c r="B13" s="35"/>
       <c r="C13" s="13" t="s">
         <v>69</v>
       </c>
@@ -2273,8 +4708,8 @@
         <v>6</v>
       </c>
       <c r="G13" s="5"/>
-      <c r="H13" s="34"/>
-      <c r="I13" s="34"/>
+      <c r="H13" s="35"/>
+      <c r="I13" s="35"/>
       <c r="J13" s="17" t="s">
         <v>70</v>
       </c>
@@ -2303,11 +4738,11 @@
       <c r="B14" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="20">
+      <c r="D14">
         <v>0</v>
       </c>
       <c r="E14" s="24"/>
-      <c r="F14" s="20">
+      <c r="F14">
         <v>0</v>
       </c>
       <c r="G14" s="8"/>
@@ -2318,17 +4753,17 @@
         <v>10</v>
       </c>
       <c r="J14" s="20"/>
-      <c r="K14" s="20">
-        <v>0</v>
-      </c>
-      <c r="L14" s="20">
+      <c r="K14">
+        <v>0</v>
+      </c>
+      <c r="L14">
         <v>0</v>
       </c>
       <c r="M14" s="24"/>
-      <c r="N14" s="20">
-        <v>0</v>
-      </c>
-      <c r="O14" s="20">
+      <c r="N14">
+        <v>0</v>
+      </c>
+      <c r="O14">
         <v>0</v>
       </c>
       <c r="P14" s="8"/>
@@ -2342,11 +4777,11 @@
         <v>11</v>
       </c>
       <c r="C15" s="20"/>
-      <c r="D15" s="20">
+      <c r="D15">
         <v>0</v>
       </c>
       <c r="E15" s="24"/>
-      <c r="F15" s="20">
+      <c r="F15">
         <v>0</v>
       </c>
       <c r="G15" s="8"/>
@@ -2357,17 +4792,17 @@
         <v>11</v>
       </c>
       <c r="J15" s="20"/>
-      <c r="K15" s="20">
-        <v>0</v>
-      </c>
-      <c r="L15" s="20">
+      <c r="K15">
+        <v>0</v>
+      </c>
+      <c r="L15">
         <v>0</v>
       </c>
       <c r="M15" s="24"/>
-      <c r="N15" s="20">
-        <v>0</v>
-      </c>
-      <c r="O15" s="20">
+      <c r="N15">
+        <v>0</v>
+      </c>
+      <c r="O15">
         <v>0</v>
       </c>
       <c r="P15" s="8"/>
@@ -2381,11 +4816,11 @@
         <v>12</v>
       </c>
       <c r="C16" s="20"/>
-      <c r="D16" s="20">
+      <c r="D16">
         <v>0</v>
       </c>
       <c r="E16" s="24"/>
-      <c r="F16" s="20">
+      <c r="F16">
         <v>0</v>
       </c>
       <c r="G16" s="8"/>
@@ -2396,18 +4831,18 @@
         <v>12</v>
       </c>
       <c r="J16" s="20"/>
-      <c r="K16" s="20">
-        <v>0</v>
-      </c>
-      <c r="L16" s="20">
-        <v>0</v>
+      <c r="K16">
+        <v>0</v>
+      </c>
+      <c r="L16">
+        <v>2</v>
       </c>
       <c r="M16" s="24"/>
-      <c r="N16" s="20">
-        <v>0</v>
-      </c>
-      <c r="O16" s="20">
-        <v>0</v>
+      <c r="N16">
+        <v>0</v>
+      </c>
+      <c r="O16">
+        <v>2</v>
       </c>
       <c r="P16" s="8"/>
       <c r="Q16" s="4"/>
@@ -2420,11 +4855,11 @@
         <v>13</v>
       </c>
       <c r="C17" s="20"/>
-      <c r="D17" s="20">
+      <c r="D17">
         <v>0</v>
       </c>
       <c r="E17" s="24"/>
-      <c r="F17" s="20">
+      <c r="F17">
         <v>0</v>
       </c>
       <c r="G17" s="8"/>
@@ -2435,17 +4870,17 @@
         <v>13</v>
       </c>
       <c r="J17" s="20"/>
-      <c r="K17" s="20">
-        <v>0</v>
-      </c>
-      <c r="L17" s="20">
+      <c r="K17">
+        <v>0</v>
+      </c>
+      <c r="L17">
         <v>0</v>
       </c>
       <c r="M17" s="24"/>
-      <c r="N17" s="20">
-        <v>0</v>
-      </c>
-      <c r="O17" s="20">
+      <c r="N17">
+        <v>0</v>
+      </c>
+      <c r="O17">
         <v>0</v>
       </c>
       <c r="P17" s="8"/>
@@ -2459,11 +4894,11 @@
         <v>14</v>
       </c>
       <c r="C18" s="20"/>
-      <c r="D18" s="20">
+      <c r="D18">
         <v>7</v>
       </c>
       <c r="E18" s="24"/>
-      <c r="F18" s="20">
+      <c r="F18">
         <v>7</v>
       </c>
       <c r="G18" s="8"/>
@@ -2474,17 +4909,17 @@
         <v>14</v>
       </c>
       <c r="J18" s="20"/>
-      <c r="K18" s="20">
-        <v>0</v>
-      </c>
-      <c r="L18" s="20">
+      <c r="K18">
+        <v>0</v>
+      </c>
+      <c r="L18">
         <v>0</v>
       </c>
       <c r="M18" s="24"/>
-      <c r="N18" s="20">
-        <v>0</v>
-      </c>
-      <c r="O18" s="20">
+      <c r="N18">
+        <v>0</v>
+      </c>
+      <c r="O18">
         <v>0</v>
       </c>
       <c r="P18" s="8"/>
@@ -2498,11 +4933,11 @@
         <v>15</v>
       </c>
       <c r="C19" s="21"/>
-      <c r="D19" s="21">
+      <c r="D19">
         <v>0</v>
       </c>
       <c r="E19" s="25"/>
-      <c r="F19" s="21">
+      <c r="F19">
         <v>0</v>
       </c>
       <c r="G19" s="8"/>
@@ -2513,17 +4948,17 @@
         <v>15</v>
       </c>
       <c r="J19" s="21"/>
-      <c r="K19" s="21">
-        <v>0</v>
-      </c>
-      <c r="L19" s="21">
+      <c r="K19">
+        <v>0</v>
+      </c>
+      <c r="L19">
         <v>0</v>
       </c>
       <c r="M19" s="25"/>
-      <c r="N19" s="21">
-        <v>0</v>
-      </c>
-      <c r="O19" s="21">
+      <c r="N19">
+        <v>0</v>
+      </c>
+      <c r="O19">
         <v>0</v>
       </c>
       <c r="P19" s="8"/>
@@ -2549,62 +4984,62 @@
       <c r="Q20" s="4"/>
     </row>
     <row r="21" spans="1:17" ht="21" x14ac:dyDescent="0.35">
-      <c r="A21" s="43" t="s">
+      <c r="A21" s="38" t="s">
         <v>16</v>
       </c>
-      <c r="B21" s="43"/>
-      <c r="C21" s="43"/>
-      <c r="D21" s="43"/>
-      <c r="E21" s="43"/>
-      <c r="F21" s="43"/>
+      <c r="B21" s="38"/>
+      <c r="C21" s="38"/>
+      <c r="D21" s="38"/>
+      <c r="E21" s="38"/>
+      <c r="F21" s="38"/>
       <c r="G21" s="19"/>
       <c r="H21" s="8"/>
-      <c r="I21" s="47" t="s">
+      <c r="I21" s="46" t="s">
         <v>16</v>
       </c>
-      <c r="J21" s="47"/>
-      <c r="K21" s="47"/>
-      <c r="L21" s="47"/>
-      <c r="M21" s="47"/>
-      <c r="N21" s="47"/>
-      <c r="O21" s="47"/>
-      <c r="P21" s="47"/>
+      <c r="J21" s="46"/>
+      <c r="K21" s="46"/>
+      <c r="L21" s="46"/>
+      <c r="M21" s="46"/>
+      <c r="N21" s="46"/>
+      <c r="O21" s="46"/>
+      <c r="P21" s="46"/>
       <c r="Q21" s="4"/>
     </row>
     <row r="22" spans="1:17" ht="21" x14ac:dyDescent="0.35">
-      <c r="A22" s="33" t="s">
+      <c r="A22" s="34" t="s">
         <v>61</v>
       </c>
-      <c r="B22" s="33"/>
-      <c r="C22" s="35" t="s">
-        <v>3</v>
-      </c>
-      <c r="D22" s="35"/>
-      <c r="E22" s="46" t="s">
-        <v>4</v>
-      </c>
-      <c r="F22" s="35"/>
+      <c r="B22" s="34"/>
+      <c r="C22" s="42" t="s">
+        <v>3</v>
+      </c>
+      <c r="D22" s="42"/>
+      <c r="E22" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="F22" s="42"/>
       <c r="G22" s="8"/>
-      <c r="H22" s="33" t="s">
+      <c r="H22" s="34" t="s">
         <v>61</v>
       </c>
-      <c r="I22" s="33"/>
-      <c r="J22" s="38" t="s">
-        <v>3</v>
-      </c>
-      <c r="K22" s="38"/>
-      <c r="L22" s="38"/>
-      <c r="M22" s="39" t="s">
-        <v>4</v>
-      </c>
-      <c r="N22" s="38"/>
-      <c r="O22" s="38"/>
+      <c r="I22" s="34"/>
+      <c r="J22" s="36" t="s">
+        <v>3</v>
+      </c>
+      <c r="K22" s="36"/>
+      <c r="L22" s="36"/>
+      <c r="M22" s="37" t="s">
+        <v>4</v>
+      </c>
+      <c r="N22" s="36"/>
+      <c r="O22" s="36"/>
       <c r="P22" s="8"/>
       <c r="Q22" s="4"/>
     </row>
     <row r="23" spans="1:17" ht="21" x14ac:dyDescent="0.35">
-      <c r="A23" s="34"/>
-      <c r="B23" s="34"/>
+      <c r="A23" s="35"/>
+      <c r="B23" s="35"/>
       <c r="C23" s="13" t="s">
         <v>69</v>
       </c>
@@ -2618,8 +5053,8 @@
         <v>6</v>
       </c>
       <c r="G23" s="8"/>
-      <c r="H23" s="34"/>
-      <c r="I23" s="34"/>
+      <c r="H23" s="35"/>
+      <c r="I23" s="35"/>
       <c r="J23" s="17" t="s">
         <v>70</v>
       </c>
@@ -2649,11 +5084,11 @@
         <v>10</v>
       </c>
       <c r="C24" s="20"/>
-      <c r="D24" s="20">
+      <c r="D24">
         <v>0</v>
       </c>
       <c r="E24" s="24"/>
-      <c r="F24" s="20">
+      <c r="F24">
         <v>0</v>
       </c>
       <c r="G24" s="10"/>
@@ -2664,17 +5099,17 @@
         <v>10</v>
       </c>
       <c r="J24" s="20"/>
-      <c r="K24" s="20">
-        <v>0</v>
-      </c>
-      <c r="L24" s="20">
+      <c r="K24">
+        <v>0</v>
+      </c>
+      <c r="L24">
         <v>0</v>
       </c>
       <c r="M24" s="24"/>
-      <c r="N24" s="20">
-        <v>0</v>
-      </c>
-      <c r="O24" s="20">
+      <c r="N24">
+        <v>0</v>
+      </c>
+      <c r="O24">
         <v>0</v>
       </c>
       <c r="P24" s="10"/>
@@ -2688,11 +5123,11 @@
         <v>11</v>
       </c>
       <c r="C25" s="20"/>
-      <c r="D25" s="20">
+      <c r="D25">
         <v>0</v>
       </c>
       <c r="E25" s="24"/>
-      <c r="F25" s="20">
+      <c r="F25">
         <v>0</v>
       </c>
       <c r="G25" s="10"/>
@@ -2703,17 +5138,17 @@
         <v>11</v>
       </c>
       <c r="J25" s="20"/>
-      <c r="K25" s="20">
-        <v>0</v>
-      </c>
-      <c r="L25" s="20">
+      <c r="K25">
+        <v>0</v>
+      </c>
+      <c r="L25">
         <v>0</v>
       </c>
       <c r="M25" s="24"/>
-      <c r="N25" s="20">
-        <v>0</v>
-      </c>
-      <c r="O25" s="20">
+      <c r="N25">
+        <v>0</v>
+      </c>
+      <c r="O25">
         <v>0</v>
       </c>
       <c r="P25" s="10"/>
@@ -2727,11 +5162,11 @@
         <v>12</v>
       </c>
       <c r="C26" s="20"/>
-      <c r="D26" s="20">
-        <v>3</v>
+      <c r="D26">
+        <v>5</v>
       </c>
       <c r="E26" s="24"/>
-      <c r="F26" s="20">
+      <c r="F26">
         <v>5</v>
       </c>
       <c r="G26" s="10"/>
@@ -2742,17 +5177,17 @@
         <v>12</v>
       </c>
       <c r="J26" s="20"/>
-      <c r="K26" s="20">
-        <v>0</v>
-      </c>
-      <c r="L26" s="20">
+      <c r="K26">
+        <v>0</v>
+      </c>
+      <c r="L26">
         <v>0</v>
       </c>
       <c r="M26" s="24"/>
-      <c r="N26" s="20">
-        <v>0</v>
-      </c>
-      <c r="O26" s="20">
+      <c r="N26">
+        <v>0</v>
+      </c>
+      <c r="O26">
         <v>0</v>
       </c>
       <c r="P26" s="10"/>
@@ -2766,11 +5201,11 @@
         <v>13</v>
       </c>
       <c r="C27" s="20"/>
-      <c r="D27" s="20">
+      <c r="D27">
         <v>0</v>
       </c>
       <c r="E27" s="24"/>
-      <c r="F27" s="20">
+      <c r="F27">
         <v>0</v>
       </c>
       <c r="G27" s="10"/>
@@ -2781,17 +5216,17 @@
         <v>13</v>
       </c>
       <c r="J27" s="20"/>
-      <c r="K27" s="20">
-        <v>0</v>
-      </c>
-      <c r="L27" s="20">
+      <c r="K27">
+        <v>0</v>
+      </c>
+      <c r="L27">
         <v>0</v>
       </c>
       <c r="M27" s="24"/>
-      <c r="N27" s="20">
-        <v>0</v>
-      </c>
-      <c r="O27" s="20">
+      <c r="N27">
+        <v>0</v>
+      </c>
+      <c r="O27">
         <v>0</v>
       </c>
       <c r="P27" s="10"/>
@@ -2805,12 +5240,12 @@
         <v>14</v>
       </c>
       <c r="C28" s="20"/>
-      <c r="D28" s="20">
-        <v>3</v>
+      <c r="D28">
+        <v>5</v>
       </c>
       <c r="E28" s="24"/>
-      <c r="F28" s="20">
-        <v>3</v>
+      <c r="F28">
+        <v>5</v>
       </c>
       <c r="G28" s="10"/>
       <c r="H28" s="9">
@@ -2820,17 +5255,17 @@
         <v>14</v>
       </c>
       <c r="J28" s="20"/>
-      <c r="K28" s="20">
-        <v>0</v>
-      </c>
-      <c r="L28" s="20">
+      <c r="K28">
+        <v>0</v>
+      </c>
+      <c r="L28">
         <v>0</v>
       </c>
       <c r="M28" s="24"/>
-      <c r="N28" s="20">
-        <v>0</v>
-      </c>
-      <c r="O28" s="20">
+      <c r="N28">
+        <v>0</v>
+      </c>
+      <c r="O28">
         <v>0</v>
       </c>
       <c r="P28" s="10"/>
@@ -2844,11 +5279,11 @@
         <v>15</v>
       </c>
       <c r="C29" s="21"/>
-      <c r="D29" s="21">
+      <c r="D29">
         <v>0</v>
       </c>
       <c r="E29" s="25"/>
-      <c r="F29" s="21">
+      <c r="F29">
         <v>0</v>
       </c>
       <c r="G29" s="10"/>
@@ -2859,17 +5294,17 @@
         <v>15</v>
       </c>
       <c r="J29" s="21"/>
-      <c r="K29" s="21">
-        <v>0</v>
-      </c>
-      <c r="L29" s="21">
+      <c r="K29">
+        <v>0</v>
+      </c>
+      <c r="L29">
         <v>0</v>
       </c>
       <c r="M29" s="25"/>
-      <c r="N29" s="21">
-        <v>0</v>
-      </c>
-      <c r="O29" s="21">
+      <c r="N29">
+        <v>0</v>
+      </c>
+      <c r="O29">
         <v>0</v>
       </c>
       <c r="P29" s="10"/>
@@ -2914,14 +5349,14 @@
       <c r="Q31" s="4"/>
     </row>
     <row r="32" spans="1:17" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="A32" s="40" t="s">
+      <c r="A32" s="39" t="s">
         <v>62</v>
       </c>
-      <c r="B32" s="40"/>
-      <c r="C32" s="40"/>
-      <c r="D32" s="40"/>
-      <c r="E32" s="40"/>
-      <c r="F32" s="40"/>
+      <c r="B32" s="39"/>
+      <c r="C32" s="39"/>
+      <c r="D32" s="39"/>
+      <c r="E32" s="39"/>
+      <c r="F32" s="39"/>
       <c r="G32" s="4"/>
       <c r="H32" s="4"/>
       <c r="I32" s="4"/>
@@ -2935,22 +5370,22 @@
       <c r="Q32" s="4"/>
     </row>
     <row r="33" spans="1:6" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A33" s="33" t="s">
+      <c r="A33" s="34" t="s">
         <v>61</v>
       </c>
-      <c r="B33" s="33"/>
-      <c r="C33" s="35" t="s">
-        <v>3</v>
-      </c>
-      <c r="D33" s="35"/>
-      <c r="E33" s="35" t="s">
-        <v>4</v>
-      </c>
-      <c r="F33" s="35"/>
+      <c r="B33" s="34"/>
+      <c r="C33" s="42" t="s">
+        <v>3</v>
+      </c>
+      <c r="D33" s="42"/>
+      <c r="E33" s="42" t="s">
+        <v>4</v>
+      </c>
+      <c r="F33" s="42"/>
     </row>
     <row r="34" spans="1:6" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A34" s="34"/>
-      <c r="B34" s="34"/>
+      <c r="A34" s="35"/>
+      <c r="B34" s="35"/>
       <c r="C34" s="13" t="s">
         <v>5</v>
       </c>
@@ -3038,6 +5473,18 @@
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="A32:F32"/>
+    <mergeCell ref="A33:B34"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="E33:F33"/>
+    <mergeCell ref="A21:F21"/>
+    <mergeCell ref="I21:P21"/>
+    <mergeCell ref="A22:B23"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="H22:I23"/>
+    <mergeCell ref="J22:L22"/>
+    <mergeCell ref="M22:O22"/>
     <mergeCell ref="A10:F10"/>
     <mergeCell ref="I10:P10"/>
     <mergeCell ref="A11:F11"/>
@@ -3048,18 +5495,6 @@
     <mergeCell ref="H12:I13"/>
     <mergeCell ref="J12:L12"/>
     <mergeCell ref="M12:O12"/>
-    <mergeCell ref="I21:P21"/>
-    <mergeCell ref="A22:B23"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="H22:I23"/>
-    <mergeCell ref="J22:L22"/>
-    <mergeCell ref="M22:O22"/>
-    <mergeCell ref="A32:F32"/>
-    <mergeCell ref="A33:B34"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="E33:F33"/>
-    <mergeCell ref="A21:F21"/>
   </mergeCells>
   <conditionalFormatting sqref="C15:C19 E14:E19">
     <cfRule type="colorScale" priority="19">
@@ -3196,7 +5631,1084 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1267B1F8-47FF-4259-BB79-A96890BCF7A6}">
+  <dimension ref="A1:Q40"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="3.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="64.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="2.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="64.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="26.42578125" customWidth="1"/>
+    <col min="11" max="11" width="28.28515625" customWidth="1"/>
+    <col min="12" max="12" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="23.140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="29" customWidth="1"/>
+    <col min="15" max="15" width="19.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J1" s="52" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>64</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="32" t="s">
+        <v>1</v>
+      </c>
+      <c r="B10" s="32"/>
+      <c r="C10" s="32"/>
+      <c r="D10" s="32"/>
+      <c r="E10" s="32"/>
+      <c r="F10" s="32"/>
+      <c r="G10" s="12"/>
+      <c r="H10" s="12"/>
+      <c r="I10" s="32" t="s">
+        <v>2</v>
+      </c>
+      <c r="J10" s="32"/>
+      <c r="K10" s="32"/>
+      <c r="L10" s="32"/>
+      <c r="M10" s="32"/>
+      <c r="N10" s="32"/>
+      <c r="O10" s="32"/>
+      <c r="P10" s="32"/>
+    </row>
+    <row r="11" spans="1:17" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="A11" s="39" t="s">
+        <v>0</v>
+      </c>
+      <c r="B11" s="39"/>
+      <c r="C11" s="39"/>
+      <c r="D11" s="39"/>
+      <c r="E11" s="39"/>
+      <c r="F11" s="39"/>
+      <c r="H11" s="39" t="s">
+        <v>0</v>
+      </c>
+      <c r="I11" s="39"/>
+      <c r="J11" s="39"/>
+      <c r="K11" s="39"/>
+      <c r="L11" s="39"/>
+      <c r="M11" s="39"/>
+      <c r="N11" s="39"/>
+      <c r="O11" s="39"/>
+    </row>
+    <row r="12" spans="1:17" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="A12" s="34" t="s">
+        <v>61</v>
+      </c>
+      <c r="B12" s="34"/>
+      <c r="C12" s="42" t="s">
+        <v>3</v>
+      </c>
+      <c r="D12" s="42"/>
+      <c r="E12" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="F12" s="42"/>
+      <c r="G12" s="4"/>
+      <c r="H12" s="34" t="s">
+        <v>61</v>
+      </c>
+      <c r="I12" s="34"/>
+      <c r="J12" s="36" t="s">
+        <v>3</v>
+      </c>
+      <c r="K12" s="36"/>
+      <c r="L12" s="36"/>
+      <c r="M12" s="37" t="s">
+        <v>4</v>
+      </c>
+      <c r="N12" s="36"/>
+      <c r="O12" s="36"/>
+      <c r="P12" s="4"/>
+      <c r="Q12" s="4"/>
+    </row>
+    <row r="13" spans="1:17" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="A13" s="35"/>
+      <c r="B13" s="35"/>
+      <c r="C13" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="D13" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="E13" s="23" t="s">
+        <v>69</v>
+      </c>
+      <c r="F13" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="G13" s="5"/>
+      <c r="H13" s="35"/>
+      <c r="I13" s="35"/>
+      <c r="J13" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="K13" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="L13" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="M13" s="23" t="s">
+        <v>70</v>
+      </c>
+      <c r="N13" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="O13" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="P13" s="5"/>
+      <c r="Q13" s="4"/>
+    </row>
+    <row r="14" spans="1:17" ht="21" x14ac:dyDescent="0.35">
+      <c r="A14" s="6">
+        <v>1</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D14">
+        <v>1</v>
+      </c>
+      <c r="E14" s="24"/>
+      <c r="F14">
+        <v>2</v>
+      </c>
+      <c r="G14" s="8"/>
+      <c r="H14" s="6">
+        <v>1</v>
+      </c>
+      <c r="I14" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="J14" s="20"/>
+      <c r="K14">
+        <v>0</v>
+      </c>
+      <c r="L14">
+        <v>0</v>
+      </c>
+      <c r="M14" s="24"/>
+      <c r="N14">
+        <v>0</v>
+      </c>
+      <c r="O14">
+        <v>0</v>
+      </c>
+      <c r="P14" s="8"/>
+      <c r="Q14" s="4"/>
+    </row>
+    <row r="15" spans="1:17" ht="21" x14ac:dyDescent="0.35">
+      <c r="A15" s="6">
+        <v>2</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C15" s="20"/>
+      <c r="D15">
+        <v>0</v>
+      </c>
+      <c r="E15" s="24"/>
+      <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="G15" s="8"/>
+      <c r="H15" s="6">
+        <v>2</v>
+      </c>
+      <c r="I15" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="J15" s="20"/>
+      <c r="K15">
+        <v>0</v>
+      </c>
+      <c r="L15">
+        <v>0</v>
+      </c>
+      <c r="M15" s="24"/>
+      <c r="N15">
+        <v>0</v>
+      </c>
+      <c r="O15">
+        <v>0</v>
+      </c>
+      <c r="P15" s="8"/>
+      <c r="Q15" s="4"/>
+    </row>
+    <row r="16" spans="1:17" ht="21" x14ac:dyDescent="0.35">
+      <c r="A16" s="6">
+        <v>3</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C16" s="20"/>
+      <c r="D16">
+        <v>5</v>
+      </c>
+      <c r="E16" s="24"/>
+      <c r="F16">
+        <v>4</v>
+      </c>
+      <c r="G16" s="8"/>
+      <c r="H16" s="6">
+        <v>3</v>
+      </c>
+      <c r="I16" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="J16" s="20"/>
+      <c r="K16">
+        <v>1</v>
+      </c>
+      <c r="L16">
+        <v>6</v>
+      </c>
+      <c r="M16" s="24"/>
+      <c r="N16">
+        <v>2</v>
+      </c>
+      <c r="O16">
+        <v>7</v>
+      </c>
+      <c r="P16" s="8"/>
+      <c r="Q16" s="4"/>
+    </row>
+    <row r="17" spans="1:17" ht="21" x14ac:dyDescent="0.35">
+      <c r="A17" s="6">
+        <v>4</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C17" s="20"/>
+      <c r="D17">
+        <v>7</v>
+      </c>
+      <c r="E17" s="24"/>
+      <c r="F17">
+        <v>6</v>
+      </c>
+      <c r="G17" s="8"/>
+      <c r="H17" s="6">
+        <v>4</v>
+      </c>
+      <c r="I17" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="J17" s="20"/>
+      <c r="K17">
+        <v>0</v>
+      </c>
+      <c r="L17">
+        <v>0</v>
+      </c>
+      <c r="M17" s="24"/>
+      <c r="N17">
+        <v>0</v>
+      </c>
+      <c r="O17">
+        <v>4</v>
+      </c>
+      <c r="P17" s="8"/>
+      <c r="Q17" s="4"/>
+    </row>
+    <row r="18" spans="1:17" ht="21" x14ac:dyDescent="0.35">
+      <c r="A18" s="6">
+        <v>5</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C18" s="20"/>
+      <c r="D18">
+        <v>7</v>
+      </c>
+      <c r="E18" s="24"/>
+      <c r="F18">
+        <v>7</v>
+      </c>
+      <c r="G18" s="8"/>
+      <c r="H18" s="6">
+        <v>5</v>
+      </c>
+      <c r="I18" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J18" s="20"/>
+      <c r="K18">
+        <v>0</v>
+      </c>
+      <c r="L18">
+        <v>1</v>
+      </c>
+      <c r="M18" s="24"/>
+      <c r="N18">
+        <v>0</v>
+      </c>
+      <c r="O18">
+        <v>1</v>
+      </c>
+      <c r="P18" s="8"/>
+      <c r="Q18" s="4"/>
+    </row>
+    <row r="19" spans="1:17" ht="21" x14ac:dyDescent="0.35">
+      <c r="A19" s="14">
+        <v>6</v>
+      </c>
+      <c r="B19" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="C19" s="21"/>
+      <c r="D19">
+        <v>6</v>
+      </c>
+      <c r="E19" s="25"/>
+      <c r="F19">
+        <v>6</v>
+      </c>
+      <c r="G19" s="8"/>
+      <c r="H19" s="6">
+        <v>6</v>
+      </c>
+      <c r="I19" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J19" s="21"/>
+      <c r="K19">
+        <v>0</v>
+      </c>
+      <c r="L19">
+        <v>1</v>
+      </c>
+      <c r="M19" s="25"/>
+      <c r="N19">
+        <v>0</v>
+      </c>
+      <c r="O19">
+        <v>4</v>
+      </c>
+      <c r="P19" s="8"/>
+      <c r="Q19" s="4"/>
+    </row>
+    <row r="20" spans="1:17" ht="21" x14ac:dyDescent="0.35">
+      <c r="A20" s="8"/>
+      <c r="B20" s="8"/>
+      <c r="C20" s="8"/>
+      <c r="D20" s="8"/>
+      <c r="E20" s="8"/>
+      <c r="F20" s="8"/>
+      <c r="G20" s="8"/>
+      <c r="H20" s="8"/>
+      <c r="I20" s="8"/>
+      <c r="J20" s="8"/>
+      <c r="K20" s="8"/>
+      <c r="L20" s="8"/>
+      <c r="M20" s="8"/>
+      <c r="N20" s="8"/>
+      <c r="O20" s="8"/>
+      <c r="P20" s="8"/>
+      <c r="Q20" s="4"/>
+    </row>
+    <row r="21" spans="1:17" ht="21" x14ac:dyDescent="0.35">
+      <c r="A21" s="38" t="s">
+        <v>16</v>
+      </c>
+      <c r="B21" s="38"/>
+      <c r="C21" s="38"/>
+      <c r="D21" s="38"/>
+      <c r="E21" s="38"/>
+      <c r="F21" s="38"/>
+      <c r="G21" s="19"/>
+      <c r="H21" s="8"/>
+      <c r="I21" s="46" t="s">
+        <v>16</v>
+      </c>
+      <c r="J21" s="46"/>
+      <c r="K21" s="46"/>
+      <c r="L21" s="46"/>
+      <c r="M21" s="46"/>
+      <c r="N21" s="46"/>
+      <c r="O21" s="46"/>
+      <c r="P21" s="46"/>
+      <c r="Q21" s="4"/>
+    </row>
+    <row r="22" spans="1:17" ht="21" x14ac:dyDescent="0.35">
+      <c r="A22" s="34" t="s">
+        <v>61</v>
+      </c>
+      <c r="B22" s="34"/>
+      <c r="C22" s="42" t="s">
+        <v>3</v>
+      </c>
+      <c r="D22" s="42"/>
+      <c r="E22" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="F22" s="42"/>
+      <c r="G22" s="8"/>
+      <c r="H22" s="34" t="s">
+        <v>61</v>
+      </c>
+      <c r="I22" s="34"/>
+      <c r="J22" s="36" t="s">
+        <v>3</v>
+      </c>
+      <c r="K22" s="36"/>
+      <c r="L22" s="36"/>
+      <c r="M22" s="37" t="s">
+        <v>4</v>
+      </c>
+      <c r="N22" s="36"/>
+      <c r="O22" s="36"/>
+      <c r="P22" s="8"/>
+      <c r="Q22" s="4"/>
+    </row>
+    <row r="23" spans="1:17" ht="21" x14ac:dyDescent="0.35">
+      <c r="A23" s="35"/>
+      <c r="B23" s="35"/>
+      <c r="C23" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="D23" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="E23" s="23" t="s">
+        <v>69</v>
+      </c>
+      <c r="F23" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="G23" s="8"/>
+      <c r="H23" s="35"/>
+      <c r="I23" s="35"/>
+      <c r="J23" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="K23" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="L23" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="M23" s="23" t="s">
+        <v>70</v>
+      </c>
+      <c r="N23" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="O23" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="P23" s="8"/>
+      <c r="Q23" s="4"/>
+    </row>
+    <row r="24" spans="1:17" ht="21" x14ac:dyDescent="0.35">
+      <c r="A24" s="9">
+        <v>1</v>
+      </c>
+      <c r="B24" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C24" s="20"/>
+      <c r="D24">
+        <v>4</v>
+      </c>
+      <c r="E24" s="24"/>
+      <c r="F24">
+        <v>5</v>
+      </c>
+      <c r="G24" s="10"/>
+      <c r="H24" s="9">
+        <v>1</v>
+      </c>
+      <c r="I24" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="J24" s="20"/>
+      <c r="K24">
+        <v>0</v>
+      </c>
+      <c r="L24">
+        <v>1</v>
+      </c>
+      <c r="M24" s="24"/>
+      <c r="N24">
+        <v>0</v>
+      </c>
+      <c r="O24">
+        <v>1</v>
+      </c>
+      <c r="P24" s="10"/>
+      <c r="Q24" s="4"/>
+    </row>
+    <row r="25" spans="1:17" ht="21" x14ac:dyDescent="0.35">
+      <c r="A25" s="9">
+        <v>2</v>
+      </c>
+      <c r="B25" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="20"/>
+      <c r="D25">
+        <v>0</v>
+      </c>
+      <c r="E25" s="24"/>
+      <c r="F25">
+        <v>0</v>
+      </c>
+      <c r="G25" s="10"/>
+      <c r="H25" s="9">
+        <v>2</v>
+      </c>
+      <c r="I25" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="J25" s="20"/>
+      <c r="K25">
+        <v>0</v>
+      </c>
+      <c r="L25">
+        <v>0</v>
+      </c>
+      <c r="M25" s="24"/>
+      <c r="N25">
+        <v>0</v>
+      </c>
+      <c r="O25">
+        <v>0</v>
+      </c>
+      <c r="P25" s="10"/>
+      <c r="Q25" s="4"/>
+    </row>
+    <row r="26" spans="1:17" ht="21" x14ac:dyDescent="0.35">
+      <c r="A26" s="9">
+        <v>3</v>
+      </c>
+      <c r="B26" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C26" s="20"/>
+      <c r="D26">
+        <v>7</v>
+      </c>
+      <c r="E26" s="24"/>
+      <c r="F26">
+        <v>7</v>
+      </c>
+      <c r="G26" s="10"/>
+      <c r="H26" s="9">
+        <v>3</v>
+      </c>
+      <c r="I26" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="J26" s="20"/>
+      <c r="K26">
+        <v>1</v>
+      </c>
+      <c r="L26">
+        <v>3</v>
+      </c>
+      <c r="M26" s="24"/>
+      <c r="N26">
+        <v>1</v>
+      </c>
+      <c r="O26">
+        <v>3</v>
+      </c>
+      <c r="P26" s="10"/>
+      <c r="Q26" s="4"/>
+    </row>
+    <row r="27" spans="1:17" ht="21" x14ac:dyDescent="0.35">
+      <c r="A27" s="9">
+        <v>4</v>
+      </c>
+      <c r="B27" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="C27" s="20"/>
+      <c r="D27">
+        <v>5</v>
+      </c>
+      <c r="E27" s="24"/>
+      <c r="F27">
+        <v>5</v>
+      </c>
+      <c r="G27" s="10"/>
+      <c r="H27" s="9">
+        <v>4</v>
+      </c>
+      <c r="I27" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J27" s="20"/>
+      <c r="K27">
+        <v>0</v>
+      </c>
+      <c r="L27">
+        <v>1</v>
+      </c>
+      <c r="M27" s="24"/>
+      <c r="N27">
+        <v>0</v>
+      </c>
+      <c r="O27">
+        <v>4</v>
+      </c>
+      <c r="P27" s="10"/>
+      <c r="Q27" s="4"/>
+    </row>
+    <row r="28" spans="1:17" ht="21" x14ac:dyDescent="0.35">
+      <c r="A28" s="9">
+        <v>5</v>
+      </c>
+      <c r="B28" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C28" s="20"/>
+      <c r="D28">
+        <v>6</v>
+      </c>
+      <c r="E28" s="24"/>
+      <c r="F28">
+        <v>7</v>
+      </c>
+      <c r="G28" s="10"/>
+      <c r="H28" s="9">
+        <v>5</v>
+      </c>
+      <c r="I28" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="J28" s="20"/>
+      <c r="K28">
+        <v>0</v>
+      </c>
+      <c r="L28">
+        <v>2</v>
+      </c>
+      <c r="M28" s="24"/>
+      <c r="N28">
+        <v>0</v>
+      </c>
+      <c r="O28">
+        <v>2</v>
+      </c>
+      <c r="P28" s="10"/>
+      <c r="Q28" s="4"/>
+    </row>
+    <row r="29" spans="1:17" ht="21" x14ac:dyDescent="0.35">
+      <c r="A29" s="16">
+        <v>6</v>
+      </c>
+      <c r="B29" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="C29" s="21"/>
+      <c r="D29">
+        <v>7</v>
+      </c>
+      <c r="E29" s="25"/>
+      <c r="F29">
+        <v>7</v>
+      </c>
+      <c r="G29" s="10"/>
+      <c r="H29" s="16">
+        <v>6</v>
+      </c>
+      <c r="I29" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="J29" s="21"/>
+      <c r="K29">
+        <v>0</v>
+      </c>
+      <c r="L29">
+        <v>0</v>
+      </c>
+      <c r="M29" s="25"/>
+      <c r="N29">
+        <v>0</v>
+      </c>
+      <c r="O29">
+        <v>0</v>
+      </c>
+      <c r="P29" s="10"/>
+      <c r="Q29" s="4"/>
+    </row>
+    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A30" s="4"/>
+      <c r="B30" s="4"/>
+      <c r="C30" s="4"/>
+      <c r="D30" s="4"/>
+      <c r="E30" s="4"/>
+      <c r="F30" s="4"/>
+      <c r="G30" s="4"/>
+      <c r="H30" s="4"/>
+      <c r="I30" s="4"/>
+      <c r="J30" s="4"/>
+      <c r="K30" s="4"/>
+      <c r="L30" s="4"/>
+      <c r="M30" s="4"/>
+      <c r="N30" s="4"/>
+      <c r="O30" s="4"/>
+      <c r="P30" s="4"/>
+      <c r="Q30" s="4"/>
+    </row>
+    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A31" s="4"/>
+      <c r="B31" s="4"/>
+      <c r="C31" s="4"/>
+      <c r="D31" s="4"/>
+      <c r="E31" s="4"/>
+      <c r="F31" s="4"/>
+      <c r="G31" s="4"/>
+      <c r="H31" s="4"/>
+      <c r="I31" s="4"/>
+      <c r="J31" s="4"/>
+      <c r="K31" s="4"/>
+      <c r="L31" s="4"/>
+      <c r="M31" s="4"/>
+      <c r="N31" s="4"/>
+      <c r="O31" s="4"/>
+      <c r="P31" s="4"/>
+      <c r="Q31" s="4"/>
+    </row>
+    <row r="32" spans="1:17" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="A32" s="39" t="s">
+        <v>62</v>
+      </c>
+      <c r="B32" s="39"/>
+      <c r="C32" s="39"/>
+      <c r="D32" s="39"/>
+      <c r="E32" s="39"/>
+      <c r="F32" s="39"/>
+      <c r="G32" s="4"/>
+      <c r="H32" s="4"/>
+      <c r="I32" s="4"/>
+      <c r="J32" s="4"/>
+      <c r="K32" s="4"/>
+      <c r="L32" s="4"/>
+      <c r="M32" s="4"/>
+      <c r="N32" s="4"/>
+      <c r="O32" s="4"/>
+      <c r="P32" s="4"/>
+      <c r="Q32" s="4"/>
+    </row>
+    <row r="33" spans="1:6" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="A33" s="34" t="s">
+        <v>61</v>
+      </c>
+      <c r="B33" s="34"/>
+      <c r="C33" s="42" t="s">
+        <v>3</v>
+      </c>
+      <c r="D33" s="42"/>
+      <c r="E33" s="42" t="s">
+        <v>4</v>
+      </c>
+      <c r="F33" s="42"/>
+    </row>
+    <row r="34" spans="1:6" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="A34" s="35"/>
+      <c r="B34" s="35"/>
+      <c r="C34" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="D34" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="E34" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="F34" s="13" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" ht="21" x14ac:dyDescent="0.35">
+      <c r="A35" s="6">
+        <v>1</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="11"/>
+      <c r="D35" s="11"/>
+      <c r="E35" s="11"/>
+      <c r="F35" s="7"/>
+    </row>
+    <row r="36" spans="1:6" ht="21" x14ac:dyDescent="0.35">
+      <c r="A36" s="6">
+        <v>2</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C36" s="7"/>
+      <c r="D36" s="7"/>
+      <c r="E36" s="7"/>
+      <c r="F36" s="7"/>
+    </row>
+    <row r="37" spans="1:6" ht="21" x14ac:dyDescent="0.35">
+      <c r="A37" s="6">
+        <v>3</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C37" s="7"/>
+      <c r="D37" s="7"/>
+      <c r="E37" s="7"/>
+      <c r="F37" s="7"/>
+    </row>
+    <row r="38" spans="1:6" ht="21" x14ac:dyDescent="0.35">
+      <c r="A38" s="6">
+        <v>4</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C38" s="7"/>
+      <c r="D38" s="7"/>
+      <c r="E38" s="7"/>
+      <c r="F38" s="7"/>
+    </row>
+    <row r="39" spans="1:6" ht="21" x14ac:dyDescent="0.35">
+      <c r="A39" s="6">
+        <v>5</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C39" s="7"/>
+      <c r="D39" s="7"/>
+      <c r="E39" s="7"/>
+      <c r="F39" s="7"/>
+    </row>
+    <row r="40" spans="1:6" ht="21" x14ac:dyDescent="0.35">
+      <c r="A40" s="14">
+        <v>6</v>
+      </c>
+      <c r="B40" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="C40" s="15"/>
+      <c r="D40" s="15"/>
+      <c r="E40" s="15"/>
+      <c r="F40" s="15"/>
+    </row>
+  </sheetData>
+  <mergeCells count="22">
+    <mergeCell ref="A32:F32"/>
+    <mergeCell ref="A33:B34"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="E33:F33"/>
+    <mergeCell ref="A21:F21"/>
+    <mergeCell ref="I21:P21"/>
+    <mergeCell ref="A22:B23"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="H22:I23"/>
+    <mergeCell ref="J22:L22"/>
+    <mergeCell ref="M22:O22"/>
+    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="I10:P10"/>
+    <mergeCell ref="A11:F11"/>
+    <mergeCell ref="H11:O11"/>
+    <mergeCell ref="A12:B13"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="H12:I13"/>
+    <mergeCell ref="J12:L12"/>
+    <mergeCell ref="M12:O12"/>
+  </mergeCells>
+  <conditionalFormatting sqref="C15:C19 E14:E19">
+    <cfRule type="colorScale" priority="13">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color theme="9"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C24:C29 E24:E29">
+    <cfRule type="colorScale" priority="11">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color theme="9"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D13">
+    <cfRule type="colorScale" priority="9">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color theme="9"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D14:D19">
+    <cfRule type="colorScale" priority="7">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="7"/>
+        <color theme="9"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D24:D29">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="7"/>
+        <color theme="9"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F14:F19">
+    <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="7"/>
+        <color theme="9"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F24:F29">
+    <cfRule type="colorScale" priority="5">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="7"/>
+        <color theme="9"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J14:J19 M14:M19">
+    <cfRule type="colorScale" priority="12">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color theme="9"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J24:J29 M24:M29">
+    <cfRule type="colorScale" priority="10">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color theme="9"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K14:L19">
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="7"/>
+        <color theme="9"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K24:L29">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="7"/>
+        <color theme="9"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N14:O19">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="7"/>
+        <color theme="9"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N24:O29">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="7"/>
+        <color theme="9"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24B48D00-D29C-48CE-9FF2-02589507B344}">
   <dimension ref="C3:N26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -3213,10 +6725,10 @@
   </cols>
   <sheetData>
     <row r="3" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="L3" s="48" t="s">
+      <c r="L3" s="47" t="s">
         <v>60</v>
       </c>
-      <c r="M3" s="48"/>
+      <c r="M3" s="47"/>
       <c r="N3" t="s">
         <v>59</v>
       </c>
@@ -3412,7 +6924,7 @@
       <c r="L17" t="s">
         <v>48</v>
       </c>
-      <c r="M17" s="48" t="s">
+      <c r="M17" s="47" t="s">
         <v>49</v>
       </c>
     </row>
@@ -3432,7 +6944,7 @@
       <c r="L18" t="s">
         <v>50</v>
       </c>
-      <c r="M18" s="48"/>
+      <c r="M18" s="47"/>
     </row>
     <row r="19" spans="6:13" x14ac:dyDescent="0.25">
       <c r="G19" t="s">
@@ -3533,6 +7045,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009074E2A1C82F3C4BA659A6C6CC51AC5F" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0765d5a41f49df217abeb23dcfb0b3cf">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="cc5908d1-2a89-4186-9c08-2c76e53ac163" xmlns:ns3="f72adabb-0ee4-4963-acd9-9efc158f92a6" xmlns:ns4="e8c8a8d2-cf65-4fdf-b6bc-794ebda6188e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="519818410c367a5844210e380df69fc7" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="cc5908d1-2a89-4186-9c08-2c76e53ac163"/>
@@ -3780,15 +7301,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{78150E95-1CCA-47FB-B6E6-99D8675B2929}">
   <ds:schemaRefs>
@@ -3808,6 +7320,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{29C58647-0154-48BC-9EDF-8ABD72381C6C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4039D020-CA7C-47AE-A105-0DAEDCC57394}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3825,12 +7345,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{29C58647-0154-48BC-9EDF-8ABD72381C6C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/output/V3_SIM_Results_Summary.xlsx
+++ b/output/V3_SIM_Results_Summary.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://adminliveunc-my.sharepoint.com/personal/beibo_ad_unc_edu/Documents/CSCC/HCHS/V3_SIM/suddan/HCHS_simulation/output/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1694" documentId="11_F25DC773A252ABDACC10487F29D85E365BDE58E9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B8EB9779-EEAE-4283-8753-38B943B85BF0}"/>
+  <xr:revisionPtr revIDLastSave="1696" documentId="11_F25DC773A252ABDACC10487F29D85E365BDE58E9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B2FEBE70-03B8-4805-83BC-77F5666734CF}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="761" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -523,7 +523,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -588,54 +588,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -645,54 +597,92 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -976,7 +966,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAB8470B-C760-491C-B73B-F574B62DA7BA}">
-  <dimension ref="A1:Y55"/>
+  <dimension ref="A1:Y53"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3.140625" bestFit="1" customWidth="1"/>
@@ -1008,7 +998,7 @@
       <c r="A1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="35" t="s">
         <v>68</v>
       </c>
       <c r="K1" s="1"/>
@@ -1061,146 +1051,146 @@
       </c>
     </row>
     <row r="10" spans="1:25" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="32" t="s">
+      <c r="A10" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="B10" s="32"/>
-      <c r="C10" s="32"/>
-      <c r="D10" s="32"/>
-      <c r="E10" s="32"/>
-      <c r="F10" s="32"/>
+      <c r="B10" s="48"/>
+      <c r="C10" s="48"/>
+      <c r="D10" s="48"/>
+      <c r="E10" s="48"/>
+      <c r="F10" s="48"/>
       <c r="G10" s="31"/>
-      <c r="H10" s="32" t="s">
+      <c r="H10" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="I10" s="32"/>
-      <c r="J10" s="32"/>
-      <c r="K10" s="32"/>
-      <c r="L10" s="32"/>
-      <c r="M10" s="32"/>
+      <c r="I10" s="48"/>
+      <c r="J10" s="48"/>
+      <c r="K10" s="48"/>
+      <c r="L10" s="48"/>
+      <c r="M10" s="48"/>
       <c r="N10" s="31"/>
       <c r="O10" s="12"/>
-      <c r="P10" s="62" t="s">
-        <v>2</v>
-      </c>
-      <c r="Q10" s="62"/>
-      <c r="R10" s="62"/>
-      <c r="S10" s="62"/>
-      <c r="T10" s="62"/>
-      <c r="U10" s="62"/>
-      <c r="V10" s="62"/>
-      <c r="W10" s="62"/>
-      <c r="X10" s="61"/>
+      <c r="P10" s="49" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q10" s="49"/>
+      <c r="R10" s="49"/>
+      <c r="S10" s="49"/>
+      <c r="T10" s="49"/>
+      <c r="U10" s="49"/>
+      <c r="V10" s="49"/>
+      <c r="W10" s="49"/>
+      <c r="X10" s="42"/>
     </row>
     <row r="11" spans="1:25" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="A11" s="39" t="s">
-        <v>0</v>
-      </c>
-      <c r="B11" s="39"/>
-      <c r="C11" s="39"/>
-      <c r="D11" s="39"/>
-      <c r="E11" s="39"/>
-      <c r="F11" s="39"/>
-      <c r="G11" s="53"/>
-      <c r="H11" s="39" t="s">
+      <c r="A11" s="51" t="s">
+        <v>0</v>
+      </c>
+      <c r="B11" s="51"/>
+      <c r="C11" s="51"/>
+      <c r="D11" s="51"/>
+      <c r="E11" s="51"/>
+      <c r="F11" s="51"/>
+      <c r="G11" s="36"/>
+      <c r="H11" s="51" t="s">
         <v>62</v>
       </c>
-      <c r="I11" s="39"/>
-      <c r="J11" s="39"/>
-      <c r="K11" s="39"/>
-      <c r="L11" s="39"/>
-      <c r="M11" s="39"/>
-      <c r="N11" s="53"/>
-      <c r="P11" s="39" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="39"/>
-      <c r="R11" s="39"/>
-      <c r="S11" s="39"/>
-      <c r="T11" s="39"/>
-      <c r="U11" s="39"/>
-      <c r="V11" s="39"/>
-      <c r="W11" s="39"/>
+      <c r="I11" s="51"/>
+      <c r="J11" s="51"/>
+      <c r="K11" s="51"/>
+      <c r="L11" s="51"/>
+      <c r="M11" s="51"/>
+      <c r="N11" s="36"/>
+      <c r="P11" s="51" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="51"/>
+      <c r="R11" s="51"/>
+      <c r="S11" s="51"/>
+      <c r="T11" s="51"/>
+      <c r="U11" s="51"/>
+      <c r="V11" s="51"/>
+      <c r="W11" s="51"/>
     </row>
     <row r="12" spans="1:25" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A12" s="34" t="s">
+      <c r="A12" s="43" t="s">
         <v>61</v>
       </c>
-      <c r="B12" s="34"/>
-      <c r="C12" s="42" t="s">
-        <v>3</v>
-      </c>
-      <c r="D12" s="42"/>
-      <c r="E12" s="43" t="s">
-        <v>4</v>
-      </c>
-      <c r="F12" s="42"/>
-      <c r="G12" s="54"/>
-      <c r="H12" s="34" t="s">
+      <c r="B12" s="43"/>
+      <c r="C12" s="45" t="s">
+        <v>3</v>
+      </c>
+      <c r="D12" s="45"/>
+      <c r="E12" s="50" t="s">
+        <v>4</v>
+      </c>
+      <c r="F12" s="45"/>
+      <c r="G12" s="37"/>
+      <c r="H12" s="43" t="s">
         <v>61</v>
       </c>
-      <c r="I12" s="34"/>
-      <c r="J12" s="42" t="s">
-        <v>3</v>
-      </c>
-      <c r="K12" s="42"/>
-      <c r="L12" s="43" t="s">
-        <v>4</v>
-      </c>
-      <c r="M12" s="42"/>
-      <c r="N12" s="54"/>
+      <c r="I12" s="43"/>
+      <c r="J12" s="45" t="s">
+        <v>3</v>
+      </c>
+      <c r="K12" s="45"/>
+      <c r="L12" s="50" t="s">
+        <v>4</v>
+      </c>
+      <c r="M12" s="45"/>
+      <c r="N12" s="37"/>
       <c r="O12" s="4"/>
-      <c r="P12" s="34" t="s">
+      <c r="P12" s="43" t="s">
         <v>61</v>
       </c>
-      <c r="Q12" s="34"/>
-      <c r="R12" s="36" t="s">
-        <v>3</v>
-      </c>
-      <c r="S12" s="36"/>
-      <c r="T12" s="36"/>
-      <c r="U12" s="37" t="s">
-        <v>4</v>
-      </c>
-      <c r="V12" s="36"/>
-      <c r="W12" s="36"/>
+      <c r="Q12" s="43"/>
+      <c r="R12" s="58" t="s">
+        <v>3</v>
+      </c>
+      <c r="S12" s="58"/>
+      <c r="T12" s="58"/>
+      <c r="U12" s="59" t="s">
+        <v>4</v>
+      </c>
+      <c r="V12" s="58"/>
+      <c r="W12" s="58"/>
       <c r="X12" s="4"/>
       <c r="Y12" s="4"/>
     </row>
     <row r="13" spans="1:25" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A13" s="35"/>
-      <c r="B13" s="35"/>
-      <c r="C13" s="48" t="s">
+      <c r="A13" s="44"/>
+      <c r="B13" s="44"/>
+      <c r="C13" s="32" t="s">
         <v>5</v>
       </c>
       <c r="D13" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="E13" s="49" t="s">
+      <c r="E13" s="33" t="s">
         <v>5</v>
       </c>
       <c r="F13" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="G13" s="55"/>
-      <c r="H13" s="35"/>
-      <c r="I13" s="35"/>
-      <c r="J13" s="48" t="s">
+      <c r="G13" s="38"/>
+      <c r="H13" s="44"/>
+      <c r="I13" s="44"/>
+      <c r="J13" s="32" t="s">
         <v>5</v>
       </c>
       <c r="K13" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="L13" s="49" t="s">
+      <c r="L13" s="33" t="s">
         <v>5</v>
       </c>
       <c r="M13" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="N13" s="55"/>
+      <c r="N13" s="38"/>
       <c r="O13" s="5"/>
-      <c r="P13" s="35"/>
-      <c r="Q13" s="35"/>
+      <c r="P13" s="44"/>
+      <c r="Q13" s="44"/>
       <c r="R13" s="17" t="s">
         <v>7</v>
       </c>
@@ -1241,7 +1231,7 @@
       <c r="F14" s="20">
         <v>1</v>
       </c>
-      <c r="G14" s="56"/>
+      <c r="G14" s="20"/>
       <c r="H14" s="6">
         <v>1</v>
       </c>
@@ -1308,7 +1298,7 @@
       <c r="F15" s="20">
         <v>6</v>
       </c>
-      <c r="G15" s="56"/>
+      <c r="G15" s="20"/>
       <c r="H15" s="6">
         <v>2</v>
       </c>
@@ -1375,7 +1365,7 @@
       <c r="F16" s="20">
         <v>2</v>
       </c>
-      <c r="G16" s="56"/>
+      <c r="G16" s="20"/>
       <c r="H16" s="6">
         <v>3</v>
       </c>
@@ -1442,7 +1432,7 @@
       <c r="F17" s="20">
         <v>2</v>
       </c>
-      <c r="G17" s="56"/>
+      <c r="G17" s="20"/>
       <c r="H17" s="6">
         <v>4</v>
       </c>
@@ -1509,7 +1499,7 @@
       <c r="F18" s="20">
         <v>6</v>
       </c>
-      <c r="G18" s="56"/>
+      <c r="G18" s="20"/>
       <c r="H18" s="6">
         <v>5</v>
       </c>
@@ -1568,7 +1558,7 @@
       <c r="F19" s="21">
         <v>5</v>
       </c>
-      <c r="G19" s="56"/>
+      <c r="G19" s="20"/>
       <c r="H19" s="14">
         <v>6</v>
       </c>
@@ -1587,7 +1577,7 @@
       <c r="M19" s="21">
         <v>6</v>
       </c>
-      <c r="N19" s="56"/>
+      <c r="N19" s="20"/>
       <c r="O19" s="8"/>
       <c r="P19" s="6">
         <v>6</v>
@@ -1623,7 +1613,7 @@
       <c r="D20" s="8"/>
       <c r="E20" s="8"/>
       <c r="F20" s="8"/>
-      <c r="G20" s="60"/>
+      <c r="G20" s="8"/>
       <c r="H20" s="8"/>
       <c r="I20" s="8"/>
       <c r="J20" s="8"/>
@@ -1638,117 +1628,117 @@
       <c r="S20" s="4"/>
     </row>
     <row r="21" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="38" t="s">
+      <c r="A21" s="47" t="s">
         <v>16</v>
       </c>
-      <c r="B21" s="38"/>
-      <c r="C21" s="38"/>
-      <c r="D21" s="38"/>
-      <c r="E21" s="38"/>
-      <c r="F21" s="38"/>
-      <c r="G21" s="57"/>
-      <c r="H21" s="38" t="s">
+      <c r="B21" s="47"/>
+      <c r="C21" s="47"/>
+      <c r="D21" s="47"/>
+      <c r="E21" s="47"/>
+      <c r="F21" s="47"/>
+      <c r="G21" s="39"/>
+      <c r="H21" s="47" t="s">
         <v>77</v>
       </c>
-      <c r="I21" s="38"/>
-      <c r="J21" s="38"/>
-      <c r="K21" s="38"/>
-      <c r="L21" s="38"/>
-      <c r="M21" s="38"/>
-      <c r="N21" s="57"/>
+      <c r="I21" s="47"/>
+      <c r="J21" s="47"/>
+      <c r="K21" s="47"/>
+      <c r="L21" s="47"/>
+      <c r="M21" s="47"/>
+      <c r="N21" s="39"/>
       <c r="O21" s="19"/>
-      <c r="P21" s="33" t="s">
+      <c r="P21" s="60" t="s">
         <v>16</v>
       </c>
-      <c r="Q21" s="33"/>
-      <c r="R21" s="33"/>
-      <c r="S21" s="33"/>
-      <c r="T21" s="33"/>
-      <c r="U21" s="33"/>
-      <c r="V21" s="33"/>
-      <c r="W21" s="33"/>
+      <c r="Q21" s="60"/>
+      <c r="R21" s="60"/>
+      <c r="S21" s="60"/>
+      <c r="T21" s="60"/>
+      <c r="U21" s="60"/>
+      <c r="V21" s="60"/>
+      <c r="W21" s="60"/>
       <c r="X21" s="19"/>
       <c r="Y21" s="4"/>
     </row>
     <row r="22" spans="1:25" ht="21" x14ac:dyDescent="0.35">
-      <c r="A22" s="34" t="s">
+      <c r="A22" s="43" t="s">
         <v>61</v>
       </c>
-      <c r="B22" s="34"/>
-      <c r="C22" s="42" t="s">
-        <v>3</v>
-      </c>
-      <c r="D22" s="42"/>
-      <c r="E22" s="44" t="s">
-        <v>4</v>
-      </c>
-      <c r="F22" s="45"/>
-      <c r="G22" s="58"/>
-      <c r="H22" s="34" t="s">
+      <c r="B22" s="43"/>
+      <c r="C22" s="45" t="s">
+        <v>3</v>
+      </c>
+      <c r="D22" s="45"/>
+      <c r="E22" s="56" t="s">
+        <v>4</v>
+      </c>
+      <c r="F22" s="57"/>
+      <c r="G22" s="40"/>
+      <c r="H22" s="43" t="s">
         <v>61</v>
       </c>
-      <c r="I22" s="34"/>
-      <c r="J22" s="42" t="s">
-        <v>3</v>
-      </c>
-      <c r="K22" s="42"/>
-      <c r="L22" s="43" t="s">
-        <v>4</v>
-      </c>
-      <c r="M22" s="42"/>
-      <c r="N22" s="54"/>
+      <c r="I22" s="43"/>
+      <c r="J22" s="45" t="s">
+        <v>3</v>
+      </c>
+      <c r="K22" s="45"/>
+      <c r="L22" s="50" t="s">
+        <v>4</v>
+      </c>
+      <c r="M22" s="45"/>
+      <c r="N22" s="37"/>
       <c r="O22" s="8"/>
-      <c r="P22" s="34" t="s">
+      <c r="P22" s="43" t="s">
         <v>61</v>
       </c>
-      <c r="Q22" s="34"/>
-      <c r="R22" s="36" t="s">
-        <v>3</v>
-      </c>
-      <c r="S22" s="36"/>
-      <c r="T22" s="36"/>
-      <c r="U22" s="40" t="s">
-        <v>4</v>
-      </c>
-      <c r="V22" s="41"/>
-      <c r="W22" s="41"/>
+      <c r="Q22" s="43"/>
+      <c r="R22" s="58" t="s">
+        <v>3</v>
+      </c>
+      <c r="S22" s="58"/>
+      <c r="T22" s="58"/>
+      <c r="U22" s="61" t="s">
+        <v>4</v>
+      </c>
+      <c r="V22" s="62"/>
+      <c r="W22" s="62"/>
       <c r="X22" s="8"/>
       <c r="Y22" s="4"/>
     </row>
     <row r="23" spans="1:25" ht="21" x14ac:dyDescent="0.35">
-      <c r="A23" s="35"/>
-      <c r="B23" s="35"/>
-      <c r="C23" s="48" t="s">
+      <c r="A23" s="44"/>
+      <c r="B23" s="44"/>
+      <c r="C23" s="32" t="s">
         <v>5</v>
       </c>
       <c r="D23" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="E23" s="50" t="s">
+      <c r="E23" s="34" t="s">
         <v>5</v>
       </c>
       <c r="F23" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="G23" s="58"/>
-      <c r="H23" s="35"/>
-      <c r="I23" s="35"/>
-      <c r="J23" s="48" t="s">
+      <c r="G23" s="40"/>
+      <c r="H23" s="44"/>
+      <c r="I23" s="44"/>
+      <c r="J23" s="32" t="s">
         <v>5</v>
       </c>
       <c r="K23" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="L23" s="49" t="s">
+      <c r="L23" s="33" t="s">
         <v>5</v>
       </c>
       <c r="M23" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="N23" s="55"/>
+      <c r="N23" s="38"/>
       <c r="O23" s="8"/>
-      <c r="P23" s="35"/>
-      <c r="Q23" s="35"/>
+      <c r="P23" s="44"/>
+      <c r="Q23" s="44"/>
       <c r="R23" s="17" t="s">
         <v>7</v>
       </c>
@@ -2116,7 +2106,7 @@
       <c r="F29" s="21">
         <v>2</v>
       </c>
-      <c r="G29" s="56"/>
+      <c r="G29" s="20"/>
       <c r="H29" s="16">
         <v>6</v>
       </c>
@@ -2135,7 +2125,7 @@
       <c r="M29" s="21">
         <v>4</v>
       </c>
-      <c r="N29" s="56"/>
+      <c r="N29" s="20"/>
       <c r="O29" s="10"/>
       <c r="P29" s="16">
         <v>6</v>
@@ -2210,76 +2200,63 @@
       <c r="R31" s="4"/>
       <c r="S31" s="4"/>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A33" s="63"/>
-      <c r="B33" s="63"/>
-      <c r="C33" s="63"/>
-      <c r="D33" s="63"/>
-      <c r="E33" s="63"/>
-      <c r="F33" s="63"/>
-    </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A34" s="64"/>
-      <c r="B34" s="63"/>
-      <c r="C34" s="63"/>
-      <c r="D34" s="63"/>
-      <c r="E34" s="63"/>
-      <c r="F34" s="63"/>
+      <c r="A34" s="1"/>
       <c r="H34" s="1"/>
       <c r="I34" s="1" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="35" spans="1:14" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="A35" s="65"/>
-      <c r="B35" s="65"/>
-      <c r="C35" s="65"/>
-      <c r="D35" s="65"/>
-      <c r="E35" s="65"/>
-      <c r="F35" s="65"/>
-      <c r="G35" s="59"/>
-      <c r="H35" s="51" t="s">
+      <c r="A35" s="55"/>
+      <c r="B35" s="55"/>
+      <c r="C35" s="55"/>
+      <c r="D35" s="55"/>
+      <c r="E35" s="55"/>
+      <c r="F35" s="55"/>
+      <c r="G35" s="41"/>
+      <c r="H35" s="46" t="s">
         <v>62</v>
       </c>
-      <c r="I35" s="51"/>
-      <c r="J35" s="51"/>
-      <c r="K35" s="51"/>
-      <c r="L35" s="51"/>
-      <c r="M35" s="51"/>
-      <c r="N35" s="59"/>
+      <c r="I35" s="46"/>
+      <c r="J35" s="46"/>
+      <c r="K35" s="46"/>
+      <c r="L35" s="46"/>
+      <c r="M35" s="46"/>
+      <c r="N35" s="41"/>
     </row>
     <row r="36" spans="1:14" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A36" s="66"/>
-      <c r="B36" s="66"/>
-      <c r="C36" s="67"/>
-      <c r="D36" s="67"/>
-      <c r="E36" s="67"/>
-      <c r="F36" s="67"/>
-      <c r="G36" s="54"/>
-      <c r="H36" s="34" t="s">
+      <c r="A36" s="52"/>
+      <c r="B36" s="52"/>
+      <c r="C36" s="53"/>
+      <c r="D36" s="53"/>
+      <c r="E36" s="53"/>
+      <c r="F36" s="53"/>
+      <c r="G36" s="37"/>
+      <c r="H36" s="43" t="s">
         <v>61</v>
       </c>
-      <c r="I36" s="34"/>
-      <c r="J36" s="42" t="s">
-        <v>3</v>
-      </c>
-      <c r="K36" s="42"/>
-      <c r="L36" s="42" t="s">
-        <v>4</v>
-      </c>
-      <c r="M36" s="42"/>
-      <c r="N36" s="54"/>
+      <c r="I36" s="43"/>
+      <c r="J36" s="45" t="s">
+        <v>3</v>
+      </c>
+      <c r="K36" s="45"/>
+      <c r="L36" s="45" t="s">
+        <v>4</v>
+      </c>
+      <c r="M36" s="45"/>
+      <c r="N36" s="37"/>
     </row>
     <row r="37" spans="1:14" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A37" s="66"/>
-      <c r="B37" s="66"/>
-      <c r="C37" s="55"/>
-      <c r="D37" s="55"/>
-      <c r="E37" s="55"/>
-      <c r="F37" s="55"/>
-      <c r="G37" s="55"/>
-      <c r="H37" s="35"/>
-      <c r="I37" s="35"/>
+      <c r="A37" s="52"/>
+      <c r="B37" s="52"/>
+      <c r="C37" s="38"/>
+      <c r="D37" s="38"/>
+      <c r="E37" s="38"/>
+      <c r="F37" s="38"/>
+      <c r="G37" s="38"/>
+      <c r="H37" s="44"/>
+      <c r="I37" s="44"/>
       <c r="J37" s="13" t="s">
         <v>5</v>
       </c>
@@ -2292,15 +2269,15 @@
       <c r="M37" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="N37" s="55"/>
+      <c r="N37" s="38"/>
     </row>
     <row r="38" spans="1:14" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="A38" s="68"/>
-      <c r="B38" s="68"/>
-      <c r="C38" s="56"/>
-      <c r="D38" s="56"/>
-      <c r="E38" s="56"/>
-      <c r="F38" s="56"/>
+      <c r="A38" s="6"/>
+      <c r="B38" s="6"/>
+      <c r="C38" s="20"/>
+      <c r="D38" s="20"/>
+      <c r="E38" s="20"/>
+      <c r="F38" s="20"/>
       <c r="G38" s="20"/>
       <c r="H38" s="6">
         <v>1</v>
@@ -2323,12 +2300,12 @@
       <c r="N38" s="20"/>
     </row>
     <row r="39" spans="1:14" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="A39" s="68"/>
-      <c r="B39" s="68"/>
-      <c r="C39" s="56"/>
-      <c r="D39" s="56"/>
-      <c r="E39" s="56"/>
-      <c r="F39" s="56"/>
+      <c r="A39" s="6"/>
+      <c r="B39" s="6"/>
+      <c r="C39" s="20"/>
+      <c r="D39" s="20"/>
+      <c r="E39" s="20"/>
+      <c r="F39" s="20"/>
       <c r="G39" s="20"/>
       <c r="H39" s="6">
         <v>2</v>
@@ -2347,12 +2324,12 @@
       <c r="N39" s="20"/>
     </row>
     <row r="40" spans="1:14" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="A40" s="68"/>
-      <c r="B40" s="68"/>
-      <c r="C40" s="56"/>
-      <c r="D40" s="56"/>
-      <c r="E40" s="56"/>
-      <c r="F40" s="56"/>
+      <c r="A40" s="6"/>
+      <c r="B40" s="6"/>
+      <c r="C40" s="20"/>
+      <c r="D40" s="20"/>
+      <c r="E40" s="20"/>
+      <c r="F40" s="20"/>
       <c r="G40" s="20"/>
       <c r="H40" s="6">
         <v>3</v>
@@ -2375,12 +2352,12 @@
       <c r="N40" s="20"/>
     </row>
     <row r="41" spans="1:14" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="A41" s="68"/>
-      <c r="B41" s="68"/>
-      <c r="C41" s="56"/>
-      <c r="D41" s="56"/>
-      <c r="E41" s="56"/>
-      <c r="F41" s="56"/>
+      <c r="A41" s="6"/>
+      <c r="B41" s="6"/>
+      <c r="C41" s="20"/>
+      <c r="D41" s="20"/>
+      <c r="E41" s="20"/>
+      <c r="F41" s="20"/>
       <c r="G41" s="20"/>
       <c r="H41" s="6">
         <v>4</v>
@@ -2403,12 +2380,12 @@
       <c r="N41" s="20"/>
     </row>
     <row r="42" spans="1:14" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="A42" s="69"/>
-      <c r="B42" s="69"/>
-      <c r="C42" s="56"/>
-      <c r="D42" s="56"/>
-      <c r="E42" s="56"/>
-      <c r="F42" s="56"/>
+      <c r="A42" s="9"/>
+      <c r="B42" s="9"/>
+      <c r="C42" s="20"/>
+      <c r="D42" s="20"/>
+      <c r="E42" s="20"/>
+      <c r="F42" s="20"/>
       <c r="G42" s="20"/>
       <c r="H42" s="9">
         <v>5</v>
@@ -2423,13 +2400,13 @@
       <c r="N42" s="20"/>
     </row>
     <row r="43" spans="1:14" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="A43" s="68"/>
-      <c r="B43" s="68"/>
-      <c r="C43" s="56"/>
-      <c r="D43" s="56"/>
-      <c r="E43" s="56"/>
-      <c r="F43" s="56"/>
-      <c r="G43" s="56"/>
+      <c r="A43" s="6"/>
+      <c r="B43" s="6"/>
+      <c r="C43" s="20"/>
+      <c r="D43" s="20"/>
+      <c r="E43" s="20"/>
+      <c r="F43" s="20"/>
+      <c r="G43" s="20"/>
       <c r="H43" s="14">
         <v>6</v>
       </c>
@@ -2448,66 +2425,58 @@
       <c r="M43" s="21">
         <v>500</v>
       </c>
-      <c r="N43" s="56"/>
-    </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A44" s="63"/>
-      <c r="B44" s="63"/>
-      <c r="C44" s="63"/>
-      <c r="D44" s="63"/>
-      <c r="E44" s="63"/>
-      <c r="F44" s="63"/>
+      <c r="N43" s="20"/>
     </row>
     <row r="45" spans="1:14" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="A45" s="70"/>
-      <c r="B45" s="70"/>
-      <c r="C45" s="70"/>
-      <c r="D45" s="70"/>
-      <c r="E45" s="70"/>
-      <c r="F45" s="70"/>
-      <c r="G45" s="57"/>
-      <c r="H45" s="38" t="s">
+      <c r="A45" s="54"/>
+      <c r="B45" s="54"/>
+      <c r="C45" s="54"/>
+      <c r="D45" s="54"/>
+      <c r="E45" s="54"/>
+      <c r="F45" s="54"/>
+      <c r="G45" s="39"/>
+      <c r="H45" s="47" t="s">
         <v>77</v>
       </c>
-      <c r="I45" s="38"/>
-      <c r="J45" s="38"/>
-      <c r="K45" s="38"/>
-      <c r="L45" s="38"/>
-      <c r="M45" s="38"/>
-      <c r="N45" s="57"/>
+      <c r="I45" s="47"/>
+      <c r="J45" s="47"/>
+      <c r="K45" s="47"/>
+      <c r="L45" s="47"/>
+      <c r="M45" s="47"/>
+      <c r="N45" s="39"/>
     </row>
     <row r="46" spans="1:14" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A46" s="66"/>
-      <c r="B46" s="66"/>
-      <c r="C46" s="67"/>
-      <c r="D46" s="67"/>
-      <c r="E46" s="67"/>
-      <c r="F46" s="67"/>
-      <c r="G46" s="54"/>
-      <c r="H46" s="34" t="s">
+      <c r="A46" s="52"/>
+      <c r="B46" s="52"/>
+      <c r="C46" s="53"/>
+      <c r="D46" s="53"/>
+      <c r="E46" s="53"/>
+      <c r="F46" s="53"/>
+      <c r="G46" s="37"/>
+      <c r="H46" s="43" t="s">
         <v>61</v>
       </c>
-      <c r="I46" s="34"/>
-      <c r="J46" s="42" t="s">
-        <v>3</v>
-      </c>
-      <c r="K46" s="42"/>
-      <c r="L46" s="42" t="s">
-        <v>4</v>
-      </c>
-      <c r="M46" s="42"/>
-      <c r="N46" s="54"/>
+      <c r="I46" s="43"/>
+      <c r="J46" s="45" t="s">
+        <v>3</v>
+      </c>
+      <c r="K46" s="45"/>
+      <c r="L46" s="45" t="s">
+        <v>4</v>
+      </c>
+      <c r="M46" s="45"/>
+      <c r="N46" s="37"/>
     </row>
     <row r="47" spans="1:14" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A47" s="66"/>
-      <c r="B47" s="66"/>
-      <c r="C47" s="55"/>
-      <c r="D47" s="55"/>
-      <c r="E47" s="55"/>
-      <c r="F47" s="55"/>
-      <c r="G47" s="55"/>
-      <c r="H47" s="35"/>
-      <c r="I47" s="35"/>
+      <c r="A47" s="52"/>
+      <c r="B47" s="52"/>
+      <c r="C47" s="38"/>
+      <c r="D47" s="38"/>
+      <c r="E47" s="38"/>
+      <c r="F47" s="38"/>
+      <c r="G47" s="38"/>
+      <c r="H47" s="44"/>
+      <c r="I47" s="44"/>
       <c r="J47" s="13" t="s">
         <v>5</v>
       </c>
@@ -2520,15 +2489,15 @@
       <c r="M47" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="N47" s="55"/>
+      <c r="N47" s="38"/>
     </row>
     <row r="48" spans="1:14" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="A48" s="68"/>
-      <c r="B48" s="68"/>
-      <c r="C48" s="56"/>
-      <c r="D48" s="56"/>
-      <c r="E48" s="56"/>
-      <c r="F48" s="56"/>
+      <c r="A48" s="6"/>
+      <c r="B48" s="6"/>
+      <c r="C48" s="20"/>
+      <c r="D48" s="20"/>
+      <c r="E48" s="20"/>
+      <c r="F48" s="20"/>
       <c r="G48" s="20"/>
       <c r="H48" s="6">
         <v>1</v>
@@ -2551,12 +2520,12 @@
       <c r="N48" s="20"/>
     </row>
     <row r="49" spans="1:14" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="A49" s="68"/>
-      <c r="B49" s="68"/>
-      <c r="C49" s="56"/>
-      <c r="D49" s="56"/>
-      <c r="E49" s="56"/>
-      <c r="F49" s="56"/>
+      <c r="A49" s="6"/>
+      <c r="B49" s="6"/>
+      <c r="C49" s="20"/>
+      <c r="D49" s="20"/>
+      <c r="E49" s="20"/>
+      <c r="F49" s="20"/>
       <c r="G49" s="20"/>
       <c r="H49" s="6">
         <v>2</v>
@@ -2575,12 +2544,12 @@
       <c r="N49" s="20"/>
     </row>
     <row r="50" spans="1:14" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="A50" s="68"/>
-      <c r="B50" s="68"/>
-      <c r="C50" s="56"/>
-      <c r="D50" s="56"/>
-      <c r="E50" s="56"/>
-      <c r="F50" s="56"/>
+      <c r="A50" s="6"/>
+      <c r="B50" s="6"/>
+      <c r="C50" s="20"/>
+      <c r="D50" s="20"/>
+      <c r="E50" s="20"/>
+      <c r="F50" s="20"/>
       <c r="G50" s="20"/>
       <c r="H50" s="6">
         <v>3</v>
@@ -2603,12 +2572,12 @@
       <c r="N50" s="20"/>
     </row>
     <row r="51" spans="1:14" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="A51" s="68"/>
-      <c r="B51" s="68"/>
-      <c r="C51" s="56"/>
-      <c r="D51" s="56"/>
-      <c r="E51" s="56"/>
-      <c r="F51" s="56"/>
+      <c r="A51" s="6"/>
+      <c r="B51" s="6"/>
+      <c r="C51" s="20"/>
+      <c r="D51" s="20"/>
+      <c r="E51" s="20"/>
+      <c r="F51" s="20"/>
       <c r="G51" s="20"/>
       <c r="H51" s="6">
         <v>4</v>
@@ -2631,12 +2600,12 @@
       <c r="N51" s="20"/>
     </row>
     <row r="52" spans="1:14" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="A52" s="69"/>
-      <c r="B52" s="69"/>
-      <c r="C52" s="56"/>
-      <c r="D52" s="56"/>
-      <c r="E52" s="56"/>
-      <c r="F52" s="56"/>
+      <c r="A52" s="9"/>
+      <c r="B52" s="9"/>
+      <c r="C52" s="20"/>
+      <c r="D52" s="20"/>
+      <c r="E52" s="20"/>
+      <c r="F52" s="20"/>
       <c r="G52" s="20"/>
       <c r="H52" s="9">
         <v>5</v>
@@ -2651,13 +2620,13 @@
       <c r="N52" s="20"/>
     </row>
     <row r="53" spans="1:14" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="A53" s="68"/>
-      <c r="B53" s="68"/>
-      <c r="C53" s="56"/>
-      <c r="D53" s="56"/>
-      <c r="E53" s="56"/>
-      <c r="F53" s="56"/>
-      <c r="G53" s="56"/>
+      <c r="A53" s="6"/>
+      <c r="B53" s="6"/>
+      <c r="C53" s="20"/>
+      <c r="D53" s="20"/>
+      <c r="E53" s="20"/>
+      <c r="F53" s="20"/>
+      <c r="G53" s="20"/>
       <c r="H53" s="14">
         <v>6</v>
       </c>
@@ -2676,34 +2645,35 @@
       <c r="M53" s="21">
         <v>500</v>
       </c>
-      <c r="N53" s="56"/>
-    </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A54" s="63"/>
-      <c r="B54" s="63"/>
-      <c r="C54" s="63"/>
-      <c r="D54" s="63"/>
-      <c r="E54" s="63"/>
-      <c r="F54" s="63"/>
-    </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A55" s="63"/>
-      <c r="B55" s="63"/>
-      <c r="C55" s="63"/>
-      <c r="D55" s="63"/>
-      <c r="E55" s="63"/>
-      <c r="F55" s="63"/>
+      <c r="N53" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="43">
-    <mergeCell ref="H46:I47"/>
-    <mergeCell ref="J46:K46"/>
-    <mergeCell ref="L46:M46"/>
-    <mergeCell ref="H35:M35"/>
-    <mergeCell ref="H36:I37"/>
-    <mergeCell ref="J36:K36"/>
-    <mergeCell ref="L36:M36"/>
-    <mergeCell ref="H45:M45"/>
+    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="P21:W21"/>
+    <mergeCell ref="A12:B13"/>
+    <mergeCell ref="P12:Q13"/>
+    <mergeCell ref="A21:F21"/>
+    <mergeCell ref="A11:F11"/>
+    <mergeCell ref="P11:W11"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="A35:F35"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="R12:T12"/>
+    <mergeCell ref="U12:W12"/>
+    <mergeCell ref="A22:B23"/>
+    <mergeCell ref="P22:Q23"/>
+    <mergeCell ref="R22:T22"/>
+    <mergeCell ref="U22:W22"/>
+    <mergeCell ref="A36:B37"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="E36:F36"/>
+    <mergeCell ref="A45:F45"/>
+    <mergeCell ref="A46:B47"/>
+    <mergeCell ref="C46:D46"/>
+    <mergeCell ref="E46:F46"/>
     <mergeCell ref="H10:M10"/>
     <mergeCell ref="P10:W10"/>
     <mergeCell ref="H21:M21"/>
@@ -2714,31 +2684,14 @@
     <mergeCell ref="H12:I13"/>
     <mergeCell ref="J12:K12"/>
     <mergeCell ref="L12:M12"/>
-    <mergeCell ref="A36:B37"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="E36:F36"/>
-    <mergeCell ref="A45:F45"/>
-    <mergeCell ref="A46:B47"/>
-    <mergeCell ref="C46:D46"/>
-    <mergeCell ref="E46:F46"/>
-    <mergeCell ref="A35:F35"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="R12:T12"/>
-    <mergeCell ref="U12:W12"/>
-    <mergeCell ref="A22:B23"/>
-    <mergeCell ref="P22:Q23"/>
-    <mergeCell ref="A10:F10"/>
-    <mergeCell ref="P21:W21"/>
-    <mergeCell ref="A12:B13"/>
-    <mergeCell ref="P12:Q13"/>
-    <mergeCell ref="A21:F21"/>
-    <mergeCell ref="A11:F11"/>
-    <mergeCell ref="P11:W11"/>
-    <mergeCell ref="R22:T22"/>
-    <mergeCell ref="U22:W22"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="H46:I47"/>
+    <mergeCell ref="J46:K46"/>
+    <mergeCell ref="L46:M46"/>
+    <mergeCell ref="H35:M35"/>
+    <mergeCell ref="H36:I37"/>
+    <mergeCell ref="J36:K36"/>
+    <mergeCell ref="L36:M36"/>
+    <mergeCell ref="H45:M45"/>
   </mergeCells>
   <conditionalFormatting sqref="C14:D19">
     <cfRule type="colorScale" priority="27">
@@ -2780,6 +2733,46 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="J14:K19">
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="7"/>
+        <color theme="9"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J24:K29">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="7"/>
+        <color theme="9"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L14:N19">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="7"/>
+        <color theme="9"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L24:N29">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="7"/>
+        <color theme="9"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="R14:T19">
     <cfRule type="colorScale" priority="23">
       <colorScale>
@@ -2802,46 +2795,6 @@
   </conditionalFormatting>
   <conditionalFormatting sqref="U14:W19">
     <cfRule type="colorScale" priority="21">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="7"/>
-        <color theme="9"/>
-        <color rgb="FFFF0000"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J14:K19">
-    <cfRule type="colorScale" priority="4">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="7"/>
-        <color theme="9"/>
-        <color rgb="FFFF0000"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L14:N19">
-    <cfRule type="colorScale" priority="3">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="7"/>
-        <color theme="9"/>
-        <color rgb="FFFF0000"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J24:K29">
-    <cfRule type="colorScale" priority="2">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="7"/>
-        <color theme="9"/>
-        <color rgb="FFFF0000"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L24:N29">
-    <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="7"/>
@@ -2880,7 +2833,7 @@
       <c r="A1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="35" t="s">
         <v>79</v>
       </c>
     </row>
@@ -2929,96 +2882,96 @@
       </c>
     </row>
     <row r="10" spans="1:17" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="32" t="s">
+      <c r="A10" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="B10" s="32"/>
-      <c r="C10" s="32"/>
-      <c r="D10" s="32"/>
-      <c r="E10" s="32"/>
-      <c r="F10" s="32"/>
+      <c r="B10" s="48"/>
+      <c r="C10" s="48"/>
+      <c r="D10" s="48"/>
+      <c r="E10" s="48"/>
+      <c r="F10" s="48"/>
       <c r="G10" s="12"/>
       <c r="H10" s="12"/>
-      <c r="I10" s="32" t="s">
-        <v>2</v>
-      </c>
-      <c r="J10" s="32"/>
-      <c r="K10" s="32"/>
-      <c r="L10" s="32"/>
-      <c r="M10" s="32"/>
-      <c r="N10" s="32"/>
-      <c r="O10" s="32"/>
-      <c r="P10" s="32"/>
+      <c r="I10" s="48" t="s">
+        <v>2</v>
+      </c>
+      <c r="J10" s="48"/>
+      <c r="K10" s="48"/>
+      <c r="L10" s="48"/>
+      <c r="M10" s="48"/>
+      <c r="N10" s="48"/>
+      <c r="O10" s="48"/>
+      <c r="P10" s="48"/>
     </row>
     <row r="11" spans="1:17" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="A11" s="39" t="s">
-        <v>0</v>
-      </c>
-      <c r="B11" s="39"/>
-      <c r="C11" s="39"/>
-      <c r="D11" s="39"/>
-      <c r="E11" s="39"/>
-      <c r="F11" s="39"/>
-      <c r="H11" s="39" t="s">
-        <v>0</v>
-      </c>
-      <c r="I11" s="39"/>
-      <c r="J11" s="39"/>
-      <c r="K11" s="39"/>
-      <c r="L11" s="39"/>
-      <c r="M11" s="39"/>
-      <c r="N11" s="39"/>
-      <c r="O11" s="39"/>
+      <c r="A11" s="51" t="s">
+        <v>0</v>
+      </c>
+      <c r="B11" s="51"/>
+      <c r="C11" s="51"/>
+      <c r="D11" s="51"/>
+      <c r="E11" s="51"/>
+      <c r="F11" s="51"/>
+      <c r="H11" s="51" t="s">
+        <v>0</v>
+      </c>
+      <c r="I11" s="51"/>
+      <c r="J11" s="51"/>
+      <c r="K11" s="51"/>
+      <c r="L11" s="51"/>
+      <c r="M11" s="51"/>
+      <c r="N11" s="51"/>
+      <c r="O11" s="51"/>
     </row>
     <row r="12" spans="1:17" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A12" s="34" t="s">
+      <c r="A12" s="43" t="s">
         <v>61</v>
       </c>
-      <c r="B12" s="34"/>
-      <c r="C12" s="42" t="s">
-        <v>3</v>
-      </c>
-      <c r="D12" s="42"/>
-      <c r="E12" s="43" t="s">
-        <v>4</v>
-      </c>
-      <c r="F12" s="42"/>
+      <c r="B12" s="43"/>
+      <c r="C12" s="45" t="s">
+        <v>3</v>
+      </c>
+      <c r="D12" s="45"/>
+      <c r="E12" s="50" t="s">
+        <v>4</v>
+      </c>
+      <c r="F12" s="45"/>
       <c r="G12" s="4"/>
-      <c r="H12" s="34" t="s">
+      <c r="H12" s="43" t="s">
         <v>61</v>
       </c>
-      <c r="I12" s="34"/>
-      <c r="J12" s="36" t="s">
-        <v>3</v>
-      </c>
-      <c r="K12" s="36"/>
-      <c r="L12" s="36"/>
-      <c r="M12" s="37" t="s">
-        <v>4</v>
-      </c>
-      <c r="N12" s="36"/>
-      <c r="O12" s="36"/>
+      <c r="I12" s="43"/>
+      <c r="J12" s="58" t="s">
+        <v>3</v>
+      </c>
+      <c r="K12" s="58"/>
+      <c r="L12" s="58"/>
+      <c r="M12" s="59" t="s">
+        <v>4</v>
+      </c>
+      <c r="N12" s="58"/>
+      <c r="O12" s="58"/>
       <c r="P12" s="4"/>
       <c r="Q12" s="4"/>
     </row>
     <row r="13" spans="1:17" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A13" s="35"/>
-      <c r="B13" s="35"/>
-      <c r="C13" s="48" t="s">
+      <c r="A13" s="44"/>
+      <c r="B13" s="44"/>
+      <c r="C13" s="32" t="s">
         <v>5</v>
       </c>
       <c r="D13" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="E13" s="49" t="s">
+      <c r="E13" s="33" t="s">
         <v>5</v>
       </c>
       <c r="F13" s="13" t="s">
         <v>6</v>
       </c>
       <c r="G13" s="5"/>
-      <c r="H13" s="35"/>
-      <c r="I13" s="35"/>
+      <c r="H13" s="44"/>
+      <c r="I13" s="44"/>
       <c r="J13" s="17" t="s">
         <v>7</v>
       </c>
@@ -3342,77 +3295,77 @@
       <c r="Q20" s="4"/>
     </row>
     <row r="21" spans="1:17" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="38" t="s">
+      <c r="A21" s="47" t="s">
         <v>16</v>
       </c>
-      <c r="B21" s="38"/>
-      <c r="C21" s="38"/>
-      <c r="D21" s="38"/>
-      <c r="E21" s="38"/>
-      <c r="F21" s="38"/>
+      <c r="B21" s="47"/>
+      <c r="C21" s="47"/>
+      <c r="D21" s="47"/>
+      <c r="E21" s="47"/>
+      <c r="F21" s="47"/>
       <c r="G21" s="19"/>
-      <c r="H21" s="33" t="s">
+      <c r="H21" s="60" t="s">
         <v>16</v>
       </c>
-      <c r="I21" s="33"/>
-      <c r="J21" s="33"/>
-      <c r="K21" s="33"/>
-      <c r="L21" s="33"/>
-      <c r="M21" s="33"/>
-      <c r="N21" s="33"/>
-      <c r="O21" s="33"/>
+      <c r="I21" s="60"/>
+      <c r="J21" s="60"/>
+      <c r="K21" s="60"/>
+      <c r="L21" s="60"/>
+      <c r="M21" s="60"/>
+      <c r="N21" s="60"/>
+      <c r="O21" s="60"/>
       <c r="P21" s="19"/>
       <c r="Q21" s="4"/>
     </row>
     <row r="22" spans="1:17" ht="21" x14ac:dyDescent="0.35">
-      <c r="A22" s="34" t="s">
+      <c r="A22" s="43" t="s">
         <v>61</v>
       </c>
-      <c r="B22" s="34"/>
-      <c r="C22" s="42" t="s">
-        <v>3</v>
-      </c>
-      <c r="D22" s="42"/>
-      <c r="E22" s="44" t="s">
-        <v>4</v>
-      </c>
-      <c r="F22" s="45"/>
+      <c r="B22" s="43"/>
+      <c r="C22" s="45" t="s">
+        <v>3</v>
+      </c>
+      <c r="D22" s="45"/>
+      <c r="E22" s="56" t="s">
+        <v>4</v>
+      </c>
+      <c r="F22" s="57"/>
       <c r="G22" s="8"/>
-      <c r="H22" s="34" t="s">
+      <c r="H22" s="43" t="s">
         <v>61</v>
       </c>
-      <c r="I22" s="34"/>
-      <c r="J22" s="36" t="s">
-        <v>3</v>
-      </c>
-      <c r="K22" s="36"/>
-      <c r="L22" s="36"/>
-      <c r="M22" s="40" t="s">
-        <v>4</v>
-      </c>
-      <c r="N22" s="41"/>
-      <c r="O22" s="41"/>
+      <c r="I22" s="43"/>
+      <c r="J22" s="58" t="s">
+        <v>3</v>
+      </c>
+      <c r="K22" s="58"/>
+      <c r="L22" s="58"/>
+      <c r="M22" s="61" t="s">
+        <v>4</v>
+      </c>
+      <c r="N22" s="62"/>
+      <c r="O22" s="62"/>
       <c r="P22" s="8"/>
       <c r="Q22" s="4"/>
     </row>
     <row r="23" spans="1:17" ht="21" x14ac:dyDescent="0.35">
-      <c r="A23" s="35"/>
-      <c r="B23" s="35"/>
-      <c r="C23" s="48" t="s">
+      <c r="A23" s="44"/>
+      <c r="B23" s="44"/>
+      <c r="C23" s="32" t="s">
         <v>5</v>
       </c>
       <c r="D23" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="E23" s="50" t="s">
+      <c r="E23" s="34" t="s">
         <v>5</v>
       </c>
       <c r="F23" s="22" t="s">
         <v>6</v>
       </c>
       <c r="G23" s="8"/>
-      <c r="H23" s="35"/>
-      <c r="I23" s="35"/>
+      <c r="H23" s="44"/>
+      <c r="I23" s="44"/>
       <c r="J23" s="17" t="s">
         <v>7</v>
       </c>
@@ -3755,59 +3708,59 @@
       <c r="Q31" s="4"/>
     </row>
     <row r="32" spans="1:17" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="A32" s="51" t="s">
+      <c r="A32" s="46" t="s">
         <v>62</v>
       </c>
-      <c r="B32" s="51"/>
-      <c r="C32" s="51"/>
-      <c r="D32" s="51"/>
-      <c r="E32" s="51"/>
-      <c r="F32" s="51"/>
+      <c r="B32" s="46"/>
+      <c r="C32" s="46"/>
+      <c r="D32" s="46"/>
+      <c r="E32" s="46"/>
+      <c r="F32" s="46"/>
       <c r="G32" s="4"/>
-      <c r="H32" s="33" t="s">
+      <c r="H32" s="60" t="s">
         <v>73</v>
       </c>
-      <c r="I32" s="33"/>
-      <c r="J32" s="33"/>
-      <c r="K32" s="33"/>
-      <c r="L32" s="33"/>
-      <c r="M32" s="33"/>
-      <c r="N32" s="33"/>
-      <c r="O32" s="33"/>
+      <c r="I32" s="60"/>
+      <c r="J32" s="60"/>
+      <c r="K32" s="60"/>
+      <c r="L32" s="60"/>
+      <c r="M32" s="60"/>
+      <c r="N32" s="60"/>
+      <c r="O32" s="60"/>
       <c r="P32" s="4"/>
       <c r="Q32" s="4"/>
     </row>
     <row r="33" spans="1:15" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A33" s="34" t="s">
+      <c r="A33" s="43" t="s">
         <v>61</v>
       </c>
-      <c r="B33" s="34"/>
-      <c r="C33" s="42" t="s">
-        <v>3</v>
-      </c>
-      <c r="D33" s="42"/>
-      <c r="E33" s="42" t="s">
-        <v>4</v>
-      </c>
-      <c r="F33" s="42"/>
-      <c r="H33" s="34" t="s">
+      <c r="B33" s="43"/>
+      <c r="C33" s="45" t="s">
+        <v>3</v>
+      </c>
+      <c r="D33" s="45"/>
+      <c r="E33" s="45" t="s">
+        <v>4</v>
+      </c>
+      <c r="F33" s="45"/>
+      <c r="H33" s="43" t="s">
         <v>61</v>
       </c>
-      <c r="I33" s="34"/>
-      <c r="J33" s="36" t="s">
-        <v>3</v>
-      </c>
-      <c r="K33" s="36"/>
-      <c r="L33" s="36"/>
-      <c r="M33" s="37" t="s">
-        <v>4</v>
-      </c>
-      <c r="N33" s="36"/>
-      <c r="O33" s="36"/>
+      <c r="I33" s="43"/>
+      <c r="J33" s="58" t="s">
+        <v>3</v>
+      </c>
+      <c r="K33" s="58"/>
+      <c r="L33" s="58"/>
+      <c r="M33" s="59" t="s">
+        <v>4</v>
+      </c>
+      <c r="N33" s="58"/>
+      <c r="O33" s="58"/>
     </row>
     <row r="34" spans="1:15" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A34" s="35"/>
-      <c r="B34" s="35"/>
+      <c r="A34" s="44"/>
+      <c r="B34" s="44"/>
       <c r="C34" s="13" t="s">
         <v>5</v>
       </c>
@@ -3820,8 +3773,8 @@
       <c r="F34" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="H34" s="35"/>
-      <c r="I34" s="35"/>
+      <c r="H34" s="44"/>
+      <c r="I34" s="44"/>
       <c r="J34" s="17" t="s">
         <v>7</v>
       </c>
@@ -3986,32 +3939,32 @@
       <c r="O40" s="21"/>
     </row>
     <row r="42" spans="1:15" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="A42" s="38" t="s">
+      <c r="A42" s="47" t="s">
         <v>77</v>
       </c>
-      <c r="B42" s="38"/>
-      <c r="C42" s="38"/>
-      <c r="D42" s="38"/>
-      <c r="E42" s="38"/>
-      <c r="F42" s="38"/>
+      <c r="B42" s="47"/>
+      <c r="C42" s="47"/>
+      <c r="D42" s="47"/>
+      <c r="E42" s="47"/>
+      <c r="F42" s="47"/>
     </row>
     <row r="43" spans="1:15" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A43" s="34" t="s">
+      <c r="A43" s="43" t="s">
         <v>61</v>
       </c>
-      <c r="B43" s="34"/>
-      <c r="C43" s="42" t="s">
-        <v>3</v>
-      </c>
-      <c r="D43" s="42"/>
-      <c r="E43" s="42" t="s">
-        <v>4</v>
-      </c>
-      <c r="F43" s="42"/>
+      <c r="B43" s="43"/>
+      <c r="C43" s="45" t="s">
+        <v>3</v>
+      </c>
+      <c r="D43" s="45"/>
+      <c r="E43" s="45" t="s">
+        <v>4</v>
+      </c>
+      <c r="F43" s="45"/>
     </row>
     <row r="44" spans="1:15" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A44" s="35"/>
-      <c r="B44" s="35"/>
+      <c r="A44" s="44"/>
+      <c r="B44" s="44"/>
       <c r="C44" s="13" t="s">
         <v>5</v>
       </c>
@@ -4103,32 +4056,32 @@
       </c>
     </row>
     <row r="54" spans="1:6" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="A54" s="51" t="s">
+      <c r="A54" s="46" t="s">
         <v>62</v>
       </c>
-      <c r="B54" s="51"/>
-      <c r="C54" s="51"/>
-      <c r="D54" s="51"/>
-      <c r="E54" s="51"/>
-      <c r="F54" s="51"/>
+      <c r="B54" s="46"/>
+      <c r="C54" s="46"/>
+      <c r="D54" s="46"/>
+      <c r="E54" s="46"/>
+      <c r="F54" s="46"/>
     </row>
     <row r="55" spans="1:6" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A55" s="34" t="s">
+      <c r="A55" s="43" t="s">
         <v>61</v>
       </c>
-      <c r="B55" s="34"/>
-      <c r="C55" s="42" t="s">
-        <v>3</v>
-      </c>
-      <c r="D55" s="42"/>
-      <c r="E55" s="42" t="s">
-        <v>4</v>
-      </c>
-      <c r="F55" s="42"/>
+      <c r="B55" s="43"/>
+      <c r="C55" s="45" t="s">
+        <v>3</v>
+      </c>
+      <c r="D55" s="45"/>
+      <c r="E55" s="45" t="s">
+        <v>4</v>
+      </c>
+      <c r="F55" s="45"/>
     </row>
     <row r="56" spans="1:6" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A56" s="35"/>
-      <c r="B56" s="35"/>
+      <c r="A56" s="44"/>
+      <c r="B56" s="44"/>
       <c r="C56" s="13" t="s">
         <v>5</v>
       </c>
@@ -4251,32 +4204,32 @@
       </c>
     </row>
     <row r="64" spans="1:6" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="A64" s="38" t="s">
+      <c r="A64" s="47" t="s">
         <v>77</v>
       </c>
-      <c r="B64" s="38"/>
-      <c r="C64" s="38"/>
-      <c r="D64" s="38"/>
-      <c r="E64" s="38"/>
-      <c r="F64" s="38"/>
+      <c r="B64" s="47"/>
+      <c r="C64" s="47"/>
+      <c r="D64" s="47"/>
+      <c r="E64" s="47"/>
+      <c r="F64" s="47"/>
     </row>
     <row r="65" spans="1:6" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A65" s="34" t="s">
+      <c r="A65" s="43" t="s">
         <v>61</v>
       </c>
-      <c r="B65" s="34"/>
-      <c r="C65" s="42" t="s">
-        <v>3</v>
-      </c>
-      <c r="D65" s="42"/>
-      <c r="E65" s="42" t="s">
-        <v>4</v>
-      </c>
-      <c r="F65" s="42"/>
+      <c r="B65" s="43"/>
+      <c r="C65" s="45" t="s">
+        <v>3</v>
+      </c>
+      <c r="D65" s="45"/>
+      <c r="E65" s="45" t="s">
+        <v>4</v>
+      </c>
+      <c r="F65" s="45"/>
     </row>
     <row r="66" spans="1:6" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A66" s="35"/>
-      <c r="B66" s="35"/>
+      <c r="A66" s="44"/>
+      <c r="B66" s="44"/>
       <c r="C66" s="13" t="s">
         <v>5</v>
       </c>
@@ -4400,6 +4353,32 @@
     </row>
   </sheetData>
   <mergeCells count="38">
+    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="I10:P10"/>
+    <mergeCell ref="A11:F11"/>
+    <mergeCell ref="H11:O11"/>
+    <mergeCell ref="A12:B13"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="H12:I13"/>
+    <mergeCell ref="J12:L12"/>
+    <mergeCell ref="M12:O12"/>
+    <mergeCell ref="A21:F21"/>
+    <mergeCell ref="H21:O21"/>
+    <mergeCell ref="A22:B23"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="H22:I23"/>
+    <mergeCell ref="J22:L22"/>
+    <mergeCell ref="M22:O22"/>
+    <mergeCell ref="A32:F32"/>
+    <mergeCell ref="H32:O32"/>
+    <mergeCell ref="A33:B34"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="E33:F33"/>
+    <mergeCell ref="H33:I34"/>
+    <mergeCell ref="J33:L33"/>
+    <mergeCell ref="M33:O33"/>
     <mergeCell ref="A64:F64"/>
     <mergeCell ref="A65:B66"/>
     <mergeCell ref="C65:D65"/>
@@ -4412,35 +4391,19 @@
     <mergeCell ref="A55:B56"/>
     <mergeCell ref="C55:D55"/>
     <mergeCell ref="E55:F55"/>
-    <mergeCell ref="A32:F32"/>
-    <mergeCell ref="H32:O32"/>
-    <mergeCell ref="A33:B34"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="E33:F33"/>
-    <mergeCell ref="H33:I34"/>
-    <mergeCell ref="J33:L33"/>
-    <mergeCell ref="M33:O33"/>
-    <mergeCell ref="A21:F21"/>
-    <mergeCell ref="H21:O21"/>
-    <mergeCell ref="A22:B23"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="H22:I23"/>
-    <mergeCell ref="J22:L22"/>
-    <mergeCell ref="M22:O22"/>
-    <mergeCell ref="A10:F10"/>
-    <mergeCell ref="I10:P10"/>
-    <mergeCell ref="A11:F11"/>
-    <mergeCell ref="H11:O11"/>
-    <mergeCell ref="A12:B13"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="E12:F12"/>
-    <mergeCell ref="H12:I13"/>
-    <mergeCell ref="J12:L12"/>
-    <mergeCell ref="M12:O12"/>
   </mergeCells>
-  <conditionalFormatting sqref="J35:O40">
-    <cfRule type="colorScale" priority="20">
+  <conditionalFormatting sqref="C14:D19">
+    <cfRule type="colorScale" priority="9">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="7"/>
+        <color theme="9"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C24:D29">
+    <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="7"/>
@@ -4459,8 +4422,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E35:F40">
-    <cfRule type="colorScale" priority="12">
+  <conditionalFormatting sqref="C45:D50">
+    <cfRule type="colorScale" priority="11">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="7"/>
@@ -4469,8 +4432,28 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C45:D50">
-    <cfRule type="colorScale" priority="11">
+  <conditionalFormatting sqref="E14:F19">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="7"/>
+        <color theme="9"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E24:F29">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="7"/>
+        <color theme="9"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E35:F40">
+    <cfRule type="colorScale" priority="12">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="7"/>
@@ -4489,26 +4472,6 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C14:D19">
-    <cfRule type="colorScale" priority="9">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="7"/>
-        <color theme="9"/>
-        <color rgb="FFFF0000"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E14:F19">
-    <cfRule type="colorScale" priority="8">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="7"/>
-        <color theme="9"/>
-        <color rgb="FFFF0000"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="J14:O19">
     <cfRule type="colorScale" priority="7">
       <colorScale>
@@ -4519,8 +4482,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C24:D29">
-    <cfRule type="colorScale" priority="3">
+  <conditionalFormatting sqref="J24:O29">
+    <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="7"/>
@@ -4529,18 +4492,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E24:F29">
-    <cfRule type="colorScale" priority="2">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="7"/>
-        <color theme="9"/>
-        <color rgb="FFFF0000"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J24:O29">
-    <cfRule type="colorScale" priority="1">
+  <conditionalFormatting sqref="J35:O40">
+    <cfRule type="colorScale" priority="20">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="7"/>
@@ -4579,7 +4532,7 @@
       <c r="A1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="J1" s="52" t="s">
+      <c r="J1" s="35" t="s">
         <v>80</v>
       </c>
     </row>
@@ -4620,81 +4573,81 @@
       </c>
     </row>
     <row r="10" spans="1:17" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="32" t="s">
+      <c r="A10" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="B10" s="32"/>
-      <c r="C10" s="32"/>
-      <c r="D10" s="32"/>
-      <c r="E10" s="32"/>
-      <c r="F10" s="32"/>
+      <c r="B10" s="48"/>
+      <c r="C10" s="48"/>
+      <c r="D10" s="48"/>
+      <c r="E10" s="48"/>
+      <c r="F10" s="48"/>
       <c r="G10" s="12"/>
       <c r="H10" s="12"/>
-      <c r="I10" s="32" t="s">
-        <v>2</v>
-      </c>
-      <c r="J10" s="32"/>
-      <c r="K10" s="32"/>
-      <c r="L10" s="32"/>
-      <c r="M10" s="32"/>
-      <c r="N10" s="32"/>
-      <c r="O10" s="32"/>
-      <c r="P10" s="32"/>
+      <c r="I10" s="48" t="s">
+        <v>2</v>
+      </c>
+      <c r="J10" s="48"/>
+      <c r="K10" s="48"/>
+      <c r="L10" s="48"/>
+      <c r="M10" s="48"/>
+      <c r="N10" s="48"/>
+      <c r="O10" s="48"/>
+      <c r="P10" s="48"/>
     </row>
     <row r="11" spans="1:17" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="A11" s="39" t="s">
-        <v>0</v>
-      </c>
-      <c r="B11" s="39"/>
-      <c r="C11" s="39"/>
-      <c r="D11" s="39"/>
-      <c r="E11" s="39"/>
-      <c r="F11" s="39"/>
-      <c r="H11" s="39" t="s">
-        <v>0</v>
-      </c>
-      <c r="I11" s="39"/>
-      <c r="J11" s="39"/>
-      <c r="K11" s="39"/>
-      <c r="L11" s="39"/>
-      <c r="M11" s="39"/>
-      <c r="N11" s="39"/>
-      <c r="O11" s="39"/>
+      <c r="A11" s="51" t="s">
+        <v>0</v>
+      </c>
+      <c r="B11" s="51"/>
+      <c r="C11" s="51"/>
+      <c r="D11" s="51"/>
+      <c r="E11" s="51"/>
+      <c r="F11" s="51"/>
+      <c r="H11" s="51" t="s">
+        <v>0</v>
+      </c>
+      <c r="I11" s="51"/>
+      <c r="J11" s="51"/>
+      <c r="K11" s="51"/>
+      <c r="L11" s="51"/>
+      <c r="M11" s="51"/>
+      <c r="N11" s="51"/>
+      <c r="O11" s="51"/>
     </row>
     <row r="12" spans="1:17" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A12" s="34" t="s">
+      <c r="A12" s="43" t="s">
         <v>61</v>
       </c>
-      <c r="B12" s="34"/>
-      <c r="C12" s="42" t="s">
-        <v>3</v>
-      </c>
-      <c r="D12" s="42"/>
-      <c r="E12" s="43" t="s">
-        <v>4</v>
-      </c>
-      <c r="F12" s="42"/>
+      <c r="B12" s="43"/>
+      <c r="C12" s="45" t="s">
+        <v>3</v>
+      </c>
+      <c r="D12" s="45"/>
+      <c r="E12" s="50" t="s">
+        <v>4</v>
+      </c>
+      <c r="F12" s="45"/>
       <c r="G12" s="4"/>
-      <c r="H12" s="34" t="s">
+      <c r="H12" s="43" t="s">
         <v>61</v>
       </c>
-      <c r="I12" s="34"/>
-      <c r="J12" s="36" t="s">
-        <v>3</v>
-      </c>
-      <c r="K12" s="36"/>
-      <c r="L12" s="36"/>
-      <c r="M12" s="37" t="s">
-        <v>4</v>
-      </c>
-      <c r="N12" s="36"/>
-      <c r="O12" s="36"/>
+      <c r="I12" s="43"/>
+      <c r="J12" s="58" t="s">
+        <v>3</v>
+      </c>
+      <c r="K12" s="58"/>
+      <c r="L12" s="58"/>
+      <c r="M12" s="59" t="s">
+        <v>4</v>
+      </c>
+      <c r="N12" s="58"/>
+      <c r="O12" s="58"/>
       <c r="P12" s="4"/>
       <c r="Q12" s="4"/>
     </row>
     <row r="13" spans="1:17" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="A13" s="35"/>
-      <c r="B13" s="35"/>
+      <c r="A13" s="44"/>
+      <c r="B13" s="44"/>
       <c r="C13" s="13" t="s">
         <v>69</v>
       </c>
@@ -4708,8 +4661,8 @@
         <v>6</v>
       </c>
       <c r="G13" s="5"/>
-      <c r="H13" s="35"/>
-      <c r="I13" s="35"/>
+      <c r="H13" s="44"/>
+      <c r="I13" s="44"/>
       <c r="J13" s="17" t="s">
         <v>70</v>
       </c>
@@ -4984,62 +4937,62 @@
       <c r="Q20" s="4"/>
     </row>
     <row r="21" spans="1:17" ht="21" x14ac:dyDescent="0.35">
-      <c r="A21" s="38" t="s">
+      <c r="A21" s="47" t="s">
         <v>16</v>
       </c>
-      <c r="B21" s="38"/>
-      <c r="C21" s="38"/>
-      <c r="D21" s="38"/>
-      <c r="E21" s="38"/>
-      <c r="F21" s="38"/>
+      <c r="B21" s="47"/>
+      <c r="C21" s="47"/>
+      <c r="D21" s="47"/>
+      <c r="E21" s="47"/>
+      <c r="F21" s="47"/>
       <c r="G21" s="19"/>
       <c r="H21" s="8"/>
-      <c r="I21" s="46" t="s">
+      <c r="I21" s="63" t="s">
         <v>16</v>
       </c>
-      <c r="J21" s="46"/>
-      <c r="K21" s="46"/>
-      <c r="L21" s="46"/>
-      <c r="M21" s="46"/>
-      <c r="N21" s="46"/>
-      <c r="O21" s="46"/>
-      <c r="P21" s="46"/>
+      <c r="J21" s="63"/>
+      <c r="K21" s="63"/>
+      <c r="L21" s="63"/>
+      <c r="M21" s="63"/>
+      <c r="N21" s="63"/>
+      <c r="O21" s="63"/>
+      <c r="P21" s="63"/>
       <c r="Q21" s="4"/>
     </row>
     <row r="22" spans="1:17" ht="21" x14ac:dyDescent="0.35">
-      <c r="A22" s="34" t="s">
+      <c r="A22" s="43" t="s">
         <v>61</v>
       </c>
-      <c r="B22" s="34"/>
-      <c r="C22" s="42" t="s">
-        <v>3</v>
-      </c>
-      <c r="D22" s="42"/>
-      <c r="E22" s="43" t="s">
-        <v>4</v>
-      </c>
-      <c r="F22" s="42"/>
+      <c r="B22" s="43"/>
+      <c r="C22" s="45" t="s">
+        <v>3</v>
+      </c>
+      <c r="D22" s="45"/>
+      <c r="E22" s="50" t="s">
+        <v>4</v>
+      </c>
+      <c r="F22" s="45"/>
       <c r="G22" s="8"/>
-      <c r="H22" s="34" t="s">
+      <c r="H22" s="43" t="s">
         <v>61</v>
       </c>
-      <c r="I22" s="34"/>
-      <c r="J22" s="36" t="s">
-        <v>3</v>
-      </c>
-      <c r="K22" s="36"/>
-      <c r="L22" s="36"/>
-      <c r="M22" s="37" t="s">
-        <v>4</v>
-      </c>
-      <c r="N22" s="36"/>
-      <c r="O22" s="36"/>
+      <c r="I22" s="43"/>
+      <c r="J22" s="58" t="s">
+        <v>3</v>
+      </c>
+      <c r="K22" s="58"/>
+      <c r="L22" s="58"/>
+      <c r="M22" s="59" t="s">
+        <v>4</v>
+      </c>
+      <c r="N22" s="58"/>
+      <c r="O22" s="58"/>
       <c r="P22" s="8"/>
       <c r="Q22" s="4"/>
     </row>
     <row r="23" spans="1:17" ht="21" x14ac:dyDescent="0.35">
-      <c r="A23" s="35"/>
-      <c r="B23" s="35"/>
+      <c r="A23" s="44"/>
+      <c r="B23" s="44"/>
       <c r="C23" s="13" t="s">
         <v>69</v>
       </c>
@@ -5053,8 +5006,8 @@
         <v>6</v>
       </c>
       <c r="G23" s="8"/>
-      <c r="H23" s="35"/>
-      <c r="I23" s="35"/>
+      <c r="H23" s="44"/>
+      <c r="I23" s="44"/>
       <c r="J23" s="17" t="s">
         <v>70</v>
       </c>
@@ -5349,14 +5302,14 @@
       <c r="Q31" s="4"/>
     </row>
     <row r="32" spans="1:17" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="A32" s="39" t="s">
+      <c r="A32" s="51" t="s">
         <v>62</v>
       </c>
-      <c r="B32" s="39"/>
-      <c r="C32" s="39"/>
-      <c r="D32" s="39"/>
-      <c r="E32" s="39"/>
-      <c r="F32" s="39"/>
+      <c r="B32" s="51"/>
+      <c r="C32" s="51"/>
+      <c r="D32" s="51"/>
+      <c r="E32" s="51"/>
+      <c r="F32" s="51"/>
       <c r="G32" s="4"/>
       <c r="H32" s="4"/>
       <c r="I32" s="4"/>
@@ -5370,22 +5323,22 @@
       <c r="Q32" s="4"/>
     </row>
     <row r="33" spans="1:6" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A33" s="34" t="s">
+      <c r="A33" s="43" t="s">
         <v>61</v>
       </c>
-      <c r="B33" s="34"/>
-      <c r="C33" s="42" t="s">
-        <v>3</v>
-      </c>
-      <c r="D33" s="42"/>
-      <c r="E33" s="42" t="s">
-        <v>4</v>
-      </c>
-      <c r="F33" s="42"/>
+      <c r="B33" s="43"/>
+      <c r="C33" s="45" t="s">
+        <v>3</v>
+      </c>
+      <c r="D33" s="45"/>
+      <c r="E33" s="45" t="s">
+        <v>4</v>
+      </c>
+      <c r="F33" s="45"/>
     </row>
     <row r="34" spans="1:6" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A34" s="35"/>
-      <c r="B34" s="35"/>
+      <c r="A34" s="44"/>
+      <c r="B34" s="44"/>
       <c r="C34" s="13" t="s">
         <v>5</v>
       </c>
@@ -5473,18 +5426,6 @@
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="A32:F32"/>
-    <mergeCell ref="A33:B34"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="E33:F33"/>
-    <mergeCell ref="A21:F21"/>
-    <mergeCell ref="I21:P21"/>
-    <mergeCell ref="A22:B23"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="H22:I23"/>
-    <mergeCell ref="J22:L22"/>
-    <mergeCell ref="M22:O22"/>
     <mergeCell ref="A10:F10"/>
     <mergeCell ref="I10:P10"/>
     <mergeCell ref="A11:F11"/>
@@ -5495,6 +5436,18 @@
     <mergeCell ref="H12:I13"/>
     <mergeCell ref="J12:L12"/>
     <mergeCell ref="M12:O12"/>
+    <mergeCell ref="I21:P21"/>
+    <mergeCell ref="A22:B23"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="H22:I23"/>
+    <mergeCell ref="J22:L22"/>
+    <mergeCell ref="M22:O22"/>
+    <mergeCell ref="A32:F32"/>
+    <mergeCell ref="A33:B34"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="E33:F33"/>
+    <mergeCell ref="A21:F21"/>
   </mergeCells>
   <conditionalFormatting sqref="C15:C19 E14:E19">
     <cfRule type="colorScale" priority="19">
@@ -5656,7 +5609,7 @@
       <c r="A1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="J1" s="52" t="s">
+      <c r="J1" s="35" t="s">
         <v>74</v>
       </c>
     </row>
@@ -5697,81 +5650,81 @@
       </c>
     </row>
     <row r="10" spans="1:17" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="32" t="s">
+      <c r="A10" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="B10" s="32"/>
-      <c r="C10" s="32"/>
-      <c r="D10" s="32"/>
-      <c r="E10" s="32"/>
-      <c r="F10" s="32"/>
+      <c r="B10" s="48"/>
+      <c r="C10" s="48"/>
+      <c r="D10" s="48"/>
+      <c r="E10" s="48"/>
+      <c r="F10" s="48"/>
       <c r="G10" s="12"/>
       <c r="H10" s="12"/>
-      <c r="I10" s="32" t="s">
-        <v>2</v>
-      </c>
-      <c r="J10" s="32"/>
-      <c r="K10" s="32"/>
-      <c r="L10" s="32"/>
-      <c r="M10" s="32"/>
-      <c r="N10" s="32"/>
-      <c r="O10" s="32"/>
-      <c r="P10" s="32"/>
+      <c r="I10" s="48" t="s">
+        <v>2</v>
+      </c>
+      <c r="J10" s="48"/>
+      <c r="K10" s="48"/>
+      <c r="L10" s="48"/>
+      <c r="M10" s="48"/>
+      <c r="N10" s="48"/>
+      <c r="O10" s="48"/>
+      <c r="P10" s="48"/>
     </row>
     <row r="11" spans="1:17" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="A11" s="39" t="s">
-        <v>0</v>
-      </c>
-      <c r="B11" s="39"/>
-      <c r="C11" s="39"/>
-      <c r="D11" s="39"/>
-      <c r="E11" s="39"/>
-      <c r="F11" s="39"/>
-      <c r="H11" s="39" t="s">
-        <v>0</v>
-      </c>
-      <c r="I11" s="39"/>
-      <c r="J11" s="39"/>
-      <c r="K11" s="39"/>
-      <c r="L11" s="39"/>
-      <c r="M11" s="39"/>
-      <c r="N11" s="39"/>
-      <c r="O11" s="39"/>
+      <c r="A11" s="51" t="s">
+        <v>0</v>
+      </c>
+      <c r="B11" s="51"/>
+      <c r="C11" s="51"/>
+      <c r="D11" s="51"/>
+      <c r="E11" s="51"/>
+      <c r="F11" s="51"/>
+      <c r="H11" s="51" t="s">
+        <v>0</v>
+      </c>
+      <c r="I11" s="51"/>
+      <c r="J11" s="51"/>
+      <c r="K11" s="51"/>
+      <c r="L11" s="51"/>
+      <c r="M11" s="51"/>
+      <c r="N11" s="51"/>
+      <c r="O11" s="51"/>
     </row>
     <row r="12" spans="1:17" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A12" s="34" t="s">
+      <c r="A12" s="43" t="s">
         <v>61</v>
       </c>
-      <c r="B12" s="34"/>
-      <c r="C12" s="42" t="s">
-        <v>3</v>
-      </c>
-      <c r="D12" s="42"/>
-      <c r="E12" s="43" t="s">
-        <v>4</v>
-      </c>
-      <c r="F12" s="42"/>
+      <c r="B12" s="43"/>
+      <c r="C12" s="45" t="s">
+        <v>3</v>
+      </c>
+      <c r="D12" s="45"/>
+      <c r="E12" s="50" t="s">
+        <v>4</v>
+      </c>
+      <c r="F12" s="45"/>
       <c r="G12" s="4"/>
-      <c r="H12" s="34" t="s">
+      <c r="H12" s="43" t="s">
         <v>61</v>
       </c>
-      <c r="I12" s="34"/>
-      <c r="J12" s="36" t="s">
-        <v>3</v>
-      </c>
-      <c r="K12" s="36"/>
-      <c r="L12" s="36"/>
-      <c r="M12" s="37" t="s">
-        <v>4</v>
-      </c>
-      <c r="N12" s="36"/>
-      <c r="O12" s="36"/>
+      <c r="I12" s="43"/>
+      <c r="J12" s="58" t="s">
+        <v>3</v>
+      </c>
+      <c r="K12" s="58"/>
+      <c r="L12" s="58"/>
+      <c r="M12" s="59" t="s">
+        <v>4</v>
+      </c>
+      <c r="N12" s="58"/>
+      <c r="O12" s="58"/>
       <c r="P12" s="4"/>
       <c r="Q12" s="4"/>
     </row>
     <row r="13" spans="1:17" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="A13" s="35"/>
-      <c r="B13" s="35"/>
+      <c r="A13" s="44"/>
+      <c r="B13" s="44"/>
       <c r="C13" s="13" t="s">
         <v>69</v>
       </c>
@@ -5785,8 +5738,8 @@
         <v>6</v>
       </c>
       <c r="G13" s="5"/>
-      <c r="H13" s="35"/>
-      <c r="I13" s="35"/>
+      <c r="H13" s="44"/>
+      <c r="I13" s="44"/>
       <c r="J13" s="17" t="s">
         <v>70</v>
       </c>
@@ -6061,62 +6014,62 @@
       <c r="Q20" s="4"/>
     </row>
     <row r="21" spans="1:17" ht="21" x14ac:dyDescent="0.35">
-      <c r="A21" s="38" t="s">
+      <c r="A21" s="47" t="s">
         <v>16</v>
       </c>
-      <c r="B21" s="38"/>
-      <c r="C21" s="38"/>
-      <c r="D21" s="38"/>
-      <c r="E21" s="38"/>
-      <c r="F21" s="38"/>
+      <c r="B21" s="47"/>
+      <c r="C21" s="47"/>
+      <c r="D21" s="47"/>
+      <c r="E21" s="47"/>
+      <c r="F21" s="47"/>
       <c r="G21" s="19"/>
       <c r="H21" s="8"/>
-      <c r="I21" s="46" t="s">
+      <c r="I21" s="63" t="s">
         <v>16</v>
       </c>
-      <c r="J21" s="46"/>
-      <c r="K21" s="46"/>
-      <c r="L21" s="46"/>
-      <c r="M21" s="46"/>
-      <c r="N21" s="46"/>
-      <c r="O21" s="46"/>
-      <c r="P21" s="46"/>
+      <c r="J21" s="63"/>
+      <c r="K21" s="63"/>
+      <c r="L21" s="63"/>
+      <c r="M21" s="63"/>
+      <c r="N21" s="63"/>
+      <c r="O21" s="63"/>
+      <c r="P21" s="63"/>
       <c r="Q21" s="4"/>
     </row>
     <row r="22" spans="1:17" ht="21" x14ac:dyDescent="0.35">
-      <c r="A22" s="34" t="s">
+      <c r="A22" s="43" t="s">
         <v>61</v>
       </c>
-      <c r="B22" s="34"/>
-      <c r="C22" s="42" t="s">
-        <v>3</v>
-      </c>
-      <c r="D22" s="42"/>
-      <c r="E22" s="43" t="s">
-        <v>4</v>
-      </c>
-      <c r="F22" s="42"/>
+      <c r="B22" s="43"/>
+      <c r="C22" s="45" t="s">
+        <v>3</v>
+      </c>
+      <c r="D22" s="45"/>
+      <c r="E22" s="50" t="s">
+        <v>4</v>
+      </c>
+      <c r="F22" s="45"/>
       <c r="G22" s="8"/>
-      <c r="H22" s="34" t="s">
+      <c r="H22" s="43" t="s">
         <v>61</v>
       </c>
-      <c r="I22" s="34"/>
-      <c r="J22" s="36" t="s">
-        <v>3</v>
-      </c>
-      <c r="K22" s="36"/>
-      <c r="L22" s="36"/>
-      <c r="M22" s="37" t="s">
-        <v>4</v>
-      </c>
-      <c r="N22" s="36"/>
-      <c r="O22" s="36"/>
+      <c r="I22" s="43"/>
+      <c r="J22" s="58" t="s">
+        <v>3</v>
+      </c>
+      <c r="K22" s="58"/>
+      <c r="L22" s="58"/>
+      <c r="M22" s="59" t="s">
+        <v>4</v>
+      </c>
+      <c r="N22" s="58"/>
+      <c r="O22" s="58"/>
       <c r="P22" s="8"/>
       <c r="Q22" s="4"/>
     </row>
     <row r="23" spans="1:17" ht="21" x14ac:dyDescent="0.35">
-      <c r="A23" s="35"/>
-      <c r="B23" s="35"/>
+      <c r="A23" s="44"/>
+      <c r="B23" s="44"/>
       <c r="C23" s="13" t="s">
         <v>69</v>
       </c>
@@ -6130,8 +6083,8 @@
         <v>6</v>
       </c>
       <c r="G23" s="8"/>
-      <c r="H23" s="35"/>
-      <c r="I23" s="35"/>
+      <c r="H23" s="44"/>
+      <c r="I23" s="44"/>
       <c r="J23" s="17" t="s">
         <v>70</v>
       </c>
@@ -6426,14 +6379,14 @@
       <c r="Q31" s="4"/>
     </row>
     <row r="32" spans="1:17" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="A32" s="39" t="s">
+      <c r="A32" s="51" t="s">
         <v>62</v>
       </c>
-      <c r="B32" s="39"/>
-      <c r="C32" s="39"/>
-      <c r="D32" s="39"/>
-      <c r="E32" s="39"/>
-      <c r="F32" s="39"/>
+      <c r="B32" s="51"/>
+      <c r="C32" s="51"/>
+      <c r="D32" s="51"/>
+      <c r="E32" s="51"/>
+      <c r="F32" s="51"/>
       <c r="G32" s="4"/>
       <c r="H32" s="4"/>
       <c r="I32" s="4"/>
@@ -6447,22 +6400,22 @@
       <c r="Q32" s="4"/>
     </row>
     <row r="33" spans="1:6" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A33" s="34" t="s">
+      <c r="A33" s="43" t="s">
         <v>61</v>
       </c>
-      <c r="B33" s="34"/>
-      <c r="C33" s="42" t="s">
-        <v>3</v>
-      </c>
-      <c r="D33" s="42"/>
-      <c r="E33" s="42" t="s">
-        <v>4</v>
-      </c>
-      <c r="F33" s="42"/>
+      <c r="B33" s="43"/>
+      <c r="C33" s="45" t="s">
+        <v>3</v>
+      </c>
+      <c r="D33" s="45"/>
+      <c r="E33" s="45" t="s">
+        <v>4</v>
+      </c>
+      <c r="F33" s="45"/>
     </row>
     <row r="34" spans="1:6" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A34" s="35"/>
-      <c r="B34" s="35"/>
+      <c r="A34" s="44"/>
+      <c r="B34" s="44"/>
       <c r="C34" s="13" t="s">
         <v>5</v>
       </c>
@@ -6550,18 +6503,6 @@
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="A32:F32"/>
-    <mergeCell ref="A33:B34"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="E33:F33"/>
-    <mergeCell ref="A21:F21"/>
-    <mergeCell ref="I21:P21"/>
-    <mergeCell ref="A22:B23"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="H22:I23"/>
-    <mergeCell ref="J22:L22"/>
-    <mergeCell ref="M22:O22"/>
     <mergeCell ref="A10:F10"/>
     <mergeCell ref="I10:P10"/>
     <mergeCell ref="A11:F11"/>
@@ -6572,6 +6513,18 @@
     <mergeCell ref="H12:I13"/>
     <mergeCell ref="J12:L12"/>
     <mergeCell ref="M12:O12"/>
+    <mergeCell ref="I21:P21"/>
+    <mergeCell ref="A22:B23"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="H22:I23"/>
+    <mergeCell ref="J22:L22"/>
+    <mergeCell ref="M22:O22"/>
+    <mergeCell ref="A32:F32"/>
+    <mergeCell ref="A33:B34"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="E33:F33"/>
+    <mergeCell ref="A21:F21"/>
   </mergeCells>
   <conditionalFormatting sqref="C15:C19 E14:E19">
     <cfRule type="colorScale" priority="13">
@@ -6725,10 +6678,10 @@
   </cols>
   <sheetData>
     <row r="3" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="L3" s="47" t="s">
+      <c r="L3" s="64" t="s">
         <v>60</v>
       </c>
-      <c r="M3" s="47"/>
+      <c r="M3" s="64"/>
       <c r="N3" t="s">
         <v>59</v>
       </c>
@@ -6924,7 +6877,7 @@
       <c r="L17" t="s">
         <v>48</v>
       </c>
-      <c r="M17" s="47" t="s">
+      <c r="M17" s="64" t="s">
         <v>49</v>
       </c>
     </row>
@@ -6944,7 +6897,7 @@
       <c r="L18" t="s">
         <v>50</v>
       </c>
-      <c r="M18" s="47"/>
+      <c r="M18" s="64"/>
     </row>
     <row r="19" spans="6:13" x14ac:dyDescent="0.25">
       <c r="G19" t="s">
@@ -7034,26 +6987,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="e8c8a8d2-cf65-4fdf-b6bc-794ebda6188e" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f72adabb-0ee4-4963-acd9-9efc158f92a6">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009074E2A1C82F3C4BA659A6C6CC51AC5F" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0765d5a41f49df217abeb23dcfb0b3cf">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="cc5908d1-2a89-4186-9c08-2c76e53ac163" xmlns:ns3="f72adabb-0ee4-4963-acd9-9efc158f92a6" xmlns:ns4="e8c8a8d2-cf65-4fdf-b6bc-794ebda6188e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="519818410c367a5844210e380df69fc7" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="cc5908d1-2a89-4186-9c08-2c76e53ac163"/>
@@ -7301,33 +7234,27 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{78150E95-1CCA-47FB-B6E6-99D8675B2929}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="f72adabb-0ee4-4963-acd9-9efc158f92a6"/>
-    <ds:schemaRef ds:uri="cc5908d1-2a89-4186-9c08-2c76e53ac163"/>
-    <ds:schemaRef ds:uri="e8c8a8d2-cf65-4fdf-b6bc-794ebda6188e"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{29C58647-0154-48BC-9EDF-8ABD72381C6C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="e8c8a8d2-cf65-4fdf-b6bc-794ebda6188e" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f72adabb-0ee4-4963-acd9-9efc158f92a6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4039D020-CA7C-47AE-A105-0DAEDCC57394}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -7345,4 +7272,30 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{29C58647-0154-48BC-9EDF-8ABD72381C6C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{78150E95-1CCA-47FB-B6E6-99D8675B2929}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="f72adabb-0ee4-4963-acd9-9efc158f92a6"/>
+    <ds:schemaRef ds:uri="cc5908d1-2a89-4186-9c08-2c76e53ac163"/>
+    <ds:schemaRef ds:uri="e8c8a8d2-cf65-4fdf-b6bc-794ebda6188e"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/output/V3_SIM_Results_Summary.xlsx
+++ b/output/V3_SIM_Results_Summary.xlsx
@@ -619,41 +619,29 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -670,14 +658,26 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1051,115 +1051,115 @@
       </c>
     </row>
     <row r="10" spans="1:25" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="48" t="s">
+      <c r="A10" s="43" t="s">
         <v>1</v>
       </c>
-      <c r="B10" s="48"/>
-      <c r="C10" s="48"/>
-      <c r="D10" s="48"/>
-      <c r="E10" s="48"/>
-      <c r="F10" s="48"/>
+      <c r="B10" s="43"/>
+      <c r="C10" s="43"/>
+      <c r="D10" s="43"/>
+      <c r="E10" s="43"/>
+      <c r="F10" s="43"/>
       <c r="G10" s="31"/>
-      <c r="H10" s="48" t="s">
+      <c r="H10" s="43" t="s">
         <v>1</v>
       </c>
-      <c r="I10" s="48"/>
-      <c r="J10" s="48"/>
-      <c r="K10" s="48"/>
-      <c r="L10" s="48"/>
-      <c r="M10" s="48"/>
+      <c r="I10" s="43"/>
+      <c r="J10" s="43"/>
+      <c r="K10" s="43"/>
+      <c r="L10" s="43"/>
+      <c r="M10" s="43"/>
       <c r="N10" s="31"/>
       <c r="O10" s="12"/>
-      <c r="P10" s="49" t="s">
-        <v>2</v>
-      </c>
-      <c r="Q10" s="49"/>
-      <c r="R10" s="49"/>
-      <c r="S10" s="49"/>
-      <c r="T10" s="49"/>
-      <c r="U10" s="49"/>
-      <c r="V10" s="49"/>
-      <c r="W10" s="49"/>
+      <c r="P10" s="61" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q10" s="61"/>
+      <c r="R10" s="61"/>
+      <c r="S10" s="61"/>
+      <c r="T10" s="61"/>
+      <c r="U10" s="61"/>
+      <c r="V10" s="61"/>
+      <c r="W10" s="61"/>
       <c r="X10" s="42"/>
     </row>
     <row r="11" spans="1:25" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="A11" s="51" t="s">
-        <v>0</v>
-      </c>
-      <c r="B11" s="51"/>
-      <c r="C11" s="51"/>
-      <c r="D11" s="51"/>
-      <c r="E11" s="51"/>
-      <c r="F11" s="51"/>
+      <c r="A11" s="48" t="s">
+        <v>0</v>
+      </c>
+      <c r="B11" s="48"/>
+      <c r="C11" s="48"/>
+      <c r="D11" s="48"/>
+      <c r="E11" s="48"/>
+      <c r="F11" s="48"/>
       <c r="G11" s="36"/>
-      <c r="H11" s="51" t="s">
+      <c r="H11" s="48" t="s">
         <v>62</v>
       </c>
-      <c r="I11" s="51"/>
-      <c r="J11" s="51"/>
-      <c r="K11" s="51"/>
-      <c r="L11" s="51"/>
-      <c r="M11" s="51"/>
+      <c r="I11" s="48"/>
+      <c r="J11" s="48"/>
+      <c r="K11" s="48"/>
+      <c r="L11" s="48"/>
+      <c r="M11" s="48"/>
       <c r="N11" s="36"/>
-      <c r="P11" s="51" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="51"/>
-      <c r="R11" s="51"/>
-      <c r="S11" s="51"/>
-      <c r="T11" s="51"/>
-      <c r="U11" s="51"/>
-      <c r="V11" s="51"/>
-      <c r="W11" s="51"/>
+      <c r="P11" s="48" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="48"/>
+      <c r="R11" s="48"/>
+      <c r="S11" s="48"/>
+      <c r="T11" s="48"/>
+      <c r="U11" s="48"/>
+      <c r="V11" s="48"/>
+      <c r="W11" s="48"/>
     </row>
     <row r="12" spans="1:25" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A12" s="43" t="s">
+      <c r="A12" s="45" t="s">
         <v>61</v>
       </c>
-      <c r="B12" s="43"/>
-      <c r="C12" s="45" t="s">
-        <v>3</v>
-      </c>
-      <c r="D12" s="45"/>
+      <c r="B12" s="45"/>
+      <c r="C12" s="49" t="s">
+        <v>3</v>
+      </c>
+      <c r="D12" s="49"/>
       <c r="E12" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="F12" s="45"/>
+      <c r="F12" s="49"/>
       <c r="G12" s="37"/>
-      <c r="H12" s="43" t="s">
+      <c r="H12" s="45" t="s">
         <v>61</v>
       </c>
-      <c r="I12" s="43"/>
-      <c r="J12" s="45" t="s">
-        <v>3</v>
-      </c>
-      <c r="K12" s="45"/>
+      <c r="I12" s="45"/>
+      <c r="J12" s="49" t="s">
+        <v>3</v>
+      </c>
+      <c r="K12" s="49"/>
       <c r="L12" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="M12" s="45"/>
+      <c r="M12" s="49"/>
       <c r="N12" s="37"/>
       <c r="O12" s="4"/>
-      <c r="P12" s="43" t="s">
+      <c r="P12" s="45" t="s">
         <v>61</v>
       </c>
-      <c r="Q12" s="43"/>
-      <c r="R12" s="58" t="s">
-        <v>3</v>
-      </c>
-      <c r="S12" s="58"/>
-      <c r="T12" s="58"/>
-      <c r="U12" s="59" t="s">
-        <v>4</v>
-      </c>
-      <c r="V12" s="58"/>
-      <c r="W12" s="58"/>
+      <c r="Q12" s="45"/>
+      <c r="R12" s="54" t="s">
+        <v>3</v>
+      </c>
+      <c r="S12" s="54"/>
+      <c r="T12" s="54"/>
+      <c r="U12" s="55" t="s">
+        <v>4</v>
+      </c>
+      <c r="V12" s="54"/>
+      <c r="W12" s="54"/>
       <c r="X12" s="4"/>
       <c r="Y12" s="4"/>
     </row>
     <row r="13" spans="1:25" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A13" s="44"/>
-      <c r="B13" s="44"/>
+      <c r="A13" s="46"/>
+      <c r="B13" s="46"/>
       <c r="C13" s="32" t="s">
         <v>5</v>
       </c>
@@ -1173,8 +1173,8 @@
         <v>6</v>
       </c>
       <c r="G13" s="38"/>
-      <c r="H13" s="44"/>
-      <c r="I13" s="44"/>
+      <c r="H13" s="46"/>
+      <c r="I13" s="46"/>
       <c r="J13" s="32" t="s">
         <v>5</v>
       </c>
@@ -1189,8 +1189,8 @@
       </c>
       <c r="N13" s="38"/>
       <c r="O13" s="5"/>
-      <c r="P13" s="44"/>
-      <c r="Q13" s="44"/>
+      <c r="P13" s="46"/>
+      <c r="Q13" s="46"/>
       <c r="R13" s="17" t="s">
         <v>7</v>
       </c>
@@ -1647,67 +1647,67 @@
       <c r="M21" s="47"/>
       <c r="N21" s="39"/>
       <c r="O21" s="19"/>
-      <c r="P21" s="60" t="s">
+      <c r="P21" s="44" t="s">
         <v>16</v>
       </c>
-      <c r="Q21" s="60"/>
-      <c r="R21" s="60"/>
-      <c r="S21" s="60"/>
-      <c r="T21" s="60"/>
-      <c r="U21" s="60"/>
-      <c r="V21" s="60"/>
-      <c r="W21" s="60"/>
+      <c r="Q21" s="44"/>
+      <c r="R21" s="44"/>
+      <c r="S21" s="44"/>
+      <c r="T21" s="44"/>
+      <c r="U21" s="44"/>
+      <c r="V21" s="44"/>
+      <c r="W21" s="44"/>
       <c r="X21" s="19"/>
       <c r="Y21" s="4"/>
     </row>
     <row r="22" spans="1:25" ht="21" x14ac:dyDescent="0.35">
-      <c r="A22" s="43" t="s">
+      <c r="A22" s="45" t="s">
         <v>61</v>
       </c>
-      <c r="B22" s="43"/>
-      <c r="C22" s="45" t="s">
-        <v>3</v>
-      </c>
-      <c r="D22" s="45"/>
-      <c r="E22" s="56" t="s">
-        <v>4</v>
-      </c>
-      <c r="F22" s="57"/>
+      <c r="B22" s="45"/>
+      <c r="C22" s="49" t="s">
+        <v>3</v>
+      </c>
+      <c r="D22" s="49"/>
+      <c r="E22" s="52" t="s">
+        <v>4</v>
+      </c>
+      <c r="F22" s="53"/>
       <c r="G22" s="40"/>
-      <c r="H22" s="43" t="s">
+      <c r="H22" s="45" t="s">
         <v>61</v>
       </c>
-      <c r="I22" s="43"/>
-      <c r="J22" s="45" t="s">
-        <v>3</v>
-      </c>
-      <c r="K22" s="45"/>
+      <c r="I22" s="45"/>
+      <c r="J22" s="49" t="s">
+        <v>3</v>
+      </c>
+      <c r="K22" s="49"/>
       <c r="L22" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="M22" s="45"/>
+      <c r="M22" s="49"/>
       <c r="N22" s="37"/>
       <c r="O22" s="8"/>
-      <c r="P22" s="43" t="s">
+      <c r="P22" s="45" t="s">
         <v>61</v>
       </c>
-      <c r="Q22" s="43"/>
-      <c r="R22" s="58" t="s">
-        <v>3</v>
-      </c>
-      <c r="S22" s="58"/>
-      <c r="T22" s="58"/>
-      <c r="U22" s="61" t="s">
-        <v>4</v>
-      </c>
-      <c r="V22" s="62"/>
-      <c r="W22" s="62"/>
+      <c r="Q22" s="45"/>
+      <c r="R22" s="54" t="s">
+        <v>3</v>
+      </c>
+      <c r="S22" s="54"/>
+      <c r="T22" s="54"/>
+      <c r="U22" s="56" t="s">
+        <v>4</v>
+      </c>
+      <c r="V22" s="57"/>
+      <c r="W22" s="57"/>
       <c r="X22" s="8"/>
       <c r="Y22" s="4"/>
     </row>
     <row r="23" spans="1:25" ht="21" x14ac:dyDescent="0.35">
-      <c r="A23" s="44"/>
-      <c r="B23" s="44"/>
+      <c r="A23" s="46"/>
+      <c r="B23" s="46"/>
       <c r="C23" s="32" t="s">
         <v>5</v>
       </c>
@@ -1721,8 +1721,8 @@
         <v>6</v>
       </c>
       <c r="G23" s="40"/>
-      <c r="H23" s="44"/>
-      <c r="I23" s="44"/>
+      <c r="H23" s="46"/>
+      <c r="I23" s="46"/>
       <c r="J23" s="32" t="s">
         <v>5</v>
       </c>
@@ -1737,8 +1737,8 @@
       </c>
       <c r="N23" s="38"/>
       <c r="O23" s="8"/>
-      <c r="P23" s="44"/>
-      <c r="Q23" s="44"/>
+      <c r="P23" s="46"/>
+      <c r="Q23" s="46"/>
       <c r="R23" s="17" t="s">
         <v>7</v>
       </c>
@@ -2208,55 +2208,55 @@
       </c>
     </row>
     <row r="35" spans="1:14" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="A35" s="55"/>
-      <c r="B35" s="55"/>
-      <c r="C35" s="55"/>
-      <c r="D35" s="55"/>
-      <c r="E35" s="55"/>
-      <c r="F35" s="55"/>
+      <c r="A35" s="51"/>
+      <c r="B35" s="51"/>
+      <c r="C35" s="51"/>
+      <c r="D35" s="51"/>
+      <c r="E35" s="51"/>
+      <c r="F35" s="51"/>
       <c r="G35" s="41"/>
-      <c r="H35" s="46" t="s">
+      <c r="H35" s="62" t="s">
         <v>62</v>
       </c>
-      <c r="I35" s="46"/>
-      <c r="J35" s="46"/>
-      <c r="K35" s="46"/>
-      <c r="L35" s="46"/>
-      <c r="M35" s="46"/>
+      <c r="I35" s="62"/>
+      <c r="J35" s="62"/>
+      <c r="K35" s="62"/>
+      <c r="L35" s="62"/>
+      <c r="M35" s="62"/>
       <c r="N35" s="41"/>
     </row>
     <row r="36" spans="1:14" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A36" s="52"/>
-      <c r="B36" s="52"/>
-      <c r="C36" s="53"/>
-      <c r="D36" s="53"/>
-      <c r="E36" s="53"/>
-      <c r="F36" s="53"/>
+      <c r="A36" s="58"/>
+      <c r="B36" s="58"/>
+      <c r="C36" s="59"/>
+      <c r="D36" s="59"/>
+      <c r="E36" s="59"/>
+      <c r="F36" s="59"/>
       <c r="G36" s="37"/>
-      <c r="H36" s="43" t="s">
+      <c r="H36" s="45" t="s">
         <v>61</v>
       </c>
-      <c r="I36" s="43"/>
-      <c r="J36" s="45" t="s">
-        <v>3</v>
-      </c>
-      <c r="K36" s="45"/>
-      <c r="L36" s="45" t="s">
-        <v>4</v>
-      </c>
-      <c r="M36" s="45"/>
+      <c r="I36" s="45"/>
+      <c r="J36" s="49" t="s">
+        <v>3</v>
+      </c>
+      <c r="K36" s="49"/>
+      <c r="L36" s="49" t="s">
+        <v>4</v>
+      </c>
+      <c r="M36" s="49"/>
       <c r="N36" s="37"/>
     </row>
     <row r="37" spans="1:14" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A37" s="52"/>
-      <c r="B37" s="52"/>
+      <c r="A37" s="58"/>
+      <c r="B37" s="58"/>
       <c r="C37" s="38"/>
       <c r="D37" s="38"/>
       <c r="E37" s="38"/>
       <c r="F37" s="38"/>
       <c r="G37" s="38"/>
-      <c r="H37" s="44"/>
-      <c r="I37" s="44"/>
+      <c r="H37" s="46"/>
+      <c r="I37" s="46"/>
       <c r="J37" s="13" t="s">
         <v>5</v>
       </c>
@@ -2428,12 +2428,12 @@
       <c r="N43" s="20"/>
     </row>
     <row r="45" spans="1:14" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="A45" s="54"/>
-      <c r="B45" s="54"/>
-      <c r="C45" s="54"/>
-      <c r="D45" s="54"/>
-      <c r="E45" s="54"/>
-      <c r="F45" s="54"/>
+      <c r="A45" s="60"/>
+      <c r="B45" s="60"/>
+      <c r="C45" s="60"/>
+      <c r="D45" s="60"/>
+      <c r="E45" s="60"/>
+      <c r="F45" s="60"/>
       <c r="G45" s="39"/>
       <c r="H45" s="47" t="s">
         <v>77</v>
@@ -2446,37 +2446,37 @@
       <c r="N45" s="39"/>
     </row>
     <row r="46" spans="1:14" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A46" s="52"/>
-      <c r="B46" s="52"/>
-      <c r="C46" s="53"/>
-      <c r="D46" s="53"/>
-      <c r="E46" s="53"/>
-      <c r="F46" s="53"/>
+      <c r="A46" s="58"/>
+      <c r="B46" s="58"/>
+      <c r="C46" s="59"/>
+      <c r="D46" s="59"/>
+      <c r="E46" s="59"/>
+      <c r="F46" s="59"/>
       <c r="G46" s="37"/>
-      <c r="H46" s="43" t="s">
+      <c r="H46" s="45" t="s">
         <v>61</v>
       </c>
-      <c r="I46" s="43"/>
-      <c r="J46" s="45" t="s">
-        <v>3</v>
-      </c>
-      <c r="K46" s="45"/>
-      <c r="L46" s="45" t="s">
-        <v>4</v>
-      </c>
-      <c r="M46" s="45"/>
+      <c r="I46" s="45"/>
+      <c r="J46" s="49" t="s">
+        <v>3</v>
+      </c>
+      <c r="K46" s="49"/>
+      <c r="L46" s="49" t="s">
+        <v>4</v>
+      </c>
+      <c r="M46" s="49"/>
       <c r="N46" s="37"/>
     </row>
     <row r="47" spans="1:14" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A47" s="52"/>
-      <c r="B47" s="52"/>
+      <c r="A47" s="58"/>
+      <c r="B47" s="58"/>
       <c r="C47" s="38"/>
       <c r="D47" s="38"/>
       <c r="E47" s="38"/>
       <c r="F47" s="38"/>
       <c r="G47" s="38"/>
-      <c r="H47" s="44"/>
-      <c r="I47" s="44"/>
+      <c r="H47" s="46"/>
+      <c r="I47" s="46"/>
       <c r="J47" s="13" t="s">
         <v>5</v>
       </c>
@@ -2649,6 +2649,37 @@
     </row>
   </sheetData>
   <mergeCells count="43">
+    <mergeCell ref="H46:I47"/>
+    <mergeCell ref="J46:K46"/>
+    <mergeCell ref="L46:M46"/>
+    <mergeCell ref="H35:M35"/>
+    <mergeCell ref="H36:I37"/>
+    <mergeCell ref="J36:K36"/>
+    <mergeCell ref="L36:M36"/>
+    <mergeCell ref="H45:M45"/>
+    <mergeCell ref="A36:B37"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="E36:F36"/>
+    <mergeCell ref="A45:F45"/>
+    <mergeCell ref="A46:B47"/>
+    <mergeCell ref="C46:D46"/>
+    <mergeCell ref="E46:F46"/>
+    <mergeCell ref="A35:F35"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="R12:T12"/>
+    <mergeCell ref="U12:W12"/>
+    <mergeCell ref="A22:B23"/>
+    <mergeCell ref="P22:Q23"/>
+    <mergeCell ref="R22:T22"/>
+    <mergeCell ref="U22:W22"/>
+    <mergeCell ref="H21:M21"/>
+    <mergeCell ref="H22:I23"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="L22:M22"/>
+    <mergeCell ref="H12:I13"/>
+    <mergeCell ref="J12:K12"/>
+    <mergeCell ref="L12:M12"/>
     <mergeCell ref="A10:F10"/>
     <mergeCell ref="P21:W21"/>
     <mergeCell ref="A12:B13"/>
@@ -2658,40 +2689,9 @@
     <mergeCell ref="P11:W11"/>
     <mergeCell ref="C12:D12"/>
     <mergeCell ref="E12:F12"/>
-    <mergeCell ref="A35:F35"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="R12:T12"/>
-    <mergeCell ref="U12:W12"/>
-    <mergeCell ref="A22:B23"/>
-    <mergeCell ref="P22:Q23"/>
-    <mergeCell ref="R22:T22"/>
-    <mergeCell ref="U22:W22"/>
-    <mergeCell ref="A36:B37"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="E36:F36"/>
-    <mergeCell ref="A45:F45"/>
-    <mergeCell ref="A46:B47"/>
-    <mergeCell ref="C46:D46"/>
-    <mergeCell ref="E46:F46"/>
     <mergeCell ref="H10:M10"/>
     <mergeCell ref="P10:W10"/>
-    <mergeCell ref="H21:M21"/>
-    <mergeCell ref="H22:I23"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="L22:M22"/>
     <mergeCell ref="H11:M11"/>
-    <mergeCell ref="H12:I13"/>
-    <mergeCell ref="J12:K12"/>
-    <mergeCell ref="L12:M12"/>
-    <mergeCell ref="H46:I47"/>
-    <mergeCell ref="J46:K46"/>
-    <mergeCell ref="L46:M46"/>
-    <mergeCell ref="H35:M35"/>
-    <mergeCell ref="H36:I37"/>
-    <mergeCell ref="J36:K36"/>
-    <mergeCell ref="L36:M36"/>
-    <mergeCell ref="H45:M45"/>
   </mergeCells>
   <conditionalFormatting sqref="C14:D19">
     <cfRule type="colorScale" priority="27">
@@ -2882,81 +2882,81 @@
       </c>
     </row>
     <row r="10" spans="1:17" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="48" t="s">
+      <c r="A10" s="43" t="s">
         <v>1</v>
       </c>
-      <c r="B10" s="48"/>
-      <c r="C10" s="48"/>
-      <c r="D10" s="48"/>
-      <c r="E10" s="48"/>
-      <c r="F10" s="48"/>
+      <c r="B10" s="43"/>
+      <c r="C10" s="43"/>
+      <c r="D10" s="43"/>
+      <c r="E10" s="43"/>
+      <c r="F10" s="43"/>
       <c r="G10" s="12"/>
       <c r="H10" s="12"/>
-      <c r="I10" s="48" t="s">
-        <v>2</v>
-      </c>
-      <c r="J10" s="48"/>
-      <c r="K10" s="48"/>
-      <c r="L10" s="48"/>
-      <c r="M10" s="48"/>
-      <c r="N10" s="48"/>
-      <c r="O10" s="48"/>
-      <c r="P10" s="48"/>
+      <c r="I10" s="43" t="s">
+        <v>2</v>
+      </c>
+      <c r="J10" s="43"/>
+      <c r="K10" s="43"/>
+      <c r="L10" s="43"/>
+      <c r="M10" s="43"/>
+      <c r="N10" s="43"/>
+      <c r="O10" s="43"/>
+      <c r="P10" s="43"/>
     </row>
     <row r="11" spans="1:17" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="A11" s="51" t="s">
-        <v>0</v>
-      </c>
-      <c r="B11" s="51"/>
-      <c r="C11" s="51"/>
-      <c r="D11" s="51"/>
-      <c r="E11" s="51"/>
-      <c r="F11" s="51"/>
-      <c r="H11" s="51" t="s">
-        <v>0</v>
-      </c>
-      <c r="I11" s="51"/>
-      <c r="J11" s="51"/>
-      <c r="K11" s="51"/>
-      <c r="L11" s="51"/>
-      <c r="M11" s="51"/>
-      <c r="N11" s="51"/>
-      <c r="O11" s="51"/>
+      <c r="A11" s="48" t="s">
+        <v>0</v>
+      </c>
+      <c r="B11" s="48"/>
+      <c r="C11" s="48"/>
+      <c r="D11" s="48"/>
+      <c r="E11" s="48"/>
+      <c r="F11" s="48"/>
+      <c r="H11" s="48" t="s">
+        <v>0</v>
+      </c>
+      <c r="I11" s="48"/>
+      <c r="J11" s="48"/>
+      <c r="K11" s="48"/>
+      <c r="L11" s="48"/>
+      <c r="M11" s="48"/>
+      <c r="N11" s="48"/>
+      <c r="O11" s="48"/>
     </row>
     <row r="12" spans="1:17" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A12" s="43" t="s">
+      <c r="A12" s="45" t="s">
         <v>61</v>
       </c>
-      <c r="B12" s="43"/>
-      <c r="C12" s="45" t="s">
-        <v>3</v>
-      </c>
-      <c r="D12" s="45"/>
+      <c r="B12" s="45"/>
+      <c r="C12" s="49" t="s">
+        <v>3</v>
+      </c>
+      <c r="D12" s="49"/>
       <c r="E12" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="F12" s="45"/>
+      <c r="F12" s="49"/>
       <c r="G12" s="4"/>
-      <c r="H12" s="43" t="s">
+      <c r="H12" s="45" t="s">
         <v>61</v>
       </c>
-      <c r="I12" s="43"/>
-      <c r="J12" s="58" t="s">
-        <v>3</v>
-      </c>
-      <c r="K12" s="58"/>
-      <c r="L12" s="58"/>
-      <c r="M12" s="59" t="s">
-        <v>4</v>
-      </c>
-      <c r="N12" s="58"/>
-      <c r="O12" s="58"/>
+      <c r="I12" s="45"/>
+      <c r="J12" s="54" t="s">
+        <v>3</v>
+      </c>
+      <c r="K12" s="54"/>
+      <c r="L12" s="54"/>
+      <c r="M12" s="55" t="s">
+        <v>4</v>
+      </c>
+      <c r="N12" s="54"/>
+      <c r="O12" s="54"/>
       <c r="P12" s="4"/>
       <c r="Q12" s="4"/>
     </row>
     <row r="13" spans="1:17" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A13" s="44"/>
-      <c r="B13" s="44"/>
+      <c r="A13" s="46"/>
+      <c r="B13" s="46"/>
       <c r="C13" s="32" t="s">
         <v>5</v>
       </c>
@@ -2970,8 +2970,8 @@
         <v>6</v>
       </c>
       <c r="G13" s="5"/>
-      <c r="H13" s="44"/>
-      <c r="I13" s="44"/>
+      <c r="H13" s="46"/>
+      <c r="I13" s="46"/>
       <c r="J13" s="17" t="s">
         <v>7</v>
       </c>
@@ -3304,53 +3304,53 @@
       <c r="E21" s="47"/>
       <c r="F21" s="47"/>
       <c r="G21" s="19"/>
-      <c r="H21" s="60" t="s">
+      <c r="H21" s="44" t="s">
         <v>16</v>
       </c>
-      <c r="I21" s="60"/>
-      <c r="J21" s="60"/>
-      <c r="K21" s="60"/>
-      <c r="L21" s="60"/>
-      <c r="M21" s="60"/>
-      <c r="N21" s="60"/>
-      <c r="O21" s="60"/>
+      <c r="I21" s="44"/>
+      <c r="J21" s="44"/>
+      <c r="K21" s="44"/>
+      <c r="L21" s="44"/>
+      <c r="M21" s="44"/>
+      <c r="N21" s="44"/>
+      <c r="O21" s="44"/>
       <c r="P21" s="19"/>
       <c r="Q21" s="4"/>
     </row>
     <row r="22" spans="1:17" ht="21" x14ac:dyDescent="0.35">
-      <c r="A22" s="43" t="s">
+      <c r="A22" s="45" t="s">
         <v>61</v>
       </c>
-      <c r="B22" s="43"/>
-      <c r="C22" s="45" t="s">
-        <v>3</v>
-      </c>
-      <c r="D22" s="45"/>
-      <c r="E22" s="56" t="s">
-        <v>4</v>
-      </c>
-      <c r="F22" s="57"/>
+      <c r="B22" s="45"/>
+      <c r="C22" s="49" t="s">
+        <v>3</v>
+      </c>
+      <c r="D22" s="49"/>
+      <c r="E22" s="52" t="s">
+        <v>4</v>
+      </c>
+      <c r="F22" s="53"/>
       <c r="G22" s="8"/>
-      <c r="H22" s="43" t="s">
+      <c r="H22" s="45" t="s">
         <v>61</v>
       </c>
-      <c r="I22" s="43"/>
-      <c r="J22" s="58" t="s">
-        <v>3</v>
-      </c>
-      <c r="K22" s="58"/>
-      <c r="L22" s="58"/>
-      <c r="M22" s="61" t="s">
-        <v>4</v>
-      </c>
-      <c r="N22" s="62"/>
-      <c r="O22" s="62"/>
+      <c r="I22" s="45"/>
+      <c r="J22" s="54" t="s">
+        <v>3</v>
+      </c>
+      <c r="K22" s="54"/>
+      <c r="L22" s="54"/>
+      <c r="M22" s="56" t="s">
+        <v>4</v>
+      </c>
+      <c r="N22" s="57"/>
+      <c r="O22" s="57"/>
       <c r="P22" s="8"/>
       <c r="Q22" s="4"/>
     </row>
     <row r="23" spans="1:17" ht="21" x14ac:dyDescent="0.35">
-      <c r="A23" s="44"/>
-      <c r="B23" s="44"/>
+      <c r="A23" s="46"/>
+      <c r="B23" s="46"/>
       <c r="C23" s="32" t="s">
         <v>5</v>
       </c>
@@ -3364,8 +3364,8 @@
         <v>6</v>
       </c>
       <c r="G23" s="8"/>
-      <c r="H23" s="44"/>
-      <c r="I23" s="44"/>
+      <c r="H23" s="46"/>
+      <c r="I23" s="46"/>
       <c r="J23" s="17" t="s">
         <v>7</v>
       </c>
@@ -3708,59 +3708,59 @@
       <c r="Q31" s="4"/>
     </row>
     <row r="32" spans="1:17" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="A32" s="46" t="s">
+      <c r="A32" s="62" t="s">
         <v>62</v>
       </c>
-      <c r="B32" s="46"/>
-      <c r="C32" s="46"/>
-      <c r="D32" s="46"/>
-      <c r="E32" s="46"/>
-      <c r="F32" s="46"/>
+      <c r="B32" s="62"/>
+      <c r="C32" s="62"/>
+      <c r="D32" s="62"/>
+      <c r="E32" s="62"/>
+      <c r="F32" s="62"/>
       <c r="G32" s="4"/>
-      <c r="H32" s="60" t="s">
+      <c r="H32" s="44" t="s">
         <v>73</v>
       </c>
-      <c r="I32" s="60"/>
-      <c r="J32" s="60"/>
-      <c r="K32" s="60"/>
-      <c r="L32" s="60"/>
-      <c r="M32" s="60"/>
-      <c r="N32" s="60"/>
-      <c r="O32" s="60"/>
+      <c r="I32" s="44"/>
+      <c r="J32" s="44"/>
+      <c r="K32" s="44"/>
+      <c r="L32" s="44"/>
+      <c r="M32" s="44"/>
+      <c r="N32" s="44"/>
+      <c r="O32" s="44"/>
       <c r="P32" s="4"/>
       <c r="Q32" s="4"/>
     </row>
     <row r="33" spans="1:15" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A33" s="43" t="s">
+      <c r="A33" s="45" t="s">
         <v>61</v>
       </c>
-      <c r="B33" s="43"/>
-      <c r="C33" s="45" t="s">
-        <v>3</v>
-      </c>
-      <c r="D33" s="45"/>
-      <c r="E33" s="45" t="s">
-        <v>4</v>
-      </c>
-      <c r="F33" s="45"/>
-      <c r="H33" s="43" t="s">
+      <c r="B33" s="45"/>
+      <c r="C33" s="49" t="s">
+        <v>3</v>
+      </c>
+      <c r="D33" s="49"/>
+      <c r="E33" s="49" t="s">
+        <v>4</v>
+      </c>
+      <c r="F33" s="49"/>
+      <c r="H33" s="45" t="s">
         <v>61</v>
       </c>
-      <c r="I33" s="43"/>
-      <c r="J33" s="58" t="s">
-        <v>3</v>
-      </c>
-      <c r="K33" s="58"/>
-      <c r="L33" s="58"/>
-      <c r="M33" s="59" t="s">
-        <v>4</v>
-      </c>
-      <c r="N33" s="58"/>
-      <c r="O33" s="58"/>
+      <c r="I33" s="45"/>
+      <c r="J33" s="54" t="s">
+        <v>3</v>
+      </c>
+      <c r="K33" s="54"/>
+      <c r="L33" s="54"/>
+      <c r="M33" s="55" t="s">
+        <v>4</v>
+      </c>
+      <c r="N33" s="54"/>
+      <c r="O33" s="54"/>
     </row>
     <row r="34" spans="1:15" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A34" s="44"/>
-      <c r="B34" s="44"/>
+      <c r="A34" s="46"/>
+      <c r="B34" s="46"/>
       <c r="C34" s="13" t="s">
         <v>5</v>
       </c>
@@ -3773,8 +3773,8 @@
       <c r="F34" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="H34" s="44"/>
-      <c r="I34" s="44"/>
+      <c r="H34" s="46"/>
+      <c r="I34" s="46"/>
       <c r="J34" s="17" t="s">
         <v>7</v>
       </c>
@@ -3949,22 +3949,22 @@
       <c r="F42" s="47"/>
     </row>
     <row r="43" spans="1:15" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A43" s="43" t="s">
+      <c r="A43" s="45" t="s">
         <v>61</v>
       </c>
-      <c r="B43" s="43"/>
-      <c r="C43" s="45" t="s">
-        <v>3</v>
-      </c>
-      <c r="D43" s="45"/>
-      <c r="E43" s="45" t="s">
-        <v>4</v>
-      </c>
-      <c r="F43" s="45"/>
+      <c r="B43" s="45"/>
+      <c r="C43" s="49" t="s">
+        <v>3</v>
+      </c>
+      <c r="D43" s="49"/>
+      <c r="E43" s="49" t="s">
+        <v>4</v>
+      </c>
+      <c r="F43" s="49"/>
     </row>
     <row r="44" spans="1:15" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A44" s="44"/>
-      <c r="B44" s="44"/>
+      <c r="A44" s="46"/>
+      <c r="B44" s="46"/>
       <c r="C44" s="13" t="s">
         <v>5</v>
       </c>
@@ -4056,32 +4056,32 @@
       </c>
     </row>
     <row r="54" spans="1:6" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="A54" s="46" t="s">
+      <c r="A54" s="62" t="s">
         <v>62</v>
       </c>
-      <c r="B54" s="46"/>
-      <c r="C54" s="46"/>
-      <c r="D54" s="46"/>
-      <c r="E54" s="46"/>
-      <c r="F54" s="46"/>
+      <c r="B54" s="62"/>
+      <c r="C54" s="62"/>
+      <c r="D54" s="62"/>
+      <c r="E54" s="62"/>
+      <c r="F54" s="62"/>
     </row>
     <row r="55" spans="1:6" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A55" s="43" t="s">
+      <c r="A55" s="45" t="s">
         <v>61</v>
       </c>
-      <c r="B55" s="43"/>
-      <c r="C55" s="45" t="s">
-        <v>3</v>
-      </c>
-      <c r="D55" s="45"/>
-      <c r="E55" s="45" t="s">
-        <v>4</v>
-      </c>
-      <c r="F55" s="45"/>
+      <c r="B55" s="45"/>
+      <c r="C55" s="49" t="s">
+        <v>3</v>
+      </c>
+      <c r="D55" s="49"/>
+      <c r="E55" s="49" t="s">
+        <v>4</v>
+      </c>
+      <c r="F55" s="49"/>
     </row>
     <row r="56" spans="1:6" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A56" s="44"/>
-      <c r="B56" s="44"/>
+      <c r="A56" s="46"/>
+      <c r="B56" s="46"/>
       <c r="C56" s="13" t="s">
         <v>5</v>
       </c>
@@ -4214,22 +4214,22 @@
       <c r="F64" s="47"/>
     </row>
     <row r="65" spans="1:6" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A65" s="43" t="s">
+      <c r="A65" s="45" t="s">
         <v>61</v>
       </c>
-      <c r="B65" s="43"/>
-      <c r="C65" s="45" t="s">
-        <v>3</v>
-      </c>
-      <c r="D65" s="45"/>
-      <c r="E65" s="45" t="s">
-        <v>4</v>
-      </c>
-      <c r="F65" s="45"/>
+      <c r="B65" s="45"/>
+      <c r="C65" s="49" t="s">
+        <v>3</v>
+      </c>
+      <c r="D65" s="49"/>
+      <c r="E65" s="49" t="s">
+        <v>4</v>
+      </c>
+      <c r="F65" s="49"/>
     </row>
     <row r="66" spans="1:6" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A66" s="44"/>
-      <c r="B66" s="44"/>
+      <c r="A66" s="46"/>
+      <c r="B66" s="46"/>
       <c r="C66" s="13" t="s">
         <v>5</v>
       </c>
@@ -4353,32 +4353,6 @@
     </row>
   </sheetData>
   <mergeCells count="38">
-    <mergeCell ref="A10:F10"/>
-    <mergeCell ref="I10:P10"/>
-    <mergeCell ref="A11:F11"/>
-    <mergeCell ref="H11:O11"/>
-    <mergeCell ref="A12:B13"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="E12:F12"/>
-    <mergeCell ref="H12:I13"/>
-    <mergeCell ref="J12:L12"/>
-    <mergeCell ref="M12:O12"/>
-    <mergeCell ref="A21:F21"/>
-    <mergeCell ref="H21:O21"/>
-    <mergeCell ref="A22:B23"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="H22:I23"/>
-    <mergeCell ref="J22:L22"/>
-    <mergeCell ref="M22:O22"/>
-    <mergeCell ref="A32:F32"/>
-    <mergeCell ref="H32:O32"/>
-    <mergeCell ref="A33:B34"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="E33:F33"/>
-    <mergeCell ref="H33:I34"/>
-    <mergeCell ref="J33:L33"/>
-    <mergeCell ref="M33:O33"/>
     <mergeCell ref="A64:F64"/>
     <mergeCell ref="A65:B66"/>
     <mergeCell ref="C65:D65"/>
@@ -4391,6 +4365,32 @@
     <mergeCell ref="A55:B56"/>
     <mergeCell ref="C55:D55"/>
     <mergeCell ref="E55:F55"/>
+    <mergeCell ref="A32:F32"/>
+    <mergeCell ref="H32:O32"/>
+    <mergeCell ref="A33:B34"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="E33:F33"/>
+    <mergeCell ref="H33:I34"/>
+    <mergeCell ref="J33:L33"/>
+    <mergeCell ref="M33:O33"/>
+    <mergeCell ref="A21:F21"/>
+    <mergeCell ref="H21:O21"/>
+    <mergeCell ref="A22:B23"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="H22:I23"/>
+    <mergeCell ref="J22:L22"/>
+    <mergeCell ref="M22:O22"/>
+    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="I10:P10"/>
+    <mergeCell ref="A11:F11"/>
+    <mergeCell ref="H11:O11"/>
+    <mergeCell ref="A12:B13"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="H12:I13"/>
+    <mergeCell ref="J12:L12"/>
+    <mergeCell ref="M12:O12"/>
   </mergeCells>
   <conditionalFormatting sqref="C14:D19">
     <cfRule type="colorScale" priority="9">
@@ -4573,81 +4573,81 @@
       </c>
     </row>
     <row r="10" spans="1:17" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="48" t="s">
+      <c r="A10" s="43" t="s">
         <v>1</v>
       </c>
-      <c r="B10" s="48"/>
-      <c r="C10" s="48"/>
-      <c r="D10" s="48"/>
-      <c r="E10" s="48"/>
-      <c r="F10" s="48"/>
+      <c r="B10" s="43"/>
+      <c r="C10" s="43"/>
+      <c r="D10" s="43"/>
+      <c r="E10" s="43"/>
+      <c r="F10" s="43"/>
       <c r="G10" s="12"/>
       <c r="H10" s="12"/>
-      <c r="I10" s="48" t="s">
-        <v>2</v>
-      </c>
-      <c r="J10" s="48"/>
-      <c r="K10" s="48"/>
-      <c r="L10" s="48"/>
-      <c r="M10" s="48"/>
-      <c r="N10" s="48"/>
-      <c r="O10" s="48"/>
-      <c r="P10" s="48"/>
+      <c r="I10" s="43" t="s">
+        <v>2</v>
+      </c>
+      <c r="J10" s="43"/>
+      <c r="K10" s="43"/>
+      <c r="L10" s="43"/>
+      <c r="M10" s="43"/>
+      <c r="N10" s="43"/>
+      <c r="O10" s="43"/>
+      <c r="P10" s="43"/>
     </row>
     <row r="11" spans="1:17" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="A11" s="51" t="s">
-        <v>0</v>
-      </c>
-      <c r="B11" s="51"/>
-      <c r="C11" s="51"/>
-      <c r="D11" s="51"/>
-      <c r="E11" s="51"/>
-      <c r="F11" s="51"/>
-      <c r="H11" s="51" t="s">
-        <v>0</v>
-      </c>
-      <c r="I11" s="51"/>
-      <c r="J11" s="51"/>
-      <c r="K11" s="51"/>
-      <c r="L11" s="51"/>
-      <c r="M11" s="51"/>
-      <c r="N11" s="51"/>
-      <c r="O11" s="51"/>
+      <c r="A11" s="48" t="s">
+        <v>0</v>
+      </c>
+      <c r="B11" s="48"/>
+      <c r="C11" s="48"/>
+      <c r="D11" s="48"/>
+      <c r="E11" s="48"/>
+      <c r="F11" s="48"/>
+      <c r="H11" s="48" t="s">
+        <v>0</v>
+      </c>
+      <c r="I11" s="48"/>
+      <c r="J11" s="48"/>
+      <c r="K11" s="48"/>
+      <c r="L11" s="48"/>
+      <c r="M11" s="48"/>
+      <c r="N11" s="48"/>
+      <c r="O11" s="48"/>
     </row>
     <row r="12" spans="1:17" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A12" s="43" t="s">
+      <c r="A12" s="45" t="s">
         <v>61</v>
       </c>
-      <c r="B12" s="43"/>
-      <c r="C12" s="45" t="s">
-        <v>3</v>
-      </c>
-      <c r="D12" s="45"/>
+      <c r="B12" s="45"/>
+      <c r="C12" s="49" t="s">
+        <v>3</v>
+      </c>
+      <c r="D12" s="49"/>
       <c r="E12" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="F12" s="45"/>
+      <c r="F12" s="49"/>
       <c r="G12" s="4"/>
-      <c r="H12" s="43" t="s">
+      <c r="H12" s="45" t="s">
         <v>61</v>
       </c>
-      <c r="I12" s="43"/>
-      <c r="J12" s="58" t="s">
-        <v>3</v>
-      </c>
-      <c r="K12" s="58"/>
-      <c r="L12" s="58"/>
-      <c r="M12" s="59" t="s">
-        <v>4</v>
-      </c>
-      <c r="N12" s="58"/>
-      <c r="O12" s="58"/>
+      <c r="I12" s="45"/>
+      <c r="J12" s="54" t="s">
+        <v>3</v>
+      </c>
+      <c r="K12" s="54"/>
+      <c r="L12" s="54"/>
+      <c r="M12" s="55" t="s">
+        <v>4</v>
+      </c>
+      <c r="N12" s="54"/>
+      <c r="O12" s="54"/>
       <c r="P12" s="4"/>
       <c r="Q12" s="4"/>
     </row>
     <row r="13" spans="1:17" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="A13" s="44"/>
-      <c r="B13" s="44"/>
+      <c r="A13" s="46"/>
+      <c r="B13" s="46"/>
       <c r="C13" s="13" t="s">
         <v>69</v>
       </c>
@@ -4661,8 +4661,8 @@
         <v>6</v>
       </c>
       <c r="G13" s="5"/>
-      <c r="H13" s="44"/>
-      <c r="I13" s="44"/>
+      <c r="H13" s="46"/>
+      <c r="I13" s="46"/>
       <c r="J13" s="17" t="s">
         <v>70</v>
       </c>
@@ -4960,39 +4960,39 @@
       <c r="Q21" s="4"/>
     </row>
     <row r="22" spans="1:17" ht="21" x14ac:dyDescent="0.35">
-      <c r="A22" s="43" t="s">
+      <c r="A22" s="45" t="s">
         <v>61</v>
       </c>
-      <c r="B22" s="43"/>
-      <c r="C22" s="45" t="s">
-        <v>3</v>
-      </c>
-      <c r="D22" s="45"/>
+      <c r="B22" s="45"/>
+      <c r="C22" s="49" t="s">
+        <v>3</v>
+      </c>
+      <c r="D22" s="49"/>
       <c r="E22" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="F22" s="45"/>
+      <c r="F22" s="49"/>
       <c r="G22" s="8"/>
-      <c r="H22" s="43" t="s">
+      <c r="H22" s="45" t="s">
         <v>61</v>
       </c>
-      <c r="I22" s="43"/>
-      <c r="J22" s="58" t="s">
-        <v>3</v>
-      </c>
-      <c r="K22" s="58"/>
-      <c r="L22" s="58"/>
-      <c r="M22" s="59" t="s">
-        <v>4</v>
-      </c>
-      <c r="N22" s="58"/>
-      <c r="O22" s="58"/>
+      <c r="I22" s="45"/>
+      <c r="J22" s="54" t="s">
+        <v>3</v>
+      </c>
+      <c r="K22" s="54"/>
+      <c r="L22" s="54"/>
+      <c r="M22" s="55" t="s">
+        <v>4</v>
+      </c>
+      <c r="N22" s="54"/>
+      <c r="O22" s="54"/>
       <c r="P22" s="8"/>
       <c r="Q22" s="4"/>
     </row>
     <row r="23" spans="1:17" ht="21" x14ac:dyDescent="0.35">
-      <c r="A23" s="44"/>
-      <c r="B23" s="44"/>
+      <c r="A23" s="46"/>
+      <c r="B23" s="46"/>
       <c r="C23" s="13" t="s">
         <v>69</v>
       </c>
@@ -5006,8 +5006,8 @@
         <v>6</v>
       </c>
       <c r="G23" s="8"/>
-      <c r="H23" s="44"/>
-      <c r="I23" s="44"/>
+      <c r="H23" s="46"/>
+      <c r="I23" s="46"/>
       <c r="J23" s="17" t="s">
         <v>70</v>
       </c>
@@ -5302,14 +5302,14 @@
       <c r="Q31" s="4"/>
     </row>
     <row r="32" spans="1:17" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="A32" s="51" t="s">
+      <c r="A32" s="48" t="s">
         <v>62</v>
       </c>
-      <c r="B32" s="51"/>
-      <c r="C32" s="51"/>
-      <c r="D32" s="51"/>
-      <c r="E32" s="51"/>
-      <c r="F32" s="51"/>
+      <c r="B32" s="48"/>
+      <c r="C32" s="48"/>
+      <c r="D32" s="48"/>
+      <c r="E32" s="48"/>
+      <c r="F32" s="48"/>
       <c r="G32" s="4"/>
       <c r="H32" s="4"/>
       <c r="I32" s="4"/>
@@ -5323,22 +5323,22 @@
       <c r="Q32" s="4"/>
     </row>
     <row r="33" spans="1:6" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A33" s="43" t="s">
+      <c r="A33" s="45" t="s">
         <v>61</v>
       </c>
-      <c r="B33" s="43"/>
-      <c r="C33" s="45" t="s">
-        <v>3</v>
-      </c>
-      <c r="D33" s="45"/>
-      <c r="E33" s="45" t="s">
-        <v>4</v>
-      </c>
-      <c r="F33" s="45"/>
+      <c r="B33" s="45"/>
+      <c r="C33" s="49" t="s">
+        <v>3</v>
+      </c>
+      <c r="D33" s="49"/>
+      <c r="E33" s="49" t="s">
+        <v>4</v>
+      </c>
+      <c r="F33" s="49"/>
     </row>
     <row r="34" spans="1:6" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A34" s="44"/>
-      <c r="B34" s="44"/>
+      <c r="A34" s="46"/>
+      <c r="B34" s="46"/>
       <c r="C34" s="13" t="s">
         <v>5</v>
       </c>
@@ -5426,6 +5426,18 @@
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="A32:F32"/>
+    <mergeCell ref="A33:B34"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="E33:F33"/>
+    <mergeCell ref="A21:F21"/>
+    <mergeCell ref="I21:P21"/>
+    <mergeCell ref="A22:B23"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="H22:I23"/>
+    <mergeCell ref="J22:L22"/>
+    <mergeCell ref="M22:O22"/>
     <mergeCell ref="A10:F10"/>
     <mergeCell ref="I10:P10"/>
     <mergeCell ref="A11:F11"/>
@@ -5436,18 +5448,6 @@
     <mergeCell ref="H12:I13"/>
     <mergeCell ref="J12:L12"/>
     <mergeCell ref="M12:O12"/>
-    <mergeCell ref="I21:P21"/>
-    <mergeCell ref="A22:B23"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="H22:I23"/>
-    <mergeCell ref="J22:L22"/>
-    <mergeCell ref="M22:O22"/>
-    <mergeCell ref="A32:F32"/>
-    <mergeCell ref="A33:B34"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="E33:F33"/>
-    <mergeCell ref="A21:F21"/>
   </mergeCells>
   <conditionalFormatting sqref="C15:C19 E14:E19">
     <cfRule type="colorScale" priority="19">
@@ -5650,81 +5650,81 @@
       </c>
     </row>
     <row r="10" spans="1:17" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="48" t="s">
+      <c r="A10" s="43" t="s">
         <v>1</v>
       </c>
-      <c r="B10" s="48"/>
-      <c r="C10" s="48"/>
-      <c r="D10" s="48"/>
-      <c r="E10" s="48"/>
-      <c r="F10" s="48"/>
+      <c r="B10" s="43"/>
+      <c r="C10" s="43"/>
+      <c r="D10" s="43"/>
+      <c r="E10" s="43"/>
+      <c r="F10" s="43"/>
       <c r="G10" s="12"/>
       <c r="H10" s="12"/>
-      <c r="I10" s="48" t="s">
-        <v>2</v>
-      </c>
-      <c r="J10" s="48"/>
-      <c r="K10" s="48"/>
-      <c r="L10" s="48"/>
-      <c r="M10" s="48"/>
-      <c r="N10" s="48"/>
-      <c r="O10" s="48"/>
-      <c r="P10" s="48"/>
+      <c r="I10" s="43" t="s">
+        <v>2</v>
+      </c>
+      <c r="J10" s="43"/>
+      <c r="K10" s="43"/>
+      <c r="L10" s="43"/>
+      <c r="M10" s="43"/>
+      <c r="N10" s="43"/>
+      <c r="O10" s="43"/>
+      <c r="P10" s="43"/>
     </row>
     <row r="11" spans="1:17" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="A11" s="51" t="s">
-        <v>0</v>
-      </c>
-      <c r="B11" s="51"/>
-      <c r="C11" s="51"/>
-      <c r="D11" s="51"/>
-      <c r="E11" s="51"/>
-      <c r="F11" s="51"/>
-      <c r="H11" s="51" t="s">
-        <v>0</v>
-      </c>
-      <c r="I11" s="51"/>
-      <c r="J11" s="51"/>
-      <c r="K11" s="51"/>
-      <c r="L11" s="51"/>
-      <c r="M11" s="51"/>
-      <c r="N11" s="51"/>
-      <c r="O11" s="51"/>
+      <c r="A11" s="48" t="s">
+        <v>0</v>
+      </c>
+      <c r="B11" s="48"/>
+      <c r="C11" s="48"/>
+      <c r="D11" s="48"/>
+      <c r="E11" s="48"/>
+      <c r="F11" s="48"/>
+      <c r="H11" s="48" t="s">
+        <v>0</v>
+      </c>
+      <c r="I11" s="48"/>
+      <c r="J11" s="48"/>
+      <c r="K11" s="48"/>
+      <c r="L11" s="48"/>
+      <c r="M11" s="48"/>
+      <c r="N11" s="48"/>
+      <c r="O11" s="48"/>
     </row>
     <row r="12" spans="1:17" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A12" s="43" t="s">
+      <c r="A12" s="45" t="s">
         <v>61</v>
       </c>
-      <c r="B12" s="43"/>
-      <c r="C12" s="45" t="s">
-        <v>3</v>
-      </c>
-      <c r="D12" s="45"/>
+      <c r="B12" s="45"/>
+      <c r="C12" s="49" t="s">
+        <v>3</v>
+      </c>
+      <c r="D12" s="49"/>
       <c r="E12" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="F12" s="45"/>
+      <c r="F12" s="49"/>
       <c r="G12" s="4"/>
-      <c r="H12" s="43" t="s">
+      <c r="H12" s="45" t="s">
         <v>61</v>
       </c>
-      <c r="I12" s="43"/>
-      <c r="J12" s="58" t="s">
-        <v>3</v>
-      </c>
-      <c r="K12" s="58"/>
-      <c r="L12" s="58"/>
-      <c r="M12" s="59" t="s">
-        <v>4</v>
-      </c>
-      <c r="N12" s="58"/>
-      <c r="O12" s="58"/>
+      <c r="I12" s="45"/>
+      <c r="J12" s="54" t="s">
+        <v>3</v>
+      </c>
+      <c r="K12" s="54"/>
+      <c r="L12" s="54"/>
+      <c r="M12" s="55" t="s">
+        <v>4</v>
+      </c>
+      <c r="N12" s="54"/>
+      <c r="O12" s="54"/>
       <c r="P12" s="4"/>
       <c r="Q12" s="4"/>
     </row>
     <row r="13" spans="1:17" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="A13" s="44"/>
-      <c r="B13" s="44"/>
+      <c r="A13" s="46"/>
+      <c r="B13" s="46"/>
       <c r="C13" s="13" t="s">
         <v>69</v>
       </c>
@@ -5738,8 +5738,8 @@
         <v>6</v>
       </c>
       <c r="G13" s="5"/>
-      <c r="H13" s="44"/>
-      <c r="I13" s="44"/>
+      <c r="H13" s="46"/>
+      <c r="I13" s="46"/>
       <c r="J13" s="17" t="s">
         <v>70</v>
       </c>
@@ -6037,39 +6037,39 @@
       <c r="Q21" s="4"/>
     </row>
     <row r="22" spans="1:17" ht="21" x14ac:dyDescent="0.35">
-      <c r="A22" s="43" t="s">
+      <c r="A22" s="45" t="s">
         <v>61</v>
       </c>
-      <c r="B22" s="43"/>
-      <c r="C22" s="45" t="s">
-        <v>3</v>
-      </c>
-      <c r="D22" s="45"/>
+      <c r="B22" s="45"/>
+      <c r="C22" s="49" t="s">
+        <v>3</v>
+      </c>
+      <c r="D22" s="49"/>
       <c r="E22" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="F22" s="45"/>
+      <c r="F22" s="49"/>
       <c r="G22" s="8"/>
-      <c r="H22" s="43" t="s">
+      <c r="H22" s="45" t="s">
         <v>61</v>
       </c>
-      <c r="I22" s="43"/>
-      <c r="J22" s="58" t="s">
-        <v>3</v>
-      </c>
-      <c r="K22" s="58"/>
-      <c r="L22" s="58"/>
-      <c r="M22" s="59" t="s">
-        <v>4</v>
-      </c>
-      <c r="N22" s="58"/>
-      <c r="O22" s="58"/>
+      <c r="I22" s="45"/>
+      <c r="J22" s="54" t="s">
+        <v>3</v>
+      </c>
+      <c r="K22" s="54"/>
+      <c r="L22" s="54"/>
+      <c r="M22" s="55" t="s">
+        <v>4</v>
+      </c>
+      <c r="N22" s="54"/>
+      <c r="O22" s="54"/>
       <c r="P22" s="8"/>
       <c r="Q22" s="4"/>
     </row>
     <row r="23" spans="1:17" ht="21" x14ac:dyDescent="0.35">
-      <c r="A23" s="44"/>
-      <c r="B23" s="44"/>
+      <c r="A23" s="46"/>
+      <c r="B23" s="46"/>
       <c r="C23" s="13" t="s">
         <v>69</v>
       </c>
@@ -6083,8 +6083,8 @@
         <v>6</v>
       </c>
       <c r="G23" s="8"/>
-      <c r="H23" s="44"/>
-      <c r="I23" s="44"/>
+      <c r="H23" s="46"/>
+      <c r="I23" s="46"/>
       <c r="J23" s="17" t="s">
         <v>70</v>
       </c>
@@ -6379,14 +6379,14 @@
       <c r="Q31" s="4"/>
     </row>
     <row r="32" spans="1:17" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="A32" s="51" t="s">
+      <c r="A32" s="48" t="s">
         <v>62</v>
       </c>
-      <c r="B32" s="51"/>
-      <c r="C32" s="51"/>
-      <c r="D32" s="51"/>
-      <c r="E32" s="51"/>
-      <c r="F32" s="51"/>
+      <c r="B32" s="48"/>
+      <c r="C32" s="48"/>
+      <c r="D32" s="48"/>
+      <c r="E32" s="48"/>
+      <c r="F32" s="48"/>
       <c r="G32" s="4"/>
       <c r="H32" s="4"/>
       <c r="I32" s="4"/>
@@ -6400,22 +6400,22 @@
       <c r="Q32" s="4"/>
     </row>
     <row r="33" spans="1:6" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A33" s="43" t="s">
+      <c r="A33" s="45" t="s">
         <v>61</v>
       </c>
-      <c r="B33" s="43"/>
-      <c r="C33" s="45" t="s">
-        <v>3</v>
-      </c>
-      <c r="D33" s="45"/>
-      <c r="E33" s="45" t="s">
-        <v>4</v>
-      </c>
-      <c r="F33" s="45"/>
+      <c r="B33" s="45"/>
+      <c r="C33" s="49" t="s">
+        <v>3</v>
+      </c>
+      <c r="D33" s="49"/>
+      <c r="E33" s="49" t="s">
+        <v>4</v>
+      </c>
+      <c r="F33" s="49"/>
     </row>
     <row r="34" spans="1:6" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A34" s="44"/>
-      <c r="B34" s="44"/>
+      <c r="A34" s="46"/>
+      <c r="B34" s="46"/>
       <c r="C34" s="13" t="s">
         <v>5</v>
       </c>
@@ -6503,6 +6503,18 @@
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="A32:F32"/>
+    <mergeCell ref="A33:B34"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="E33:F33"/>
+    <mergeCell ref="A21:F21"/>
+    <mergeCell ref="I21:P21"/>
+    <mergeCell ref="A22:B23"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="H22:I23"/>
+    <mergeCell ref="J22:L22"/>
+    <mergeCell ref="M22:O22"/>
     <mergeCell ref="A10:F10"/>
     <mergeCell ref="I10:P10"/>
     <mergeCell ref="A11:F11"/>
@@ -6513,18 +6525,6 @@
     <mergeCell ref="H12:I13"/>
     <mergeCell ref="J12:L12"/>
     <mergeCell ref="M12:O12"/>
-    <mergeCell ref="I21:P21"/>
-    <mergeCell ref="A22:B23"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="H22:I23"/>
-    <mergeCell ref="J22:L22"/>
-    <mergeCell ref="M22:O22"/>
-    <mergeCell ref="A32:F32"/>
-    <mergeCell ref="A33:B34"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="E33:F33"/>
-    <mergeCell ref="A21:F21"/>
   </mergeCells>
   <conditionalFormatting sqref="C15:C19 E14:E19">
     <cfRule type="colorScale" priority="13">
@@ -6987,6 +6987,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="e8c8a8d2-cf65-4fdf-b6bc-794ebda6188e" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f72adabb-0ee4-4963-acd9-9efc158f92a6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009074E2A1C82F3C4BA659A6C6CC51AC5F" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0765d5a41f49df217abeb23dcfb0b3cf">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="cc5908d1-2a89-4186-9c08-2c76e53ac163" xmlns:ns3="f72adabb-0ee4-4963-acd9-9efc158f92a6" xmlns:ns4="e8c8a8d2-cf65-4fdf-b6bc-794ebda6188e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="519818410c367a5844210e380df69fc7" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="cc5908d1-2a89-4186-9c08-2c76e53ac163"/>
@@ -7234,27 +7254,33 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{78150E95-1CCA-47FB-B6E6-99D8675B2929}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="f72adabb-0ee4-4963-acd9-9efc158f92a6"/>
+    <ds:schemaRef ds:uri="cc5908d1-2a89-4186-9c08-2c76e53ac163"/>
+    <ds:schemaRef ds:uri="e8c8a8d2-cf65-4fdf-b6bc-794ebda6188e"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="e8c8a8d2-cf65-4fdf-b6bc-794ebda6188e" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f72adabb-0ee4-4963-acd9-9efc158f92a6">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{29C58647-0154-48BC-9EDF-8ABD72381C6C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4039D020-CA7C-47AE-A105-0DAEDCC57394}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -7272,30 +7298,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{29C58647-0154-48BC-9EDF-8ABD72381C6C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{78150E95-1CCA-47FB-B6E6-99D8675B2929}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="f72adabb-0ee4-4963-acd9-9efc158f92a6"/>
-    <ds:schemaRef ds:uri="cc5908d1-2a89-4186-9c08-2c76e53ac163"/>
-    <ds:schemaRef ds:uri="e8c8a8d2-cf65-4fdf-b6bc-794ebda6188e"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/output/V3_SIM_Results_Summary.xlsx
+++ b/output/V3_SIM_Results_Summary.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="J:\HCHS\STATISTICS\GRAS\Beibo\Computing Requests\HCHS_simulation\output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D9AA0CE-A3EE-4C0B-84B0-CBEB18ED9AD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22226D07-A136-49FD-A8C8-BE267114AC34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="761" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Summary  (coverage)" sheetId="16" r:id="rId1"/>
+    <sheet name="Summary  (coverage) 0.920 0.980" sheetId="16" r:id="rId1"/>
     <sheet name="Eff comparison" sheetId="20" r:id="rId2"/>
     <sheet name="note" sheetId="3" r:id="rId3"/>
   </sheets>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="419" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="423" uniqueCount="98">
   <si>
     <t>Continous Outcome, PROC GENMOD</t>
   </si>
@@ -416,12 +416,18 @@
   <si>
     <t>Good coverage range: [0.920, 0.980]</t>
   </si>
+  <si>
+    <t>Efficiency comparsion, 1 &gt; 6 &gt; 4 &gt; 3</t>
+  </si>
+  <si>
+    <t>Efficiency comparsion, 6 &gt; 4</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -539,6 +545,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -627,9 +640,10 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -723,20 +737,43 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -747,39 +784,17 @@
     <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{DF275C86-0B03-4CFF-ABD8-37BCBF4B170E}"/>
+    <cellStyle name="Normal 3" xfId="2" xr:uid="{6986CE76-6DA6-4463-B446-A1AC80E040AE}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1057,7 +1072,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAB8470B-C760-491C-B73B-F574B62DA7BA}">
-  <dimension ref="A1:Y53"/>
+  <dimension ref="A1:Y54"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3.140625" bestFit="1" customWidth="1"/>
@@ -1091,10 +1106,10 @@
       <c r="I1" s="23" t="s">
         <v>95</v>
       </c>
-      <c r="J1" s="54"/>
-      <c r="K1" s="54"/>
-      <c r="L1" s="54"/>
-      <c r="M1" s="54"/>
+      <c r="J1" s="37"/>
+      <c r="K1" s="37"/>
+      <c r="L1" s="37"/>
+      <c r="M1" s="37"/>
     </row>
     <row r="2" spans="1:25" ht="20.25" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
@@ -1103,10 +1118,10 @@
       <c r="I2" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="J2" s="54"/>
-      <c r="K2" s="54"/>
-      <c r="L2" s="54"/>
-      <c r="M2" s="54"/>
+      <c r="J2" s="37"/>
+      <c r="K2" s="37"/>
+      <c r="L2" s="37"/>
+      <c r="M2" s="37"/>
     </row>
     <row r="3" spans="1:25" ht="20.25" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
@@ -1115,10 +1130,10 @@
       <c r="I3" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="J3" s="54"/>
-      <c r="K3" s="54"/>
-      <c r="L3" s="54"/>
-      <c r="M3" s="54"/>
+      <c r="J3" s="37"/>
+      <c r="K3" s="37"/>
+      <c r="L3" s="37"/>
+      <c r="M3" s="37"/>
     </row>
     <row r="4" spans="1:25" ht="20.25" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
@@ -1127,43 +1142,43 @@
       <c r="I4" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="J4" s="54"/>
-      <c r="K4" s="54"/>
-      <c r="L4" s="54"/>
-      <c r="M4" s="54"/>
+      <c r="J4" s="37"/>
+      <c r="K4" s="37"/>
+      <c r="L4" s="37"/>
+      <c r="M4" s="37"/>
     </row>
     <row r="5" spans="1:25" ht="20.25" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>65</v>
       </c>
-      <c r="J5" s="54"/>
-      <c r="K5" s="54"/>
-      <c r="L5" s="54"/>
-      <c r="M5" s="54"/>
+      <c r="J5" s="37"/>
+      <c r="K5" s="37"/>
+      <c r="L5" s="37"/>
+      <c r="M5" s="37"/>
     </row>
     <row r="6" spans="1:25" ht="20.25" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>66</v>
       </c>
-      <c r="J6" s="54"/>
-      <c r="K6" s="54"/>
-      <c r="L6" s="54"/>
-      <c r="M6" s="54"/>
+      <c r="J6" s="37"/>
+      <c r="K6" s="37"/>
+      <c r="L6" s="37"/>
+      <c r="M6" s="37"/>
     </row>
     <row r="7" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>67</v>
       </c>
-      <c r="J7" s="55"/>
-      <c r="K7" s="55"/>
-      <c r="L7" s="55"/>
-      <c r="M7" s="55"/>
+      <c r="J7" s="38"/>
+      <c r="K7" s="38"/>
+      <c r="L7" s="38"/>
+      <c r="M7" s="38"/>
     </row>
     <row r="8" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="J8" s="55"/>
-      <c r="K8" s="55"/>
-      <c r="L8" s="55"/>
-      <c r="M8" s="55"/>
+      <c r="J8" s="38"/>
+      <c r="K8" s="38"/>
+      <c r="L8" s="38"/>
+      <c r="M8" s="38"/>
     </row>
     <row r="9" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
@@ -1171,115 +1186,115 @@
       </c>
     </row>
     <row r="10" spans="1:25" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="49" t="s">
+      <c r="A10" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="B10" s="49"/>
-      <c r="C10" s="49"/>
-      <c r="D10" s="49"/>
-      <c r="E10" s="49"/>
-      <c r="F10" s="49"/>
+      <c r="B10" s="39"/>
+      <c r="C10" s="39"/>
+      <c r="D10" s="39"/>
+      <c r="E10" s="39"/>
+      <c r="F10" s="39"/>
       <c r="G10" s="20"/>
-      <c r="H10" s="49" t="s">
+      <c r="H10" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="I10" s="49"/>
-      <c r="J10" s="49"/>
-      <c r="K10" s="49"/>
-      <c r="L10" s="49"/>
-      <c r="M10" s="49"/>
+      <c r="I10" s="39"/>
+      <c r="J10" s="39"/>
+      <c r="K10" s="39"/>
+      <c r="L10" s="39"/>
+      <c r="M10" s="39"/>
       <c r="N10" s="20"/>
       <c r="O10" s="10"/>
-      <c r="P10" s="52" t="s">
+      <c r="P10" s="47" t="s">
         <v>2</v>
       </c>
-      <c r="Q10" s="52"/>
-      <c r="R10" s="52"/>
-      <c r="S10" s="52"/>
-      <c r="T10" s="52"/>
-      <c r="U10" s="52"/>
-      <c r="V10" s="52"/>
-      <c r="W10" s="52"/>
+      <c r="Q10" s="47"/>
+      <c r="R10" s="47"/>
+      <c r="S10" s="47"/>
+      <c r="T10" s="47"/>
+      <c r="U10" s="47"/>
+      <c r="V10" s="47"/>
+      <c r="W10" s="47"/>
       <c r="X10" s="30"/>
     </row>
     <row r="11" spans="1:25" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="A11" s="51" t="s">
-        <v>0</v>
-      </c>
-      <c r="B11" s="51"/>
-      <c r="C11" s="51"/>
-      <c r="D11" s="51"/>
-      <c r="E11" s="51"/>
-      <c r="F11" s="51"/>
+      <c r="A11" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="B11" s="44"/>
+      <c r="C11" s="44"/>
+      <c r="D11" s="44"/>
+      <c r="E11" s="44"/>
+      <c r="F11" s="44"/>
       <c r="G11" s="24"/>
-      <c r="H11" s="51" t="s">
+      <c r="H11" s="44" t="s">
         <v>62</v>
       </c>
-      <c r="I11" s="51"/>
-      <c r="J11" s="51"/>
-      <c r="K11" s="51"/>
-      <c r="L11" s="51"/>
-      <c r="M11" s="51"/>
+      <c r="I11" s="44"/>
+      <c r="J11" s="44"/>
+      <c r="K11" s="44"/>
+      <c r="L11" s="44"/>
+      <c r="M11" s="44"/>
       <c r="N11" s="24"/>
-      <c r="P11" s="51" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="51"/>
-      <c r="R11" s="51"/>
-      <c r="S11" s="51"/>
-      <c r="T11" s="51"/>
-      <c r="U11" s="51"/>
-      <c r="V11" s="51"/>
-      <c r="W11" s="51"/>
+      <c r="P11" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="44"/>
+      <c r="R11" s="44"/>
+      <c r="S11" s="44"/>
+      <c r="T11" s="44"/>
+      <c r="U11" s="44"/>
+      <c r="V11" s="44"/>
+      <c r="W11" s="44"/>
     </row>
     <row r="12" spans="1:25" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A12" s="37" t="s">
+      <c r="A12" s="41" t="s">
         <v>61</v>
       </c>
-      <c r="B12" s="37"/>
-      <c r="C12" s="39" t="s">
+      <c r="B12" s="41"/>
+      <c r="C12" s="45" t="s">
         <v>3</v>
       </c>
-      <c r="D12" s="39"/>
+      <c r="D12" s="45"/>
       <c r="E12" s="46" t="s">
         <v>4</v>
       </c>
-      <c r="F12" s="39"/>
+      <c r="F12" s="45"/>
       <c r="G12" s="25"/>
-      <c r="H12" s="37" t="s">
+      <c r="H12" s="41" t="s">
         <v>61</v>
       </c>
-      <c r="I12" s="37"/>
-      <c r="J12" s="39" t="s">
+      <c r="I12" s="41"/>
+      <c r="J12" s="45" t="s">
         <v>3</v>
       </c>
-      <c r="K12" s="39"/>
+      <c r="K12" s="45"/>
       <c r="L12" s="46" t="s">
         <v>4</v>
       </c>
-      <c r="M12" s="39"/>
+      <c r="M12" s="45"/>
       <c r="N12" s="25"/>
       <c r="O12" s="4"/>
-      <c r="P12" s="37" t="s">
+      <c r="P12" s="41" t="s">
         <v>61</v>
       </c>
-      <c r="Q12" s="37"/>
-      <c r="R12" s="47" t="s">
+      <c r="Q12" s="41"/>
+      <c r="R12" s="49" t="s">
         <v>3</v>
       </c>
-      <c r="S12" s="47"/>
-      <c r="T12" s="47"/>
-      <c r="U12" s="48" t="s">
+      <c r="S12" s="49"/>
+      <c r="T12" s="49"/>
+      <c r="U12" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="V12" s="47"/>
-      <c r="W12" s="47"/>
+      <c r="V12" s="49"/>
+      <c r="W12" s="49"/>
       <c r="X12" s="4"/>
       <c r="Y12" s="4"/>
     </row>
     <row r="13" spans="1:25" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A13" s="38"/>
-      <c r="B13" s="38"/>
+      <c r="A13" s="42"/>
+      <c r="B13" s="42"/>
       <c r="C13" s="21" t="s">
         <v>5</v>
       </c>
@@ -1293,8 +1308,8 @@
         <v>6</v>
       </c>
       <c r="G13" s="26"/>
-      <c r="H13" s="38"/>
-      <c r="I13" s="38"/>
+      <c r="H13" s="42"/>
+      <c r="I13" s="42"/>
       <c r="J13" s="21" t="s">
         <v>5</v>
       </c>
@@ -1309,8 +1324,8 @@
       </c>
       <c r="N13" s="26"/>
       <c r="O13" s="5"/>
-      <c r="P13" s="38"/>
-      <c r="Q13" s="38"/>
+      <c r="P13" s="42"/>
+      <c r="Q13" s="42"/>
       <c r="R13" s="14" t="s">
         <v>7</v>
       </c>
@@ -1734,233 +1749,191 @@
       <c r="X19" s="7"/>
       <c r="Y19" s="4"/>
     </row>
-    <row r="20" spans="1:25" ht="21" x14ac:dyDescent="0.35">
-      <c r="A20" s="7"/>
-      <c r="B20" s="7"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="7"/>
-      <c r="F20" s="7"/>
-      <c r="G20" s="7"/>
-      <c r="H20" s="7"/>
-      <c r="I20" s="7"/>
-      <c r="J20" s="7"/>
-      <c r="K20" s="7"/>
-      <c r="L20" s="7"/>
-      <c r="M20" s="7"/>
-      <c r="N20" s="7"/>
-      <c r="O20" s="7"/>
-      <c r="P20" s="7"/>
-      <c r="Q20" s="7"/>
-      <c r="R20" s="7"/>
+    <row r="20" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A20" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="B20" s="4"/>
+      <c r="C20" s="4"/>
+      <c r="D20" s="4"/>
+      <c r="E20" s="4"/>
+      <c r="F20" s="4"/>
+      <c r="G20" s="4"/>
+      <c r="H20" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="I20" s="4"/>
+      <c r="J20" s="4"/>
+      <c r="K20" s="4"/>
+      <c r="L20" s="4"/>
+      <c r="M20" s="4"/>
+      <c r="N20" s="4"/>
+      <c r="O20" s="4"/>
+      <c r="P20" s="4"/>
+      <c r="Q20" s="4"/>
+      <c r="R20" s="4"/>
       <c r="S20" s="4"/>
     </row>
-    <row r="21" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="41" t="s">
+    <row r="21" spans="1:25" ht="21" x14ac:dyDescent="0.35">
+      <c r="A21" s="7"/>
+      <c r="B21" s="7"/>
+      <c r="C21" s="7"/>
+      <c r="D21" s="7"/>
+      <c r="E21" s="7"/>
+      <c r="F21" s="7"/>
+      <c r="G21" s="7"/>
+      <c r="H21" s="7"/>
+      <c r="I21" s="7"/>
+      <c r="J21" s="7"/>
+      <c r="K21" s="7"/>
+      <c r="L21" s="7"/>
+      <c r="M21" s="7"/>
+      <c r="N21" s="7"/>
+      <c r="O21" s="7"/>
+      <c r="P21" s="7"/>
+      <c r="Q21" s="7"/>
+      <c r="R21" s="7"/>
+      <c r="S21" s="4"/>
+    </row>
+    <row r="22" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="43" t="s">
         <v>16</v>
       </c>
-      <c r="B21" s="41"/>
-      <c r="C21" s="41"/>
-      <c r="D21" s="41"/>
-      <c r="E21" s="41"/>
-      <c r="F21" s="41"/>
-      <c r="G21" s="27"/>
-      <c r="H21" s="41" t="s">
+      <c r="B22" s="43"/>
+      <c r="C22" s="43"/>
+      <c r="D22" s="43"/>
+      <c r="E22" s="43"/>
+      <c r="F22" s="43"/>
+      <c r="G22" s="27"/>
+      <c r="H22" s="43" t="s">
         <v>71</v>
       </c>
-      <c r="I21" s="41"/>
-      <c r="J21" s="41"/>
-      <c r="K21" s="41"/>
-      <c r="L21" s="41"/>
-      <c r="M21" s="41"/>
-      <c r="N21" s="27"/>
-      <c r="O21" s="15"/>
-      <c r="P21" s="50" t="s">
+      <c r="I22" s="43"/>
+      <c r="J22" s="43"/>
+      <c r="K22" s="43"/>
+      <c r="L22" s="43"/>
+      <c r="M22" s="43"/>
+      <c r="N22" s="27"/>
+      <c r="O22" s="15"/>
+      <c r="P22" s="40" t="s">
         <v>16</v>
       </c>
-      <c r="Q21" s="50"/>
-      <c r="R21" s="50"/>
-      <c r="S21" s="50"/>
-      <c r="T21" s="50"/>
-      <c r="U21" s="50"/>
-      <c r="V21" s="50"/>
-      <c r="W21" s="50"/>
-      <c r="X21" s="15"/>
-      <c r="Y21" s="4"/>
-    </row>
-    <row r="22" spans="1:25" ht="21" x14ac:dyDescent="0.35">
-      <c r="A22" s="37" t="s">
+      <c r="Q22" s="40"/>
+      <c r="R22" s="40"/>
+      <c r="S22" s="40"/>
+      <c r="T22" s="40"/>
+      <c r="U22" s="40"/>
+      <c r="V22" s="40"/>
+      <c r="W22" s="40"/>
+      <c r="X22" s="15"/>
+      <c r="Y22" s="4"/>
+    </row>
+    <row r="23" spans="1:25" ht="21" x14ac:dyDescent="0.35">
+      <c r="A23" s="41" t="s">
         <v>61</v>
       </c>
-      <c r="B22" s="37"/>
-      <c r="C22" s="39" t="s">
+      <c r="B23" s="41"/>
+      <c r="C23" s="45" t="s">
         <v>3</v>
       </c>
-      <c r="D22" s="39"/>
-      <c r="E22" s="46" t="s">
+      <c r="D23" s="45"/>
+      <c r="E23" s="46" t="s">
         <v>4</v>
       </c>
-      <c r="F22" s="39"/>
-      <c r="G22" s="28"/>
-      <c r="H22" s="37" t="s">
+      <c r="F23" s="45"/>
+      <c r="G23" s="28"/>
+      <c r="H23" s="41" t="s">
         <v>61</v>
       </c>
-      <c r="I22" s="37"/>
-      <c r="J22" s="39" t="s">
+      <c r="I23" s="41"/>
+      <c r="J23" s="45" t="s">
         <v>3</v>
       </c>
-      <c r="K22" s="39"/>
-      <c r="L22" s="46" t="s">
+      <c r="K23" s="45"/>
+      <c r="L23" s="46" t="s">
         <v>4</v>
       </c>
-      <c r="M22" s="39"/>
-      <c r="N22" s="25"/>
-      <c r="O22" s="7"/>
-      <c r="P22" s="37" t="s">
+      <c r="M23" s="45"/>
+      <c r="N23" s="25"/>
+      <c r="O23" s="7"/>
+      <c r="P23" s="41" t="s">
         <v>61</v>
       </c>
-      <c r="Q22" s="37"/>
-      <c r="R22" s="47" t="s">
+      <c r="Q23" s="41"/>
+      <c r="R23" s="49" t="s">
         <v>3</v>
       </c>
-      <c r="S22" s="47"/>
-      <c r="T22" s="47"/>
-      <c r="U22" s="48" t="s">
+      <c r="S23" s="49"/>
+      <c r="T23" s="49"/>
+      <c r="U23" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="V22" s="47"/>
-      <c r="W22" s="47"/>
-      <c r="X22" s="7"/>
-      <c r="Y22" s="4"/>
-    </row>
-    <row r="23" spans="1:25" ht="21" x14ac:dyDescent="0.35">
-      <c r="A23" s="38"/>
-      <c r="B23" s="38"/>
-      <c r="C23" s="21" t="s">
-        <v>5</v>
-      </c>
-      <c r="D23" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="E23" s="22" t="s">
-        <v>5</v>
-      </c>
-      <c r="F23" s="31" t="s">
-        <v>6</v>
-      </c>
-      <c r="G23" s="28"/>
-      <c r="H23" s="38"/>
-      <c r="I23" s="38"/>
-      <c r="J23" s="21" t="s">
-        <v>5</v>
-      </c>
-      <c r="K23" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="L23" s="22" t="s">
-        <v>5</v>
-      </c>
-      <c r="M23" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="N23" s="26"/>
-      <c r="O23" s="7"/>
-      <c r="P23" s="38"/>
-      <c r="Q23" s="38"/>
-      <c r="R23" s="14" t="s">
-        <v>7</v>
-      </c>
-      <c r="S23" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="T23" s="19" t="s">
-        <v>9</v>
-      </c>
-      <c r="U23" s="18" t="s">
-        <v>7</v>
-      </c>
-      <c r="V23" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="W23" s="19" t="s">
-        <v>9</v>
-      </c>
+      <c r="V23" s="49"/>
+      <c r="W23" s="49"/>
       <c r="X23" s="7"/>
       <c r="Y23" s="4"/>
     </row>
     <row r="24" spans="1:25" ht="21" x14ac:dyDescent="0.35">
-      <c r="A24" s="8">
-        <v>1</v>
-      </c>
-      <c r="B24" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="C24" s="16">
-        <v>4</v>
-      </c>
-      <c r="D24" s="16">
-        <v>4</v>
-      </c>
-      <c r="E24" s="16">
-        <v>4</v>
-      </c>
-      <c r="F24" s="16">
-        <v>3</v>
-      </c>
-      <c r="G24" s="16"/>
-      <c r="H24" s="8">
-        <v>1</v>
-      </c>
-      <c r="I24" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="J24" s="16">
-        <v>5</v>
-      </c>
-      <c r="K24" s="16">
-        <v>4</v>
-      </c>
-      <c r="L24" s="16">
-        <v>4</v>
-      </c>
-      <c r="M24" s="16">
-        <v>4</v>
-      </c>
-      <c r="N24" s="16"/>
-      <c r="O24" s="9"/>
-      <c r="P24" s="8">
-        <v>1</v>
-      </c>
-      <c r="Q24" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="R24" s="16">
-        <v>0</v>
-      </c>
-      <c r="S24" s="16">
-        <v>0</v>
-      </c>
-      <c r="T24" s="16">
-        <v>0</v>
-      </c>
-      <c r="U24" s="16">
-        <v>0</v>
-      </c>
-      <c r="V24" s="16">
-        <v>0</v>
-      </c>
-      <c r="W24" s="16">
-        <v>0</v>
-      </c>
-      <c r="X24" s="9"/>
+      <c r="A24" s="42"/>
+      <c r="B24" s="42"/>
+      <c r="C24" s="21" t="s">
+        <v>5</v>
+      </c>
+      <c r="D24" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="E24" s="22" t="s">
+        <v>5</v>
+      </c>
+      <c r="F24" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="G24" s="28"/>
+      <c r="H24" s="42"/>
+      <c r="I24" s="42"/>
+      <c r="J24" s="21" t="s">
+        <v>5</v>
+      </c>
+      <c r="K24" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="L24" s="22" t="s">
+        <v>5</v>
+      </c>
+      <c r="M24" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="N24" s="26"/>
+      <c r="O24" s="7"/>
+      <c r="P24" s="42"/>
+      <c r="Q24" s="42"/>
+      <c r="R24" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="S24" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="T24" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="U24" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="V24" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="W24" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="X24" s="7"/>
       <c r="Y24" s="4"/>
     </row>
     <row r="25" spans="1:25" ht="21" x14ac:dyDescent="0.35">
       <c r="A25" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C25" s="16">
         <v>4</v>
@@ -1969,20 +1942,20 @@
         <v>4</v>
       </c>
       <c r="E25" s="16">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F25" s="16">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G25" s="16"/>
       <c r="H25" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I25" s="8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J25" s="16">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K25" s="16">
         <v>4</v>
@@ -1996,77 +1969,77 @@
       <c r="N25" s="16"/>
       <c r="O25" s="9"/>
       <c r="P25" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q25" s="8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R25" s="16">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S25" s="16">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T25" s="16">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U25" s="16">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V25" s="16">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="W25" s="16">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="X25" s="9"/>
       <c r="Y25" s="4"/>
     </row>
     <row r="26" spans="1:25" ht="21" x14ac:dyDescent="0.35">
       <c r="A26" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C26" s="16">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D26" s="16">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E26" s="16">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F26" s="16">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G26" s="16"/>
       <c r="H26" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I26" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J26" s="16">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K26" s="16">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L26" s="16">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M26" s="16">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N26" s="16"/>
       <c r="O26" s="9"/>
       <c r="P26" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q26" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="R26" s="16">
         <v>3</v>
@@ -2075,54 +2048,54 @@
         <v>3</v>
       </c>
       <c r="T26" s="16">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U26" s="16">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V26" s="16">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W26" s="16">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X26" s="9"/>
       <c r="Y26" s="4"/>
     </row>
     <row r="27" spans="1:25" ht="21" x14ac:dyDescent="0.35">
       <c r="A27" s="8">
+        <v>3</v>
+      </c>
+      <c r="B27" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C27" s="16">
         <v>4</v>
       </c>
-      <c r="B27" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C27" s="16">
-        <v>0</v>
-      </c>
       <c r="D27" s="16">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E27" s="16">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F27" s="16">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G27" s="16"/>
       <c r="H27" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I27" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J27" s="16">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K27" s="16">
         <v>2</v>
       </c>
       <c r="L27" s="16">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M27" s="16">
         <v>2</v>
@@ -2130,196 +2103,246 @@
       <c r="N27" s="16"/>
       <c r="O27" s="9"/>
       <c r="P27" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q27" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="R27" s="16">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S27" s="16">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T27" s="16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U27" s="16">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V27" s="16">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W27" s="16">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X27" s="9"/>
       <c r="Y27" s="4"/>
     </row>
     <row r="28" spans="1:25" ht="21" x14ac:dyDescent="0.35">
       <c r="A28" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C28" s="16">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D28" s="16">
         <v>2</v>
       </c>
       <c r="E28" s="16">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F28" s="16">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G28" s="16"/>
       <c r="H28" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I28" s="8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J28" s="16">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K28" s="16">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L28" s="16">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M28" s="16">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N28" s="16"/>
       <c r="O28" s="9"/>
       <c r="P28" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q28" s="8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="R28" s="16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S28" s="16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T28" s="16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U28" s="16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V28" s="16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W28" s="16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X28" s="9"/>
       <c r="Y28" s="4"/>
     </row>
     <row r="29" spans="1:25" ht="21" x14ac:dyDescent="0.35">
-      <c r="A29" s="13">
-        <v>6</v>
-      </c>
-      <c r="B29" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="C29" s="17">
-        <v>0</v>
-      </c>
-      <c r="D29" s="17">
+      <c r="A29" s="8">
+        <v>5</v>
+      </c>
+      <c r="B29" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C29" s="16">
+        <v>5</v>
+      </c>
+      <c r="D29" s="16">
         <v>2</v>
       </c>
-      <c r="E29" s="17">
-        <v>0</v>
-      </c>
-      <c r="F29" s="17">
-        <v>2</v>
+      <c r="E29" s="16">
+        <v>5</v>
+      </c>
+      <c r="F29" s="16">
+        <v>3</v>
       </c>
       <c r="G29" s="16"/>
-      <c r="H29" s="13">
-        <v>6</v>
-      </c>
-      <c r="I29" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="J29" s="17">
-        <v>0</v>
-      </c>
-      <c r="K29" s="17">
-        <v>2</v>
-      </c>
-      <c r="L29" s="17">
-        <v>2</v>
-      </c>
-      <c r="M29" s="17">
-        <v>3</v>
+      <c r="H29" s="8">
+        <v>5</v>
+      </c>
+      <c r="I29" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="J29" s="16">
+        <v>5</v>
+      </c>
+      <c r="K29" s="16">
+        <v>5</v>
+      </c>
+      <c r="L29" s="16">
+        <v>5</v>
+      </c>
+      <c r="M29" s="16">
+        <v>4</v>
       </c>
       <c r="N29" s="16"/>
       <c r="O29" s="9"/>
-      <c r="P29" s="13">
-        <v>6</v>
-      </c>
-      <c r="Q29" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="R29" s="17">
-        <v>0</v>
-      </c>
-      <c r="S29" s="17">
-        <v>0</v>
-      </c>
-      <c r="T29" s="17">
-        <v>0</v>
-      </c>
-      <c r="U29" s="17">
-        <v>0</v>
-      </c>
-      <c r="V29" s="17">
-        <v>0</v>
-      </c>
-      <c r="W29" s="17">
-        <v>0</v>
+      <c r="P29" s="8">
+        <v>5</v>
+      </c>
+      <c r="Q29" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="R29" s="16">
+        <v>1</v>
+      </c>
+      <c r="S29" s="16">
+        <v>1</v>
+      </c>
+      <c r="T29" s="16">
+        <v>1</v>
+      </c>
+      <c r="U29" s="16">
+        <v>1</v>
+      </c>
+      <c r="V29" s="16">
+        <v>1</v>
+      </c>
+      <c r="W29" s="16">
+        <v>1</v>
       </c>
       <c r="X29" s="9"/>
       <c r="Y29" s="4"/>
     </row>
-    <row r="30" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A30" s="4"/>
-      <c r="B30" s="4"/>
-      <c r="C30" s="4"/>
-      <c r="D30" s="4"/>
-      <c r="E30" s="4"/>
-      <c r="F30" s="4"/>
-      <c r="G30" s="4"/>
-      <c r="H30" s="4"/>
-      <c r="I30" s="4"/>
-      <c r="J30" s="4"/>
-      <c r="K30" s="4"/>
-      <c r="L30" s="4"/>
-      <c r="M30" s="4"/>
-      <c r="N30" s="4"/>
-      <c r="O30" s="4"/>
-      <c r="P30" s="4"/>
-      <c r="Q30" s="4"/>
-      <c r="R30" s="4"/>
-      <c r="S30" s="4"/>
+    <row r="30" spans="1:25" ht="21" x14ac:dyDescent="0.35">
+      <c r="A30" s="13">
+        <v>6</v>
+      </c>
+      <c r="B30" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="C30" s="17">
+        <v>0</v>
+      </c>
+      <c r="D30" s="17">
+        <v>2</v>
+      </c>
+      <c r="E30" s="17">
+        <v>0</v>
+      </c>
+      <c r="F30" s="17">
+        <v>2</v>
+      </c>
+      <c r="G30" s="16"/>
+      <c r="H30" s="13">
+        <v>6</v>
+      </c>
+      <c r="I30" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="J30" s="17">
+        <v>0</v>
+      </c>
+      <c r="K30" s="17">
+        <v>2</v>
+      </c>
+      <c r="L30" s="17">
+        <v>2</v>
+      </c>
+      <c r="M30" s="17">
+        <v>3</v>
+      </c>
+      <c r="N30" s="16"/>
+      <c r="O30" s="9"/>
+      <c r="P30" s="13">
+        <v>6</v>
+      </c>
+      <c r="Q30" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="R30" s="17">
+        <v>0</v>
+      </c>
+      <c r="S30" s="17">
+        <v>0</v>
+      </c>
+      <c r="T30" s="17">
+        <v>0</v>
+      </c>
+      <c r="U30" s="17">
+        <v>0</v>
+      </c>
+      <c r="V30" s="17">
+        <v>0</v>
+      </c>
+      <c r="W30" s="17">
+        <v>0</v>
+      </c>
+      <c r="X30" s="9"/>
+      <c r="Y30" s="4"/>
     </row>
     <row r="31" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A31" s="4"/>
+      <c r="A31" s="4" t="s">
+        <v>97</v>
+      </c>
       <c r="B31" s="4"/>
       <c r="C31" s="4"/>
       <c r="D31" s="4"/>
       <c r="E31" s="4"/>
       <c r="F31" s="4"/>
       <c r="G31" s="4"/>
-      <c r="H31" s="4"/>
+      <c r="H31" s="4" t="s">
+        <v>97</v>
+      </c>
       <c r="I31" s="4"/>
       <c r="J31" s="4"/>
       <c r="K31" s="4"/>
@@ -2332,104 +2355,97 @@
       <c r="R31" s="4"/>
       <c r="S31" s="4"/>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A34" s="1"/>
-      <c r="H34" s="1"/>
-      <c r="I34" s="1" t="s">
+    <row r="32" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A32" s="4"/>
+      <c r="B32" s="4"/>
+      <c r="C32" s="4"/>
+      <c r="D32" s="4"/>
+      <c r="E32" s="4"/>
+      <c r="F32" s="4"/>
+      <c r="G32" s="4"/>
+      <c r="H32" s="4"/>
+      <c r="I32" s="4"/>
+      <c r="J32" s="4"/>
+      <c r="K32" s="4"/>
+      <c r="L32" s="4"/>
+      <c r="M32" s="4"/>
+      <c r="N32" s="4"/>
+      <c r="O32" s="4"/>
+      <c r="P32" s="4"/>
+      <c r="Q32" s="4"/>
+      <c r="R32" s="4"/>
+      <c r="S32" s="4"/>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A35" s="1"/>
+      <c r="H35" s="1"/>
+      <c r="I35" s="1" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="35" spans="1:14" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="A35" s="45"/>
-      <c r="B35" s="45"/>
-      <c r="C35" s="45"/>
-      <c r="D35" s="45"/>
-      <c r="E35" s="45"/>
-      <c r="F35" s="45"/>
-      <c r="G35" s="29"/>
-      <c r="H35" s="40" t="s">
+    <row r="36" spans="1:14" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="A36" s="48"/>
+      <c r="B36" s="48"/>
+      <c r="C36" s="48"/>
+      <c r="D36" s="48"/>
+      <c r="E36" s="48"/>
+      <c r="F36" s="48"/>
+      <c r="G36" s="29"/>
+      <c r="H36" s="54" t="s">
         <v>62</v>
       </c>
-      <c r="I35" s="40"/>
-      <c r="J35" s="40"/>
-      <c r="K35" s="40"/>
-      <c r="L35" s="40"/>
-      <c r="M35" s="40"/>
-      <c r="N35" s="29"/>
-    </row>
-    <row r="36" spans="1:14" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A36" s="42"/>
-      <c r="B36" s="42"/>
-      <c r="C36" s="43"/>
-      <c r="D36" s="43"/>
-      <c r="E36" s="43"/>
-      <c r="F36" s="43"/>
-      <c r="G36" s="25"/>
-      <c r="H36" s="37" t="s">
+      <c r="I36" s="54"/>
+      <c r="J36" s="54"/>
+      <c r="K36" s="54"/>
+      <c r="L36" s="54"/>
+      <c r="M36" s="54"/>
+      <c r="N36" s="29"/>
+    </row>
+    <row r="37" spans="1:14" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="A37" s="51"/>
+      <c r="B37" s="51"/>
+      <c r="C37" s="52"/>
+      <c r="D37" s="52"/>
+      <c r="E37" s="52"/>
+      <c r="F37" s="52"/>
+      <c r="G37" s="25"/>
+      <c r="H37" s="41" t="s">
         <v>61</v>
       </c>
-      <c r="I36" s="37"/>
-      <c r="J36" s="39" t="s">
+      <c r="I37" s="41"/>
+      <c r="J37" s="45" t="s">
         <v>3</v>
       </c>
-      <c r="K36" s="39"/>
-      <c r="L36" s="39" t="s">
+      <c r="K37" s="45"/>
+      <c r="L37" s="45" t="s">
         <v>4</v>
       </c>
-      <c r="M36" s="39"/>
-      <c r="N36" s="25"/>
-    </row>
-    <row r="37" spans="1:14" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A37" s="42"/>
-      <c r="B37" s="42"/>
-      <c r="C37" s="26"/>
-      <c r="D37" s="26"/>
-      <c r="E37" s="26"/>
-      <c r="F37" s="26"/>
-      <c r="G37" s="26"/>
-      <c r="H37" s="38"/>
-      <c r="I37" s="38"/>
-      <c r="J37" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="K37" s="11" t="s">
+      <c r="M37" s="45"/>
+      <c r="N37" s="25"/>
+    </row>
+    <row r="38" spans="1:14" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="A38" s="51"/>
+      <c r="B38" s="51"/>
+      <c r="C38" s="26"/>
+      <c r="D38" s="26"/>
+      <c r="E38" s="26"/>
+      <c r="F38" s="26"/>
+      <c r="G38" s="26"/>
+      <c r="H38" s="42"/>
+      <c r="I38" s="42"/>
+      <c r="J38" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="K38" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="L37" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="M37" s="11" t="s">
+      <c r="L38" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="M38" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="N37" s="26"/>
-    </row>
-    <row r="38" spans="1:14" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="A38" s="6"/>
-      <c r="B38" s="6"/>
-      <c r="C38" s="16"/>
-      <c r="D38" s="16"/>
-      <c r="E38" s="16"/>
-      <c r="F38" s="16"/>
-      <c r="G38" s="16"/>
-      <c r="H38" s="6">
-        <v>1</v>
-      </c>
-      <c r="I38" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="J38" s="16">
-        <v>999</v>
-      </c>
-      <c r="K38" s="16">
-        <v>1000</v>
-      </c>
-      <c r="L38" s="16">
-        <v>1000</v>
-      </c>
-      <c r="M38" s="16">
-        <v>1000</v>
-      </c>
-      <c r="N38" s="16"/>
+      <c r="N38" s="26"/>
     </row>
     <row r="39" spans="1:14" ht="20.25" x14ac:dyDescent="0.3">
       <c r="A39" s="6"/>
@@ -2440,19 +2456,23 @@
       <c r="F39" s="16"/>
       <c r="G39" s="16"/>
       <c r="H39" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I39" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J39" s="16">
-        <v>500</v>
-      </c>
-      <c r="K39" s="16"/>
+        <v>999</v>
+      </c>
+      <c r="K39" s="16">
+        <v>1000</v>
+      </c>
       <c r="L39" s="16">
-        <v>500</v>
-      </c>
-      <c r="M39" s="16"/>
+        <v>1000</v>
+      </c>
+      <c r="M39" s="16">
+        <v>1000</v>
+      </c>
       <c r="N39" s="16"/>
     </row>
     <row r="40" spans="1:14" ht="20.25" x14ac:dyDescent="0.3">
@@ -2464,23 +2484,19 @@
       <c r="F40" s="16"/>
       <c r="G40" s="16"/>
       <c r="H40" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I40" s="6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J40" s="16">
-        <v>1000</v>
-      </c>
-      <c r="K40" s="16">
-        <v>1000</v>
-      </c>
+        <v>500</v>
+      </c>
+      <c r="K40" s="16"/>
       <c r="L40" s="16">
-        <v>1000</v>
-      </c>
-      <c r="M40" s="16">
-        <v>1000</v>
-      </c>
+        <v>500</v>
+      </c>
+      <c r="M40" s="16"/>
       <c r="N40" s="16"/>
     </row>
     <row r="41" spans="1:14" ht="20.25" x14ac:dyDescent="0.3">
@@ -2492,10 +2508,10 @@
       <c r="F41" s="16"/>
       <c r="G41" s="16"/>
       <c r="H41" s="6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I41" s="6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J41" s="16">
         <v>1000</v>
@@ -2512,152 +2528,152 @@
       <c r="N41" s="16"/>
     </row>
     <row r="42" spans="1:14" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="A42" s="8"/>
-      <c r="B42" s="8"/>
+      <c r="A42" s="6"/>
+      <c r="B42" s="6"/>
       <c r="C42" s="16"/>
       <c r="D42" s="16"/>
       <c r="E42" s="16"/>
       <c r="F42" s="16"/>
       <c r="G42" s="16"/>
-      <c r="H42" s="8">
-        <v>5</v>
-      </c>
-      <c r="I42" s="8" t="s">
-        <v>14</v>
+      <c r="H42" s="6">
+        <v>4</v>
+      </c>
+      <c r="I42" s="6" t="s">
+        <v>13</v>
       </c>
       <c r="J42" s="16">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="K42" s="16">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="L42" s="16">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="M42" s="16">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="N42" s="16"/>
     </row>
     <row r="43" spans="1:14" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="A43" s="6"/>
-      <c r="B43" s="6"/>
+      <c r="A43" s="8"/>
+      <c r="B43" s="8"/>
       <c r="C43" s="16"/>
       <c r="D43" s="16"/>
       <c r="E43" s="16"/>
       <c r="F43" s="16"/>
       <c r="G43" s="16"/>
-      <c r="H43" s="12">
+      <c r="H43" s="8">
+        <v>5</v>
+      </c>
+      <c r="I43" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="J43" s="16">
+        <v>100</v>
+      </c>
+      <c r="K43" s="16">
+        <v>100</v>
+      </c>
+      <c r="L43" s="16">
+        <v>100</v>
+      </c>
+      <c r="M43" s="16">
+        <v>100</v>
+      </c>
+      <c r="N43" s="16"/>
+    </row>
+    <row r="44" spans="1:14" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="A44" s="6"/>
+      <c r="B44" s="6"/>
+      <c r="C44" s="16"/>
+      <c r="D44" s="16"/>
+      <c r="E44" s="16"/>
+      <c r="F44" s="16"/>
+      <c r="G44" s="16"/>
+      <c r="H44" s="12">
         <v>6</v>
       </c>
-      <c r="I43" s="12" t="s">
+      <c r="I44" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="J43" s="17">
+      <c r="J44" s="17">
         <v>1000</v>
       </c>
-      <c r="K43" s="17">
+      <c r="K44" s="17">
         <v>1000</v>
       </c>
-      <c r="L43" s="17">
+      <c r="L44" s="17">
         <v>1000</v>
       </c>
-      <c r="M43" s="17">
+      <c r="M44" s="17">
         <v>999</v>
       </c>
-      <c r="N43" s="16"/>
-    </row>
-    <row r="45" spans="1:14" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="A45" s="44"/>
-      <c r="B45" s="44"/>
-      <c r="C45" s="44"/>
-      <c r="D45" s="44"/>
-      <c r="E45" s="44"/>
-      <c r="F45" s="44"/>
-      <c r="G45" s="27"/>
-      <c r="H45" s="41" t="s">
+      <c r="N44" s="16"/>
+    </row>
+    <row r="46" spans="1:14" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="A46" s="53"/>
+      <c r="B46" s="53"/>
+      <c r="C46" s="53"/>
+      <c r="D46" s="53"/>
+      <c r="E46" s="53"/>
+      <c r="F46" s="53"/>
+      <c r="G46" s="27"/>
+      <c r="H46" s="43" t="s">
         <v>71</v>
       </c>
-      <c r="I45" s="41"/>
-      <c r="J45" s="41"/>
-      <c r="K45" s="41"/>
-      <c r="L45" s="41"/>
-      <c r="M45" s="41"/>
-      <c r="N45" s="27"/>
-    </row>
-    <row r="46" spans="1:14" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A46" s="42"/>
-      <c r="B46" s="42"/>
-      <c r="C46" s="43"/>
-      <c r="D46" s="43"/>
-      <c r="E46" s="43"/>
-      <c r="F46" s="43"/>
-      <c r="G46" s="25"/>
-      <c r="H46" s="37" t="s">
+      <c r="I46" s="43"/>
+      <c r="J46" s="43"/>
+      <c r="K46" s="43"/>
+      <c r="L46" s="43"/>
+      <c r="M46" s="43"/>
+      <c r="N46" s="27"/>
+    </row>
+    <row r="47" spans="1:14" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="A47" s="51"/>
+      <c r="B47" s="51"/>
+      <c r="C47" s="52"/>
+      <c r="D47" s="52"/>
+      <c r="E47" s="52"/>
+      <c r="F47" s="52"/>
+      <c r="G47" s="25"/>
+      <c r="H47" s="41" t="s">
         <v>61</v>
       </c>
-      <c r="I46" s="37"/>
-      <c r="J46" s="39" t="s">
+      <c r="I47" s="41"/>
+      <c r="J47" s="45" t="s">
         <v>3</v>
       </c>
-      <c r="K46" s="39"/>
-      <c r="L46" s="39" t="s">
+      <c r="K47" s="45"/>
+      <c r="L47" s="45" t="s">
         <v>4</v>
       </c>
-      <c r="M46" s="39"/>
-      <c r="N46" s="25"/>
-    </row>
-    <row r="47" spans="1:14" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A47" s="42"/>
-      <c r="B47" s="42"/>
-      <c r="C47" s="26"/>
-      <c r="D47" s="26"/>
-      <c r="E47" s="26"/>
-      <c r="F47" s="26"/>
-      <c r="G47" s="26"/>
-      <c r="H47" s="38"/>
-      <c r="I47" s="38"/>
-      <c r="J47" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="K47" s="11" t="s">
+      <c r="M47" s="45"/>
+      <c r="N47" s="25"/>
+    </row>
+    <row r="48" spans="1:14" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="A48" s="51"/>
+      <c r="B48" s="51"/>
+      <c r="C48" s="26"/>
+      <c r="D48" s="26"/>
+      <c r="E48" s="26"/>
+      <c r="F48" s="26"/>
+      <c r="G48" s="26"/>
+      <c r="H48" s="42"/>
+      <c r="I48" s="42"/>
+      <c r="J48" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="K48" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="L47" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="M47" s="11" t="s">
+      <c r="L48" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="M48" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="N47" s="26"/>
-    </row>
-    <row r="48" spans="1:14" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="A48" s="6"/>
-      <c r="B48" s="6"/>
-      <c r="C48" s="16"/>
-      <c r="D48" s="16"/>
-      <c r="E48" s="16"/>
-      <c r="F48" s="16"/>
-      <c r="G48" s="16"/>
-      <c r="H48" s="6">
-        <v>1</v>
-      </c>
-      <c r="I48" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="J48" s="16">
-        <v>100</v>
-      </c>
-      <c r="K48" s="16">
-        <v>100</v>
-      </c>
-      <c r="L48" s="16">
-        <v>100</v>
-      </c>
-      <c r="M48" s="16">
-        <v>100</v>
-      </c>
-      <c r="N48" s="16"/>
+      <c r="N48" s="26"/>
     </row>
     <row r="49" spans="1:14" ht="20.25" x14ac:dyDescent="0.3">
       <c r="A49" s="6"/>
@@ -2668,19 +2684,23 @@
       <c r="F49" s="16"/>
       <c r="G49" s="16"/>
       <c r="H49" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I49" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J49" s="16">
-        <v>500</v>
-      </c>
-      <c r="K49" s="16"/>
+        <v>100</v>
+      </c>
+      <c r="K49" s="16">
+        <v>100</v>
+      </c>
       <c r="L49" s="16">
-        <v>500</v>
-      </c>
-      <c r="M49" s="16"/>
+        <v>100</v>
+      </c>
+      <c r="M49" s="16">
+        <v>100</v>
+      </c>
       <c r="N49" s="16"/>
     </row>
     <row r="50" spans="1:14" ht="20.25" x14ac:dyDescent="0.3">
@@ -2692,23 +2712,19 @@
       <c r="F50" s="16"/>
       <c r="G50" s="16"/>
       <c r="H50" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I50" s="6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J50" s="16">
-        <v>100</v>
-      </c>
-      <c r="K50" s="16">
-        <v>100</v>
-      </c>
+        <v>500</v>
+      </c>
+      <c r="K50" s="16"/>
       <c r="L50" s="16">
-        <v>100</v>
-      </c>
-      <c r="M50" s="16">
-        <v>100</v>
-      </c>
+        <v>500</v>
+      </c>
+      <c r="M50" s="16"/>
       <c r="N50" s="16"/>
     </row>
     <row r="51" spans="1:14" ht="20.25" x14ac:dyDescent="0.3">
@@ -2720,88 +2736,147 @@
       <c r="F51" s="16"/>
       <c r="G51" s="16"/>
       <c r="H51" s="6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I51" s="6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J51" s="16">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="K51" s="16">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="L51" s="16">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="M51" s="16">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="N51" s="16"/>
     </row>
     <row r="52" spans="1:14" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="A52" s="8"/>
-      <c r="B52" s="8"/>
+      <c r="A52" s="6"/>
+      <c r="B52" s="6"/>
       <c r="C52" s="16"/>
       <c r="D52" s="16"/>
       <c r="E52" s="16"/>
       <c r="F52" s="16"/>
       <c r="G52" s="16"/>
-      <c r="H52" s="8">
-        <v>5</v>
-      </c>
-      <c r="I52" s="8" t="s">
-        <v>14</v>
+      <c r="H52" s="6">
+        <v>4</v>
+      </c>
+      <c r="I52" s="6" t="s">
+        <v>13</v>
       </c>
       <c r="J52" s="16">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="K52" s="16">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="L52" s="16">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="M52" s="16">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="N52" s="16"/>
     </row>
     <row r="53" spans="1:14" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="A53" s="6"/>
-      <c r="B53" s="6"/>
+      <c r="A53" s="8"/>
+      <c r="B53" s="8"/>
       <c r="C53" s="16"/>
       <c r="D53" s="16"/>
       <c r="E53" s="16"/>
       <c r="F53" s="16"/>
       <c r="G53" s="16"/>
-      <c r="H53" s="12">
+      <c r="H53" s="8">
+        <v>5</v>
+      </c>
+      <c r="I53" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="J53" s="16">
+        <v>100</v>
+      </c>
+      <c r="K53" s="16">
+        <v>100</v>
+      </c>
+      <c r="L53" s="16">
+        <v>100</v>
+      </c>
+      <c r="M53" s="16">
+        <v>100</v>
+      </c>
+      <c r="N53" s="16"/>
+    </row>
+    <row r="54" spans="1:14" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="A54" s="6"/>
+      <c r="B54" s="6"/>
+      <c r="C54" s="16"/>
+      <c r="D54" s="16"/>
+      <c r="E54" s="16"/>
+      <c r="F54" s="16"/>
+      <c r="G54" s="16"/>
+      <c r="H54" s="12">
         <v>6</v>
       </c>
-      <c r="I53" s="12" t="s">
+      <c r="I54" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="J53" s="17">
+      <c r="J54" s="17">
         <v>1000</v>
       </c>
-      <c r="K53" s="17">
+      <c r="K54" s="17">
         <v>1000</v>
       </c>
-      <c r="L53" s="17">
+      <c r="L54" s="17">
         <v>1000</v>
       </c>
-      <c r="M53" s="17">
+      <c r="M54" s="17">
         <v>1000</v>
       </c>
-      <c r="N53" s="16"/>
+      <c r="N54" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="43">
+    <mergeCell ref="H47:I48"/>
+    <mergeCell ref="J47:K47"/>
+    <mergeCell ref="L47:M47"/>
+    <mergeCell ref="H36:M36"/>
+    <mergeCell ref="H37:I38"/>
+    <mergeCell ref="J37:K37"/>
+    <mergeCell ref="L37:M37"/>
+    <mergeCell ref="H46:M46"/>
+    <mergeCell ref="A37:B38"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="E37:F37"/>
+    <mergeCell ref="A46:F46"/>
+    <mergeCell ref="A47:B48"/>
+    <mergeCell ref="C47:D47"/>
+    <mergeCell ref="E47:F47"/>
+    <mergeCell ref="A36:F36"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="R12:T12"/>
+    <mergeCell ref="U12:W12"/>
+    <mergeCell ref="A23:B24"/>
+    <mergeCell ref="P23:Q24"/>
+    <mergeCell ref="R23:T23"/>
+    <mergeCell ref="U23:W23"/>
+    <mergeCell ref="H22:M22"/>
+    <mergeCell ref="H23:I24"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="L23:M23"/>
+    <mergeCell ref="H12:I13"/>
+    <mergeCell ref="J12:K12"/>
+    <mergeCell ref="L12:M12"/>
     <mergeCell ref="A10:F10"/>
-    <mergeCell ref="P21:W21"/>
+    <mergeCell ref="P22:W22"/>
     <mergeCell ref="A12:B13"/>
     <mergeCell ref="P12:Q13"/>
-    <mergeCell ref="A21:F21"/>
+    <mergeCell ref="A22:F22"/>
     <mergeCell ref="A11:F11"/>
     <mergeCell ref="P11:W11"/>
     <mergeCell ref="C12:D12"/>
@@ -2809,40 +2884,9 @@
     <mergeCell ref="H10:M10"/>
     <mergeCell ref="P10:W10"/>
     <mergeCell ref="H11:M11"/>
-    <mergeCell ref="A35:F35"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="R12:T12"/>
-    <mergeCell ref="U12:W12"/>
-    <mergeCell ref="A22:B23"/>
-    <mergeCell ref="P22:Q23"/>
-    <mergeCell ref="R22:T22"/>
-    <mergeCell ref="U22:W22"/>
-    <mergeCell ref="H21:M21"/>
-    <mergeCell ref="H22:I23"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="L22:M22"/>
-    <mergeCell ref="H12:I13"/>
-    <mergeCell ref="J12:K12"/>
-    <mergeCell ref="L12:M12"/>
-    <mergeCell ref="A36:B37"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="E36:F36"/>
-    <mergeCell ref="A45:F45"/>
-    <mergeCell ref="A46:B47"/>
-    <mergeCell ref="C46:D46"/>
-    <mergeCell ref="E46:F46"/>
-    <mergeCell ref="H46:I47"/>
-    <mergeCell ref="J46:K46"/>
-    <mergeCell ref="L46:M46"/>
-    <mergeCell ref="H35:M35"/>
-    <mergeCell ref="H36:I37"/>
-    <mergeCell ref="J36:K36"/>
-    <mergeCell ref="L36:M36"/>
-    <mergeCell ref="H45:M45"/>
   </mergeCells>
   <conditionalFormatting sqref="G14:G19">
-    <cfRule type="colorScale" priority="41">
+    <cfRule type="colorScale" priority="45">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="7"/>
@@ -2851,8 +2895,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G24:G29">
-    <cfRule type="colorScale" priority="39">
+  <conditionalFormatting sqref="G25:G30">
+    <cfRule type="colorScale" priority="43">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="7"/>
@@ -2862,7 +2906,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N14:N19">
-    <cfRule type="colorScale" priority="18">
+    <cfRule type="colorScale" priority="22">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="7"/>
@@ -2871,8 +2915,38 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N24:N29">
-    <cfRule type="colorScale" priority="16">
+  <conditionalFormatting sqref="N25:N30">
+    <cfRule type="colorScale" priority="20">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="7"/>
+        <color theme="9"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J1:M6">
+    <cfRule type="colorScale" priority="7">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="7"/>
+        <color theme="9"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J25:M30">
+    <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="7"/>
+        <color theme="9"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J14:M19">
+    <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="7"/>
@@ -2882,7 +2956,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R14:W19">
-    <cfRule type="colorScale" priority="9">
+    <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="7"/>
@@ -2892,36 +2966,6 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C14:F19">
-    <cfRule type="colorScale" priority="8">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="7"/>
-        <color theme="9"/>
-        <color rgb="FFFF0000"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="R24:W29">
-    <cfRule type="colorScale" priority="7">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="7"/>
-        <color theme="9"/>
-        <color rgb="FFFF0000"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C24:F29">
-    <cfRule type="colorScale" priority="6">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="7"/>
-        <color theme="9"/>
-        <color rgb="FFFF0000"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J1:M6">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -2931,7 +2975,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J24:M29">
+  <conditionalFormatting sqref="R25:W30">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -2941,7 +2985,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J14:M19">
+  <conditionalFormatting sqref="C25:F30">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -3051,115 +3095,115 @@
       </c>
     </row>
     <row r="12" spans="1:25" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="49" t="s">
+      <c r="A12" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="B12" s="49"/>
-      <c r="C12" s="49"/>
-      <c r="D12" s="49"/>
-      <c r="E12" s="49"/>
-      <c r="F12" s="49"/>
+      <c r="B12" s="39"/>
+      <c r="C12" s="39"/>
+      <c r="D12" s="39"/>
+      <c r="E12" s="39"/>
+      <c r="F12" s="39"/>
       <c r="G12" s="32"/>
-      <c r="H12" s="49" t="s">
+      <c r="H12" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="I12" s="49"/>
-      <c r="J12" s="49"/>
-      <c r="K12" s="49"/>
-      <c r="L12" s="49"/>
-      <c r="M12" s="49"/>
+      <c r="I12" s="39"/>
+      <c r="J12" s="39"/>
+      <c r="K12" s="39"/>
+      <c r="L12" s="39"/>
+      <c r="M12" s="39"/>
       <c r="N12" s="32"/>
       <c r="O12" s="10"/>
-      <c r="P12" s="52" t="s">
+      <c r="P12" s="47" t="s">
         <v>2</v>
       </c>
-      <c r="Q12" s="52"/>
-      <c r="R12" s="52"/>
-      <c r="S12" s="52"/>
-      <c r="T12" s="52"/>
-      <c r="U12" s="52"/>
-      <c r="V12" s="52"/>
-      <c r="W12" s="52"/>
+      <c r="Q12" s="47"/>
+      <c r="R12" s="47"/>
+      <c r="S12" s="47"/>
+      <c r="T12" s="47"/>
+      <c r="U12" s="47"/>
+      <c r="V12" s="47"/>
+      <c r="W12" s="47"/>
       <c r="X12" s="30"/>
     </row>
     <row r="13" spans="1:25" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="A13" s="51" t="s">
-        <v>0</v>
-      </c>
-      <c r="B13" s="51"/>
-      <c r="C13" s="51"/>
-      <c r="D13" s="51"/>
-      <c r="E13" s="51"/>
-      <c r="F13" s="51"/>
+      <c r="A13" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="B13" s="44"/>
+      <c r="C13" s="44"/>
+      <c r="D13" s="44"/>
+      <c r="E13" s="44"/>
+      <c r="F13" s="44"/>
       <c r="G13" s="24"/>
-      <c r="H13" s="51" t="s">
+      <c r="H13" s="44" t="s">
         <v>62</v>
       </c>
-      <c r="I13" s="51"/>
-      <c r="J13" s="51"/>
-      <c r="K13" s="51"/>
-      <c r="L13" s="51"/>
-      <c r="M13" s="51"/>
+      <c r="I13" s="44"/>
+      <c r="J13" s="44"/>
+      <c r="K13" s="44"/>
+      <c r="L13" s="44"/>
+      <c r="M13" s="44"/>
       <c r="N13" s="24"/>
-      <c r="P13" s="51" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="51"/>
-      <c r="R13" s="51"/>
-      <c r="S13" s="51"/>
-      <c r="T13" s="51"/>
-      <c r="U13" s="51"/>
-      <c r="V13" s="51"/>
-      <c r="W13" s="51"/>
+      <c r="P13" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="44"/>
+      <c r="R13" s="44"/>
+      <c r="S13" s="44"/>
+      <c r="T13" s="44"/>
+      <c r="U13" s="44"/>
+      <c r="V13" s="44"/>
+      <c r="W13" s="44"/>
     </row>
     <row r="14" spans="1:25" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A14" s="37" t="s">
+      <c r="A14" s="41" t="s">
         <v>61</v>
       </c>
-      <c r="B14" s="37"/>
-      <c r="C14" s="39" t="s">
+      <c r="B14" s="41"/>
+      <c r="C14" s="45" t="s">
         <v>3</v>
       </c>
-      <c r="D14" s="39"/>
+      <c r="D14" s="45"/>
       <c r="E14" s="46" t="s">
         <v>4</v>
       </c>
-      <c r="F14" s="39"/>
+      <c r="F14" s="45"/>
       <c r="G14" s="34"/>
-      <c r="H14" s="37" t="s">
+      <c r="H14" s="41" t="s">
         <v>61</v>
       </c>
-      <c r="I14" s="37"/>
-      <c r="J14" s="39" t="s">
+      <c r="I14" s="41"/>
+      <c r="J14" s="45" t="s">
         <v>3</v>
       </c>
-      <c r="K14" s="39"/>
+      <c r="K14" s="45"/>
       <c r="L14" s="46" t="s">
         <v>4</v>
       </c>
-      <c r="M14" s="39"/>
+      <c r="M14" s="45"/>
       <c r="N14" s="34"/>
       <c r="O14" s="4"/>
-      <c r="P14" s="37" t="s">
+      <c r="P14" s="41" t="s">
         <v>61</v>
       </c>
-      <c r="Q14" s="37"/>
-      <c r="R14" s="47" t="s">
+      <c r="Q14" s="41"/>
+      <c r="R14" s="49" t="s">
         <v>3</v>
       </c>
-      <c r="S14" s="47"/>
-      <c r="T14" s="47"/>
-      <c r="U14" s="48" t="s">
+      <c r="S14" s="49"/>
+      <c r="T14" s="49"/>
+      <c r="U14" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="V14" s="47"/>
-      <c r="W14" s="47"/>
+      <c r="V14" s="49"/>
+      <c r="W14" s="49"/>
       <c r="X14" s="4"/>
       <c r="Y14" s="4"/>
     </row>
     <row r="15" spans="1:25" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A15" s="38"/>
-      <c r="B15" s="38"/>
+      <c r="A15" s="42"/>
+      <c r="B15" s="42"/>
       <c r="C15" s="21" t="s">
         <v>5</v>
       </c>
@@ -3173,8 +3217,8 @@
         <v>6</v>
       </c>
       <c r="G15" s="33"/>
-      <c r="H15" s="38"/>
-      <c r="I15" s="38"/>
+      <c r="H15" s="42"/>
+      <c r="I15" s="42"/>
       <c r="J15" s="21" t="s">
         <v>5</v>
       </c>
@@ -3189,8 +3233,8 @@
       </c>
       <c r="N15" s="33"/>
       <c r="O15" s="5"/>
-      <c r="P15" s="38"/>
-      <c r="Q15" s="38"/>
+      <c r="P15" s="42"/>
+      <c r="Q15" s="42"/>
       <c r="R15" s="14" t="s">
         <v>7</v>
       </c>
@@ -3540,86 +3584,86 @@
       <c r="S22" s="4"/>
     </row>
     <row r="23" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="41" t="s">
+      <c r="A23" s="43" t="s">
         <v>16</v>
       </c>
-      <c r="B23" s="41"/>
-      <c r="C23" s="41"/>
-      <c r="D23" s="41"/>
-      <c r="E23" s="41"/>
-      <c r="F23" s="41"/>
+      <c r="B23" s="43"/>
+      <c r="C23" s="43"/>
+      <c r="D23" s="43"/>
+      <c r="E23" s="43"/>
+      <c r="F23" s="43"/>
       <c r="G23" s="35"/>
-      <c r="H23" s="41" t="s">
+      <c r="H23" s="43" t="s">
         <v>71</v>
       </c>
-      <c r="I23" s="41"/>
-      <c r="J23" s="41"/>
-      <c r="K23" s="41"/>
-      <c r="L23" s="41"/>
-      <c r="M23" s="41"/>
+      <c r="I23" s="43"/>
+      <c r="J23" s="43"/>
+      <c r="K23" s="43"/>
+      <c r="L23" s="43"/>
+      <c r="M23" s="43"/>
       <c r="N23" s="35"/>
       <c r="O23" s="15"/>
-      <c r="P23" s="50" t="s">
+      <c r="P23" s="40" t="s">
         <v>16</v>
       </c>
-      <c r="Q23" s="50"/>
-      <c r="R23" s="50"/>
-      <c r="S23" s="50"/>
-      <c r="T23" s="50"/>
-      <c r="U23" s="50"/>
-      <c r="V23" s="50"/>
-      <c r="W23" s="50"/>
+      <c r="Q23" s="40"/>
+      <c r="R23" s="40"/>
+      <c r="S23" s="40"/>
+      <c r="T23" s="40"/>
+      <c r="U23" s="40"/>
+      <c r="V23" s="40"/>
+      <c r="W23" s="40"/>
       <c r="X23" s="15"/>
       <c r="Y23" s="4"/>
     </row>
     <row r="24" spans="1:25" ht="21" x14ac:dyDescent="0.35">
-      <c r="A24" s="37" t="s">
+      <c r="A24" s="41" t="s">
         <v>61</v>
       </c>
-      <c r="B24" s="37"/>
-      <c r="C24" s="39" t="s">
+      <c r="B24" s="41"/>
+      <c r="C24" s="45" t="s">
         <v>3</v>
       </c>
-      <c r="D24" s="39"/>
-      <c r="E24" s="39" t="s">
+      <c r="D24" s="45"/>
+      <c r="E24" s="45" t="s">
         <v>4</v>
       </c>
-      <c r="F24" s="39"/>
+      <c r="F24" s="45"/>
       <c r="G24" s="28"/>
-      <c r="H24" s="37" t="s">
+      <c r="H24" s="41" t="s">
         <v>61</v>
       </c>
-      <c r="I24" s="37"/>
-      <c r="J24" s="39" t="s">
+      <c r="I24" s="41"/>
+      <c r="J24" s="45" t="s">
         <v>3</v>
       </c>
-      <c r="K24" s="39"/>
+      <c r="K24" s="45"/>
       <c r="L24" s="46" t="s">
         <v>4</v>
       </c>
-      <c r="M24" s="39"/>
+      <c r="M24" s="45"/>
       <c r="N24" s="34"/>
       <c r="O24" s="7"/>
-      <c r="P24" s="37" t="s">
+      <c r="P24" s="41" t="s">
         <v>61</v>
       </c>
-      <c r="Q24" s="37"/>
-      <c r="R24" s="47" t="s">
+      <c r="Q24" s="41"/>
+      <c r="R24" s="49" t="s">
         <v>3</v>
       </c>
-      <c r="S24" s="47"/>
-      <c r="T24" s="47"/>
-      <c r="U24" s="48" t="s">
+      <c r="S24" s="49"/>
+      <c r="T24" s="49"/>
+      <c r="U24" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="V24" s="47"/>
-      <c r="W24" s="47"/>
+      <c r="V24" s="49"/>
+      <c r="W24" s="49"/>
       <c r="X24" s="7"/>
       <c r="Y24" s="4"/>
     </row>
     <row r="25" spans="1:25" ht="21" x14ac:dyDescent="0.35">
-      <c r="A25" s="38"/>
-      <c r="B25" s="38"/>
+      <c r="A25" s="42"/>
+      <c r="B25" s="42"/>
       <c r="C25" s="21" t="s">
         <v>5</v>
       </c>
@@ -3633,8 +3677,8 @@
         <v>6</v>
       </c>
       <c r="G25" s="28"/>
-      <c r="H25" s="38"/>
-      <c r="I25" s="38"/>
+      <c r="H25" s="42"/>
+      <c r="I25" s="42"/>
       <c r="J25" s="21" t="s">
         <v>5</v>
       </c>
@@ -3649,8 +3693,8 @@
       </c>
       <c r="N25" s="33"/>
       <c r="O25" s="7"/>
-      <c r="P25" s="38"/>
-      <c r="Q25" s="38"/>
+      <c r="P25" s="42"/>
+      <c r="Q25" s="42"/>
       <c r="R25" s="14" t="s">
         <v>7</v>
       </c>
@@ -4032,55 +4076,55 @@
       </c>
     </row>
     <row r="37" spans="1:19" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="A37" s="45"/>
-      <c r="B37" s="45"/>
-      <c r="C37" s="45"/>
-      <c r="D37" s="45"/>
-      <c r="E37" s="45"/>
-      <c r="F37" s="45"/>
+      <c r="A37" s="48"/>
+      <c r="B37" s="48"/>
+      <c r="C37" s="48"/>
+      <c r="D37" s="48"/>
+      <c r="E37" s="48"/>
+      <c r="F37" s="48"/>
       <c r="G37" s="36"/>
-      <c r="H37" s="40" t="s">
+      <c r="H37" s="54" t="s">
         <v>62</v>
       </c>
-      <c r="I37" s="40"/>
-      <c r="J37" s="40"/>
-      <c r="K37" s="40"/>
-      <c r="L37" s="40"/>
-      <c r="M37" s="40"/>
+      <c r="I37" s="54"/>
+      <c r="J37" s="54"/>
+      <c r="K37" s="54"/>
+      <c r="L37" s="54"/>
+      <c r="M37" s="54"/>
       <c r="N37" s="36"/>
     </row>
     <row r="38" spans="1:19" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A38" s="42"/>
-      <c r="B38" s="42"/>
-      <c r="C38" s="43"/>
-      <c r="D38" s="43"/>
-      <c r="E38" s="43"/>
-      <c r="F38" s="43"/>
+      <c r="A38" s="51"/>
+      <c r="B38" s="51"/>
+      <c r="C38" s="52"/>
+      <c r="D38" s="52"/>
+      <c r="E38" s="52"/>
+      <c r="F38" s="52"/>
       <c r="G38" s="34"/>
-      <c r="H38" s="37" t="s">
+      <c r="H38" s="41" t="s">
         <v>61</v>
       </c>
-      <c r="I38" s="37"/>
-      <c r="J38" s="39" t="s">
+      <c r="I38" s="41"/>
+      <c r="J38" s="45" t="s">
         <v>3</v>
       </c>
-      <c r="K38" s="39"/>
-      <c r="L38" s="39" t="s">
+      <c r="K38" s="45"/>
+      <c r="L38" s="45" t="s">
         <v>4</v>
       </c>
-      <c r="M38" s="39"/>
+      <c r="M38" s="45"/>
       <c r="N38" s="34"/>
     </row>
     <row r="39" spans="1:19" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A39" s="42"/>
-      <c r="B39" s="42"/>
+      <c r="A39" s="51"/>
+      <c r="B39" s="51"/>
       <c r="C39" s="33"/>
       <c r="D39" s="33"/>
       <c r="E39" s="33"/>
       <c r="F39" s="33"/>
       <c r="G39" s="33"/>
-      <c r="H39" s="38"/>
-      <c r="I39" s="38"/>
+      <c r="H39" s="42"/>
+      <c r="I39" s="42"/>
       <c r="J39" s="31" t="s">
         <v>5</v>
       </c>
@@ -4260,55 +4304,55 @@
       <c r="N45" s="16"/>
     </row>
     <row r="47" spans="1:19" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="A47" s="44"/>
-      <c r="B47" s="44"/>
-      <c r="C47" s="44"/>
-      <c r="D47" s="44"/>
-      <c r="E47" s="44"/>
-      <c r="F47" s="44"/>
+      <c r="A47" s="53"/>
+      <c r="B47" s="53"/>
+      <c r="C47" s="53"/>
+      <c r="D47" s="53"/>
+      <c r="E47" s="53"/>
+      <c r="F47" s="53"/>
       <c r="G47" s="35"/>
-      <c r="H47" s="41" t="s">
+      <c r="H47" s="43" t="s">
         <v>71</v>
       </c>
-      <c r="I47" s="41"/>
-      <c r="J47" s="41"/>
-      <c r="K47" s="41"/>
-      <c r="L47" s="41"/>
-      <c r="M47" s="41"/>
+      <c r="I47" s="43"/>
+      <c r="J47" s="43"/>
+      <c r="K47" s="43"/>
+      <c r="L47" s="43"/>
+      <c r="M47" s="43"/>
       <c r="N47" s="35"/>
     </row>
     <row r="48" spans="1:19" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A48" s="42"/>
-      <c r="B48" s="42"/>
-      <c r="C48" s="43"/>
-      <c r="D48" s="43"/>
-      <c r="E48" s="43"/>
-      <c r="F48" s="43"/>
+      <c r="A48" s="51"/>
+      <c r="B48" s="51"/>
+      <c r="C48" s="52"/>
+      <c r="D48" s="52"/>
+      <c r="E48" s="52"/>
+      <c r="F48" s="52"/>
       <c r="G48" s="34"/>
-      <c r="H48" s="37" t="s">
+      <c r="H48" s="41" t="s">
         <v>61</v>
       </c>
-      <c r="I48" s="37"/>
-      <c r="J48" s="39" t="s">
+      <c r="I48" s="41"/>
+      <c r="J48" s="45" t="s">
         <v>3</v>
       </c>
-      <c r="K48" s="39"/>
-      <c r="L48" s="39" t="s">
+      <c r="K48" s="45"/>
+      <c r="L48" s="45" t="s">
         <v>4</v>
       </c>
-      <c r="M48" s="39"/>
+      <c r="M48" s="45"/>
       <c r="N48" s="34"/>
     </row>
     <row r="49" spans="1:14" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A49" s="42"/>
-      <c r="B49" s="42"/>
+      <c r="A49" s="51"/>
+      <c r="B49" s="51"/>
       <c r="C49" s="33"/>
       <c r="D49" s="33"/>
       <c r="E49" s="33"/>
       <c r="F49" s="33"/>
       <c r="G49" s="33"/>
-      <c r="H49" s="38"/>
-      <c r="I49" s="38"/>
+      <c r="H49" s="42"/>
+      <c r="I49" s="42"/>
       <c r="J49" s="31" t="s">
         <v>5</v>
       </c>
@@ -4489,35 +4533,6 @@
     </row>
   </sheetData>
   <mergeCells count="43">
-    <mergeCell ref="A12:F12"/>
-    <mergeCell ref="H12:M12"/>
-    <mergeCell ref="P12:W12"/>
-    <mergeCell ref="A13:F13"/>
-    <mergeCell ref="H13:M13"/>
-    <mergeCell ref="P13:W13"/>
-    <mergeCell ref="P14:Q15"/>
-    <mergeCell ref="R14:T14"/>
-    <mergeCell ref="U14:W14"/>
-    <mergeCell ref="A23:F23"/>
-    <mergeCell ref="H23:M23"/>
-    <mergeCell ref="P23:W23"/>
-    <mergeCell ref="A14:B15"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="H14:I15"/>
-    <mergeCell ref="J14:K14"/>
-    <mergeCell ref="L14:M14"/>
-    <mergeCell ref="P24:Q25"/>
-    <mergeCell ref="R24:T24"/>
-    <mergeCell ref="U24:W24"/>
-    <mergeCell ref="A37:F37"/>
-    <mergeCell ref="H37:M37"/>
-    <mergeCell ref="A24:B25"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="H24:I25"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="L24:M24"/>
     <mergeCell ref="L38:M38"/>
     <mergeCell ref="A47:F47"/>
     <mergeCell ref="H47:M47"/>
@@ -4532,6 +4547,35 @@
     <mergeCell ref="E38:F38"/>
     <mergeCell ref="H38:I39"/>
     <mergeCell ref="J38:K38"/>
+    <mergeCell ref="P24:Q25"/>
+    <mergeCell ref="R24:T24"/>
+    <mergeCell ref="U24:W24"/>
+    <mergeCell ref="A37:F37"/>
+    <mergeCell ref="H37:M37"/>
+    <mergeCell ref="A24:B25"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="H24:I25"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="L24:M24"/>
+    <mergeCell ref="P14:Q15"/>
+    <mergeCell ref="R14:T14"/>
+    <mergeCell ref="U14:W14"/>
+    <mergeCell ref="A23:F23"/>
+    <mergeCell ref="H23:M23"/>
+    <mergeCell ref="P23:W23"/>
+    <mergeCell ref="A14:B15"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="H14:I15"/>
+    <mergeCell ref="J14:K14"/>
+    <mergeCell ref="L14:M14"/>
+    <mergeCell ref="A12:F12"/>
+    <mergeCell ref="H12:M12"/>
+    <mergeCell ref="P12:W12"/>
+    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="H13:M13"/>
+    <mergeCell ref="P13:W13"/>
   </mergeCells>
   <conditionalFormatting sqref="C16:C21">
     <cfRule type="colorScale" priority="19">
@@ -4715,10 +4759,10 @@
   </cols>
   <sheetData>
     <row r="3" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="L3" s="53" t="s">
+      <c r="L3" s="55" t="s">
         <v>60</v>
       </c>
-      <c r="M3" s="53"/>
+      <c r="M3" s="55"/>
       <c r="N3" t="s">
         <v>59</v>
       </c>
@@ -4914,7 +4958,7 @@
       <c r="L17" t="s">
         <v>48</v>
       </c>
-      <c r="M17" s="53" t="s">
+      <c r="M17" s="55" t="s">
         <v>49</v>
       </c>
     </row>
@@ -4934,7 +4978,7 @@
       <c r="L18" t="s">
         <v>50</v>
       </c>
-      <c r="M18" s="53"/>
+      <c r="M18" s="55"/>
     </row>
     <row r="19" spans="6:13" x14ac:dyDescent="0.25">
       <c r="G19" t="s">
@@ -5024,17 +5068,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="e8c8a8d2-cf65-4fdf-b6bc-794ebda6188e" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f72adabb-0ee4-4963-acd9-9efc158f92a6">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009074E2A1C82F3C4BA659A6C6CC51AC5F" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0765d5a41f49df217abeb23dcfb0b3cf">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="cc5908d1-2a89-4186-9c08-2c76e53ac163" xmlns:ns3="f72adabb-0ee4-4963-acd9-9efc158f92a6" xmlns:ns4="e8c8a8d2-cf65-4fdf-b6bc-794ebda6188e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="519818410c367a5844210e380df69fc7" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="cc5908d1-2a89-4186-9c08-2c76e53ac163"/>
@@ -5282,6 +5315,17 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="e8c8a8d2-cf65-4fdf-b6bc-794ebda6188e" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f72adabb-0ee4-4963-acd9-9efc158f92a6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -5292,24 +5336,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{78150E95-1CCA-47FB-B6E6-99D8675B2929}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="f72adabb-0ee4-4963-acd9-9efc158f92a6"/>
-    <ds:schemaRef ds:uri="cc5908d1-2a89-4186-9c08-2c76e53ac163"/>
-    <ds:schemaRef ds:uri="e8c8a8d2-cf65-4fdf-b6bc-794ebda6188e"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4039D020-CA7C-47AE-A105-0DAEDCC57394}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -5329,6 +5355,24 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{78150E95-1CCA-47FB-B6E6-99D8675B2929}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="f72adabb-0ee4-4963-acd9-9efc158f92a6"/>
+    <ds:schemaRef ds:uri="cc5908d1-2a89-4186-9c08-2c76e53ac163"/>
+    <ds:schemaRef ds:uri="e8c8a8d2-cf65-4fdf-b6bc-794ebda6188e"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{29C58647-0154-48BC-9EDF-8ABD72381C6C}">
   <ds:schemaRefs>

--- a/output/V3_SIM_Results_Summary.xlsx
+++ b/output/V3_SIM_Results_Summary.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="J:\HCHS\STATISTICS\GRAS\Beibo\Computing Requests\HCHS_simulation\output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22226D07-A136-49FD-A8C8-BE267114AC34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{681E050A-03FD-463F-8CA3-6E2B9F6BAF0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="761" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="423" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="423" uniqueCount="102">
   <si>
     <t>Continous Outcome, PROC GENMOD</t>
   </si>
@@ -422,12 +422,24 @@
   <si>
     <t>Efficiency comparsion, 6 &gt; 4</t>
   </si>
+  <si>
+    <t>MI + V3 IPW Weight (Restricted Sample)</t>
+  </si>
+  <si>
+    <t>No MI + V3 IPW Weight (Restricted Sample)</t>
+  </si>
+  <si>
+    <t>MI + Visit-specific IPW Weights (Full Sample)</t>
+  </si>
+  <si>
+    <t>No MI + Visit-specific IPW Weights (Full Sample)</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -552,6 +564,12 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="16"/>
+      <color rgb="FFFF0000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -645,7 +663,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -739,41 +757,20 @@
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -784,11 +781,39 @@
     <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1186,99 +1211,99 @@
       </c>
     </row>
     <row r="10" spans="1:25" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="39" t="s">
+      <c r="A10" s="51" t="s">
         <v>1</v>
       </c>
-      <c r="B10" s="39"/>
-      <c r="C10" s="39"/>
-      <c r="D10" s="39"/>
-      <c r="E10" s="39"/>
-      <c r="F10" s="39"/>
+      <c r="B10" s="51"/>
+      <c r="C10" s="51"/>
+      <c r="D10" s="51"/>
+      <c r="E10" s="51"/>
+      <c r="F10" s="51"/>
       <c r="G10" s="20"/>
-      <c r="H10" s="39" t="s">
+      <c r="H10" s="51" t="s">
         <v>1</v>
       </c>
-      <c r="I10" s="39"/>
-      <c r="J10" s="39"/>
-      <c r="K10" s="39"/>
-      <c r="L10" s="39"/>
-      <c r="M10" s="39"/>
+      <c r="I10" s="51"/>
+      <c r="J10" s="51"/>
+      <c r="K10" s="51"/>
+      <c r="L10" s="51"/>
+      <c r="M10" s="51"/>
       <c r="N10" s="20"/>
       <c r="O10" s="10"/>
-      <c r="P10" s="47" t="s">
+      <c r="P10" s="54" t="s">
         <v>2</v>
       </c>
-      <c r="Q10" s="47"/>
-      <c r="R10" s="47"/>
-      <c r="S10" s="47"/>
-      <c r="T10" s="47"/>
-      <c r="U10" s="47"/>
-      <c r="V10" s="47"/>
-      <c r="W10" s="47"/>
+      <c r="Q10" s="54"/>
+      <c r="R10" s="54"/>
+      <c r="S10" s="54"/>
+      <c r="T10" s="54"/>
+      <c r="U10" s="54"/>
+      <c r="V10" s="54"/>
+      <c r="W10" s="54"/>
       <c r="X10" s="30"/>
     </row>
     <row r="11" spans="1:25" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="A11" s="44" t="s">
-        <v>0</v>
-      </c>
-      <c r="B11" s="44"/>
-      <c r="C11" s="44"/>
-      <c r="D11" s="44"/>
-      <c r="E11" s="44"/>
-      <c r="F11" s="44"/>
+      <c r="A11" s="53" t="s">
+        <v>0</v>
+      </c>
+      <c r="B11" s="53"/>
+      <c r="C11" s="53"/>
+      <c r="D11" s="53"/>
+      <c r="E11" s="53"/>
+      <c r="F11" s="53"/>
       <c r="G11" s="24"/>
-      <c r="H11" s="44" t="s">
+      <c r="H11" s="53" t="s">
         <v>62</v>
       </c>
-      <c r="I11" s="44"/>
-      <c r="J11" s="44"/>
-      <c r="K11" s="44"/>
-      <c r="L11" s="44"/>
-      <c r="M11" s="44"/>
+      <c r="I11" s="53"/>
+      <c r="J11" s="53"/>
+      <c r="K11" s="53"/>
+      <c r="L11" s="53"/>
+      <c r="M11" s="53"/>
       <c r="N11" s="24"/>
-      <c r="P11" s="44" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="44"/>
-      <c r="R11" s="44"/>
-      <c r="S11" s="44"/>
-      <c r="T11" s="44"/>
-      <c r="U11" s="44"/>
-      <c r="V11" s="44"/>
-      <c r="W11" s="44"/>
+      <c r="P11" s="53" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="53"/>
+      <c r="R11" s="53"/>
+      <c r="S11" s="53"/>
+      <c r="T11" s="53"/>
+      <c r="U11" s="53"/>
+      <c r="V11" s="53"/>
+      <c r="W11" s="53"/>
     </row>
     <row r="12" spans="1:25" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A12" s="41" t="s">
+      <c r="A12" s="39" t="s">
         <v>61</v>
       </c>
-      <c r="B12" s="41"/>
-      <c r="C12" s="45" t="s">
+      <c r="B12" s="39"/>
+      <c r="C12" s="41" t="s">
         <v>3</v>
       </c>
-      <c r="D12" s="45"/>
-      <c r="E12" s="46" t="s">
+      <c r="D12" s="41"/>
+      <c r="E12" s="48" t="s">
         <v>4</v>
       </c>
-      <c r="F12" s="45"/>
+      <c r="F12" s="41"/>
       <c r="G12" s="25"/>
-      <c r="H12" s="41" t="s">
+      <c r="H12" s="39" t="s">
         <v>61</v>
       </c>
-      <c r="I12" s="41"/>
-      <c r="J12" s="45" t="s">
+      <c r="I12" s="39"/>
+      <c r="J12" s="41" t="s">
         <v>3</v>
       </c>
-      <c r="K12" s="45"/>
-      <c r="L12" s="46" t="s">
+      <c r="K12" s="41"/>
+      <c r="L12" s="48" t="s">
         <v>4</v>
       </c>
-      <c r="M12" s="45"/>
+      <c r="M12" s="41"/>
       <c r="N12" s="25"/>
       <c r="O12" s="4"/>
-      <c r="P12" s="41" t="s">
+      <c r="P12" s="39" t="s">
         <v>61</v>
       </c>
-      <c r="Q12" s="41"/>
+      <c r="Q12" s="39"/>
       <c r="R12" s="49" t="s">
         <v>3</v>
       </c>
@@ -1293,12 +1318,12 @@
       <c r="Y12" s="4"/>
     </row>
     <row r="13" spans="1:25" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A13" s="42"/>
-      <c r="B13" s="42"/>
+      <c r="A13" s="40"/>
+      <c r="B13" s="40"/>
       <c r="C13" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="D13" s="11" t="s">
+      <c r="D13" s="56" t="s">
         <v>6</v>
       </c>
       <c r="E13" s="22" t="s">
@@ -1308,8 +1333,8 @@
         <v>6</v>
       </c>
       <c r="G13" s="26"/>
-      <c r="H13" s="42"/>
-      <c r="I13" s="42"/>
+      <c r="H13" s="40"/>
+      <c r="I13" s="40"/>
       <c r="J13" s="21" t="s">
         <v>5</v>
       </c>
@@ -1324,8 +1349,8 @@
       </c>
       <c r="N13" s="26"/>
       <c r="O13" s="5"/>
-      <c r="P13" s="42"/>
-      <c r="Q13" s="42"/>
+      <c r="P13" s="40"/>
+      <c r="Q13" s="40"/>
       <c r="R13" s="14" t="s">
         <v>7</v>
       </c>
@@ -1357,7 +1382,7 @@
       <c r="C14" s="16">
         <v>0</v>
       </c>
-      <c r="D14" s="16">
+      <c r="D14" s="57">
         <v>0</v>
       </c>
       <c r="E14" s="16">
@@ -1486,7 +1511,7 @@
         <v>3</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>12</v>
+        <v>98</v>
       </c>
       <c r="C16" s="16">
         <v>0</v>
@@ -1505,7 +1530,7 @@
         <v>3</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>12</v>
+        <v>98</v>
       </c>
       <c r="J16" s="16">
         <v>1</v>
@@ -1552,8 +1577,8 @@
       <c r="A17" s="6">
         <v>4</v>
       </c>
-      <c r="B17" s="6" t="s">
-        <v>13</v>
+      <c r="B17" s="58" t="s">
+        <v>99</v>
       </c>
       <c r="C17" s="16">
         <v>0</v>
@@ -1571,8 +1596,8 @@
       <c r="H17" s="6">
         <v>4</v>
       </c>
-      <c r="I17" s="6" t="s">
-        <v>13</v>
+      <c r="I17" s="58" t="s">
+        <v>99</v>
       </c>
       <c r="J17" s="16">
         <v>0</v>
@@ -1620,7 +1645,7 @@
         <v>5</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>14</v>
+        <v>100</v>
       </c>
       <c r="C18" s="16">
         <v>4</v>
@@ -1639,7 +1664,7 @@
         <v>5</v>
       </c>
       <c r="I18" s="6" t="s">
-        <v>14</v>
+        <v>100</v>
       </c>
       <c r="J18" s="16">
         <v>3</v>
@@ -1687,7 +1712,7 @@
         <v>6</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>15</v>
+        <v>101</v>
       </c>
       <c r="C19" s="17">
         <v>0</v>
@@ -1706,7 +1731,7 @@
         <v>6</v>
       </c>
       <c r="I19" s="12" t="s">
-        <v>15</v>
+        <v>101</v>
       </c>
       <c r="J19" s="17">
         <v>0</v>
@@ -1815,51 +1840,51 @@
       <c r="M22" s="43"/>
       <c r="N22" s="27"/>
       <c r="O22" s="15"/>
-      <c r="P22" s="40" t="s">
+      <c r="P22" s="52" t="s">
         <v>16</v>
       </c>
-      <c r="Q22" s="40"/>
-      <c r="R22" s="40"/>
-      <c r="S22" s="40"/>
-      <c r="T22" s="40"/>
-      <c r="U22" s="40"/>
-      <c r="V22" s="40"/>
-      <c r="W22" s="40"/>
+      <c r="Q22" s="52"/>
+      <c r="R22" s="52"/>
+      <c r="S22" s="52"/>
+      <c r="T22" s="52"/>
+      <c r="U22" s="52"/>
+      <c r="V22" s="52"/>
+      <c r="W22" s="52"/>
       <c r="X22" s="15"/>
       <c r="Y22" s="4"/>
     </row>
     <row r="23" spans="1:25" ht="21" x14ac:dyDescent="0.35">
-      <c r="A23" s="41" t="s">
+      <c r="A23" s="39" t="s">
         <v>61</v>
       </c>
-      <c r="B23" s="41"/>
-      <c r="C23" s="45" t="s">
+      <c r="B23" s="39"/>
+      <c r="C23" s="41" t="s">
         <v>3</v>
       </c>
-      <c r="D23" s="45"/>
-      <c r="E23" s="46" t="s">
+      <c r="D23" s="41"/>
+      <c r="E23" s="48" t="s">
         <v>4</v>
       </c>
-      <c r="F23" s="45"/>
+      <c r="F23" s="41"/>
       <c r="G23" s="28"/>
-      <c r="H23" s="41" t="s">
+      <c r="H23" s="39" t="s">
         <v>61</v>
       </c>
-      <c r="I23" s="41"/>
-      <c r="J23" s="45" t="s">
+      <c r="I23" s="39"/>
+      <c r="J23" s="41" t="s">
         <v>3</v>
       </c>
-      <c r="K23" s="45"/>
-      <c r="L23" s="46" t="s">
+      <c r="K23" s="41"/>
+      <c r="L23" s="48" t="s">
         <v>4</v>
       </c>
-      <c r="M23" s="45"/>
+      <c r="M23" s="41"/>
       <c r="N23" s="25"/>
       <c r="O23" s="7"/>
-      <c r="P23" s="41" t="s">
+      <c r="P23" s="39" t="s">
         <v>61</v>
       </c>
-      <c r="Q23" s="41"/>
+      <c r="Q23" s="39"/>
       <c r="R23" s="49" t="s">
         <v>3</v>
       </c>
@@ -1874,8 +1899,8 @@
       <c r="Y23" s="4"/>
     </row>
     <row r="24" spans="1:25" ht="21" x14ac:dyDescent="0.35">
-      <c r="A24" s="42"/>
-      <c r="B24" s="42"/>
+      <c r="A24" s="40"/>
+      <c r="B24" s="40"/>
       <c r="C24" s="21" t="s">
         <v>5</v>
       </c>
@@ -1889,8 +1914,8 @@
         <v>6</v>
       </c>
       <c r="G24" s="28"/>
-      <c r="H24" s="42"/>
-      <c r="I24" s="42"/>
+      <c r="H24" s="40"/>
+      <c r="I24" s="40"/>
       <c r="J24" s="21" t="s">
         <v>5</v>
       </c>
@@ -1905,8 +1930,8 @@
       </c>
       <c r="N24" s="26"/>
       <c r="O24" s="7"/>
-      <c r="P24" s="42"/>
-      <c r="Q24" s="42"/>
+      <c r="P24" s="40"/>
+      <c r="Q24" s="40"/>
       <c r="R24" s="14" t="s">
         <v>7</v>
       </c>
@@ -2066,8 +2091,8 @@
       <c r="A27" s="8">
         <v>3</v>
       </c>
-      <c r="B27" s="8" t="s">
-        <v>12</v>
+      <c r="B27" s="6" t="s">
+        <v>98</v>
       </c>
       <c r="C27" s="16">
         <v>4</v>
@@ -2085,8 +2110,8 @@
       <c r="H27" s="8">
         <v>3</v>
       </c>
-      <c r="I27" s="8" t="s">
-        <v>12</v>
+      <c r="I27" s="6" t="s">
+        <v>98</v>
       </c>
       <c r="J27" s="16">
         <v>3</v>
@@ -2134,7 +2159,7 @@
         <v>4</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>13</v>
+        <v>99</v>
       </c>
       <c r="C28" s="16">
         <v>0</v>
@@ -2153,7 +2178,7 @@
         <v>4</v>
       </c>
       <c r="I28" s="8" t="s">
-        <v>13</v>
+        <v>99</v>
       </c>
       <c r="J28" s="16">
         <v>0</v>
@@ -2200,8 +2225,8 @@
       <c r="A29" s="8">
         <v>5</v>
       </c>
-      <c r="B29" s="8" t="s">
-        <v>14</v>
+      <c r="B29" s="6" t="s">
+        <v>100</v>
       </c>
       <c r="C29" s="16">
         <v>5</v>
@@ -2219,8 +2244,8 @@
       <c r="H29" s="8">
         <v>5</v>
       </c>
-      <c r="I29" s="8" t="s">
-        <v>14</v>
+      <c r="I29" s="6" t="s">
+        <v>100</v>
       </c>
       <c r="J29" s="16">
         <v>5</v>
@@ -2267,8 +2292,8 @@
       <c r="A30" s="13">
         <v>6</v>
       </c>
-      <c r="B30" s="13" t="s">
-        <v>15</v>
+      <c r="B30" s="12" t="s">
+        <v>101</v>
       </c>
       <c r="C30" s="17">
         <v>0</v>
@@ -2286,8 +2311,8 @@
       <c r="H30" s="13">
         <v>6</v>
       </c>
-      <c r="I30" s="13" t="s">
-        <v>15</v>
+      <c r="I30" s="12" t="s">
+        <v>101</v>
       </c>
       <c r="J30" s="17">
         <v>0</v>
@@ -2384,55 +2409,55 @@
       </c>
     </row>
     <row r="36" spans="1:14" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="A36" s="48"/>
-      <c r="B36" s="48"/>
-      <c r="C36" s="48"/>
-      <c r="D36" s="48"/>
-      <c r="E36" s="48"/>
-      <c r="F36" s="48"/>
+      <c r="A36" s="47"/>
+      <c r="B36" s="47"/>
+      <c r="C36" s="47"/>
+      <c r="D36" s="47"/>
+      <c r="E36" s="47"/>
+      <c r="F36" s="47"/>
       <c r="G36" s="29"/>
-      <c r="H36" s="54" t="s">
+      <c r="H36" s="42" t="s">
         <v>62</v>
       </c>
-      <c r="I36" s="54"/>
-      <c r="J36" s="54"/>
-      <c r="K36" s="54"/>
-      <c r="L36" s="54"/>
-      <c r="M36" s="54"/>
+      <c r="I36" s="42"/>
+      <c r="J36" s="42"/>
+      <c r="K36" s="42"/>
+      <c r="L36" s="42"/>
+      <c r="M36" s="42"/>
       <c r="N36" s="29"/>
     </row>
     <row r="37" spans="1:14" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A37" s="51"/>
-      <c r="B37" s="51"/>
-      <c r="C37" s="52"/>
-      <c r="D37" s="52"/>
-      <c r="E37" s="52"/>
-      <c r="F37" s="52"/>
+      <c r="A37" s="44"/>
+      <c r="B37" s="44"/>
+      <c r="C37" s="45"/>
+      <c r="D37" s="45"/>
+      <c r="E37" s="45"/>
+      <c r="F37" s="45"/>
       <c r="G37" s="25"/>
-      <c r="H37" s="41" t="s">
+      <c r="H37" s="39" t="s">
         <v>61</v>
       </c>
-      <c r="I37" s="41"/>
-      <c r="J37" s="45" t="s">
+      <c r="I37" s="39"/>
+      <c r="J37" s="41" t="s">
         <v>3</v>
       </c>
-      <c r="K37" s="45"/>
-      <c r="L37" s="45" t="s">
+      <c r="K37" s="41"/>
+      <c r="L37" s="41" t="s">
         <v>4</v>
       </c>
-      <c r="M37" s="45"/>
+      <c r="M37" s="41"/>
       <c r="N37" s="25"/>
     </row>
     <row r="38" spans="1:14" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A38" s="51"/>
-      <c r="B38" s="51"/>
+      <c r="A38" s="44"/>
+      <c r="B38" s="44"/>
       <c r="C38" s="26"/>
       <c r="D38" s="26"/>
       <c r="E38" s="26"/>
       <c r="F38" s="26"/>
       <c r="G38" s="26"/>
-      <c r="H38" s="42"/>
-      <c r="I38" s="42"/>
+      <c r="H38" s="40"/>
+      <c r="I38" s="40"/>
       <c r="J38" s="11" t="s">
         <v>5</v>
       </c>
@@ -2612,12 +2637,12 @@
       <c r="N44" s="16"/>
     </row>
     <row r="46" spans="1:14" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="A46" s="53"/>
-      <c r="B46" s="53"/>
-      <c r="C46" s="53"/>
-      <c r="D46" s="53"/>
-      <c r="E46" s="53"/>
-      <c r="F46" s="53"/>
+      <c r="A46" s="46"/>
+      <c r="B46" s="46"/>
+      <c r="C46" s="46"/>
+      <c r="D46" s="46"/>
+      <c r="E46" s="46"/>
+      <c r="F46" s="46"/>
       <c r="G46" s="27"/>
       <c r="H46" s="43" t="s">
         <v>71</v>
@@ -2630,37 +2655,37 @@
       <c r="N46" s="27"/>
     </row>
     <row r="47" spans="1:14" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A47" s="51"/>
-      <c r="B47" s="51"/>
-      <c r="C47" s="52"/>
-      <c r="D47" s="52"/>
-      <c r="E47" s="52"/>
-      <c r="F47" s="52"/>
+      <c r="A47" s="44"/>
+      <c r="B47" s="44"/>
+      <c r="C47" s="45"/>
+      <c r="D47" s="45"/>
+      <c r="E47" s="45"/>
+      <c r="F47" s="45"/>
       <c r="G47" s="25"/>
-      <c r="H47" s="41" t="s">
+      <c r="H47" s="39" t="s">
         <v>61</v>
       </c>
-      <c r="I47" s="41"/>
-      <c r="J47" s="45" t="s">
+      <c r="I47" s="39"/>
+      <c r="J47" s="41" t="s">
         <v>3</v>
       </c>
-      <c r="K47" s="45"/>
-      <c r="L47" s="45" t="s">
+      <c r="K47" s="41"/>
+      <c r="L47" s="41" t="s">
         <v>4</v>
       </c>
-      <c r="M47" s="45"/>
+      <c r="M47" s="41"/>
       <c r="N47" s="25"/>
     </row>
     <row r="48" spans="1:14" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A48" s="51"/>
-      <c r="B48" s="51"/>
+      <c r="A48" s="44"/>
+      <c r="B48" s="44"/>
       <c r="C48" s="26"/>
       <c r="D48" s="26"/>
       <c r="E48" s="26"/>
       <c r="F48" s="26"/>
       <c r="G48" s="26"/>
-      <c r="H48" s="42"/>
-      <c r="I48" s="42"/>
+      <c r="H48" s="40"/>
+      <c r="I48" s="40"/>
       <c r="J48" s="11" t="s">
         <v>5</v>
       </c>
@@ -2841,21 +2866,18 @@
     </row>
   </sheetData>
   <mergeCells count="43">
-    <mergeCell ref="H47:I48"/>
-    <mergeCell ref="J47:K47"/>
-    <mergeCell ref="L47:M47"/>
-    <mergeCell ref="H36:M36"/>
-    <mergeCell ref="H37:I38"/>
-    <mergeCell ref="J37:K37"/>
-    <mergeCell ref="L37:M37"/>
-    <mergeCell ref="H46:M46"/>
-    <mergeCell ref="A37:B38"/>
-    <mergeCell ref="C37:D37"/>
-    <mergeCell ref="E37:F37"/>
-    <mergeCell ref="A46:F46"/>
-    <mergeCell ref="A47:B48"/>
-    <mergeCell ref="C47:D47"/>
-    <mergeCell ref="E47:F47"/>
+    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="P22:W22"/>
+    <mergeCell ref="A12:B13"/>
+    <mergeCell ref="P12:Q13"/>
+    <mergeCell ref="A22:F22"/>
+    <mergeCell ref="A11:F11"/>
+    <mergeCell ref="P11:W11"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="H10:M10"/>
+    <mergeCell ref="P10:W10"/>
+    <mergeCell ref="H11:M11"/>
     <mergeCell ref="A36:F36"/>
     <mergeCell ref="C23:D23"/>
     <mergeCell ref="E23:F23"/>
@@ -2872,18 +2894,21 @@
     <mergeCell ref="H12:I13"/>
     <mergeCell ref="J12:K12"/>
     <mergeCell ref="L12:M12"/>
-    <mergeCell ref="A10:F10"/>
-    <mergeCell ref="P22:W22"/>
-    <mergeCell ref="A12:B13"/>
-    <mergeCell ref="P12:Q13"/>
-    <mergeCell ref="A22:F22"/>
-    <mergeCell ref="A11:F11"/>
-    <mergeCell ref="P11:W11"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="E12:F12"/>
-    <mergeCell ref="H10:M10"/>
-    <mergeCell ref="P10:W10"/>
-    <mergeCell ref="H11:M11"/>
+    <mergeCell ref="A37:B38"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="E37:F37"/>
+    <mergeCell ref="A46:F46"/>
+    <mergeCell ref="A47:B48"/>
+    <mergeCell ref="C47:D47"/>
+    <mergeCell ref="E47:F47"/>
+    <mergeCell ref="H47:I48"/>
+    <mergeCell ref="J47:K47"/>
+    <mergeCell ref="L47:M47"/>
+    <mergeCell ref="H36:M36"/>
+    <mergeCell ref="H37:I38"/>
+    <mergeCell ref="J37:K37"/>
+    <mergeCell ref="L37:M37"/>
+    <mergeCell ref="H46:M46"/>
   </mergeCells>
   <conditionalFormatting sqref="G14:G19">
     <cfRule type="colorScale" priority="45">
@@ -3095,99 +3120,99 @@
       </c>
     </row>
     <row r="12" spans="1:25" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="39" t="s">
+      <c r="A12" s="51" t="s">
         <v>1</v>
       </c>
-      <c r="B12" s="39"/>
-      <c r="C12" s="39"/>
-      <c r="D12" s="39"/>
-      <c r="E12" s="39"/>
-      <c r="F12" s="39"/>
+      <c r="B12" s="51"/>
+      <c r="C12" s="51"/>
+      <c r="D12" s="51"/>
+      <c r="E12" s="51"/>
+      <c r="F12" s="51"/>
       <c r="G12" s="32"/>
-      <c r="H12" s="39" t="s">
+      <c r="H12" s="51" t="s">
         <v>1</v>
       </c>
-      <c r="I12" s="39"/>
-      <c r="J12" s="39"/>
-      <c r="K12" s="39"/>
-      <c r="L12" s="39"/>
-      <c r="M12" s="39"/>
+      <c r="I12" s="51"/>
+      <c r="J12" s="51"/>
+      <c r="K12" s="51"/>
+      <c r="L12" s="51"/>
+      <c r="M12" s="51"/>
       <c r="N12" s="32"/>
       <c r="O12" s="10"/>
-      <c r="P12" s="47" t="s">
+      <c r="P12" s="54" t="s">
         <v>2</v>
       </c>
-      <c r="Q12" s="47"/>
-      <c r="R12" s="47"/>
-      <c r="S12" s="47"/>
-      <c r="T12" s="47"/>
-      <c r="U12" s="47"/>
-      <c r="V12" s="47"/>
-      <c r="W12" s="47"/>
+      <c r="Q12" s="54"/>
+      <c r="R12" s="54"/>
+      <c r="S12" s="54"/>
+      <c r="T12" s="54"/>
+      <c r="U12" s="54"/>
+      <c r="V12" s="54"/>
+      <c r="W12" s="54"/>
       <c r="X12" s="30"/>
     </row>
     <row r="13" spans="1:25" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="A13" s="44" t="s">
-        <v>0</v>
-      </c>
-      <c r="B13" s="44"/>
-      <c r="C13" s="44"/>
-      <c r="D13" s="44"/>
-      <c r="E13" s="44"/>
-      <c r="F13" s="44"/>
+      <c r="A13" s="53" t="s">
+        <v>0</v>
+      </c>
+      <c r="B13" s="53"/>
+      <c r="C13" s="53"/>
+      <c r="D13" s="53"/>
+      <c r="E13" s="53"/>
+      <c r="F13" s="53"/>
       <c r="G13" s="24"/>
-      <c r="H13" s="44" t="s">
+      <c r="H13" s="53" t="s">
         <v>62</v>
       </c>
-      <c r="I13" s="44"/>
-      <c r="J13" s="44"/>
-      <c r="K13" s="44"/>
-      <c r="L13" s="44"/>
-      <c r="M13" s="44"/>
+      <c r="I13" s="53"/>
+      <c r="J13" s="53"/>
+      <c r="K13" s="53"/>
+      <c r="L13" s="53"/>
+      <c r="M13" s="53"/>
       <c r="N13" s="24"/>
-      <c r="P13" s="44" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="44"/>
-      <c r="R13" s="44"/>
-      <c r="S13" s="44"/>
-      <c r="T13" s="44"/>
-      <c r="U13" s="44"/>
-      <c r="V13" s="44"/>
-      <c r="W13" s="44"/>
+      <c r="P13" s="53" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="53"/>
+      <c r="R13" s="53"/>
+      <c r="S13" s="53"/>
+      <c r="T13" s="53"/>
+      <c r="U13" s="53"/>
+      <c r="V13" s="53"/>
+      <c r="W13" s="53"/>
     </row>
     <row r="14" spans="1:25" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A14" s="41" t="s">
+      <c r="A14" s="39" t="s">
         <v>61</v>
       </c>
-      <c r="B14" s="41"/>
-      <c r="C14" s="45" t="s">
+      <c r="B14" s="39"/>
+      <c r="C14" s="41" t="s">
         <v>3</v>
       </c>
-      <c r="D14" s="45"/>
-      <c r="E14" s="46" t="s">
+      <c r="D14" s="41"/>
+      <c r="E14" s="48" t="s">
         <v>4</v>
       </c>
-      <c r="F14" s="45"/>
+      <c r="F14" s="41"/>
       <c r="G14" s="34"/>
-      <c r="H14" s="41" t="s">
+      <c r="H14" s="39" t="s">
         <v>61</v>
       </c>
-      <c r="I14" s="41"/>
-      <c r="J14" s="45" t="s">
+      <c r="I14" s="39"/>
+      <c r="J14" s="41" t="s">
         <v>3</v>
       </c>
-      <c r="K14" s="45"/>
-      <c r="L14" s="46" t="s">
+      <c r="K14" s="41"/>
+      <c r="L14" s="48" t="s">
         <v>4</v>
       </c>
-      <c r="M14" s="45"/>
+      <c r="M14" s="41"/>
       <c r="N14" s="34"/>
       <c r="O14" s="4"/>
-      <c r="P14" s="41" t="s">
+      <c r="P14" s="39" t="s">
         <v>61</v>
       </c>
-      <c r="Q14" s="41"/>
+      <c r="Q14" s="39"/>
       <c r="R14" s="49" t="s">
         <v>3</v>
       </c>
@@ -3202,8 +3227,8 @@
       <c r="Y14" s="4"/>
     </row>
     <row r="15" spans="1:25" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A15" s="42"/>
-      <c r="B15" s="42"/>
+      <c r="A15" s="40"/>
+      <c r="B15" s="40"/>
       <c r="C15" s="21" t="s">
         <v>5</v>
       </c>
@@ -3217,8 +3242,8 @@
         <v>6</v>
       </c>
       <c r="G15" s="33"/>
-      <c r="H15" s="42"/>
-      <c r="I15" s="42"/>
+      <c r="H15" s="40"/>
+      <c r="I15" s="40"/>
       <c r="J15" s="21" t="s">
         <v>5</v>
       </c>
@@ -3233,8 +3258,8 @@
       </c>
       <c r="N15" s="33"/>
       <c r="O15" s="5"/>
-      <c r="P15" s="42"/>
-      <c r="Q15" s="42"/>
+      <c r="P15" s="40"/>
+      <c r="Q15" s="40"/>
       <c r="R15" s="14" t="s">
         <v>7</v>
       </c>
@@ -3603,51 +3628,51 @@
       <c r="M23" s="43"/>
       <c r="N23" s="35"/>
       <c r="O23" s="15"/>
-      <c r="P23" s="40" t="s">
+      <c r="P23" s="52" t="s">
         <v>16</v>
       </c>
-      <c r="Q23" s="40"/>
-      <c r="R23" s="40"/>
-      <c r="S23" s="40"/>
-      <c r="T23" s="40"/>
-      <c r="U23" s="40"/>
-      <c r="V23" s="40"/>
-      <c r="W23" s="40"/>
+      <c r="Q23" s="52"/>
+      <c r="R23" s="52"/>
+      <c r="S23" s="52"/>
+      <c r="T23" s="52"/>
+      <c r="U23" s="52"/>
+      <c r="V23" s="52"/>
+      <c r="W23" s="52"/>
       <c r="X23" s="15"/>
       <c r="Y23" s="4"/>
     </row>
     <row r="24" spans="1:25" ht="21" x14ac:dyDescent="0.35">
-      <c r="A24" s="41" t="s">
+      <c r="A24" s="39" t="s">
         <v>61</v>
       </c>
-      <c r="B24" s="41"/>
-      <c r="C24" s="45" t="s">
+      <c r="B24" s="39"/>
+      <c r="C24" s="41" t="s">
         <v>3</v>
       </c>
-      <c r="D24" s="45"/>
-      <c r="E24" s="45" t="s">
+      <c r="D24" s="41"/>
+      <c r="E24" s="41" t="s">
         <v>4</v>
       </c>
-      <c r="F24" s="45"/>
+      <c r="F24" s="41"/>
       <c r="G24" s="28"/>
-      <c r="H24" s="41" t="s">
+      <c r="H24" s="39" t="s">
         <v>61</v>
       </c>
-      <c r="I24" s="41"/>
-      <c r="J24" s="45" t="s">
+      <c r="I24" s="39"/>
+      <c r="J24" s="41" t="s">
         <v>3</v>
       </c>
-      <c r="K24" s="45"/>
-      <c r="L24" s="46" t="s">
+      <c r="K24" s="41"/>
+      <c r="L24" s="48" t="s">
         <v>4</v>
       </c>
-      <c r="M24" s="45"/>
+      <c r="M24" s="41"/>
       <c r="N24" s="34"/>
       <c r="O24" s="7"/>
-      <c r="P24" s="41" t="s">
+      <c r="P24" s="39" t="s">
         <v>61</v>
       </c>
-      <c r="Q24" s="41"/>
+      <c r="Q24" s="39"/>
       <c r="R24" s="49" t="s">
         <v>3</v>
       </c>
@@ -3662,8 +3687,8 @@
       <c r="Y24" s="4"/>
     </row>
     <row r="25" spans="1:25" ht="21" x14ac:dyDescent="0.35">
-      <c r="A25" s="42"/>
-      <c r="B25" s="42"/>
+      <c r="A25" s="40"/>
+      <c r="B25" s="40"/>
       <c r="C25" s="21" t="s">
         <v>5</v>
       </c>
@@ -3677,8 +3702,8 @@
         <v>6</v>
       </c>
       <c r="G25" s="28"/>
-      <c r="H25" s="42"/>
-      <c r="I25" s="42"/>
+      <c r="H25" s="40"/>
+      <c r="I25" s="40"/>
       <c r="J25" s="21" t="s">
         <v>5</v>
       </c>
@@ -3693,8 +3718,8 @@
       </c>
       <c r="N25" s="33"/>
       <c r="O25" s="7"/>
-      <c r="P25" s="42"/>
-      <c r="Q25" s="42"/>
+      <c r="P25" s="40"/>
+      <c r="Q25" s="40"/>
       <c r="R25" s="14" t="s">
         <v>7</v>
       </c>
@@ -4076,55 +4101,55 @@
       </c>
     </row>
     <row r="37" spans="1:19" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="A37" s="48"/>
-      <c r="B37" s="48"/>
-      <c r="C37" s="48"/>
-      <c r="D37" s="48"/>
-      <c r="E37" s="48"/>
-      <c r="F37" s="48"/>
+      <c r="A37" s="47"/>
+      <c r="B37" s="47"/>
+      <c r="C37" s="47"/>
+      <c r="D37" s="47"/>
+      <c r="E37" s="47"/>
+      <c r="F37" s="47"/>
       <c r="G37" s="36"/>
-      <c r="H37" s="54" t="s">
+      <c r="H37" s="42" t="s">
         <v>62</v>
       </c>
-      <c r="I37" s="54"/>
-      <c r="J37" s="54"/>
-      <c r="K37" s="54"/>
-      <c r="L37" s="54"/>
-      <c r="M37" s="54"/>
+      <c r="I37" s="42"/>
+      <c r="J37" s="42"/>
+      <c r="K37" s="42"/>
+      <c r="L37" s="42"/>
+      <c r="M37" s="42"/>
       <c r="N37" s="36"/>
     </row>
     <row r="38" spans="1:19" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A38" s="51"/>
-      <c r="B38" s="51"/>
-      <c r="C38" s="52"/>
-      <c r="D38" s="52"/>
-      <c r="E38" s="52"/>
-      <c r="F38" s="52"/>
+      <c r="A38" s="44"/>
+      <c r="B38" s="44"/>
+      <c r="C38" s="45"/>
+      <c r="D38" s="45"/>
+      <c r="E38" s="45"/>
+      <c r="F38" s="45"/>
       <c r="G38" s="34"/>
-      <c r="H38" s="41" t="s">
+      <c r="H38" s="39" t="s">
         <v>61</v>
       </c>
-      <c r="I38" s="41"/>
-      <c r="J38" s="45" t="s">
+      <c r="I38" s="39"/>
+      <c r="J38" s="41" t="s">
         <v>3</v>
       </c>
-      <c r="K38" s="45"/>
-      <c r="L38" s="45" t="s">
+      <c r="K38" s="41"/>
+      <c r="L38" s="41" t="s">
         <v>4</v>
       </c>
-      <c r="M38" s="45"/>
+      <c r="M38" s="41"/>
       <c r="N38" s="34"/>
     </row>
     <row r="39" spans="1:19" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A39" s="51"/>
-      <c r="B39" s="51"/>
+      <c r="A39" s="44"/>
+      <c r="B39" s="44"/>
       <c r="C39" s="33"/>
       <c r="D39" s="33"/>
       <c r="E39" s="33"/>
       <c r="F39" s="33"/>
       <c r="G39" s="33"/>
-      <c r="H39" s="42"/>
-      <c r="I39" s="42"/>
+      <c r="H39" s="40"/>
+      <c r="I39" s="40"/>
       <c r="J39" s="31" t="s">
         <v>5</v>
       </c>
@@ -4304,12 +4329,12 @@
       <c r="N45" s="16"/>
     </row>
     <row r="47" spans="1:19" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="A47" s="53"/>
-      <c r="B47" s="53"/>
-      <c r="C47" s="53"/>
-      <c r="D47" s="53"/>
-      <c r="E47" s="53"/>
-      <c r="F47" s="53"/>
+      <c r="A47" s="46"/>
+      <c r="B47" s="46"/>
+      <c r="C47" s="46"/>
+      <c r="D47" s="46"/>
+      <c r="E47" s="46"/>
+      <c r="F47" s="46"/>
       <c r="G47" s="35"/>
       <c r="H47" s="43" t="s">
         <v>71</v>
@@ -4322,37 +4347,37 @@
       <c r="N47" s="35"/>
     </row>
     <row r="48" spans="1:19" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A48" s="51"/>
-      <c r="B48" s="51"/>
-      <c r="C48" s="52"/>
-      <c r="D48" s="52"/>
-      <c r="E48" s="52"/>
-      <c r="F48" s="52"/>
+      <c r="A48" s="44"/>
+      <c r="B48" s="44"/>
+      <c r="C48" s="45"/>
+      <c r="D48" s="45"/>
+      <c r="E48" s="45"/>
+      <c r="F48" s="45"/>
       <c r="G48" s="34"/>
-      <c r="H48" s="41" t="s">
+      <c r="H48" s="39" t="s">
         <v>61</v>
       </c>
-      <c r="I48" s="41"/>
-      <c r="J48" s="45" t="s">
+      <c r="I48" s="39"/>
+      <c r="J48" s="41" t="s">
         <v>3</v>
       </c>
-      <c r="K48" s="45"/>
-      <c r="L48" s="45" t="s">
+      <c r="K48" s="41"/>
+      <c r="L48" s="41" t="s">
         <v>4</v>
       </c>
-      <c r="M48" s="45"/>
+      <c r="M48" s="41"/>
       <c r="N48" s="34"/>
     </row>
     <row r="49" spans="1:14" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A49" s="51"/>
-      <c r="B49" s="51"/>
+      <c r="A49" s="44"/>
+      <c r="B49" s="44"/>
       <c r="C49" s="33"/>
       <c r="D49" s="33"/>
       <c r="E49" s="33"/>
       <c r="F49" s="33"/>
       <c r="G49" s="33"/>
-      <c r="H49" s="42"/>
-      <c r="I49" s="42"/>
+      <c r="H49" s="40"/>
+      <c r="I49" s="40"/>
       <c r="J49" s="31" t="s">
         <v>5</v>
       </c>
@@ -4533,6 +4558,35 @@
     </row>
   </sheetData>
   <mergeCells count="43">
+    <mergeCell ref="A12:F12"/>
+    <mergeCell ref="H12:M12"/>
+    <mergeCell ref="P12:W12"/>
+    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="H13:M13"/>
+    <mergeCell ref="P13:W13"/>
+    <mergeCell ref="P14:Q15"/>
+    <mergeCell ref="R14:T14"/>
+    <mergeCell ref="U14:W14"/>
+    <mergeCell ref="A23:F23"/>
+    <mergeCell ref="H23:M23"/>
+    <mergeCell ref="P23:W23"/>
+    <mergeCell ref="A14:B15"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="H14:I15"/>
+    <mergeCell ref="J14:K14"/>
+    <mergeCell ref="L14:M14"/>
+    <mergeCell ref="P24:Q25"/>
+    <mergeCell ref="R24:T24"/>
+    <mergeCell ref="U24:W24"/>
+    <mergeCell ref="A37:F37"/>
+    <mergeCell ref="H37:M37"/>
+    <mergeCell ref="A24:B25"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="H24:I25"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="L24:M24"/>
     <mergeCell ref="L38:M38"/>
     <mergeCell ref="A47:F47"/>
     <mergeCell ref="H47:M47"/>
@@ -4547,35 +4601,6 @@
     <mergeCell ref="E38:F38"/>
     <mergeCell ref="H38:I39"/>
     <mergeCell ref="J38:K38"/>
-    <mergeCell ref="P24:Q25"/>
-    <mergeCell ref="R24:T24"/>
-    <mergeCell ref="U24:W24"/>
-    <mergeCell ref="A37:F37"/>
-    <mergeCell ref="H37:M37"/>
-    <mergeCell ref="A24:B25"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="H24:I25"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="L24:M24"/>
-    <mergeCell ref="P14:Q15"/>
-    <mergeCell ref="R14:T14"/>
-    <mergeCell ref="U14:W14"/>
-    <mergeCell ref="A23:F23"/>
-    <mergeCell ref="H23:M23"/>
-    <mergeCell ref="P23:W23"/>
-    <mergeCell ref="A14:B15"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="H14:I15"/>
-    <mergeCell ref="J14:K14"/>
-    <mergeCell ref="L14:M14"/>
-    <mergeCell ref="A12:F12"/>
-    <mergeCell ref="H12:M12"/>
-    <mergeCell ref="P12:W12"/>
-    <mergeCell ref="A13:F13"/>
-    <mergeCell ref="H13:M13"/>
-    <mergeCell ref="P13:W13"/>
   </mergeCells>
   <conditionalFormatting sqref="C16:C21">
     <cfRule type="colorScale" priority="19">
@@ -5068,6 +5093,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="e8c8a8d2-cf65-4fdf-b6bc-794ebda6188e" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f72adabb-0ee4-4963-acd9-9efc158f92a6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009074E2A1C82F3C4BA659A6C6CC51AC5F" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0765d5a41f49df217abeb23dcfb0b3cf">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="cc5908d1-2a89-4186-9c08-2c76e53ac163" xmlns:ns3="f72adabb-0ee4-4963-acd9-9efc158f92a6" xmlns:ns4="e8c8a8d2-cf65-4fdf-b6bc-794ebda6188e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="519818410c367a5844210e380df69fc7" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="cc5908d1-2a89-4186-9c08-2c76e53ac163"/>
@@ -5315,42 +5360,10 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="e8c8a8d2-cf65-4fdf-b6bc-794ebda6188e" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f72adabb-0ee4-4963-acd9-9efc158f92a6">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4039D020-CA7C-47AE-A105-0DAEDCC57394}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{29C58647-0154-48BC-9EDF-8ABD72381C6C}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="cc5908d1-2a89-4186-9c08-2c76e53ac163"/>
-    <ds:schemaRef ds:uri="f72adabb-0ee4-4963-acd9-9efc158f92a6"/>
-    <ds:schemaRef ds:uri="e8c8a8d2-cf65-4fdf-b6bc-794ebda6188e"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -5374,9 +5387,21 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{29C58647-0154-48BC-9EDF-8ABD72381C6C}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4039D020-CA7C-47AE-A105-0DAEDCC57394}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="cc5908d1-2a89-4186-9c08-2c76e53ac163"/>
+    <ds:schemaRef ds:uri="f72adabb-0ee4-4963-acd9-9efc158f92a6"/>
+    <ds:schemaRef ds:uri="e8c8a8d2-cf65-4fdf-b6bc-794ebda6188e"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>